--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20600" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20600" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,11 +22,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -128,7 +127,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,7 +174,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5715,8 +5713,13 @@
           <t>found form (2017-07-29)</t>
         </is>
       </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D60" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
@@ -5777,8 +5780,13 @@
           <t>found form (2024-11-18 I)</t>
         </is>
       </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D61" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
@@ -5839,8 +5847,13 @@
           <t>found form (2024-11-18 II)</t>
         </is>
       </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D62" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
@@ -5901,8 +5914,13 @@
           <t>found form (2024-11-18 III)</t>
         </is>
       </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D63" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
@@ -5963,8 +5981,13 @@
           <t>found form (2025-07-02)</t>
         </is>
       </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D64" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
@@ -6025,8 +6048,13 @@
           <t>found form (2025-07-15 I)</t>
         </is>
       </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D65" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
@@ -6087,8 +6115,13 @@
           <t>found form (2025-07-15 II)</t>
         </is>
       </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D66" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
@@ -6149,8 +6182,13 @@
           <t>found form (2025-07-26)</t>
         </is>
       </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D67" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
@@ -6211,8 +6249,13 @@
           <t>found form (2025-11-01 I)</t>
         </is>
       </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D68" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
@@ -6273,8 +6316,13 @@
           <t>found form (2025-11-01 II)</t>
         </is>
       </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D69" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
@@ -6335,8 +6383,13 @@
           <t>found form 01</t>
         </is>
       </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D70" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
@@ -6397,8 +6450,13 @@
           <t>found form 02</t>
         </is>
       </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D71" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
@@ -6459,8 +6517,13 @@
           <t>found form 03</t>
         </is>
       </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D72" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
@@ -6521,8 +6584,13 @@
           <t>found form 04</t>
         </is>
       </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D73" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
@@ -6583,8 +6651,13 @@
           <t>found form 05</t>
         </is>
       </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D74" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
@@ -6645,8 +6718,13 @@
           <t>found form 06</t>
         </is>
       </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D75" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
@@ -6707,8 +6785,13 @@
           <t>found form 07</t>
         </is>
       </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D76" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
@@ -6769,8 +6852,13 @@
           <t>found form 08</t>
         </is>
       </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D77" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
@@ -6831,8 +6919,13 @@
           <t>found form 09</t>
         </is>
       </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D78" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
@@ -6893,8 +6986,13 @@
           <t>found form 10</t>
         </is>
       </c>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D79" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
@@ -6955,8 +7053,13 @@
           <t>found form 11</t>
         </is>
       </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D80" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
@@ -7017,8 +7120,13 @@
           <t>found form 12</t>
         </is>
       </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D81" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
@@ -7079,8 +7187,13 @@
           <t>found form 13 (mother and child)</t>
         </is>
       </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D82" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
@@ -7141,8 +7254,13 @@
           <t>found form 14</t>
         </is>
       </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D83" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
@@ -7203,8 +7321,13 @@
           <t>found form 15</t>
         </is>
       </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D84" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
@@ -7265,8 +7388,13 @@
           <t>found form 16</t>
         </is>
       </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D85" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
@@ -7327,8 +7455,13 @@
           <t>found form 17</t>
         </is>
       </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D86" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
@@ -7389,8 +7522,13 @@
           <t>found form 18</t>
         </is>
       </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D87" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
@@ -7451,8 +7589,13 @@
           <t>found form 19</t>
         </is>
       </c>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D88" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
@@ -7513,8 +7656,13 @@
           <t>found form 20</t>
         </is>
       </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D89" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
@@ -7575,8 +7723,13 @@
           <t>found form 21</t>
         </is>
       </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D90" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
@@ -7637,8 +7790,13 @@
           <t>found form 22</t>
         </is>
       </c>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D91" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
@@ -7699,8 +7857,13 @@
           <t>found form 23</t>
         </is>
       </c>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D92" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
@@ -7761,8 +7924,13 @@
           <t>found form 24</t>
         </is>
       </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D93" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
@@ -7823,8 +7991,13 @@
           <t>found form 25</t>
         </is>
       </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D94" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
@@ -7885,8 +8058,13 @@
           <t>found form 26</t>
         </is>
       </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D95" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
@@ -7947,8 +8125,13 @@
           <t>found form 27</t>
         </is>
       </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D96" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
@@ -8009,8 +8192,13 @@
           <t>found form 28</t>
         </is>
       </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D97" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
@@ -8071,8 +8259,13 @@
           <t>found form 29</t>
         </is>
       </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D98" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
@@ -8133,8 +8326,13 @@
           <t>found form 30</t>
         </is>
       </c>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D99" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
@@ -8195,8 +8393,13 @@
           <t>found form 31</t>
         </is>
       </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D100" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
@@ -8257,8 +8460,13 @@
           <t>found form 32</t>
         </is>
       </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D101" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
@@ -8319,8 +8527,13 @@
           <t>found form 33</t>
         </is>
       </c>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D102" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
@@ -8381,8 +8594,13 @@
           <t>found form 34</t>
         </is>
       </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D103" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
@@ -8443,8 +8661,13 @@
           <t>found form 35</t>
         </is>
       </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D104" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
@@ -8505,8 +8728,13 @@
           <t>found form 36</t>
         </is>
       </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D105" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
@@ -8567,8 +8795,13 @@
           <t>found form 37</t>
         </is>
       </c>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D106" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
@@ -8629,8 +8862,13 @@
           <t>found form 38</t>
         </is>
       </c>
+      <c r="C107" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="D107" s="17" t="n">
-        <v>46053</v>
+        <v>46069</v>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
@@ -9365,11 +9603,8 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="n">
-        <v>46069</v>
+          <t>draft</t>
+        </is>
       </c>
       <c r="E8" s="1" t="n">
         <v>2013</v>

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'index - old version'!$A$1:$G$803</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -28,7 +28,7 @@
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -108,12 +108,6 @@
       <family val="2"/>
       <color rgb="FF000000"/>
       <sz val="13"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1287,7 +1281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z116"/>
+  <dimension ref="A1:Z117"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="11.33203125" customWidth="1" style="1" min="1" max="1"/>
@@ -1301,7 +1295,8 @@
     <col width="20.83203125" customWidth="1" style="1" min="9" max="9"/>
     <col width="10.83203125" customWidth="1" style="9" min="10" max="10"/>
     <col width="26.1640625" bestFit="1" customWidth="1" style="9" min="11" max="11"/>
-    <col width="20.83203125" customWidth="1" style="1" min="12" max="13"/>
+    <col width="25.33203125" bestFit="1" customWidth="1" style="1" min="12" max="12"/>
+    <col width="20.83203125" customWidth="1" style="1" min="13" max="13"/>
     <col width="29.5" bestFit="1" customWidth="1" style="1" min="14" max="14"/>
     <col width="10.83203125" customWidth="1" style="1" min="15" max="15"/>
     <col width="14" customWidth="1" style="1" min="16" max="16"/>
@@ -1313,8 +1308,8 @@
     <col width="15.5" customWidth="1" style="1" min="24" max="24"/>
     <col width="15.1640625" customWidth="1" style="1" min="25" max="25"/>
     <col width="51" bestFit="1" customWidth="1" style="1" min="26" max="26"/>
-    <col width="10.83203125" customWidth="1" style="1" min="27" max="40"/>
-    <col width="10.83203125" customWidth="1" style="1" min="41" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="1" min="27" max="41"/>
+    <col width="10.83203125" customWidth="1" style="1" min="42" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -9368,7 +9363,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="D114" s="26" t="n">
+      <c r="D114" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="E114" s="1" t="inlineStr">
@@ -9435,7 +9430,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="D115" s="26" t="n">
+      <c r="D115" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="E115" s="1" t="inlineStr">
@@ -9502,7 +9497,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="D116" s="26" t="n">
+      <c r="D116" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="E116" s="1" t="inlineStr">
@@ -9548,6 +9543,75 @@
         </is>
       </c>
       <c r="W116" s="5" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>00463</t>
+        </is>
+      </c>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t>living surface hand form</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="D117" s="26" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E117" s="1" t="inlineStr">
+        <is>
+          <t>living surface hand form</t>
+        </is>
+      </c>
+      <c r="F117" s="1" t="inlineStr">
+        <is>
+          <t>living surface hand form.jpg</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="K117" s="9" t="inlineStr">
+        <is>
+          <t>1989, 2004</t>
+        </is>
+      </c>
+      <c r="L117" s="1" t="inlineStr">
+        <is>
+          <t>living-surface-hand-form</t>
+        </is>
+      </c>
+      <c r="M117" s="1" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="N117" s="1" t="inlineStr">
+        <is>
+          <t>digital c-type print</t>
+        </is>
+      </c>
+      <c r="P117" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q117" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="T117" s="1" t="inlineStr">
+        <is>
+          <t>living surface</t>
+        </is>
+      </c>
+      <c r="W117" s="5" t="inlineStr">
         <is>
           <t>Michael Davies</t>
         </is>
@@ -9565,18 +9629,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="25.83203125" customWidth="1" style="1" min="1" max="1"/>
-    <col width="20.83203125" customWidth="1" style="1" min="2" max="3"/>
+    <col width="24.83203125" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="20.83203125" customWidth="1" style="1" min="3" max="3"/>
     <col width="17" bestFit="1" customWidth="1" style="17" min="4" max="4"/>
     <col width="10.83203125" customWidth="1" style="1" min="5" max="5"/>
     <col width="21" bestFit="1" customWidth="1" style="9" min="6" max="6"/>
     <col width="21" customWidth="1" style="9" min="7" max="7"/>
     <col width="51" bestFit="1" customWidth="1" style="1" min="8" max="8"/>
-    <col width="10.83203125" customWidth="1" style="1" min="9" max="22"/>
-    <col width="10.83203125" customWidth="1" style="1" min="23" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="1" min="9" max="23"/>
+    <col width="10.83203125" customWidth="1" style="1" min="24" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -9841,7 +9906,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="D8" s="26" t="n">
+      <c r="D8" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="E8" s="1" t="n">
@@ -9853,6 +9918,34 @@
       <c r="G8" s="5" t="inlineStr">
         <is>
           <t>00460</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>living-surface-hand-form</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>living surface hand form</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>1989, 2004</t>
         </is>
       </c>
     </row>
@@ -20660,7 +20753,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E263" s="26" t="n">
+      <c r="E263" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F263" s="1" t="inlineStr">
@@ -20701,7 +20794,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E264" s="26" t="n">
+      <c r="E264" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F264" s="1" t="inlineStr">
@@ -20742,7 +20835,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E265" s="26" t="n">
+      <c r="E265" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F265" s="1" t="inlineStr">
@@ -20783,7 +20876,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E266" s="26" t="n">
+      <c r="E266" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F266" s="1" t="inlineStr">
@@ -20824,7 +20917,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E267" s="26" t="n">
+      <c r="E267" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F267" s="1" t="inlineStr">
@@ -20865,7 +20958,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E268" s="26" t="n">
+      <c r="E268" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F268" s="1" t="inlineStr">
@@ -20906,7 +20999,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E269" s="26" t="n">
+      <c r="E269" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F269" s="1" t="inlineStr">
@@ -20947,7 +21040,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E270" s="26" t="n">
+      <c r="E270" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F270" s="1" t="inlineStr">
@@ -20988,7 +21081,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E271" s="26" t="n">
+      <c r="E271" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F271" s="1" t="inlineStr">
@@ -21029,7 +21122,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E272" s="26" t="n">
+      <c r="E272" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F272" s="1" t="inlineStr">
@@ -21070,7 +21163,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E273" s="26" t="n">
+      <c r="E273" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F273" s="1" t="inlineStr">
@@ -21111,7 +21204,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E274" s="26" t="n">
+      <c r="E274" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F274" s="1" t="inlineStr">
@@ -21152,7 +21245,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E275" s="26" t="n">
+      <c r="E275" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F275" s="1" t="inlineStr">
@@ -21193,7 +21286,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E276" s="26" t="n">
+      <c r="E276" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F276" s="1" t="inlineStr">
@@ -21234,7 +21327,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E277" s="26" t="n">
+      <c r="E277" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F277" s="1" t="inlineStr">
@@ -21275,7 +21368,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E278" s="26" t="n">
+      <c r="E278" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F278" s="1" t="inlineStr">
@@ -21316,7 +21409,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E279" s="26" t="n">
+      <c r="E279" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F279" s="1" t="inlineStr">
@@ -21357,7 +21450,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E280" s="26" t="n">
+      <c r="E280" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F280" s="1" t="inlineStr">
@@ -21398,7 +21491,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E281" s="26" t="n">
+      <c r="E281" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F281" s="1" t="inlineStr">
@@ -21439,7 +21532,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E282" s="26" t="n">
+      <c r="E282" s="18" t="n">
         <v>46069</v>
       </c>
       <c r="F282" s="1" t="inlineStr">
@@ -21484,8 +21577,8 @@
     <col width="11.33203125" bestFit="1" customWidth="1" style="21" min="9" max="9"/>
     <col width="12.1640625" bestFit="1" customWidth="1" style="21" min="10" max="10"/>
     <col width="33.6640625" customWidth="1" style="21" min="11" max="11"/>
-    <col width="10.83203125" customWidth="1" style="21" min="12" max="16"/>
-    <col width="10.83203125" customWidth="1" style="21" min="17" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="21" min="12" max="17"/>
+    <col width="10.83203125" customWidth="1" style="21" min="18" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23657,8 +23750,8 @@
     <col width="20.1640625" bestFit="1" customWidth="1" style="12" min="6" max="6"/>
     <col width="48.1640625" bestFit="1" customWidth="1" style="12" min="7" max="7"/>
     <col width="21.83203125" customWidth="1" style="12" min="8" max="256"/>
-    <col width="21.83203125" customWidth="1" style="16" min="257" max="266"/>
-    <col width="21.83203125" customWidth="1" style="16" min="267" max="16384"/>
+    <col width="21.83203125" customWidth="1" style="16" min="257" max="267"/>
+    <col width="21.83203125" customWidth="1" style="16" min="268" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20600" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20600" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,10 +22,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -145,7 +146,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -214,6 +215,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -615,7 +618,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="21.83203125" customWidth="1" style="4" min="1" max="1"/>
     <col width="75.83203125" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
@@ -1399,15 +1402,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y169"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <dimension ref="A1:Y189"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="11.33203125" customWidth="1" style="7" min="1" max="1"/>
     <col width="13.33203125" customWidth="1" style="7" min="2" max="2"/>
     <col width="17" bestFit="1" customWidth="1" style="28" min="3" max="3"/>
-    <col width="22.6640625" customWidth="1" style="7" min="4" max="4"/>
-    <col width="31.6640625" customWidth="1" style="7" min="5" max="5"/>
-    <col width="27.6640625" customWidth="1" style="7" min="6" max="6"/>
+    <col width="29.1640625" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
+    <col width="43.1640625" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
+    <col width="72.83203125" bestFit="1" customWidth="1" style="7" min="6" max="6"/>
     <col width="13.1640625" customWidth="1" style="7" min="7" max="7"/>
     <col width="14" customWidth="1" style="7" min="8" max="8"/>
     <col width="10.83203125" customWidth="1" style="7" min="9" max="9"/>
@@ -1426,8 +1429,8 @@
     <col width="21.5" customWidth="1" style="7" min="23" max="23"/>
     <col width="26.83203125" customWidth="1" style="7" min="24" max="24"/>
     <col width="20.83203125" customWidth="1" style="7" min="25" max="25"/>
-    <col width="10.83203125" customWidth="1" style="7" min="26" max="43"/>
-    <col width="10.83203125" customWidth="1" style="7" min="44" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="7" min="26" max="46"/>
+    <col width="10.83203125" customWidth="1" style="7" min="47" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="6">
@@ -12369,6 +12372,1280 @@
         </is>
       </c>
       <c r="X169" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="22" t="inlineStr">
+        <is>
+          <t>00516</t>
+        </is>
+      </c>
+      <c r="B170" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C170" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D170" s="32" t="inlineStr">
+        <is>
+          <t>landscapes</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>landscape 1.jpg</t>
+        </is>
+      </c>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>landscape 1</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="H170" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I170" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J170" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K170" s="32" t="inlineStr">
+        <is>
+          <t>landscapes</t>
+        </is>
+      </c>
+      <c r="L170" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="M170" s="7" t="inlineStr">
+        <is>
+          <t>digital c-type print</t>
+        </is>
+      </c>
+      <c r="X170" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="22" t="inlineStr">
+        <is>
+          <t>00517</t>
+        </is>
+      </c>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C171" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D171" s="32" t="inlineStr">
+        <is>
+          <t>landscapes</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>landscape 2.jpg</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>landscape 2</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="H171" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I171" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J171" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K171" s="32" t="inlineStr">
+        <is>
+          <t>landscapes</t>
+        </is>
+      </c>
+      <c r="L171" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="M171" s="7" t="inlineStr">
+        <is>
+          <t>digital c-type print</t>
+        </is>
+      </c>
+      <c r="X171" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="22" t="inlineStr">
+        <is>
+          <t>00518</t>
+        </is>
+      </c>
+      <c r="B172" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C172" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D172" s="32" t="inlineStr">
+        <is>
+          <t>landscapes</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t>landscape 2.1.jpg</t>
+        </is>
+      </c>
+      <c r="F172" s="7" t="inlineStr">
+        <is>
+          <t>landscape 2.1</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="H172" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I172" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J172" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K172" s="32" t="inlineStr">
+        <is>
+          <t>landscapes</t>
+        </is>
+      </c>
+      <c r="L172" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="M172" s="7" t="inlineStr">
+        <is>
+          <t>digital c-type print</t>
+        </is>
+      </c>
+      <c r="X172" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="22" t="inlineStr">
+        <is>
+          <t>00114</t>
+        </is>
+      </c>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C173" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D173" s="1" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 1.jpg</t>
+        </is>
+      </c>
+      <c r="F173" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 1</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H173" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I173" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J173" s="7" t="inlineStr">
+        <is>
+          <t>c. 2010?</t>
+        </is>
+      </c>
+      <c r="K173" s="1" t="inlineStr">
+        <is>
+          <t>learning-to-draw-landscapes</t>
+        </is>
+      </c>
+      <c r="L173" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M173" s="7" t="inlineStr">
+        <is>
+          <t>pencil on paper</t>
+        </is>
+      </c>
+      <c r="X173" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="22" t="inlineStr">
+        <is>
+          <t>00115</t>
+        </is>
+      </c>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C174" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D174" s="1" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 2.jpg</t>
+        </is>
+      </c>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 2</t>
+        </is>
+      </c>
+      <c r="G174" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H174" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I174" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J174" s="7" t="inlineStr">
+        <is>
+          <t>c. 2010?</t>
+        </is>
+      </c>
+      <c r="K174" s="1" t="inlineStr">
+        <is>
+          <t>learning-to-draw-landscapes</t>
+        </is>
+      </c>
+      <c r="L174" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M174" s="7" t="inlineStr">
+        <is>
+          <t>pencil on paper</t>
+        </is>
+      </c>
+      <c r="X174" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="22" t="inlineStr">
+        <is>
+          <t>00116</t>
+        </is>
+      </c>
+      <c r="B175" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C175" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D175" s="1" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 3.jpg</t>
+        </is>
+      </c>
+      <c r="F175" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 3</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H175" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I175" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J175" s="7" t="inlineStr">
+        <is>
+          <t>c. 2010?</t>
+        </is>
+      </c>
+      <c r="K175" s="1" t="inlineStr">
+        <is>
+          <t>learning-to-draw-landscapes</t>
+        </is>
+      </c>
+      <c r="L175" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M175" s="7" t="inlineStr">
+        <is>
+          <t>pencil on paper</t>
+        </is>
+      </c>
+      <c r="X175" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="22" t="inlineStr">
+        <is>
+          <t>00117</t>
+        </is>
+      </c>
+      <c r="B176" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C176" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D176" s="1" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 4.jpg</t>
+        </is>
+      </c>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 4</t>
+        </is>
+      </c>
+      <c r="G176" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H176" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I176" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J176" s="7" t="inlineStr">
+        <is>
+          <t>c. 2010?</t>
+        </is>
+      </c>
+      <c r="K176" s="1" t="inlineStr">
+        <is>
+          <t>learning-to-draw-landscapes</t>
+        </is>
+      </c>
+      <c r="L176" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M176" s="7" t="inlineStr">
+        <is>
+          <t>pencil on paper</t>
+        </is>
+      </c>
+      <c r="X176" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="22" t="inlineStr">
+        <is>
+          <t>00118</t>
+        </is>
+      </c>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C177" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D177" s="1" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 5.jpg</t>
+        </is>
+      </c>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 5</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H177" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I177" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J177" s="7" t="inlineStr">
+        <is>
+          <t>c. 2010?</t>
+        </is>
+      </c>
+      <c r="K177" s="1" t="inlineStr">
+        <is>
+          <t>learning-to-draw-landscapes</t>
+        </is>
+      </c>
+      <c r="L177" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M177" s="7" t="inlineStr">
+        <is>
+          <t>pencil on paper</t>
+        </is>
+      </c>
+      <c r="X177" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="22" t="inlineStr">
+        <is>
+          <t>00119</t>
+        </is>
+      </c>
+      <c r="B178" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C178" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D178" s="1" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 6.jpg</t>
+        </is>
+      </c>
+      <c r="F178" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 6</t>
+        </is>
+      </c>
+      <c r="G178" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H178" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I178" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J178" s="7" t="inlineStr">
+        <is>
+          <t>c. 2010?</t>
+        </is>
+      </c>
+      <c r="K178" s="1" t="inlineStr">
+        <is>
+          <t>learning-to-draw-landscapes</t>
+        </is>
+      </c>
+      <c r="L178" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M178" s="7" t="inlineStr">
+        <is>
+          <t>pencil on paper</t>
+        </is>
+      </c>
+      <c r="X178" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="22" t="inlineStr">
+        <is>
+          <t>00120</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C179" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D179" s="1" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 7.jpg</t>
+        </is>
+      </c>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 7</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H179" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I179" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J179" s="7" t="inlineStr">
+        <is>
+          <t>c. 2010?</t>
+        </is>
+      </c>
+      <c r="K179" s="1" t="inlineStr">
+        <is>
+          <t>learning-to-draw-landscapes</t>
+        </is>
+      </c>
+      <c r="L179" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M179" s="7" t="inlineStr">
+        <is>
+          <t>pencil on paper</t>
+        </is>
+      </c>
+      <c r="X179" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="22" t="inlineStr">
+        <is>
+          <t>00121</t>
+        </is>
+      </c>
+      <c r="B180" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C180" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D180" s="1" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 8.jpg</t>
+        </is>
+      </c>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 8</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H180" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I180" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J180" s="7" t="inlineStr">
+        <is>
+          <t>c. 2010?</t>
+        </is>
+      </c>
+      <c r="K180" s="1" t="inlineStr">
+        <is>
+          <t>learning-to-draw-landscapes</t>
+        </is>
+      </c>
+      <c r="L180" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M180" s="7" t="inlineStr">
+        <is>
+          <t>pencil on paper</t>
+        </is>
+      </c>
+      <c r="X180" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="22" t="inlineStr">
+        <is>
+          <t>00122</t>
+        </is>
+      </c>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C181" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D181" s="1" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 9.jpg</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 9</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H181" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I181" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J181" s="7" t="inlineStr">
+        <is>
+          <t>c. 2010?</t>
+        </is>
+      </c>
+      <c r="K181" s="1" t="inlineStr">
+        <is>
+          <t>learning-to-draw-landscapes</t>
+        </is>
+      </c>
+      <c r="L181" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M181" s="7" t="inlineStr">
+        <is>
+          <t>pencil on paper</t>
+        </is>
+      </c>
+      <c r="X181" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="22" t="inlineStr">
+        <is>
+          <t>00123</t>
+        </is>
+      </c>
+      <c r="B182" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C182" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D182" s="1" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 10.jpg</t>
+        </is>
+      </c>
+      <c r="F182" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 10</t>
+        </is>
+      </c>
+      <c r="G182" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H182" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I182" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J182" s="7" t="inlineStr">
+        <is>
+          <t>c. 2010?</t>
+        </is>
+      </c>
+      <c r="K182" s="1" t="inlineStr">
+        <is>
+          <t>learning-to-draw-landscapes</t>
+        </is>
+      </c>
+      <c r="L182" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M182" s="7" t="inlineStr">
+        <is>
+          <t>pencil on paper</t>
+        </is>
+      </c>
+      <c r="X182" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="22" t="inlineStr">
+        <is>
+          <t>00124</t>
+        </is>
+      </c>
+      <c r="B183" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C183" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D183" s="1" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes</t>
+        </is>
+      </c>
+      <c r="E183" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 11.jpg</t>
+        </is>
+      </c>
+      <c r="F183" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 11</t>
+        </is>
+      </c>
+      <c r="G183" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H183" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I183" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J183" s="7" t="inlineStr">
+        <is>
+          <t>c. 2010?</t>
+        </is>
+      </c>
+      <c r="K183" s="1" t="inlineStr">
+        <is>
+          <t>learning-to-draw-landscapes</t>
+        </is>
+      </c>
+      <c r="L183" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M183" s="7" t="inlineStr">
+        <is>
+          <t>pencil on paper</t>
+        </is>
+      </c>
+      <c r="X183" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="22" t="inlineStr">
+        <is>
+          <t>00125</t>
+        </is>
+      </c>
+      <c r="B184" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C184" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D184" s="1" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 12.jpg</t>
+        </is>
+      </c>
+      <c r="F184" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 12</t>
+        </is>
+      </c>
+      <c r="G184" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H184" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I184" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J184" s="7" t="inlineStr">
+        <is>
+          <t>c. 2010?</t>
+        </is>
+      </c>
+      <c r="K184" s="1" t="inlineStr">
+        <is>
+          <t>learning-to-draw-landscapes</t>
+        </is>
+      </c>
+      <c r="L184" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M184" s="7" t="inlineStr">
+        <is>
+          <t>pencil on paper</t>
+        </is>
+      </c>
+      <c r="X184" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="22" t="inlineStr">
+        <is>
+          <t>00126</t>
+        </is>
+      </c>
+      <c r="B185" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C185" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D185" s="1" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 13.jpg</t>
+        </is>
+      </c>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 13</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H185" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I185" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J185" s="7" t="inlineStr">
+        <is>
+          <t>c. 2010?</t>
+        </is>
+      </c>
+      <c r="K185" s="1" t="inlineStr">
+        <is>
+          <t>learning-to-draw-landscapes</t>
+        </is>
+      </c>
+      <c r="L185" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M185" s="7" t="inlineStr">
+        <is>
+          <t>pencil on paper</t>
+        </is>
+      </c>
+      <c r="X185" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="22" t="inlineStr">
+        <is>
+          <t>00127</t>
+        </is>
+      </c>
+      <c r="B186" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C186" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D186" s="1" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 14.jpg</t>
+        </is>
+      </c>
+      <c r="F186" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 14</t>
+        </is>
+      </c>
+      <c r="G186" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H186" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I186" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J186" s="7" t="inlineStr">
+        <is>
+          <t>c. 2010?</t>
+        </is>
+      </c>
+      <c r="K186" s="1" t="inlineStr">
+        <is>
+          <t>learning-to-draw-landscapes</t>
+        </is>
+      </c>
+      <c r="L186" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M186" s="7" t="inlineStr">
+        <is>
+          <t>pencil on paper</t>
+        </is>
+      </c>
+      <c r="X186" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="22" t="inlineStr">
+        <is>
+          <t>00128</t>
+        </is>
+      </c>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C187" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D187" s="1" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 15.jpg</t>
+        </is>
+      </c>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 15</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H187" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I187" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J187" s="7" t="inlineStr">
+        <is>
+          <t>c. 2010?</t>
+        </is>
+      </c>
+      <c r="K187" s="1" t="inlineStr">
+        <is>
+          <t>learning-to-draw-landscapes</t>
+        </is>
+      </c>
+      <c r="L187" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M187" s="7" t="inlineStr">
+        <is>
+          <t>pencil on paper</t>
+        </is>
+      </c>
+      <c r="X187" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="22" t="inlineStr">
+        <is>
+          <t>00129</t>
+        </is>
+      </c>
+      <c r="B188" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C188" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D188" s="1" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes</t>
+        </is>
+      </c>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 16.jpg</t>
+        </is>
+      </c>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes 16</t>
+        </is>
+      </c>
+      <c r="G188" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H188" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I188" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J188" s="7" t="inlineStr">
+        <is>
+          <t>c. 2010?</t>
+        </is>
+      </c>
+      <c r="K188" s="1" t="inlineStr">
+        <is>
+          <t>learning-to-draw-landscapes</t>
+        </is>
+      </c>
+      <c r="L188" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M188" s="7" t="inlineStr">
+        <is>
+          <t>pencil on paper</t>
+        </is>
+      </c>
+      <c r="X188" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C189" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D189" s="1" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes</t>
+        </is>
+      </c>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes (versions).jpg</t>
+        </is>
+      </c>
+      <c r="F189" s="7" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes (versions)</t>
+        </is>
+      </c>
+      <c r="G189" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H189" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="I189" s="7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J189" s="7" t="inlineStr">
+        <is>
+          <t>c. 2022?</t>
+        </is>
+      </c>
+      <c r="K189" s="1" t="inlineStr">
+        <is>
+          <t>learning-to-draw-landscapes</t>
+        </is>
+      </c>
+      <c r="L189" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="M189" s="7" t="inlineStr">
+        <is>
+          <t>digital c-type print</t>
+        </is>
+      </c>
+      <c r="X189" s="22" t="inlineStr">
         <is>
           <t>Michael Davies</t>
         </is>
@@ -12386,11 +13663,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
-    <col width="25.83203125" customWidth="1" style="1" min="1" max="1"/>
-    <col width="24.83203125" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="31.83203125" customWidth="1" style="1" min="1" max="1"/>
+    <col width="43.1640625" customWidth="1" style="1" min="2" max="2"/>
     <col width="20.83203125" customWidth="1" style="1" min="3" max="3"/>
     <col width="17" bestFit="1" customWidth="1" style="15" min="4" max="4"/>
     <col width="10.83203125" customWidth="1" style="1" min="5" max="5"/>
@@ -12398,8 +13675,8 @@
     <col width="21" customWidth="1" style="7" min="7" max="7"/>
     <col width="28.1640625" customWidth="1" style="7" min="8" max="8"/>
     <col width="51" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" style="1" min="10" max="28"/>
-    <col width="10.83203125" customWidth="1" style="1" min="29" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="1" min="10" max="31"/>
+    <col width="10.83203125" customWidth="1" style="1" min="32" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -12890,6 +14167,80 @@
       <c r="I13" s="1" t="inlineStr">
         <is>
           <t>add dall-e versions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>landscapes</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>landscapes</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>00516</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>landscape</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>learning-to-draw-landscapes</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>learning to draw landscapes</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>2010</v>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>c. 2010?, 2022</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>00127</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>landscape,drawing</t>
         </is>
       </c>
     </row>
@@ -12904,8 +14255,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J372"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <dimension ref="A1:J447"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="9.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -28186,6 +29537,3081 @@
         <v>4429</v>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B373" s="5" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>version dall-e - 1.0 (run source).jpg</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>version dall-e - 1.0 (run source)</t>
+        </is>
+      </c>
+      <c r="F373" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G373" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H373" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I373" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B374" s="5" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>version dall-e - 1.1.jpg</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>version dall-e - 1.1</t>
+        </is>
+      </c>
+      <c r="F374" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G374" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H374" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I374" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B375" s="5" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>version dall-e - 1.2.jpg</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>version dall-e - 1.2</t>
+        </is>
+      </c>
+      <c r="F375" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G375" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H375" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I375" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B376" s="5" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>version dall-e - 1.3.jpg</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>version dall-e - 1.3</t>
+        </is>
+      </c>
+      <c r="F376" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G376" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H376" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I376" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B377" s="5" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>version dall-e - 1.4.jpg</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>version dall-e - 1.4</t>
+        </is>
+      </c>
+      <c r="F377" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G377" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H377" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I377" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B378" s="5" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>version dall-e - 2.0 (run source).jpg</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>version dall-e - 2.0 (run source)</t>
+        </is>
+      </c>
+      <c r="F378" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G378" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H378" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I378" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B379" s="5" t="inlineStr">
+        <is>
+          <t>007</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>version dall-e - 2.1.jpg</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>version dall-e - 2.1</t>
+        </is>
+      </c>
+      <c r="F379" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G379" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H379" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I379" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B380" s="5" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>version dall-e - 2.2.jpg</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>version dall-e - 2.2</t>
+        </is>
+      </c>
+      <c r="F380" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G380" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H380" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I380" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B381" s="5" t="inlineStr">
+        <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>version dall-e - 2.3.jpg</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>version dall-e - 2.3</t>
+        </is>
+      </c>
+      <c r="F381" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G381" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H381" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I381" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B382" s="5" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>version dall-e - 2.4.jpg</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>version dall-e - 2.4</t>
+        </is>
+      </c>
+      <c r="F382" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G382" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H382" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I382" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B383" s="5" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>version dall-e - 3.0 (run source).jpg</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>version dall-e - 3.0 (run source)</t>
+        </is>
+      </c>
+      <c r="F383" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G383" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H383" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I383" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B384" s="5" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>version dall-e - 3.1.jpg</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>version dall-e - 3.1</t>
+        </is>
+      </c>
+      <c r="F384" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G384" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H384" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I384" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B385" s="5" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>version dall-e - 3.2.jpg</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>version dall-e - 3.2</t>
+        </is>
+      </c>
+      <c r="F385" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G385" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H385" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I385" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B386" s="5" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>version dall-e - 3.3.jpg</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>version dall-e - 3.3</t>
+        </is>
+      </c>
+      <c r="F386" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G386" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H386" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I386" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B387" s="5" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>version dall-e - 3.4.jpg</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>version dall-e - 3.4</t>
+        </is>
+      </c>
+      <c r="F387" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G387" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H387" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I387" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B388" s="5" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>version dall-e - 4.0 (run source).jpg</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>version dall-e - 4.0 (run source)</t>
+        </is>
+      </c>
+      <c r="F388" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G388" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H388" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I388" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B389" s="5" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>version dall-e - 4.1.jpg</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>version dall-e - 4.1</t>
+        </is>
+      </c>
+      <c r="F389" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G389" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H389" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I389" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B390" s="5" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>version dall-e - 4.2.jpg</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>version dall-e - 4.2</t>
+        </is>
+      </c>
+      <c r="F390" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G390" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H390" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I390" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B391" s="5" t="inlineStr">
+        <is>
+          <t>019</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>version dall-e - 4.3.jpg</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>version dall-e - 4.3</t>
+        </is>
+      </c>
+      <c r="F391" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G391" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H391" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I391" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B392" s="5" t="inlineStr">
+        <is>
+          <t>020</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>version dall-e - 4.4.jpg</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>version dall-e - 4.4</t>
+        </is>
+      </c>
+      <c r="F392" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G392" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H392" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I392" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B393" s="5" t="inlineStr">
+        <is>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>version dall-e - 5.0 (run source).jpg</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>version dall-e - 5.0 (run source)</t>
+        </is>
+      </c>
+      <c r="F393" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G393" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H393" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I393" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B394" s="5" t="inlineStr">
+        <is>
+          <t>022</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>version dall-e - 5.1.jpg</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>version dall-e - 5.1</t>
+        </is>
+      </c>
+      <c r="F394" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G394" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H394" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I394" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B395" s="5" t="inlineStr">
+        <is>
+          <t>023</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>version dall-e - 5.2.jpg</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>version dall-e - 5.2</t>
+        </is>
+      </c>
+      <c r="F395" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G395" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H395" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I395" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B396" s="5" t="inlineStr">
+        <is>
+          <t>024</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>version dall-e - 5.3.jpg</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>version dall-e - 5.3</t>
+        </is>
+      </c>
+      <c r="F396" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G396" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H396" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I396" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B397" s="5" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>version dall-e - 5.4.jpg</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>version dall-e - 5.4</t>
+        </is>
+      </c>
+      <c r="F397" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G397" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H397" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I397" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B398" s="5" t="inlineStr">
+        <is>
+          <t>026</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>version dall-e - 6.0 (run source).jpg</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>version dall-e - 6.0 (run source)</t>
+        </is>
+      </c>
+      <c r="F398" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G398" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H398" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I398" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B399" s="5" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>version dall-e - 6.1.jpg</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>version dall-e - 6.1</t>
+        </is>
+      </c>
+      <c r="F399" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G399" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H399" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I399" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B400" s="5" t="inlineStr">
+        <is>
+          <t>028</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>version dall-e - 6.2.jpg</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>version dall-e - 6.2</t>
+        </is>
+      </c>
+      <c r="F400" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G400" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H400" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I400" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B401" s="5" t="inlineStr">
+        <is>
+          <t>029</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>version dall-e - 6.3.jpg</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>version dall-e - 6.3</t>
+        </is>
+      </c>
+      <c r="F401" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G401" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H401" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I401" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B402" s="5" t="inlineStr">
+        <is>
+          <t>030</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>version dall-e - 6.4.jpg</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>version dall-e - 6.4</t>
+        </is>
+      </c>
+      <c r="F402" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G402" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H402" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I402" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B403" s="5" t="inlineStr">
+        <is>
+          <t>031</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>version dall-e - 7.0 (run source).jpg</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>version dall-e - 7.0 (run source)</t>
+        </is>
+      </c>
+      <c r="F403" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G403" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H403" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I403" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B404" s="5" t="inlineStr">
+        <is>
+          <t>032</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>version dall-e - 7.1.jpg</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>version dall-e - 7.1</t>
+        </is>
+      </c>
+      <c r="F404" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G404" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H404" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I404" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B405" s="5" t="inlineStr">
+        <is>
+          <t>033</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>version dall-e - 7.2.jpg</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>version dall-e - 7.2</t>
+        </is>
+      </c>
+      <c r="F405" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G405" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H405" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I405" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B406" s="5" t="inlineStr">
+        <is>
+          <t>034</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>version dall-e - 7.3.jpg</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>version dall-e - 7.3</t>
+        </is>
+      </c>
+      <c r="F406" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G406" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H406" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I406" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B407" s="5" t="inlineStr">
+        <is>
+          <t>035</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>version dall-e - 7.4.jpg</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>version dall-e - 7.4</t>
+        </is>
+      </c>
+      <c r="F407" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G407" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H407" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I407" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B408" s="5" t="inlineStr">
+        <is>
+          <t>036</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>version dall-e - 8.0 (run source).jpg</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>version dall-e - 8.0 (run source)</t>
+        </is>
+      </c>
+      <c r="F408" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G408" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H408" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I408" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B409" s="5" t="inlineStr">
+        <is>
+          <t>037</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>version dall-e - 8.1.jpg</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>version dall-e - 8.1</t>
+        </is>
+      </c>
+      <c r="F409" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G409" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H409" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I409" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B410" s="5" t="inlineStr">
+        <is>
+          <t>038</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>version dall-e - 8.2.jpg</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>version dall-e - 8.2</t>
+        </is>
+      </c>
+      <c r="F410" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G410" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H410" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I410" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B411" s="5" t="inlineStr">
+        <is>
+          <t>039</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>version dall-e - 8.3.jpg</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>version dall-e - 8.3</t>
+        </is>
+      </c>
+      <c r="F411" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G411" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H411" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I411" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B412" s="5" t="inlineStr">
+        <is>
+          <t>040</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>version dall-e - 8.4.jpg</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>version dall-e - 8.4</t>
+        </is>
+      </c>
+      <c r="F412" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G412" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H412" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I412" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B413" s="5" t="inlineStr">
+        <is>
+          <t>041</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>version dall-e - 9.0 (run source).jpg</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>version dall-e - 9.0 (run source)</t>
+        </is>
+      </c>
+      <c r="F413" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G413" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H413" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I413" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B414" s="5" t="inlineStr">
+        <is>
+          <t>042</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>version dall-e - 9.1.jpg</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>version dall-e - 9.1</t>
+        </is>
+      </c>
+      <c r="F414" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G414" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H414" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I414" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B415" s="5" t="inlineStr">
+        <is>
+          <t>043</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>version dall-e - 9.2.jpg</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>version dall-e - 9.2</t>
+        </is>
+      </c>
+      <c r="F415" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G415" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H415" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I415" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B416" s="5" t="inlineStr">
+        <is>
+          <t>044</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>version dall-e - 9.3.jpg</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>version dall-e - 9.3</t>
+        </is>
+      </c>
+      <c r="F416" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G416" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H416" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I416" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B417" s="5" t="inlineStr">
+        <is>
+          <t>045</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>version dall-e - 9.4.jpg</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>version dall-e - 9.4</t>
+        </is>
+      </c>
+      <c r="F417" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G417" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H417" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I417" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B418" s="5" t="inlineStr">
+        <is>
+          <t>046</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>version dall-e - 10.0 (run source).jpg</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>version dall-e - 10.0 (run source)</t>
+        </is>
+      </c>
+      <c r="F418" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G418" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H418" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I418" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B419" s="5" t="inlineStr">
+        <is>
+          <t>047</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>version dall-e - 10.1.jpg</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>version dall-e - 10.1</t>
+        </is>
+      </c>
+      <c r="F419" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G419" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H419" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I419" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B420" s="5" t="inlineStr">
+        <is>
+          <t>048</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>version dall-e - 10.2.jpg</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>version dall-e - 10.2</t>
+        </is>
+      </c>
+      <c r="F420" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G420" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H420" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I420" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B421" s="5" t="inlineStr">
+        <is>
+          <t>049</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>version dall-e - 10.3.jpg</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>version dall-e - 10.3</t>
+        </is>
+      </c>
+      <c r="F421" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G421" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H421" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I421" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B422" s="5" t="inlineStr">
+        <is>
+          <t>050</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>version dall-e - 10.4.jpg</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>version dall-e - 10.4</t>
+        </is>
+      </c>
+      <c r="F422" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G422" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H422" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I422" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B423" s="5" t="inlineStr">
+        <is>
+          <t>051</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>version dall-e - 11.0 (run source).jpg</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>version dall-e - 11.0 (run source)</t>
+        </is>
+      </c>
+      <c r="F423" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G423" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H423" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I423" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B424" s="5" t="inlineStr">
+        <is>
+          <t>052</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>version dall-e - 11.1.jpg</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>version dall-e - 11.1</t>
+        </is>
+      </c>
+      <c r="F424" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G424" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H424" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I424" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B425" s="5" t="inlineStr">
+        <is>
+          <t>053</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>version dall-e - 11.2.jpg</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>version dall-e - 11.2</t>
+        </is>
+      </c>
+      <c r="F425" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G425" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H425" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I425" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B426" s="5" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>version dall-e - 11.3.jpg</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>version dall-e - 11.3</t>
+        </is>
+      </c>
+      <c r="F426" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G426" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H426" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I426" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B427" s="5" t="inlineStr">
+        <is>
+          <t>055</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>version dall-e - 11.4.jpg</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>version dall-e - 11.4</t>
+        </is>
+      </c>
+      <c r="F427" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G427" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H427" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I427" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B428" s="5" t="inlineStr">
+        <is>
+          <t>056</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>version dall-e - 12.0 (run source).jpg</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>version dall-e - 12.0 (run source)</t>
+        </is>
+      </c>
+      <c r="F428" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G428" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H428" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I428" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B429" s="5" t="inlineStr">
+        <is>
+          <t>057</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>version dall-e - 12.1.jpg</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>version dall-e - 12.1</t>
+        </is>
+      </c>
+      <c r="F429" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G429" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H429" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I429" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B430" s="5" t="inlineStr">
+        <is>
+          <t>058</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>version dall-e - 12.2.jpg</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>version dall-e - 12.2</t>
+        </is>
+      </c>
+      <c r="F430" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G430" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H430" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I430" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B431" s="5" t="inlineStr">
+        <is>
+          <t>059</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>version dall-e - 12.3.jpg</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>version dall-e - 12.3</t>
+        </is>
+      </c>
+      <c r="F431" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G431" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H431" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I431" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B432" s="5" t="inlineStr">
+        <is>
+          <t>060</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>version dall-e - 12.4.jpg</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>version dall-e - 12.4</t>
+        </is>
+      </c>
+      <c r="F432" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G432" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H432" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I432" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B433" s="5" t="inlineStr">
+        <is>
+          <t>061</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>version dall-e - 13.0 (run source).jpg</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>version dall-e - 13.0 (run source)</t>
+        </is>
+      </c>
+      <c r="F433" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G433" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H433" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I433" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B434" s="5" t="inlineStr">
+        <is>
+          <t>062</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>version dall-e - 13.1.jpg</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>version dall-e - 13.1</t>
+        </is>
+      </c>
+      <c r="F434" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G434" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H434" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I434" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B435" s="5" t="inlineStr">
+        <is>
+          <t>063</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>version dall-e - 13.2.jpg</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>version dall-e - 13.2</t>
+        </is>
+      </c>
+      <c r="F435" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G435" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H435" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I435" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B436" s="5" t="inlineStr">
+        <is>
+          <t>064</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>version dall-e - 13.3.jpg</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>version dall-e - 13.3</t>
+        </is>
+      </c>
+      <c r="F436" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G436" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H436" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I436" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B437" s="5" t="inlineStr">
+        <is>
+          <t>065</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>version dall-e - 13.4.jpg</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>version dall-e - 13.4</t>
+        </is>
+      </c>
+      <c r="F437" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G437" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H437" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I437" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B438" s="5" t="inlineStr">
+        <is>
+          <t>066</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>version dall-e - 14.0 (run source).jpg</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>version dall-e - 14.0 (run source)</t>
+        </is>
+      </c>
+      <c r="F438" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G438" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H438" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I438" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B439" s="5" t="inlineStr">
+        <is>
+          <t>067</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>version dall-e - 14.1.jpg</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>version dall-e - 14.1</t>
+        </is>
+      </c>
+      <c r="F439" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G439" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H439" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I439" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B440" s="5" t="inlineStr">
+        <is>
+          <t>068</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>version dall-e - 14.2.jpg</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>version dall-e - 14.2</t>
+        </is>
+      </c>
+      <c r="F440" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G440" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H440" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I440" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B441" s="5" t="inlineStr">
+        <is>
+          <t>069</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>version dall-e - 14.3.jpg</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>version dall-e - 14.3</t>
+        </is>
+      </c>
+      <c r="F441" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G441" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H441" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I441" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B442" s="5" t="inlineStr">
+        <is>
+          <t>070</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>version dall-e - 14.4.jpg</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>version dall-e - 14.4</t>
+        </is>
+      </c>
+      <c r="F442" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G442" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H442" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I442" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B443" s="5" t="inlineStr">
+        <is>
+          <t>071</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>version dall-e - 15.0 (run source).jpg</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>version dall-e - 15.0 (run source)</t>
+        </is>
+      </c>
+      <c r="F443" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G443" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H443" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I443" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B444" s="5" t="inlineStr">
+        <is>
+          <t>072</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>version dall-e - 15.1.jpg</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>version dall-e - 15.1</t>
+        </is>
+      </c>
+      <c r="F444" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G444" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H444" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I444" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B445" s="5" t="inlineStr">
+        <is>
+          <t>073</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>version dall-e - 15.2.jpg</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>version dall-e - 15.2</t>
+        </is>
+      </c>
+      <c r="F445" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G445" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H445" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I445" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B446" s="5" t="inlineStr">
+        <is>
+          <t>074</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>version dall-e - 15.3.jpg</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>version dall-e - 15.3</t>
+        </is>
+      </c>
+      <c r="F446" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G446" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H446" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I446" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="22" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B447" s="5" t="inlineStr">
+        <is>
+          <t>075</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>version dall-e - 15.4.jpg</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>version dall-e - 15.4</t>
+        </is>
+      </c>
+      <c r="F447" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G447" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H447" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I447" t="n">
+        <v>3543</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -28198,7 +32624,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" outlineLevelCol="0"/>
   <cols>
     <col width="24.1640625" customWidth="1" style="19" min="1" max="1"/>
     <col width="34.83203125" customWidth="1" style="19" min="2" max="2"/>
@@ -28211,8 +32637,8 @@
     <col width="11.33203125" bestFit="1" customWidth="1" style="19" min="9" max="9"/>
     <col width="12.1640625" bestFit="1" customWidth="1" style="19" min="10" max="10"/>
     <col width="33.6640625" customWidth="1" style="19" min="11" max="11"/>
-    <col width="10.83203125" customWidth="1" style="19" min="12" max="21"/>
-    <col width="10.83203125" customWidth="1" style="19" min="22" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="19" min="12" max="24"/>
+    <col width="10.83203125" customWidth="1" style="19" min="25" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30374,7 +34800,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G839"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="21.83203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="21.83203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="41.6640625" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
     <col width="9.33203125" customWidth="1" style="10" min="2" max="2"/>
@@ -30384,8 +34810,8 @@
     <col width="20.1640625" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
     <col width="48.1640625" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
     <col width="21.83203125" customWidth="1" style="10" min="8" max="256"/>
-    <col width="21.83203125" customWidth="1" style="14" min="257" max="271"/>
-    <col width="21.83203125" customWidth="1" style="14" min="272" max="16384"/>
+    <col width="21.83203125" customWidth="1" style="14" min="257" max="274"/>
+    <col width="21.83203125" customWidth="1" style="14" min="275" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -22,13 +22,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -109,12 +108,6 @@
       <color rgb="FF000000"/>
       <sz val="13"/>
     </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -146,7 +139,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -216,7 +209,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -618,10 +610,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="21.83203125" customWidth="1" style="4" min="1" max="1"/>
-    <col width="75.83203125" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="77.33203125" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
     <col width="85.6640625" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
     <col width="85.5" customWidth="1" style="1" min="4" max="4"/>
   </cols>
@@ -1020,14 +1012,14 @@
           <t>artist</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>can be more than one if collaboration</t>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">can be more than one if collaboration. pipeline defaults to "Michael Davies" </t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>public label</t>
+          <t>public label if needed</t>
         </is>
       </c>
     </row>
@@ -1402,8 +1394,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y189"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <dimension ref="A1:Y193"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="11.33203125" customWidth="1" style="7" min="1" max="1"/>
     <col width="13.33203125" customWidth="1" style="7" min="2" max="2"/>
@@ -1429,8 +1421,8 @@
     <col width="21.5" customWidth="1" style="7" min="23" max="23"/>
     <col width="26.83203125" customWidth="1" style="7" min="24" max="24"/>
     <col width="20.83203125" customWidth="1" style="7" min="25" max="25"/>
-    <col width="10.83203125" customWidth="1" style="7" min="26" max="46"/>
-    <col width="10.83203125" customWidth="1" style="7" min="47" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="7" min="26" max="49"/>
+    <col width="10.83203125" customWidth="1" style="7" min="50" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="6">
@@ -12574,7 +12566,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C173" s="33" t="n">
+      <c r="C173" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D173" s="1" t="inlineStr">
@@ -12638,7 +12630,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C174" s="33" t="n">
+      <c r="C174" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D174" s="1" t="inlineStr">
@@ -12702,7 +12694,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C175" s="33" t="n">
+      <c r="C175" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D175" s="1" t="inlineStr">
@@ -12766,7 +12758,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C176" s="33" t="n">
+      <c r="C176" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D176" s="1" t="inlineStr">
@@ -12830,7 +12822,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C177" s="33" t="n">
+      <c r="C177" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D177" s="1" t="inlineStr">
@@ -12894,7 +12886,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C178" s="33" t="n">
+      <c r="C178" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D178" s="1" t="inlineStr">
@@ -12958,7 +12950,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C179" s="33" t="n">
+      <c r="C179" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D179" s="1" t="inlineStr">
@@ -13022,7 +13014,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C180" s="33" t="n">
+      <c r="C180" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D180" s="1" t="inlineStr">
@@ -13086,7 +13078,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C181" s="33" t="n">
+      <c r="C181" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D181" s="1" t="inlineStr">
@@ -13150,7 +13142,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C182" s="33" t="n">
+      <c r="C182" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D182" s="1" t="inlineStr">
@@ -13214,7 +13206,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C183" s="33" t="n">
+      <c r="C183" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D183" s="1" t="inlineStr">
@@ -13278,7 +13270,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C184" s="33" t="n">
+      <c r="C184" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D184" s="1" t="inlineStr">
@@ -13342,7 +13334,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C185" s="33" t="n">
+      <c r="C185" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D185" s="1" t="inlineStr">
@@ -13406,7 +13398,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C186" s="33" t="n">
+      <c r="C186" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D186" s="1" t="inlineStr">
@@ -13470,7 +13462,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C187" s="33" t="n">
+      <c r="C187" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D187" s="1" t="inlineStr">
@@ -13534,7 +13526,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C188" s="33" t="n">
+      <c r="C188" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D188" s="1" t="inlineStr">
@@ -13598,7 +13590,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C189" s="33" t="n">
+      <c r="C189" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D189" s="1" t="inlineStr">
@@ -13650,6 +13642,238 @@
           <t>Michael Davies</t>
         </is>
       </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="22" t="inlineStr">
+        <is>
+          <t>00520</t>
+        </is>
+      </c>
+      <c r="B190" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C190" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>kylie structures</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t>kylie structure 1.jpg</t>
+        </is>
+      </c>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>kylie structure 1</t>
+        </is>
+      </c>
+      <c r="G190" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H190" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="I190" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J190" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K190" s="1" t="inlineStr">
+        <is>
+          <t>kylie-structures</t>
+        </is>
+      </c>
+      <c r="L190" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="M190" s="7" t="inlineStr">
+        <is>
+          <t>digital c-type print</t>
+        </is>
+      </c>
+      <c r="X190" s="22" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="22" t="inlineStr">
+        <is>
+          <t>00521</t>
+        </is>
+      </c>
+      <c r="B191" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C191" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D191" s="7" t="inlineStr">
+        <is>
+          <t>kylie structures</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>kylie structure 2.jpg</t>
+        </is>
+      </c>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>kylie structure 2</t>
+        </is>
+      </c>
+      <c r="G191" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H191" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="I191" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J191" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K191" s="1" t="inlineStr">
+        <is>
+          <t>kylie-structures</t>
+        </is>
+      </c>
+      <c r="L191" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="M191" s="7" t="inlineStr">
+        <is>
+          <t>digital c-type print</t>
+        </is>
+      </c>
+      <c r="X191" s="22" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="22" t="inlineStr">
+        <is>
+          <t>00522</t>
+        </is>
+      </c>
+      <c r="B192" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C192" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D192" s="7" t="inlineStr">
+        <is>
+          <t>kylie structures</t>
+        </is>
+      </c>
+      <c r="E192" s="7" t="inlineStr">
+        <is>
+          <t>kylie structure 3.jpg</t>
+        </is>
+      </c>
+      <c r="F192" s="7" t="inlineStr">
+        <is>
+          <t>kylie structure 3</t>
+        </is>
+      </c>
+      <c r="G192" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="H192" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="I192" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J192" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K192" s="1" t="inlineStr">
+        <is>
+          <t>kylie-structures</t>
+        </is>
+      </c>
+      <c r="L192" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="M192" s="7" t="inlineStr">
+        <is>
+          <t>digital c-type print</t>
+        </is>
+      </c>
+      <c r="X192" s="22" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="22" t="inlineStr">
+        <is>
+          <t>00523</t>
+        </is>
+      </c>
+      <c r="B193" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C193" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D193" s="7" t="inlineStr">
+        <is>
+          <t>kylie structures</t>
+        </is>
+      </c>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
+          <t>kylie structure 4.jpg</t>
+        </is>
+      </c>
+      <c r="F193" s="7" t="inlineStr">
+        <is>
+          <t>kylie structure 4</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="H193" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="I193" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J193" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K193" s="1" t="inlineStr">
+        <is>
+          <t>kylie-structures</t>
+        </is>
+      </c>
+      <c r="L193" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="M193" s="7" t="inlineStr">
+        <is>
+          <t>digital c-type print</t>
+        </is>
+      </c>
+      <c r="X193" s="22" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13663,8 +13887,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="31.83203125" customWidth="1" style="1" min="1" max="1"/>
     <col width="43.1640625" customWidth="1" style="1" min="2" max="2"/>
@@ -13675,8 +13899,8 @@
     <col width="21" customWidth="1" style="7" min="7" max="7"/>
     <col width="28.1640625" customWidth="1" style="7" min="8" max="8"/>
     <col width="51" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" style="1" min="10" max="31"/>
-    <col width="10.83203125" customWidth="1" style="1" min="32" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="1" min="10" max="34"/>
+    <col width="10.83203125" customWidth="1" style="1" min="35" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -14222,7 +14446,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="D15" s="33" t="n">
+      <c r="D15" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="E15" s="1" t="n">
@@ -14241,6 +14465,42 @@
       <c r="H15" s="7" t="inlineStr">
         <is>
           <t>landscape,drawing</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>kylie-structures</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>kylie structures</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>00520</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>kylie,composite</t>
         </is>
       </c>
     </row>
@@ -14255,8 +14515,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J447"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <dimension ref="A1:J463"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="9.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -29568,7 +29828,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G373" s="33" t="n">
+      <c r="G373" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H373" t="n">
@@ -29609,7 +29869,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G374" s="33" t="n">
+      <c r="G374" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H374" t="n">
@@ -29650,7 +29910,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G375" s="33" t="n">
+      <c r="G375" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H375" t="n">
@@ -29691,7 +29951,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G376" s="33" t="n">
+      <c r="G376" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H376" t="n">
@@ -29732,7 +29992,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G377" s="33" t="n">
+      <c r="G377" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H377" t="n">
@@ -29773,7 +30033,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G378" s="33" t="n">
+      <c r="G378" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H378" t="n">
@@ -29814,7 +30074,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G379" s="33" t="n">
+      <c r="G379" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H379" t="n">
@@ -29855,7 +30115,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G380" s="33" t="n">
+      <c r="G380" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H380" t="n">
@@ -29896,7 +30156,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G381" s="33" t="n">
+      <c r="G381" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H381" t="n">
@@ -29937,7 +30197,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G382" s="33" t="n">
+      <c r="G382" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H382" t="n">
@@ -29978,7 +30238,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G383" s="33" t="n">
+      <c r="G383" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H383" t="n">
@@ -30019,7 +30279,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G384" s="33" t="n">
+      <c r="G384" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H384" t="n">
@@ -30060,7 +30320,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G385" s="33" t="n">
+      <c r="G385" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H385" t="n">
@@ -30101,7 +30361,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G386" s="33" t="n">
+      <c r="G386" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H386" t="n">
@@ -30142,7 +30402,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G387" s="33" t="n">
+      <c r="G387" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H387" t="n">
@@ -30183,7 +30443,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G388" s="33" t="n">
+      <c r="G388" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H388" t="n">
@@ -30224,7 +30484,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G389" s="33" t="n">
+      <c r="G389" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H389" t="n">
@@ -30265,7 +30525,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G390" s="33" t="n">
+      <c r="G390" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H390" t="n">
@@ -30306,7 +30566,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G391" s="33" t="n">
+      <c r="G391" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H391" t="n">
@@ -30347,7 +30607,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G392" s="33" t="n">
+      <c r="G392" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H392" t="n">
@@ -30388,7 +30648,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G393" s="33" t="n">
+      <c r="G393" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H393" t="n">
@@ -30429,7 +30689,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G394" s="33" t="n">
+      <c r="G394" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H394" t="n">
@@ -30470,7 +30730,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G395" s="33" t="n">
+      <c r="G395" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H395" t="n">
@@ -30511,7 +30771,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G396" s="33" t="n">
+      <c r="G396" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H396" t="n">
@@ -30552,7 +30812,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G397" s="33" t="n">
+      <c r="G397" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H397" t="n">
@@ -30593,7 +30853,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G398" s="33" t="n">
+      <c r="G398" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H398" t="n">
@@ -30634,7 +30894,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G399" s="33" t="n">
+      <c r="G399" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H399" t="n">
@@ -30675,7 +30935,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G400" s="33" t="n">
+      <c r="G400" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H400" t="n">
@@ -30716,7 +30976,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G401" s="33" t="n">
+      <c r="G401" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H401" t="n">
@@ -30757,7 +31017,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G402" s="33" t="n">
+      <c r="G402" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H402" t="n">
@@ -30798,7 +31058,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G403" s="33" t="n">
+      <c r="G403" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H403" t="n">
@@ -30839,7 +31099,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G404" s="33" t="n">
+      <c r="G404" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H404" t="n">
@@ -30880,7 +31140,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G405" s="33" t="n">
+      <c r="G405" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H405" t="n">
@@ -30921,7 +31181,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G406" s="33" t="n">
+      <c r="G406" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H406" t="n">
@@ -30962,7 +31222,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G407" s="33" t="n">
+      <c r="G407" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H407" t="n">
@@ -31003,7 +31263,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G408" s="33" t="n">
+      <c r="G408" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H408" t="n">
@@ -31044,7 +31304,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G409" s="33" t="n">
+      <c r="G409" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H409" t="n">
@@ -31085,7 +31345,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G410" s="33" t="n">
+      <c r="G410" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H410" t="n">
@@ -31126,7 +31386,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G411" s="33" t="n">
+      <c r="G411" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H411" t="n">
@@ -31167,7 +31427,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G412" s="33" t="n">
+      <c r="G412" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H412" t="n">
@@ -31208,7 +31468,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G413" s="33" t="n">
+      <c r="G413" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H413" t="n">
@@ -31249,7 +31509,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G414" s="33" t="n">
+      <c r="G414" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H414" t="n">
@@ -31290,7 +31550,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G415" s="33" t="n">
+      <c r="G415" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H415" t="n">
@@ -31331,7 +31591,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G416" s="33" t="n">
+      <c r="G416" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H416" t="n">
@@ -31372,7 +31632,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G417" s="33" t="n">
+      <c r="G417" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H417" t="n">
@@ -31413,7 +31673,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G418" s="33" t="n">
+      <c r="G418" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H418" t="n">
@@ -31454,7 +31714,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G419" s="33" t="n">
+      <c r="G419" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H419" t="n">
@@ -31495,7 +31755,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G420" s="33" t="n">
+      <c r="G420" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H420" t="n">
@@ -31536,7 +31796,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G421" s="33" t="n">
+      <c r="G421" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H421" t="n">
@@ -31577,7 +31837,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G422" s="33" t="n">
+      <c r="G422" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H422" t="n">
@@ -31618,7 +31878,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G423" s="33" t="n">
+      <c r="G423" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H423" t="n">
@@ -31659,7 +31919,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G424" s="33" t="n">
+      <c r="G424" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H424" t="n">
@@ -31700,7 +31960,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G425" s="33" t="n">
+      <c r="G425" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H425" t="n">
@@ -31741,7 +32001,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G426" s="33" t="n">
+      <c r="G426" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H426" t="n">
@@ -31782,7 +32042,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G427" s="33" t="n">
+      <c r="G427" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H427" t="n">
@@ -31823,7 +32083,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G428" s="33" t="n">
+      <c r="G428" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H428" t="n">
@@ -31864,7 +32124,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G429" s="33" t="n">
+      <c r="G429" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H429" t="n">
@@ -31905,7 +32165,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G430" s="33" t="n">
+      <c r="G430" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H430" t="n">
@@ -31946,7 +32206,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G431" s="33" t="n">
+      <c r="G431" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H431" t="n">
@@ -31987,7 +32247,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G432" s="33" t="n">
+      <c r="G432" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H432" t="n">
@@ -32028,7 +32288,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G433" s="33" t="n">
+      <c r="G433" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H433" t="n">
@@ -32069,7 +32329,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G434" s="33" t="n">
+      <c r="G434" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H434" t="n">
@@ -32110,7 +32370,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G435" s="33" t="n">
+      <c r="G435" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H435" t="n">
@@ -32151,7 +32411,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G436" s="33" t="n">
+      <c r="G436" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H436" t="n">
@@ -32192,7 +32452,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G437" s="33" t="n">
+      <c r="G437" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H437" t="n">
@@ -32233,7 +32493,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G438" s="33" t="n">
+      <c r="G438" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H438" t="n">
@@ -32274,7 +32534,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G439" s="33" t="n">
+      <c r="G439" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H439" t="n">
@@ -32315,7 +32575,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G440" s="33" t="n">
+      <c r="G440" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H440" t="n">
@@ -32356,7 +32616,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G441" s="33" t="n">
+      <c r="G441" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H441" t="n">
@@ -32397,7 +32657,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G442" s="33" t="n">
+      <c r="G442" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H442" t="n">
@@ -32438,7 +32698,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G443" s="33" t="n">
+      <c r="G443" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H443" t="n">
@@ -32479,7 +32739,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G444" s="33" t="n">
+      <c r="G444" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H444" t="n">
@@ -32520,7 +32780,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G445" s="33" t="n">
+      <c r="G445" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H445" t="n">
@@ -32561,7 +32821,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G446" s="33" t="n">
+      <c r="G446" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H446" t="n">
@@ -32602,7 +32862,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G447" s="33" t="n">
+      <c r="G447" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H447" t="n">
@@ -32610,6 +32870,662 @@
       </c>
       <c r="I447" t="n">
         <v>3543</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="22" t="inlineStr">
+        <is>
+          <t>00520</t>
+        </is>
+      </c>
+      <c r="B448" s="5" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>kylie structure 1.1.jpg</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>kylie structure 1.1</t>
+        </is>
+      </c>
+      <c r="F448" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G448" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H448" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I448" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="22" t="inlineStr">
+        <is>
+          <t>00520</t>
+        </is>
+      </c>
+      <c r="B449" s="5" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>kylie structure 1.2.jpg</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>kylie structure 1.2</t>
+        </is>
+      </c>
+      <c r="F449" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G449" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H449" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I449" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="22" t="inlineStr">
+        <is>
+          <t>00520</t>
+        </is>
+      </c>
+      <c r="B450" s="5" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>kylie structure 1.3.jpg</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>kylie structure 1.3</t>
+        </is>
+      </c>
+      <c r="F450" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G450" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H450" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I450" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="22" t="inlineStr">
+        <is>
+          <t>00520</t>
+        </is>
+      </c>
+      <c r="B451" s="5" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>kylie structure 1.4.jpg</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>kylie structure 1.4</t>
+        </is>
+      </c>
+      <c r="F451" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G451" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H451" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I451" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="22" t="inlineStr">
+        <is>
+          <t>00520</t>
+        </is>
+      </c>
+      <c r="B452" s="5" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>kylie structure 1.5.jpg</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>kylie structure 1.5</t>
+        </is>
+      </c>
+      <c r="F452" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G452" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H452" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I452" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="22" t="inlineStr">
+        <is>
+          <t>00520</t>
+        </is>
+      </c>
+      <c r="B453" s="5" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>kylie structure 1.6.jpg</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>kylie structure 1.6</t>
+        </is>
+      </c>
+      <c r="F453" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G453" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H453" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I453" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="22" t="inlineStr">
+        <is>
+          <t>00521</t>
+        </is>
+      </c>
+      <c r="B454" s="5" t="inlineStr">
+        <is>
+          <t>007</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>kylie structure 2.1.jpg</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>kylie structure 2.1</t>
+        </is>
+      </c>
+      <c r="F454" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G454" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H454" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I454" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="22" t="inlineStr">
+        <is>
+          <t>00521</t>
+        </is>
+      </c>
+      <c r="B455" s="5" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>kylie structure 2.2.jpg</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>kylie structure 2.2</t>
+        </is>
+      </c>
+      <c r="F455" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G455" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H455" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I455" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="22" t="inlineStr">
+        <is>
+          <t>00521</t>
+        </is>
+      </c>
+      <c r="B456" s="5" t="inlineStr">
+        <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>kylie structure 2.3.jpg</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>kylie structure 2.3</t>
+        </is>
+      </c>
+      <c r="F456" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G456" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H456" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I456" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="22" t="inlineStr">
+        <is>
+          <t>00521</t>
+        </is>
+      </c>
+      <c r="B457" s="5" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>kylie structure 2.4.jpg</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>kylie structure 2.4</t>
+        </is>
+      </c>
+      <c r="F457" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G457" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H457" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I457" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="22" t="inlineStr">
+        <is>
+          <t>00521</t>
+        </is>
+      </c>
+      <c r="B458" s="5" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>kylie structure 2.5.jpg</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>kylie structure 2.5</t>
+        </is>
+      </c>
+      <c r="F458" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G458" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H458" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I458" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="22" t="inlineStr">
+        <is>
+          <t>00521</t>
+        </is>
+      </c>
+      <c r="B459" s="5" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>kylie structure 2.6.jpg</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>kylie structure 2.6</t>
+        </is>
+      </c>
+      <c r="F459" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G459" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H459" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I459" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="22" t="inlineStr">
+        <is>
+          <t>00522</t>
+        </is>
+      </c>
+      <c r="B460" s="5" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>kylie structure 3.1.jpg</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>kylie structure 3.1</t>
+        </is>
+      </c>
+      <c r="F460" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G460" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H460" t="n">
+        <v>3316</v>
+      </c>
+      <c r="I460" t="n">
+        <v>3316</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="22" t="inlineStr">
+        <is>
+          <t>00522</t>
+        </is>
+      </c>
+      <c r="B461" s="5" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>kylie structure 3.2.jpg</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>kylie structure 3.2</t>
+        </is>
+      </c>
+      <c r="F461" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G461" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H461" t="n">
+        <v>3316</v>
+      </c>
+      <c r="I461" t="n">
+        <v>3316</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="22" t="inlineStr">
+        <is>
+          <t>00523</t>
+        </is>
+      </c>
+      <c r="B462" s="5" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>kylie structure 4.1.jpg</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>kylie structure 4.1</t>
+        </is>
+      </c>
+      <c r="F462" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G462" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H462" t="n">
+        <v>2785</v>
+      </c>
+      <c r="I462" t="n">
+        <v>2785</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="22" t="inlineStr">
+        <is>
+          <t>00523</t>
+        </is>
+      </c>
+      <c r="B463" s="5" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>kylie structure 4.2.jpg</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>kylie structure 4.2</t>
+        </is>
+      </c>
+      <c r="F463" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G463" s="16" t="n">
+        <v>46071</v>
+      </c>
+      <c r="H463" t="n">
+        <v>2785</v>
+      </c>
+      <c r="I463" t="n">
+        <v>2785</v>
       </c>
     </row>
   </sheetData>
@@ -32624,7 +33540,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col width="24.1640625" customWidth="1" style="19" min="1" max="1"/>
     <col width="34.83203125" customWidth="1" style="19" min="2" max="2"/>
@@ -32637,8 +33553,8 @@
     <col width="11.33203125" bestFit="1" customWidth="1" style="19" min="9" max="9"/>
     <col width="12.1640625" bestFit="1" customWidth="1" style="19" min="10" max="10"/>
     <col width="33.6640625" customWidth="1" style="19" min="11" max="11"/>
-    <col width="10.83203125" customWidth="1" style="19" min="12" max="24"/>
-    <col width="10.83203125" customWidth="1" style="19" min="25" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="19" min="12" max="27"/>
+    <col width="10.83203125" customWidth="1" style="19" min="28" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34800,7 +35716,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G839"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="21.83203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="21.83203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="41.6640625" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
     <col width="9.33203125" customWidth="1" style="10" min="2" max="2"/>
@@ -34810,8 +35726,8 @@
     <col width="20.1640625" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
     <col width="48.1640625" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
     <col width="21.83203125" customWidth="1" style="10" min="8" max="256"/>
-    <col width="21.83203125" customWidth="1" style="14" min="257" max="274"/>
-    <col width="21.83203125" customWidth="1" style="14" min="275" max="16384"/>
+    <col width="21.83203125" customWidth="1" style="14" min="257" max="277"/>
+    <col width="21.83203125" customWidth="1" style="14" min="278" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -618,7 +618,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="21.83203125" customWidth="1" style="4" min="1" max="1"/>
     <col width="77.33203125" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
@@ -1402,8 +1402,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y197"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <dimension ref="A1:Y250"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="11.33203125" customWidth="1" style="7" min="1" max="1"/>
     <col width="13.33203125" customWidth="1" style="7" min="2" max="2"/>
@@ -1429,8 +1429,8 @@
     <col width="21.5" customWidth="1" style="7" min="23" max="23"/>
     <col width="26.83203125" customWidth="1" style="7" min="24" max="24"/>
     <col width="20.83203125" customWidth="1" style="7" min="25" max="25"/>
-    <col width="10.83203125" customWidth="1" style="7" min="26" max="50"/>
-    <col width="10.83203125" customWidth="1" style="7" min="51" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="7" min="26" max="52"/>
+    <col width="10.83203125" customWidth="1" style="7" min="53" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="6">
@@ -9547,8 +9547,13 @@
           <t>00454</t>
         </is>
       </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="C124" s="28" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
@@ -9808,55 +9813,48 @@
         </is>
       </c>
       <c r="C128" s="30" t="n">
-        <v>46068</v>
+        <v>46071</v>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>nerve</t>
+          <t>leaf</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>nerve.jpg</t>
+          <t>leaf.jpg</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>nerve</t>
+          <t>leaf</t>
         </is>
       </c>
       <c r="G128" s="7" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H128" s="7" t="n">
-        <v>29.7</v>
+        <v>30</v>
       </c>
       <c r="I128" s="7" t="n">
-        <v>1995</v>
-      </c>
-      <c r="J128" s="7" t="inlineStr">
-        <is>
-          <t>July 1990 – January 1995</t>
-        </is>
+        <v>2016</v>
+      </c>
+      <c r="J128" s="7" t="n">
+        <v>2016</v>
       </c>
       <c r="K128" s="7" t="inlineStr">
         <is>
-          <t>nerve</t>
+          <t>leaf</t>
         </is>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
-          <t>writing</t>
+          <t>digital print</t>
         </is>
       </c>
       <c r="M128" s="7" t="inlineStr">
         <is>
-          <t>loose bound book, 48p</t>
-        </is>
-      </c>
-      <c r="R128" s="7" t="inlineStr">
-        <is>
-          <t>nerve.pdf</t>
+          <t>digital c-type print</t>
         </is>
       </c>
       <c r="X128" s="22" t="inlineStr">
@@ -13894,7 +13892,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C194" s="33" t="n">
+      <c r="C194" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D194" s="7" t="inlineStr">
@@ -13956,7 +13954,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C195" s="33" t="n">
+      <c r="C195" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D195" s="7" t="inlineStr">
@@ -14018,7 +14016,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C196" s="33" t="n">
+      <c r="C196" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D196" s="7" t="inlineStr">
@@ -14080,7 +14078,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C197" s="33" t="n">
+      <c r="C197" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="D197" s="7" t="inlineStr">
@@ -14130,6 +14128,344 @@
           <t>box 1 (A4)</t>
         </is>
       </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="22" t="inlineStr">
+        <is>
+          <t>00005</t>
+        </is>
+      </c>
+      <c r="D198" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E198" s="7" t="inlineStr">
+        <is>
+          <t>00005 untitled forms.jpg</t>
+        </is>
+      </c>
+      <c r="F198" s="7" t="inlineStr">
+        <is>
+          <t>untitled forms</t>
+        </is>
+      </c>
+      <c r="G198" s="7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H198" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="I198" s="7" t="n">
+        <v>1998</v>
+      </c>
+      <c r="J198" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K198" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L198" s="7" t="inlineStr">
+        <is>
+          <t>painting</t>
+        </is>
+      </c>
+      <c r="M198" s="7" t="inlineStr">
+        <is>
+          <t>mixed meda</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="22" t="inlineStr">
+        <is>
+          <t>00006</t>
+        </is>
+      </c>
+      <c r="E199" s="7" t="inlineStr">
+        <is>
+          <t>00006 gesture in grey.jpg</t>
+        </is>
+      </c>
+      <c r="F199" s="7" t="inlineStr">
+        <is>
+          <t>gesture in grey</t>
+        </is>
+      </c>
+      <c r="G199" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H199" s="7" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="I199" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J199" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="L199" s="7" t="inlineStr">
+        <is>
+          <t>painting</t>
+        </is>
+      </c>
+      <c r="M199" s="7" t="inlineStr">
+        <is>
+          <t>acrylic on paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="22" t="inlineStr">
+        <is>
+          <t>00007</t>
+        </is>
+      </c>
+      <c r="E200" s="7" t="inlineStr">
+        <is>
+          <t>00007 skeletal.jpg</t>
+        </is>
+      </c>
+      <c r="F200" s="7" t="inlineStr">
+        <is>
+          <t>skeletal</t>
+        </is>
+      </c>
+      <c r="G200" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H200" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I200" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J200" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="L200" s="7" t="inlineStr">
+        <is>
+          <t>painting</t>
+        </is>
+      </c>
+      <c r="M200" s="7" t="inlineStr">
+        <is>
+          <t>acrylic on paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="22" t="inlineStr">
+        <is>
+          <t>00008</t>
+        </is>
+      </c>
+      <c r="C201" s="30" t="n"/>
+      <c r="D201" s="7" t="inlineStr">
+        <is>
+          <t>nerve</t>
+        </is>
+      </c>
+      <c r="E201" s="7" t="inlineStr">
+        <is>
+          <t>nerve.jpg</t>
+        </is>
+      </c>
+      <c r="F201" s="7" t="inlineStr">
+        <is>
+          <t>nerve</t>
+        </is>
+      </c>
+      <c r="G201" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H201" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I201" s="7" t="n">
+        <v>1995</v>
+      </c>
+      <c r="J201" s="7" t="inlineStr">
+        <is>
+          <t>July 1990 – January 1995</t>
+        </is>
+      </c>
+      <c r="K201" s="7" t="inlineStr">
+        <is>
+          <t>nerve</t>
+        </is>
+      </c>
+      <c r="L201" s="7" t="inlineStr">
+        <is>
+          <t>writing</t>
+        </is>
+      </c>
+      <c r="M201" s="7" t="inlineStr">
+        <is>
+          <t>loose bound book, 48p</t>
+        </is>
+      </c>
+      <c r="R201" s="7" t="inlineStr">
+        <is>
+          <t>nerve.pdf</t>
+        </is>
+      </c>
+      <c r="X201" s="22" t="inlineStr">
+        <is>
+          <t>Michael Davies</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="22" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="22" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="22" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="22" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="22" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="22" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="22" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="22" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="22" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="22" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="22" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="22" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="22" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="22" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="22" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="22" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="22" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="22" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="22" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="22" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="22" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="22" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="22" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="22" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="22" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="22" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="22" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="22" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="22" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="22" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="22" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="22" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="22" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="22" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="22" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="22" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="22" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="22" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="22" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="22" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="22" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="22" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="22" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="22" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="22" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="22" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="22" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="22" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="22" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14143,8 +14479,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="31.83203125" customWidth="1" style="1" min="1" max="1"/>
     <col width="43.1640625" customWidth="1" style="1" min="2" max="2"/>
@@ -14155,8 +14491,8 @@
     <col width="21" customWidth="1" style="7" min="7" max="7"/>
     <col width="28.1640625" customWidth="1" style="7" min="8" max="8"/>
     <col width="51" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" style="1" min="10" max="35"/>
-    <col width="10.83203125" customWidth="1" style="1" min="36" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="1" min="10" max="37"/>
+    <col width="10.83203125" customWidth="1" style="1" min="38" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -14776,7 +15112,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="D17" s="33" t="n">
+      <c r="D17" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="E17" s="1" t="n">
@@ -14798,6 +15134,67 @@
       <c r="I17" s="1" t="inlineStr">
         <is>
           <t>details attached to 00001</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>1998</v>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>leaf</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>leaf</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>2016</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>2016</v>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>leaf,nature</t>
+        </is>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>add details</t>
         </is>
       </c>
     </row>
@@ -14813,7 +15210,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J480"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="9.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -33856,7 +34253,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G464" s="33" t="n">
+      <c r="G464" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H464" t="n">
@@ -33897,7 +34294,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G465" s="33" t="n">
+      <c r="G465" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H465" t="n">
@@ -33938,7 +34335,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G466" s="33" t="n">
+      <c r="G466" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H466" t="n">
@@ -33979,7 +34376,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G467" s="33" t="n">
+      <c r="G467" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H467" t="n">
@@ -34020,7 +34417,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G468" s="33" t="n">
+      <c r="G468" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H468" t="n">
@@ -34061,7 +34458,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G469" s="33" t="n">
+      <c r="G469" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H469" t="n">
@@ -34102,7 +34499,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G470" s="33" t="n">
+      <c r="G470" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H470" t="n">
@@ -34143,7 +34540,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G471" s="33" t="n">
+      <c r="G471" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H471" t="n">
@@ -34184,7 +34581,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G472" s="33" t="n">
+      <c r="G472" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H472" t="n">
@@ -34225,7 +34622,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G473" s="33" t="n">
+      <c r="G473" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H473" t="n">
@@ -34266,7 +34663,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G474" s="33" t="n">
+      <c r="G474" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H474" t="n">
@@ -34307,7 +34704,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G475" s="33" t="n">
+      <c r="G475" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H475" t="n">
@@ -34348,7 +34745,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G476" s="33" t="n">
+      <c r="G476" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H476" t="n">
@@ -34389,7 +34786,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G477" s="33" t="n">
+      <c r="G477" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H477" t="n">
@@ -34430,7 +34827,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G478" s="33" t="n">
+      <c r="G478" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H478" t="n">
@@ -34471,7 +34868,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G479" s="33" t="n">
+      <c r="G479" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H479" t="n">
@@ -34512,7 +34909,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G480" s="33" t="n">
+      <c r="G480" s="16" t="n">
         <v>46071</v>
       </c>
       <c r="H480" t="n">
@@ -34534,7 +34931,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col width="24.1640625" customWidth="1" style="19" min="1" max="1"/>
     <col width="34.83203125" customWidth="1" style="19" min="2" max="2"/>
@@ -34547,8 +34944,8 @@
     <col width="11.33203125" bestFit="1" customWidth="1" style="19" min="9" max="9"/>
     <col width="12.1640625" bestFit="1" customWidth="1" style="19" min="10" max="10"/>
     <col width="33.6640625" customWidth="1" style="19" min="11" max="11"/>
-    <col width="10.83203125" customWidth="1" style="19" min="12" max="28"/>
-    <col width="10.83203125" customWidth="1" style="19" min="29" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="19" min="12" max="30"/>
+    <col width="10.83203125" customWidth="1" style="19" min="31" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36710,7 +37107,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G839"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="21.83203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="21.83203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="41.6640625" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
     <col width="9.33203125" customWidth="1" style="10" min="2" max="2"/>
@@ -36720,8 +37117,8 @@
     <col width="20.1640625" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
     <col width="48.1640625" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
     <col width="21.83203125" customWidth="1" style="10" min="8" max="256"/>
-    <col width="21.83203125" customWidth="1" style="14" min="257" max="278"/>
-    <col width="21.83203125" customWidth="1" style="14" min="279" max="16384"/>
+    <col width="21.83203125" customWidth="1" style="14" min="257" max="280"/>
+    <col width="21.83203125" customWidth="1" style="14" min="281" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20600" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20600" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,12 +22,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -108,6 +109,12 @@
       <color rgb="FF000000"/>
       <sz val="13"/>
     </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -139,7 +146,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -209,6 +216,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -610,7 +618,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="21.83203125" customWidth="1" style="4" min="1" max="1"/>
     <col width="77.33203125" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
@@ -1394,8 +1402,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y250"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <dimension ref="A1:Y306"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="11.33203125" customWidth="1" style="7" min="1" max="1"/>
     <col width="13.33203125" customWidth="1" style="7" min="2" max="2"/>
@@ -1421,8 +1429,8 @@
     <col width="21.5" customWidth="1" style="7" min="23" max="23"/>
     <col width="26.83203125" customWidth="1" style="7" min="24" max="24"/>
     <col width="20.83203125" customWidth="1" style="7" min="25" max="25"/>
-    <col width="10.83203125" customWidth="1" style="7" min="26" max="53"/>
-    <col width="10.83203125" customWidth="1" style="7" min="54" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="7" min="26" max="54"/>
+    <col width="10.83203125" customWidth="1" style="7" min="55" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="6">
@@ -14127,6 +14135,14 @@
           <t>00005</t>
         </is>
       </c>
+      <c r="B198" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C198" s="33" t="n">
+        <v>46071</v>
+      </c>
       <c r="D198" s="7" t="inlineStr">
         <is>
           <t>collected 1989-1998</t>
@@ -14134,7 +14150,7 @@
       </c>
       <c r="E198" s="7" t="inlineStr">
         <is>
-          <t>00005 untitled forms.jpg</t>
+          <t>untitled forms.jpg</t>
         </is>
       </c>
       <c r="F198" s="7" t="inlineStr">
@@ -14171,6 +14187,11 @@
           <t>mixed meda</t>
         </is>
       </c>
+      <c r="S198" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="22" t="inlineStr">
@@ -14178,6 +14199,14 @@
           <t>00006</t>
         </is>
       </c>
+      <c r="B199" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C199" s="33" t="n">
+        <v>46071</v>
+      </c>
       <c r="D199" s="7" t="inlineStr">
         <is>
           <t>collected 1989-1998</t>
@@ -14185,12 +14214,12 @@
       </c>
       <c r="E199" s="7" t="inlineStr">
         <is>
-          <t>00006 gesture in grey.jpg</t>
+          <t>gesture in grey 1.jpg</t>
         </is>
       </c>
       <c r="F199" s="7" t="inlineStr">
         <is>
-          <t>gesture in grey</t>
+          <t>gesture in grey 1</t>
         </is>
       </c>
       <c r="G199" s="7" t="n">
@@ -14202,8 +14231,10 @@
       <c r="I199" s="7" t="n">
         <v>1989</v>
       </c>
-      <c r="J199" s="7" t="n">
-        <v>1989</v>
+      <c r="J199" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
       </c>
       <c r="K199" s="7" t="inlineStr">
         <is>
@@ -14218,6 +14249,11 @@
       <c r="M199" s="7" t="inlineStr">
         <is>
           <t>acrylic on paper</t>
+        </is>
+      </c>
+      <c r="S199" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
         </is>
       </c>
     </row>
@@ -14227,6 +14263,14 @@
           <t>00007</t>
         </is>
       </c>
+      <c r="B200" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C200" s="33" t="n">
+        <v>46071</v>
+      </c>
       <c r="D200" s="7" t="inlineStr">
         <is>
           <t>collected 1989-1998</t>
@@ -14234,7 +14278,7 @@
       </c>
       <c r="E200" s="7" t="inlineStr">
         <is>
-          <t>00007 skeletal.jpg</t>
+          <t>skeletal.jpg</t>
         </is>
       </c>
       <c r="F200" s="7" t="inlineStr">
@@ -14251,8 +14295,10 @@
       <c r="I200" s="7" t="n">
         <v>1989</v>
       </c>
-      <c r="J200" s="7" t="n">
-        <v>1989</v>
+      <c r="J200" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
       </c>
       <c r="K200" s="7" t="inlineStr">
         <is>
@@ -14267,6 +14313,11 @@
       <c r="M200" s="7" t="inlineStr">
         <is>
           <t>acrylic on paper</t>
+        </is>
+      </c>
+      <c r="S200" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
         </is>
       </c>
     </row>
@@ -14333,6 +14384,11 @@
           <t>nerve.pdf</t>
         </is>
       </c>
+      <c r="S201" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
       <c r="X201" s="22" t="inlineStr">
         <is>
           <t>Michael Davies</t>
@@ -14340,151 +14396,6708 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="22" t="n"/>
+      <c r="A202" s="22" t="inlineStr">
+        <is>
+          <t>00009</t>
+        </is>
+      </c>
+      <c r="B202" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C202" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D202" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E202" s="7" t="inlineStr">
+        <is>
+          <t>internal organs (wireframe).jpg</t>
+        </is>
+      </c>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>internal organs (wireframe)</t>
+        </is>
+      </c>
+      <c r="G202" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H202" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I202" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J202" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K202" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L202" s="7" t="inlineStr">
+        <is>
+          <t>mixed media</t>
+        </is>
+      </c>
+      <c r="M202" s="7" t="inlineStr">
+        <is>
+          <t>wire on paper</t>
+        </is>
+      </c>
+      <c r="S202" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="203">
-      <c r="A203" s="22" t="n"/>
+      <c r="A203" s="22" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C203" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D203" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E203" s="7" t="inlineStr">
+        <is>
+          <t>slaughter (composite).jpg</t>
+        </is>
+      </c>
+      <c r="F203" s="7" t="inlineStr">
+        <is>
+          <t>slaughter (composite)</t>
+        </is>
+      </c>
+      <c r="G203" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H203" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I203" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J203" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K203" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L203" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M203" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S203" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="204">
-      <c r="A204" s="22" t="n"/>
+      <c r="A204" s="22" t="inlineStr">
+        <is>
+          <t>00011</t>
+        </is>
+      </c>
+      <c r="B204" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C204" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D204" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E204" s="7" t="inlineStr">
+        <is>
+          <t>prototype for repeating pattern.jpg</t>
+        </is>
+      </c>
+      <c r="F204" s="7" t="inlineStr">
+        <is>
+          <t>prototype for repeating pattern</t>
+        </is>
+      </c>
+      <c r="G204" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H204" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I204" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J204" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K204" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L204" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M204" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S204" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="205">
-      <c r="A205" s="22" t="n"/>
+      <c r="A205" s="22" t="inlineStr">
+        <is>
+          <t>00012</t>
+        </is>
+      </c>
+      <c r="B205" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C205" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D205" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E205" s="7" t="inlineStr">
+        <is>
+          <t>frame (positive).jpg</t>
+        </is>
+      </c>
+      <c r="F205" s="7" t="inlineStr">
+        <is>
+          <t>frame (positive)</t>
+        </is>
+      </c>
+      <c r="G205" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H205" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I205" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J205" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K205" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L205" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M205" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S205" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="206">
-      <c r="A206" s="22" t="n"/>
+      <c r="A206" s="22" t="inlineStr">
+        <is>
+          <t>00013</t>
+        </is>
+      </c>
+      <c r="B206" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C206" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D206" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t>frame (negative).jpg</t>
+        </is>
+      </c>
+      <c r="F206" s="7" t="inlineStr">
+        <is>
+          <t>frame (negative)</t>
+        </is>
+      </c>
+      <c r="G206" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H206" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I206" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J206" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K206" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L206" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M206" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S206" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="207">
-      <c r="A207" s="22" t="n"/>
+      <c r="A207" s="22" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="B207" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C207" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D207" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E207" s="7" t="inlineStr">
+        <is>
+          <t>forms (ink and water 1).jpg</t>
+        </is>
+      </c>
+      <c r="F207" s="7" t="inlineStr">
+        <is>
+          <t>forms (ink and water 1)</t>
+        </is>
+      </c>
+      <c r="G207" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H207" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I207" s="7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="J207" s="7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="K207" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L207" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M207" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S207" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="208">
-      <c r="A208" s="22" t="n"/>
+      <c r="A208" s="22" t="inlineStr">
+        <is>
+          <t>00015</t>
+        </is>
+      </c>
+      <c r="B208" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C208" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D208" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E208" s="7" t="inlineStr">
+        <is>
+          <t>forms (ink and water 2).jpg</t>
+        </is>
+      </c>
+      <c r="F208" s="7" t="inlineStr">
+        <is>
+          <t>forms (ink and water 2)</t>
+        </is>
+      </c>
+      <c r="G208" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H208" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I208" s="7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="J208" s="7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="K208" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L208" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M208" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S208" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="209">
-      <c r="A209" s="22" t="n"/>
+      <c r="A209" s="22" t="inlineStr">
+        <is>
+          <t>00016</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C209" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D209" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E209" s="7" t="inlineStr">
+        <is>
+          <t>forms (ink and water 3).jpg</t>
+        </is>
+      </c>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>forms (ink and water 3)</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H209" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I209" s="7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="J209" s="7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="K209" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L209" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M209" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S209" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="210">
-      <c r="A210" s="22" t="n"/>
+      <c r="A210" s="22" t="inlineStr">
+        <is>
+          <t>00017</t>
+        </is>
+      </c>
+      <c r="B210" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C210" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D210" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E210" s="7" t="inlineStr">
+        <is>
+          <t>forms (ink and water 4).jpg</t>
+        </is>
+      </c>
+      <c r="F210" s="7" t="inlineStr">
+        <is>
+          <t>forms (ink and water 4)</t>
+        </is>
+      </c>
+      <c r="G210" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H210" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I210" s="7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="J210" s="7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="K210" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L210" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M210" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S210" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="211">
-      <c r="A211" s="22" t="n"/>
+      <c r="A211" s="22" t="inlineStr">
+        <is>
+          <t>00018</t>
+        </is>
+      </c>
+      <c r="B211" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C211" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D211" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E211" s="7" t="inlineStr">
+        <is>
+          <t>forms (ink and water 5).jpg</t>
+        </is>
+      </c>
+      <c r="F211" s="7" t="inlineStr">
+        <is>
+          <t>forms (ink and water 5)</t>
+        </is>
+      </c>
+      <c r="G211" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H211" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I211" s="7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="J211" s="7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="K211" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L211" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M211" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S211" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="212">
-      <c r="A212" s="22" t="n"/>
+      <c r="A212" s="22" t="inlineStr">
+        <is>
+          <t>00019</t>
+        </is>
+      </c>
+      <c r="B212" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C212" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D212" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E212" s="7" t="inlineStr">
+        <is>
+          <t>forms (ink and water 6).jpg</t>
+        </is>
+      </c>
+      <c r="F212" s="7" t="inlineStr">
+        <is>
+          <t>forms (ink and water 6)</t>
+        </is>
+      </c>
+      <c r="G212" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H212" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I212" s="7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="J212" s="7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="K212" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L212" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M212" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S212" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="213">
-      <c r="A213" s="22" t="n"/>
+      <c r="A213" s="22" t="inlineStr">
+        <is>
+          <t>00020</t>
+        </is>
+      </c>
+      <c r="B213" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C213" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D213" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E213" s="7" t="inlineStr">
+        <is>
+          <t>forms (internal 1).jpg</t>
+        </is>
+      </c>
+      <c r="F213" s="7" t="inlineStr">
+        <is>
+          <t>forms (internal 1)</t>
+        </is>
+      </c>
+      <c r="G213" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H213" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I213" s="7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="J213" s="7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="K213" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L213" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M213" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S213" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="214">
-      <c r="A214" s="22" t="n"/>
+      <c r="A214" s="22" t="inlineStr">
+        <is>
+          <t>00021</t>
+        </is>
+      </c>
+      <c r="B214" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C214" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D214" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E214" s="7" t="inlineStr">
+        <is>
+          <t>forms (internal 2).jpg</t>
+        </is>
+      </c>
+      <c r="F214" s="7" t="inlineStr">
+        <is>
+          <t>forms (internal 2)</t>
+        </is>
+      </c>
+      <c r="G214" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H214" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I214" s="7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="J214" s="7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="K214" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L214" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M214" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S214" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="215">
-      <c r="A215" s="22" t="n"/>
+      <c r="A215" s="22" t="inlineStr">
+        <is>
+          <t>00022</t>
+        </is>
+      </c>
+      <c r="B215" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C215" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D215" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E215" s="7" t="inlineStr">
+        <is>
+          <t>collage 1.jpg</t>
+        </is>
+      </c>
+      <c r="F215" s="7" t="inlineStr">
+        <is>
+          <t>collage 1</t>
+        </is>
+      </c>
+      <c r="G215" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H215" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I215" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J215" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K215" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L215" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M215" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S215" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="216">
-      <c r="A216" s="22" t="n"/>
+      <c r="A216" s="22" t="inlineStr">
+        <is>
+          <t>00023</t>
+        </is>
+      </c>
+      <c r="B216" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C216" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D216" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E216" s="7" t="inlineStr">
+        <is>
+          <t>collage 2.jpg</t>
+        </is>
+      </c>
+      <c r="F216" s="7" t="inlineStr">
+        <is>
+          <t>collage 2</t>
+        </is>
+      </c>
+      <c r="G216" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H216" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I216" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J216" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K216" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L216" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M216" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S216" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="217">
-      <c r="A217" s="22" t="n"/>
+      <c r="A217" s="22" t="inlineStr">
+        <is>
+          <t>00024</t>
+        </is>
+      </c>
+      <c r="B217" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C217" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D217" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E217" s="7" t="inlineStr">
+        <is>
+          <t>collage 3.jpg</t>
+        </is>
+      </c>
+      <c r="F217" s="7" t="inlineStr">
+        <is>
+          <t>collage 3</t>
+        </is>
+      </c>
+      <c r="G217" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H217" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I217" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J217" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K217" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L217" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M217" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S217" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="218">
-      <c r="A218" s="22" t="n"/>
+      <c r="A218" s="22" t="inlineStr">
+        <is>
+          <t>00025</t>
+        </is>
+      </c>
+      <c r="B218" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C218" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D218" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E218" s="7" t="inlineStr">
+        <is>
+          <t>collage 4.jpg</t>
+        </is>
+      </c>
+      <c r="F218" s="7" t="inlineStr">
+        <is>
+          <t>collage 4</t>
+        </is>
+      </c>
+      <c r="G218" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H218" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I218" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J218" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K218" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L218" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M218" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S218" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="219">
-      <c r="A219" s="22" t="n"/>
+      <c r="A219" s="22" t="inlineStr">
+        <is>
+          <t>00026</t>
+        </is>
+      </c>
+      <c r="B219" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C219" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D219" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E219" s="7" t="inlineStr">
+        <is>
+          <t>collage 5.jpg</t>
+        </is>
+      </c>
+      <c r="F219" s="7" t="inlineStr">
+        <is>
+          <t>collage 5</t>
+        </is>
+      </c>
+      <c r="G219" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H219" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I219" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J219" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K219" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L219" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M219" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S219" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="220">
-      <c r="A220" s="22" t="n"/>
+      <c r="A220" s="22" t="inlineStr">
+        <is>
+          <t>00027</t>
+        </is>
+      </c>
+      <c r="B220" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C220" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D220" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E220" s="7" t="inlineStr">
+        <is>
+          <t>doll forms [00027].jpg</t>
+        </is>
+      </c>
+      <c r="F220" s="7" t="inlineStr">
+        <is>
+          <t>doll forms</t>
+        </is>
+      </c>
+      <c r="G220" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H220" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I220" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J220" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K220" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L220" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M220" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S220" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="221">
-      <c r="A221" s="22" t="n"/>
+      <c r="A221" s="22" t="inlineStr">
+        <is>
+          <t>00028</t>
+        </is>
+      </c>
+      <c r="B221" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C221" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D221" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E221" s="7" t="inlineStr">
+        <is>
+          <t>forms [00028].jpg</t>
+        </is>
+      </c>
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>forms</t>
+        </is>
+      </c>
+      <c r="G221" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H221" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I221" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J221" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K221" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L221" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M221" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S221" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="222">
-      <c r="A222" s="22" t="n"/>
+      <c r="A222" s="22" t="inlineStr">
+        <is>
+          <t>00029</t>
+        </is>
+      </c>
+      <c r="B222" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C222" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D222" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E222" s="7" t="inlineStr">
+        <is>
+          <t>forms [00029].jpg</t>
+        </is>
+      </c>
+      <c r="F222" s="7" t="inlineStr">
+        <is>
+          <t>forms</t>
+        </is>
+      </c>
+      <c r="G222" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H222" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I222" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J222" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K222" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L222" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M222" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S222" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="223">
-      <c r="A223" s="22" t="n"/>
+      <c r="A223" s="22" t="inlineStr">
+        <is>
+          <t>00030</t>
+        </is>
+      </c>
+      <c r="B223" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C223" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D223" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E223" s="7" t="inlineStr">
+        <is>
+          <t>forms [00030].jpg</t>
+        </is>
+      </c>
+      <c r="F223" s="7" t="inlineStr">
+        <is>
+          <t>forms</t>
+        </is>
+      </c>
+      <c r="G223" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H223" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I223" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J223" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K223" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L223" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M223" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S223" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="224">
-      <c r="A224" s="22" t="n"/>
+      <c r="A224" s="22" t="inlineStr">
+        <is>
+          <t>00031</t>
+        </is>
+      </c>
+      <c r="B224" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C224" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D224" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E224" s="7" t="inlineStr">
+        <is>
+          <t>slaughter 4.jpg</t>
+        </is>
+      </c>
+      <c r="F224" s="7" t="inlineStr">
+        <is>
+          <t>slaughter 4</t>
+        </is>
+      </c>
+      <c r="G224" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H224" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I224" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J224" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K224" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L224" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M224" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S224" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="225">
-      <c r="A225" s="22" t="n"/>
+      <c r="A225" s="22" t="inlineStr">
+        <is>
+          <t>00032</t>
+        </is>
+      </c>
+      <c r="B225" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C225" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D225" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E225" s="7" t="inlineStr">
+        <is>
+          <t>slaughter 5.jpg</t>
+        </is>
+      </c>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>slaughter 5</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H225" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I225" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J225" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K225" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L225" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M225" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S225" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="226">
-      <c r="A226" s="22" t="n"/>
+      <c r="A226" s="22" t="inlineStr">
+        <is>
+          <t>00033</t>
+        </is>
+      </c>
+      <c r="B226" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C226" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D226" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E226" s="7" t="inlineStr">
+        <is>
+          <t>slaughter 6.jpg</t>
+        </is>
+      </c>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>slaughter 6</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H226" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I226" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J226" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K226" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L226" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M226" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S226" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="227">
-      <c r="A227" s="22" t="n"/>
+      <c r="A227" s="22" t="inlineStr">
+        <is>
+          <t>00034</t>
+        </is>
+      </c>
+      <c r="B227" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C227" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D227" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E227" s="7" t="inlineStr">
+        <is>
+          <t>slaughter 7.jpg</t>
+        </is>
+      </c>
+      <c r="F227" s="7" t="inlineStr">
+        <is>
+          <t>slaughter 7</t>
+        </is>
+      </c>
+      <c r="G227" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H227" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I227" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J227" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K227" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L227" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M227" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S227" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="228">
-      <c r="A228" s="22" t="n"/>
+      <c r="A228" s="22" t="inlineStr">
+        <is>
+          <t>00035</t>
+        </is>
+      </c>
+      <c r="B228" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C228" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D228" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E228" s="7" t="inlineStr">
+        <is>
+          <t>slaughter (nerve 1).jpg</t>
+        </is>
+      </c>
+      <c r="F228" s="7" t="inlineStr">
+        <is>
+          <t>slaughter (nerve 1)</t>
+        </is>
+      </c>
+      <c r="G228" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H228" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I228" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J228" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K228" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L228" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M228" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S228" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="229">
-      <c r="A229" s="22" t="n"/>
+      <c r="A229" s="22" t="inlineStr">
+        <is>
+          <t>00036</t>
+        </is>
+      </c>
+      <c r="B229" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C229" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D229" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E229" s="7" t="inlineStr">
+        <is>
+          <t>slaughter (nerve 2).jpg</t>
+        </is>
+      </c>
+      <c r="F229" s="7" t="inlineStr">
+        <is>
+          <t>slaughter (nerve 2)</t>
+        </is>
+      </c>
+      <c r="G229" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H229" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I229" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J229" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K229" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L229" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M229" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S229" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="230">
-      <c r="A230" s="22" t="n"/>
+      <c r="A230" s="22" t="inlineStr">
+        <is>
+          <t>00037</t>
+        </is>
+      </c>
+      <c r="B230" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C230" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D230" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E230" s="7" t="inlineStr">
+        <is>
+          <t>slaughter (nerve 3).jpg</t>
+        </is>
+      </c>
+      <c r="F230" s="7" t="inlineStr">
+        <is>
+          <t>slaughter (nerve 3)</t>
+        </is>
+      </c>
+      <c r="G230" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H230" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I230" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J230" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K230" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L230" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M230" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S230" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="231">
-      <c r="A231" s="22" t="n"/>
+      <c r="A231" s="22" t="inlineStr">
+        <is>
+          <t>00038</t>
+        </is>
+      </c>
+      <c r="B231" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C231" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D231" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E231" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 10 (surface).jpg</t>
+        </is>
+      </c>
+      <c r="F231" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 10 (surface)</t>
+        </is>
+      </c>
+      <c r="G231" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H231" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I231" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J231" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K231" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L231" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M231" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S231" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="232">
-      <c r="A232" s="22" t="n"/>
+      <c r="A232" s="22" t="inlineStr">
+        <is>
+          <t>00039</t>
+        </is>
+      </c>
+      <c r="B232" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C232" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D232" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E232" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 11 (surface).jpg</t>
+        </is>
+      </c>
+      <c r="F232" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 11 (surface)</t>
+        </is>
+      </c>
+      <c r="G232" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H232" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I232" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J232" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K232" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L232" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M232" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S232" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="233">
-      <c r="A233" s="22" t="n"/>
+      <c r="A233" s="22" t="inlineStr">
+        <is>
+          <t>00040</t>
+        </is>
+      </c>
+      <c r="B233" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C233" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D233" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E233" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 12.jpg</t>
+        </is>
+      </c>
+      <c r="F233" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 12</t>
+        </is>
+      </c>
+      <c r="G233" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H233" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I233" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J233" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K233" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L233" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M233" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S233" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="234">
-      <c r="A234" s="22" t="n"/>
+      <c r="A234" s="22" t="inlineStr">
+        <is>
+          <t>00041</t>
+        </is>
+      </c>
+      <c r="B234" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C234" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D234" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E234" s="7" t="inlineStr">
+        <is>
+          <t>hair.jpg</t>
+        </is>
+      </c>
+      <c r="F234" s="7" t="inlineStr">
+        <is>
+          <t>hair</t>
+        </is>
+      </c>
+      <c r="G234" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H234" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I234" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J234" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K234" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L234" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M234" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S234" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="235">
-      <c r="A235" s="22" t="n"/>
+      <c r="A235" s="22" t="inlineStr">
+        <is>
+          <t>00042</t>
+        </is>
+      </c>
+      <c r="B235" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C235" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D235" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E235" s="7" t="inlineStr">
+        <is>
+          <t>model face.jpg</t>
+        </is>
+      </c>
+      <c r="F235" s="7" t="inlineStr">
+        <is>
+          <t>model face</t>
+        </is>
+      </c>
+      <c r="G235" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H235" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I235" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J235" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K235" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L235" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M235" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S235" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="236">
-      <c r="A236" s="22" t="n"/>
+      <c r="A236" s="22" t="inlineStr">
+        <is>
+          <t>00043</t>
+        </is>
+      </c>
+      <c r="B236" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C236" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D236" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E236" s="7" t="inlineStr">
+        <is>
+          <t>form symbol (superimposed) 1.jpg</t>
+        </is>
+      </c>
+      <c r="F236" s="7" t="inlineStr">
+        <is>
+          <t>form symbol (superimposed) 1</t>
+        </is>
+      </c>
+      <c r="G236" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H236" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I236" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J236" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K236" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L236" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M236" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S236" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="237">
-      <c r="A237" s="22" t="n"/>
+      <c r="A237" s="22" t="inlineStr">
+        <is>
+          <t>00044</t>
+        </is>
+      </c>
+      <c r="B237" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C237" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D237" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E237" s="7" t="inlineStr">
+        <is>
+          <t>form symbol (superimposed) 2.jpg</t>
+        </is>
+      </c>
+      <c r="F237" s="7" t="inlineStr">
+        <is>
+          <t>form symbol (superimposed) 2</t>
+        </is>
+      </c>
+      <c r="G237" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H237" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I237" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J237" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K237" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L237" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M237" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S237" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="238">
-      <c r="A238" s="22" t="n"/>
+      <c r="A238" s="22" t="inlineStr">
+        <is>
+          <t>00045</t>
+        </is>
+      </c>
+      <c r="B238" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C238" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D238" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E238" s="7" t="inlineStr">
+        <is>
+          <t>outline form.jpg</t>
+        </is>
+      </c>
+      <c r="F238" s="7" t="inlineStr">
+        <is>
+          <t>outline form</t>
+        </is>
+      </c>
+      <c r="G238" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H238" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I238" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J238" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K238" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L238" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M238" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S238" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="239">
-      <c r="A239" s="22" t="n"/>
+      <c r="A239" s="22" t="inlineStr">
+        <is>
+          <t>00046</t>
+        </is>
+      </c>
+      <c r="B239" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C239" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D239" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E239" s="7" t="inlineStr">
+        <is>
+          <t>ink legs.jpg</t>
+        </is>
+      </c>
+      <c r="F239" s="7" t="inlineStr">
+        <is>
+          <t>ink legs</t>
+        </is>
+      </c>
+      <c r="G239" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H239" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I239" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J239" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K239" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L239" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M239" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S239" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="240">
-      <c r="A240" s="22" t="n"/>
+      <c r="A240" s="22" t="inlineStr">
+        <is>
+          <t>00047</t>
+        </is>
+      </c>
+      <c r="B240" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C240" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D240" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E240" s="7" t="inlineStr">
+        <is>
+          <t>slaughter 1.jpg</t>
+        </is>
+      </c>
+      <c r="F240" s="7" t="inlineStr">
+        <is>
+          <t>slaughter 1</t>
+        </is>
+      </c>
+      <c r="G240" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H240" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I240" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J240" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K240" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L240" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M240" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S240" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="241">
-      <c r="A241" s="22" t="n"/>
+      <c r="A241" s="22" t="inlineStr">
+        <is>
+          <t>00048</t>
+        </is>
+      </c>
+      <c r="B241" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C241" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D241" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E241" s="7" t="inlineStr">
+        <is>
+          <t>slaughter 2.jpg</t>
+        </is>
+      </c>
+      <c r="F241" s="7" t="inlineStr">
+        <is>
+          <t>slaughter 2</t>
+        </is>
+      </c>
+      <c r="G241" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H241" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I241" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J241" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K241" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L241" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M241" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S241" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="242">
-      <c r="A242" s="22" t="n"/>
+      <c r="A242" s="22" t="inlineStr">
+        <is>
+          <t>00049</t>
+        </is>
+      </c>
+      <c r="B242" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C242" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D242" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E242" s="7" t="inlineStr">
+        <is>
+          <t>slaughter 3.jpg</t>
+        </is>
+      </c>
+      <c r="F242" s="7" t="inlineStr">
+        <is>
+          <t>slaughter 3</t>
+        </is>
+      </c>
+      <c r="G242" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H242" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I242" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J242" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K242" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L242" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M242" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S242" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="243">
-      <c r="A243" s="22" t="n"/>
+      <c r="A243" s="22" t="inlineStr">
+        <is>
+          <t>00050</t>
+        </is>
+      </c>
+      <c r="B243" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C243" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D243" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E243" s="7" t="inlineStr">
+        <is>
+          <t>perspective 1.jpg</t>
+        </is>
+      </c>
+      <c r="F243" s="7" t="inlineStr">
+        <is>
+          <t>perspective 1</t>
+        </is>
+      </c>
+      <c r="G243" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H243" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I243" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J243" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K243" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L243" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M243" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S243" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="244">
-      <c r="A244" s="22" t="n"/>
+      <c r="A244" s="22" t="inlineStr">
+        <is>
+          <t>00051</t>
+        </is>
+      </c>
+      <c r="B244" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C244" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D244" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E244" s="7" t="inlineStr">
+        <is>
+          <t>perspective 2.jpg</t>
+        </is>
+      </c>
+      <c r="F244" s="7" t="inlineStr">
+        <is>
+          <t>perspective 2</t>
+        </is>
+      </c>
+      <c r="G244" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H244" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I244" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J244" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K244" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L244" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M244" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S244" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="245">
-      <c r="A245" s="22" t="n"/>
+      <c r="A245" s="22" t="inlineStr">
+        <is>
+          <t>00052</t>
+        </is>
+      </c>
+      <c r="B245" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C245" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D245" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E245" s="7" t="inlineStr">
+        <is>
+          <t>perspective 3.jpg</t>
+        </is>
+      </c>
+      <c r="F245" s="7" t="inlineStr">
+        <is>
+          <t>perspective 3</t>
+        </is>
+      </c>
+      <c r="G245" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H245" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I245" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J245" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K245" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L245" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M245" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S245" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="246">
-      <c r="A246" s="22" t="n"/>
+      <c r="A246" s="22" t="inlineStr">
+        <is>
+          <t>00053</t>
+        </is>
+      </c>
+      <c r="B246" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C246" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D246" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E246" s="7" t="inlineStr">
+        <is>
+          <t>internal organs of doll.jpg</t>
+        </is>
+      </c>
+      <c r="F246" s="7" t="inlineStr">
+        <is>
+          <t>internal organs of doll</t>
+        </is>
+      </c>
+      <c r="G246" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H246" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I246" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J246" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K246" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L246" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M246" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S246" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="247">
-      <c r="A247" s="22" t="n"/>
+      <c r="A247" s="22" t="inlineStr">
+        <is>
+          <t>00054</t>
+        </is>
+      </c>
+      <c r="B247" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C247" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D247" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E247" s="7" t="inlineStr">
+        <is>
+          <t>preparation for mannequin.jpg</t>
+        </is>
+      </c>
+      <c r="F247" s="7" t="inlineStr">
+        <is>
+          <t>preparation for mannequin</t>
+        </is>
+      </c>
+      <c r="G247" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H247" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I247" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J247" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K247" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L247" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M247" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S247" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="248">
-      <c r="A248" s="22" t="n"/>
+      <c r="A248" s="22" t="inlineStr">
+        <is>
+          <t>00055</t>
+        </is>
+      </c>
+      <c r="B248" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C248" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D248" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E248" s="7" t="inlineStr">
+        <is>
+          <t>mannequin (legs).jpg</t>
+        </is>
+      </c>
+      <c r="F248" s="7" t="inlineStr">
+        <is>
+          <t>mannequin (legs)</t>
+        </is>
+      </c>
+      <c r="G248" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H248" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I248" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J248" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K248" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L248" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M248" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S248" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="249">
-      <c r="A249" s="22" t="n"/>
+      <c r="A249" s="22" t="inlineStr">
+        <is>
+          <t>00056</t>
+        </is>
+      </c>
+      <c r="B249" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C249" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D249" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E249" s="7" t="inlineStr">
+        <is>
+          <t>open form.jpg</t>
+        </is>
+      </c>
+      <c r="F249" s="7" t="inlineStr">
+        <is>
+          <t>open form</t>
+        </is>
+      </c>
+      <c r="G249" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H249" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I249" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J249" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K249" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L249" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M249" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S249" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
     <row r="250">
-      <c r="A250" s="22" t="n"/>
+      <c r="A250" s="22" t="inlineStr">
+        <is>
+          <t>00057</t>
+        </is>
+      </c>
+      <c r="B250" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C250" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D250" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E250" s="7" t="inlineStr">
+        <is>
+          <t>joining forms 1.jpg</t>
+        </is>
+      </c>
+      <c r="F250" s="7" t="inlineStr">
+        <is>
+          <t>joining forms 1</t>
+        </is>
+      </c>
+      <c r="G250" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H250" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I250" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J250" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K250" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L250" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M250" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S250" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="22" t="inlineStr">
+        <is>
+          <t>00058</t>
+        </is>
+      </c>
+      <c r="B251" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C251" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D251" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E251" s="7" t="inlineStr">
+        <is>
+          <t>joining forms 2.jpg</t>
+        </is>
+      </c>
+      <c r="F251" s="7" t="inlineStr">
+        <is>
+          <t>joining forms 2</t>
+        </is>
+      </c>
+      <c r="G251" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H251" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I251" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J251" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K251" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L251" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M251" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S251" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="22" t="inlineStr">
+        <is>
+          <t>00059</t>
+        </is>
+      </c>
+      <c r="B252" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C252" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D252" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E252" s="7" t="inlineStr">
+        <is>
+          <t>joining forms 3.jpg</t>
+        </is>
+      </c>
+      <c r="F252" s="7" t="inlineStr">
+        <is>
+          <t>joining forms 3</t>
+        </is>
+      </c>
+      <c r="G252" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H252" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I252" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J252" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K252" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L252" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M252" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S252" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="22" t="inlineStr">
+        <is>
+          <t>00060</t>
+        </is>
+      </c>
+      <c r="B253" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C253" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D253" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E253" s="7" t="inlineStr">
+        <is>
+          <t>mesh forms 1.jpg</t>
+        </is>
+      </c>
+      <c r="F253" s="7" t="inlineStr">
+        <is>
+          <t>mesh forms 1</t>
+        </is>
+      </c>
+      <c r="G253" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H253" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I253" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J253" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K253" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L253" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M253" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S253" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="22" t="inlineStr">
+        <is>
+          <t>00061</t>
+        </is>
+      </c>
+      <c r="B254" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C254" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D254" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E254" s="7" t="inlineStr">
+        <is>
+          <t>mesh forms 2.jpg</t>
+        </is>
+      </c>
+      <c r="F254" s="7" t="inlineStr">
+        <is>
+          <t>mesh forms 2</t>
+        </is>
+      </c>
+      <c r="G254" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H254" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I254" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J254" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K254" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L254" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M254" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S254" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="22" t="inlineStr">
+        <is>
+          <t>00062</t>
+        </is>
+      </c>
+      <c r="B255" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C255" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D255" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E255" s="7" t="inlineStr">
+        <is>
+          <t>dissecting forms 1.jpg</t>
+        </is>
+      </c>
+      <c r="F255" s="7" t="inlineStr">
+        <is>
+          <t>dissecting forms 1</t>
+        </is>
+      </c>
+      <c r="G255" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H255" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I255" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J255" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K255" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L255" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M255" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S255" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="22" t="inlineStr">
+        <is>
+          <t>00063</t>
+        </is>
+      </c>
+      <c r="B256" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C256" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D256" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E256" s="7" t="inlineStr">
+        <is>
+          <t>dissecting forms 2.jpg</t>
+        </is>
+      </c>
+      <c r="F256" s="7" t="inlineStr">
+        <is>
+          <t>dissecting forms 2</t>
+        </is>
+      </c>
+      <c r="G256" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H256" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I256" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J256" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K256" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L256" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M256" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S256" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="22" t="inlineStr">
+        <is>
+          <t>00064</t>
+        </is>
+      </c>
+      <c r="B257" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C257" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D257" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E257" s="7" t="inlineStr">
+        <is>
+          <t>fly.jpg</t>
+        </is>
+      </c>
+      <c r="F257" s="7" t="inlineStr">
+        <is>
+          <t>fly</t>
+        </is>
+      </c>
+      <c r="G257" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H257" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I257" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J257" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K257" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L257" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M257" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S257" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="22" t="inlineStr">
+        <is>
+          <t>00065</t>
+        </is>
+      </c>
+      <c r="B258" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C258" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D258" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E258" s="7" t="inlineStr">
+        <is>
+          <t>fly (broken).jpg</t>
+        </is>
+      </c>
+      <c r="F258" s="7" t="inlineStr">
+        <is>
+          <t>fly (broken)</t>
+        </is>
+      </c>
+      <c r="G258" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H258" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I258" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J258" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K258" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L258" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M258" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S258" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="22" t="inlineStr">
+        <is>
+          <t>00066</t>
+        </is>
+      </c>
+      <c r="B259" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C259" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D259" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E259" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 1.jpg</t>
+        </is>
+      </c>
+      <c r="F259" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 1</t>
+        </is>
+      </c>
+      <c r="G259" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H259" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I259" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J259" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K259" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L259" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M259" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S259" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="22" t="inlineStr">
+        <is>
+          <t>00067</t>
+        </is>
+      </c>
+      <c r="B260" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C260" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D260" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E260" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 2.jpg</t>
+        </is>
+      </c>
+      <c r="F260" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 2</t>
+        </is>
+      </c>
+      <c r="G260" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H260" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I260" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J260" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K260" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L260" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M260" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S260" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="22" t="inlineStr">
+        <is>
+          <t>00068</t>
+        </is>
+      </c>
+      <c r="B261" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C261" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D261" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E261" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 3.jpg</t>
+        </is>
+      </c>
+      <c r="F261" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 3</t>
+        </is>
+      </c>
+      <c r="G261" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H261" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I261" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J261" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K261" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L261" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M261" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S261" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="22" t="inlineStr">
+        <is>
+          <t>00069</t>
+        </is>
+      </c>
+      <c r="B262" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C262" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D262" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E262" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 4.jpg</t>
+        </is>
+      </c>
+      <c r="F262" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 4</t>
+        </is>
+      </c>
+      <c r="G262" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H262" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I262" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J262" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K262" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L262" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M262" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S262" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="22" t="inlineStr">
+        <is>
+          <t>00070</t>
+        </is>
+      </c>
+      <c r="B263" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C263" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D263" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E263" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 5.jpg</t>
+        </is>
+      </c>
+      <c r="F263" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 5</t>
+        </is>
+      </c>
+      <c r="G263" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H263" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I263" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J263" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K263" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L263" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M263" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S263" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="22" t="inlineStr">
+        <is>
+          <t>00071</t>
+        </is>
+      </c>
+      <c r="B264" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C264" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D264" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E264" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 6.jpg</t>
+        </is>
+      </c>
+      <c r="F264" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 6</t>
+        </is>
+      </c>
+      <c r="G264" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H264" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I264" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J264" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K264" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L264" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M264" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S264" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="22" t="inlineStr">
+        <is>
+          <t>00072</t>
+        </is>
+      </c>
+      <c r="B265" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C265" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D265" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E265" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 7.jpg</t>
+        </is>
+      </c>
+      <c r="F265" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 7</t>
+        </is>
+      </c>
+      <c r="G265" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H265" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I265" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J265" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K265" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L265" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M265" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S265" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="22" t="inlineStr">
+        <is>
+          <t>00073</t>
+        </is>
+      </c>
+      <c r="B266" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C266" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D266" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E266" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 8 (internal frame).jpg</t>
+        </is>
+      </c>
+      <c r="F266" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 8 (internal frame)</t>
+        </is>
+      </c>
+      <c r="G266" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H266" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I266" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J266" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K266" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L266" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M266" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S266" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="22" t="inlineStr">
+        <is>
+          <t>00074</t>
+        </is>
+      </c>
+      <c r="B267" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C267" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D267" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E267" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 9.jpg</t>
+        </is>
+      </c>
+      <c r="F267" s="7" t="inlineStr">
+        <is>
+          <t>nude frame 9</t>
+        </is>
+      </c>
+      <c r="G267" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H267" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I267" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J267" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K267" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L267" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M267" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S267" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="22" t="inlineStr">
+        <is>
+          <t>00075</t>
+        </is>
+      </c>
+      <c r="B268" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C268" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D268" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E268" s="7" t="inlineStr">
+        <is>
+          <t>body forms 2.jpg</t>
+        </is>
+      </c>
+      <c r="F268" s="7" t="inlineStr">
+        <is>
+          <t>body forms 2</t>
+        </is>
+      </c>
+      <c r="G268" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H268" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I268" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J268" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K268" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L268" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M268" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S268" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="22" t="inlineStr">
+        <is>
+          <t>00076</t>
+        </is>
+      </c>
+      <c r="B269" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C269" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D269" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E269" s="7" t="inlineStr">
+        <is>
+          <t>body forms 3.jpg</t>
+        </is>
+      </c>
+      <c r="F269" s="7" t="inlineStr">
+        <is>
+          <t>body forms 3</t>
+        </is>
+      </c>
+      <c r="G269" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H269" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I269" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J269" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K269" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L269" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M269" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S269" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="22" t="inlineStr">
+        <is>
+          <t>00077</t>
+        </is>
+      </c>
+      <c r="B270" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C270" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D270" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E270" s="7" t="inlineStr">
+        <is>
+          <t>body forms 4.jpg</t>
+        </is>
+      </c>
+      <c r="F270" s="7" t="inlineStr">
+        <is>
+          <t>body forms 4</t>
+        </is>
+      </c>
+      <c r="G270" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H270" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I270" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J270" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K270" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L270" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M270" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S270" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="22" t="inlineStr">
+        <is>
+          <t>00078</t>
+        </is>
+      </c>
+      <c r="B271" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C271" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D271" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E271" s="7" t="inlineStr">
+        <is>
+          <t>body forms 5.jpg</t>
+        </is>
+      </c>
+      <c r="F271" s="7" t="inlineStr">
+        <is>
+          <t>body forms 5</t>
+        </is>
+      </c>
+      <c r="G271" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H271" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I271" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J271" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K271" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L271" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M271" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S271" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="22" t="inlineStr">
+        <is>
+          <t>00079</t>
+        </is>
+      </c>
+      <c r="B272" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C272" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D272" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E272" s="7" t="inlineStr">
+        <is>
+          <t>body forms 6.jpg</t>
+        </is>
+      </c>
+      <c r="F272" s="7" t="inlineStr">
+        <is>
+          <t>body forms 6</t>
+        </is>
+      </c>
+      <c r="G272" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H272" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I272" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J272" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K272" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L272" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M272" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S272" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="22" t="inlineStr">
+        <is>
+          <t>00080</t>
+        </is>
+      </c>
+      <c r="B273" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C273" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D273" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E273" s="7" t="inlineStr">
+        <is>
+          <t>body forms 7.jpg</t>
+        </is>
+      </c>
+      <c r="F273" s="7" t="inlineStr">
+        <is>
+          <t>body forms 7</t>
+        </is>
+      </c>
+      <c r="G273" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H273" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I273" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J273" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K273" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L273" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M273" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S273" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="22" t="inlineStr">
+        <is>
+          <t>00081</t>
+        </is>
+      </c>
+      <c r="B274" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C274" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D274" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E274" s="7" t="inlineStr">
+        <is>
+          <t>body forms 8.jpg</t>
+        </is>
+      </c>
+      <c r="F274" s="7" t="inlineStr">
+        <is>
+          <t>body forms 8</t>
+        </is>
+      </c>
+      <c r="G274" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H274" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I274" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J274" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K274" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L274" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M274" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S274" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="22" t="inlineStr">
+        <is>
+          <t>00082</t>
+        </is>
+      </c>
+      <c r="B275" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C275" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D275" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E275" s="7" t="inlineStr">
+        <is>
+          <t>body series dissected 1.jpg</t>
+        </is>
+      </c>
+      <c r="F275" s="7" t="inlineStr">
+        <is>
+          <t>body series dissected 1</t>
+        </is>
+      </c>
+      <c r="G275" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H275" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I275" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J275" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K275" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L275" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M275" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S275" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="22" t="inlineStr">
+        <is>
+          <t>00083</t>
+        </is>
+      </c>
+      <c r="B276" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C276" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D276" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E276" s="7" t="inlineStr">
+        <is>
+          <t>body series dissected 2.jpg</t>
+        </is>
+      </c>
+      <c r="F276" s="7" t="inlineStr">
+        <is>
+          <t>body series dissected 2</t>
+        </is>
+      </c>
+      <c r="G276" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H276" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I276" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J276" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K276" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L276" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M276" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S276" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="22" t="inlineStr">
+        <is>
+          <t>00084</t>
+        </is>
+      </c>
+      <c r="B277" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C277" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D277" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E277" s="7" t="inlineStr">
+        <is>
+          <t>body series dissected 3.jpg</t>
+        </is>
+      </c>
+      <c r="F277" s="7" t="inlineStr">
+        <is>
+          <t>body series dissected 3</t>
+        </is>
+      </c>
+      <c r="G277" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H277" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I277" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J277" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K277" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L277" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M277" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S277" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="22" t="inlineStr">
+        <is>
+          <t>00085</t>
+        </is>
+      </c>
+      <c r="B278" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C278" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D278" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E278" s="7" t="inlineStr">
+        <is>
+          <t>body series dissected 4.jpg</t>
+        </is>
+      </c>
+      <c r="F278" s="7" t="inlineStr">
+        <is>
+          <t>body series dissected 4</t>
+        </is>
+      </c>
+      <c r="G278" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H278" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I278" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J278" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K278" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L278" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M278" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S278" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="22" t="inlineStr">
+        <is>
+          <t>00086</t>
+        </is>
+      </c>
+      <c r="B279" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C279" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D279" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E279" s="7" t="inlineStr">
+        <is>
+          <t>body series opened 1.jpg</t>
+        </is>
+      </c>
+      <c r="F279" s="7" t="inlineStr">
+        <is>
+          <t>body series opened 1</t>
+        </is>
+      </c>
+      <c r="G279" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H279" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I279" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J279" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K279" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L279" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M279" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S279" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="22" t="inlineStr">
+        <is>
+          <t>00087</t>
+        </is>
+      </c>
+      <c r="B280" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C280" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D280" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E280" s="7" t="inlineStr">
+        <is>
+          <t>body series opened 2.jpg</t>
+        </is>
+      </c>
+      <c r="F280" s="7" t="inlineStr">
+        <is>
+          <t>body series opened 2</t>
+        </is>
+      </c>
+      <c r="G280" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H280" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I280" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J280" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K280" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L280" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M280" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S280" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="22" t="inlineStr">
+        <is>
+          <t>00088</t>
+        </is>
+      </c>
+      <c r="B281" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C281" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D281" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E281" s="7" t="inlineStr">
+        <is>
+          <t>body series opened 3.jpg</t>
+        </is>
+      </c>
+      <c r="F281" s="7" t="inlineStr">
+        <is>
+          <t>body series opened 3</t>
+        </is>
+      </c>
+      <c r="G281" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H281" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I281" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J281" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K281" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L281" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M281" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S281" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="22" t="inlineStr">
+        <is>
+          <t>00089</t>
+        </is>
+      </c>
+      <c r="B282" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C282" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D282" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E282" s="7" t="inlineStr">
+        <is>
+          <t>body series opened 4.jpg</t>
+        </is>
+      </c>
+      <c r="F282" s="7" t="inlineStr">
+        <is>
+          <t>body series opened 4</t>
+        </is>
+      </c>
+      <c r="G282" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H282" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I282" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J282" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K282" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L282" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M282" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S282" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="22" t="inlineStr">
+        <is>
+          <t>00090</t>
+        </is>
+      </c>
+      <c r="B283" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C283" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D283" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E283" s="7" t="inlineStr">
+        <is>
+          <t>dissection (identification of points on a surface).jpg</t>
+        </is>
+      </c>
+      <c r="F283" s="7" t="inlineStr">
+        <is>
+          <t>dissection (identification of points on a surface)</t>
+        </is>
+      </c>
+      <c r="G283" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H283" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I283" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J283" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K283" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L283" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M283" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S283" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="22" t="inlineStr">
+        <is>
+          <t>00091</t>
+        </is>
+      </c>
+      <c r="B284" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C284" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D284" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E284" s="7" t="inlineStr">
+        <is>
+          <t>dissection.jpg</t>
+        </is>
+      </c>
+      <c r="F284" s="7" t="inlineStr">
+        <is>
+          <t>dissection</t>
+        </is>
+      </c>
+      <c r="G284" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H284" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I284" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J284" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K284" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L284" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M284" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S284" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="22" t="inlineStr">
+        <is>
+          <t>00092</t>
+        </is>
+      </c>
+      <c r="B285" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C285" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D285" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E285" s="7" t="inlineStr">
+        <is>
+          <t>healing dissection.jpg</t>
+        </is>
+      </c>
+      <c r="F285" s="7" t="inlineStr">
+        <is>
+          <t>healing dissection</t>
+        </is>
+      </c>
+      <c r="G285" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H285" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I285" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J285" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K285" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L285" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M285" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S285" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="22" t="inlineStr">
+        <is>
+          <t>00093</t>
+        </is>
+      </c>
+      <c r="B286" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C286" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D286" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E286" s="7" t="inlineStr">
+        <is>
+          <t>3 elements of a body.jpg</t>
+        </is>
+      </c>
+      <c r="F286" s="7" t="inlineStr">
+        <is>
+          <t>3 elements of a body</t>
+        </is>
+      </c>
+      <c r="G286" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H286" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I286" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J286" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K286" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L286" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M286" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S286" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="22" t="inlineStr">
+        <is>
+          <t>00094</t>
+        </is>
+      </c>
+      <c r="B287" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C287" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D287" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E287" s="7" t="inlineStr">
+        <is>
+          <t>body forms 1.jpg</t>
+        </is>
+      </c>
+      <c r="F287" s="7" t="inlineStr">
+        <is>
+          <t>body forms 1</t>
+        </is>
+      </c>
+      <c r="G287" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H287" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I287" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J287" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K287" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L287" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M287" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S287" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="22" t="inlineStr">
+        <is>
+          <t>00095</t>
+        </is>
+      </c>
+      <c r="B288" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C288" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D288" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E288" s="7" t="inlineStr">
+        <is>
+          <t>death.jpg</t>
+        </is>
+      </c>
+      <c r="F288" s="7" t="inlineStr">
+        <is>
+          <t>death</t>
+        </is>
+      </c>
+      <c r="G288" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H288" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I288" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J288" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K288" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L288" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M288" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S288" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="22" t="inlineStr">
+        <is>
+          <t>00096</t>
+        </is>
+      </c>
+      <c r="B289" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C289" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D289" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E289" s="7" t="inlineStr">
+        <is>
+          <t>dissection (prepared body 1).jpg</t>
+        </is>
+      </c>
+      <c r="F289" s="7" t="inlineStr">
+        <is>
+          <t>dissection (prepared body 1)</t>
+        </is>
+      </c>
+      <c r="G289" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H289" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I289" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J289" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K289" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L289" s="7" t="inlineStr">
+        <is>
+          <t>painting</t>
+        </is>
+      </c>
+      <c r="M289" s="7" t="inlineStr">
+        <is>
+          <t>ink on paper</t>
+        </is>
+      </c>
+      <c r="S289" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="22" t="inlineStr">
+        <is>
+          <t>00097</t>
+        </is>
+      </c>
+      <c r="B290" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C290" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D290" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E290" s="7" t="inlineStr">
+        <is>
+          <t>dissection (prepared body 2).jpg</t>
+        </is>
+      </c>
+      <c r="F290" s="7" t="inlineStr">
+        <is>
+          <t>dissection (prepared body 2)</t>
+        </is>
+      </c>
+      <c r="G290" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H290" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I290" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J290" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K290" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L290" s="7" t="inlineStr">
+        <is>
+          <t>painting</t>
+        </is>
+      </c>
+      <c r="M290" s="7" t="inlineStr">
+        <is>
+          <t>ink and watercolour on paper</t>
+        </is>
+      </c>
+      <c r="S290" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="22" t="inlineStr">
+        <is>
+          <t>00098</t>
+        </is>
+      </c>
+      <c r="B291" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C291" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D291" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E291" s="7" t="inlineStr">
+        <is>
+          <t>dissected body 1.jpg</t>
+        </is>
+      </c>
+      <c r="F291" s="7" t="inlineStr">
+        <is>
+          <t>dissected body 1</t>
+        </is>
+      </c>
+      <c r="G291" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H291" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I291" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J291" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K291" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L291" s="7" t="inlineStr">
+        <is>
+          <t>painting</t>
+        </is>
+      </c>
+      <c r="M291" s="7" t="inlineStr">
+        <is>
+          <t>ink and watercolour on paper</t>
+        </is>
+      </c>
+      <c r="S291" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="22" t="inlineStr">
+        <is>
+          <t>00099</t>
+        </is>
+      </c>
+      <c r="B292" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C292" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D292" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E292" s="7" t="inlineStr">
+        <is>
+          <t>dissected body 2.jpg</t>
+        </is>
+      </c>
+      <c r="F292" s="7" t="inlineStr">
+        <is>
+          <t>dissected body 2</t>
+        </is>
+      </c>
+      <c r="G292" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H292" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I292" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J292" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K292" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L292" s="7" t="inlineStr">
+        <is>
+          <t>painting</t>
+        </is>
+      </c>
+      <c r="M292" s="7" t="inlineStr">
+        <is>
+          <t>ink and watercolour on paper</t>
+        </is>
+      </c>
+      <c r="S292" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="22" t="inlineStr">
+        <is>
+          <t>00100</t>
+        </is>
+      </c>
+      <c r="B293" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C293" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D293" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E293" s="7" t="inlineStr">
+        <is>
+          <t>preparation for dissection.jpg</t>
+        </is>
+      </c>
+      <c r="F293" s="7" t="inlineStr">
+        <is>
+          <t>preparation for dissection</t>
+        </is>
+      </c>
+      <c r="G293" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H293" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I293" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J293" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K293" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L293" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M293" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S293" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="22" t="inlineStr">
+        <is>
+          <t>00101</t>
+        </is>
+      </c>
+      <c r="B294" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C294" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D294" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E294" s="7" t="inlineStr">
+        <is>
+          <t>dissection in progress.jpg</t>
+        </is>
+      </c>
+      <c r="F294" s="7" t="inlineStr">
+        <is>
+          <t>dissection in progress</t>
+        </is>
+      </c>
+      <c r="G294" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H294" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I294" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J294" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K294" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L294" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M294" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S294" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="22" t="inlineStr">
+        <is>
+          <t>00102</t>
+        </is>
+      </c>
+      <c r="B295" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C295" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D295" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E295" s="7" t="inlineStr">
+        <is>
+          <t>ink (front).jpg</t>
+        </is>
+      </c>
+      <c r="F295" s="7" t="inlineStr">
+        <is>
+          <t>ink (front)</t>
+        </is>
+      </c>
+      <c r="G295" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H295" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I295" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J295" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K295" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L295" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M295" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S295" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="22" t="inlineStr">
+        <is>
+          <t>00103</t>
+        </is>
+      </c>
+      <c r="B296" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C296" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D296" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E296" s="7" t="inlineStr">
+        <is>
+          <t>ink (back).jpg</t>
+        </is>
+      </c>
+      <c r="F296" s="7" t="inlineStr">
+        <is>
+          <t>ink (back)</t>
+        </is>
+      </c>
+      <c r="G296" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H296" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I296" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J296" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K296" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L296" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M296" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S296" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="22" t="inlineStr">
+        <is>
+          <t>00104</t>
+        </is>
+      </c>
+      <c r="B297" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C297" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D297" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E297" s="7" t="inlineStr">
+        <is>
+          <t>healing symbol.jpg</t>
+        </is>
+      </c>
+      <c r="F297" s="7" t="inlineStr">
+        <is>
+          <t>healing symbol</t>
+        </is>
+      </c>
+      <c r="G297" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H297" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I297" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J297" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K297" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L297" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M297" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S297" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="22" t="inlineStr">
+        <is>
+          <t>00105</t>
+        </is>
+      </c>
+      <c r="B298" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C298" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D298" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E298" s="7" t="inlineStr">
+        <is>
+          <t>symbol frame.jpg</t>
+        </is>
+      </c>
+      <c r="F298" s="7" t="inlineStr">
+        <is>
+          <t>symbol frame</t>
+        </is>
+      </c>
+      <c r="G298" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H298" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I298" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J298" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K298" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L298" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M298" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S298" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="22" t="inlineStr">
+        <is>
+          <t>00106</t>
+        </is>
+      </c>
+      <c r="B299" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C299" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D299" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E299" s="7" t="inlineStr">
+        <is>
+          <t>form 1.jpg</t>
+        </is>
+      </c>
+      <c r="F299" s="7" t="inlineStr">
+        <is>
+          <t>form 1</t>
+        </is>
+      </c>
+      <c r="G299" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H299" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I299" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J299" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K299" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L299" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M299" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S299" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="22" t="inlineStr">
+        <is>
+          <t>00107</t>
+        </is>
+      </c>
+      <c r="B300" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C300" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D300" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E300" s="7" t="inlineStr">
+        <is>
+          <t>form 2.jpg</t>
+        </is>
+      </c>
+      <c r="F300" s="7" t="inlineStr">
+        <is>
+          <t>form 2</t>
+        </is>
+      </c>
+      <c r="G300" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H300" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I300" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J300" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K300" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L300" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M300" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S300" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="22" t="inlineStr">
+        <is>
+          <t>00108</t>
+        </is>
+      </c>
+      <c r="B301" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C301" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D301" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E301" s="7" t="inlineStr">
+        <is>
+          <t>joined forms.jpg</t>
+        </is>
+      </c>
+      <c r="F301" s="7" t="inlineStr">
+        <is>
+          <t>joined forms</t>
+        </is>
+      </c>
+      <c r="G301" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H301" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I301" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J301" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K301" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L301" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M301" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S301" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="22" t="inlineStr">
+        <is>
+          <t>00109</t>
+        </is>
+      </c>
+      <c r="B302" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C302" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D302" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E302" s="7" t="inlineStr">
+        <is>
+          <t>joined forms 2.jpg</t>
+        </is>
+      </c>
+      <c r="F302" s="7" t="inlineStr">
+        <is>
+          <t>joined forms 2</t>
+        </is>
+      </c>
+      <c r="G302" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H302" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I302" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J302" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K302" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L302" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M302" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S302" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="22" t="inlineStr">
+        <is>
+          <t>00110</t>
+        </is>
+      </c>
+      <c r="B303" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C303" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D303" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E303" s="7" t="inlineStr">
+        <is>
+          <t>healing symbol joined.jpg</t>
+        </is>
+      </c>
+      <c r="F303" s="7" t="inlineStr">
+        <is>
+          <t>healing symbol joined</t>
+        </is>
+      </c>
+      <c r="G303" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H303" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I303" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J303" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K303" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L303" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M303" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S303" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="22" t="inlineStr">
+        <is>
+          <t>00111</t>
+        </is>
+      </c>
+      <c r="B304" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C304" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D304" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E304" s="7" t="inlineStr">
+        <is>
+          <t>response to standing nude.jpg</t>
+        </is>
+      </c>
+      <c r="F304" s="7" t="inlineStr">
+        <is>
+          <t>response to standing nude</t>
+        </is>
+      </c>
+      <c r="G304" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H304" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I304" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J304" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K304" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L304" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M304" s="7" t="inlineStr">
+        <is>
+          <t>ink on paper</t>
+        </is>
+      </c>
+      <c r="S304" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="22" t="inlineStr">
+        <is>
+          <t>00112</t>
+        </is>
+      </c>
+      <c r="B305" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C305" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D305" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E305" s="7" t="inlineStr">
+        <is>
+          <t>life.jpg</t>
+        </is>
+      </c>
+      <c r="F305" s="7" t="inlineStr">
+        <is>
+          <t>life</t>
+        </is>
+      </c>
+      <c r="G305" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H305" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I305" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J305" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K305" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L305" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="M305" s="7" t="inlineStr">
+        <is>
+          <t>photocopy</t>
+        </is>
+      </c>
+      <c r="S305" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="22" t="inlineStr">
+        <is>
+          <t>00113</t>
+        </is>
+      </c>
+      <c r="B306" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C306" s="33" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D306" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E306" s="7" t="inlineStr">
+        <is>
+          <t>gesture in grey 1.jpg</t>
+        </is>
+      </c>
+      <c r="F306" s="7" t="inlineStr">
+        <is>
+          <t>gesture in grey 1</t>
+        </is>
+      </c>
+      <c r="G306" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H306" s="7" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="I306" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J306" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K306" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L306" s="7" t="inlineStr">
+        <is>
+          <t>painting</t>
+        </is>
+      </c>
+      <c r="M306" s="7" t="inlineStr">
+        <is>
+          <t>acrylic on paper</t>
+        </is>
+      </c>
+      <c r="S306" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14499,7 +21112,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="31.83203125" customWidth="1" style="1" min="1" max="1"/>
     <col width="43.1640625" customWidth="1" style="1" min="2" max="2"/>
@@ -14510,8 +21123,8 @@
     <col width="21" customWidth="1" style="7" min="7" max="7"/>
     <col width="28.1640625" customWidth="1" style="7" min="8" max="8"/>
     <col width="51" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" style="1" min="10" max="38"/>
-    <col width="10.83203125" customWidth="1" style="1" min="39" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="1" min="10" max="39"/>
+    <col width="10.83203125" customWidth="1" style="1" min="40" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -15167,12 +21780,25 @@
           <t>collected 1989-1998</t>
         </is>
       </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="n">
+        <v>46071</v>
+      </c>
       <c r="E18" s="1" t="n">
         <v>1998</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
           <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>00049</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -15229,7 +21855,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J480"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="9.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -34950,7 +41576,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" outlineLevelCol="0"/>
   <cols>
     <col width="24.1640625" customWidth="1" style="19" min="1" max="1"/>
     <col width="34.83203125" customWidth="1" style="19" min="2" max="2"/>
@@ -34963,8 +41589,8 @@
     <col width="11.33203125" bestFit="1" customWidth="1" style="19" min="9" max="9"/>
     <col width="12.1640625" bestFit="1" customWidth="1" style="19" min="10" max="10"/>
     <col width="33.6640625" customWidth="1" style="19" min="11" max="11"/>
-    <col width="10.83203125" customWidth="1" style="19" min="12" max="31"/>
-    <col width="10.83203125" customWidth="1" style="19" min="32" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="19" min="12" max="32"/>
+    <col width="10.83203125" customWidth="1" style="19" min="33" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37126,7 +43752,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G839"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="21.83203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="21.83203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="41.6640625" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
     <col width="9.33203125" customWidth="1" style="10" min="2" max="2"/>
@@ -37136,8 +43762,8 @@
     <col width="20.1640625" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
     <col width="48.1640625" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
     <col width="21.83203125" customWidth="1" style="10" min="8" max="256"/>
-    <col width="21.83203125" customWidth="1" style="14" min="257" max="281"/>
-    <col width="21.83203125" customWidth="1" style="14" min="282" max="16384"/>
+    <col width="21.83203125" customWidth="1" style="14" min="257" max="282"/>
+    <col width="21.83203125" customWidth="1" style="14" min="283" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -618,7 +618,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="21.83203125" customWidth="1" style="4" min="1" max="1"/>
     <col width="77.33203125" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
@@ -1403,7 +1403,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Y306"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="11.33203125" customWidth="1" style="7" min="1" max="1"/>
     <col width="13.33203125" customWidth="1" style="7" min="2" max="2"/>
@@ -21112,7 +21112,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="31.83203125" customWidth="1" style="1" min="1" max="1"/>
     <col width="43.1640625" customWidth="1" style="1" min="2" max="2"/>
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="D2" s="15" t="n">
-        <v>46067</v>
+        <v>46072</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>2025</v>
@@ -21234,7 +21234,7 @@
         </is>
       </c>
       <c r="D3" s="15" t="n">
-        <v>46067</v>
+        <v>46072</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>2025</v>
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="D4" s="15" t="n">
-        <v>46067</v>
+        <v>46072</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>2021</v>
@@ -21313,7 +21313,7 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>46067</v>
+        <v>46072</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>2010</v>
@@ -21349,7 +21349,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>46067</v>
+        <v>46072</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>2020</v>
@@ -21387,7 +21387,7 @@
         </is>
       </c>
       <c r="D7" s="16" t="n">
-        <v>46068</v>
+        <v>46072</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>1995</v>
@@ -21425,7 +21425,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>46069</v>
+        <v>46072</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>2013</v>
@@ -21461,7 +21461,7 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>2004</v>
@@ -21494,7 +21494,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>2023</v>
@@ -21525,7 +21525,7 @@
         </is>
       </c>
       <c r="D11" s="16" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>2023</v>
@@ -21561,7 +21561,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>2011</v>
@@ -21592,7 +21592,7 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>2009</v>
@@ -21635,7 +21635,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>2023</v>
@@ -21671,7 +21671,7 @@
         </is>
       </c>
       <c r="D15" s="16" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>2010</v>
@@ -21709,7 +21709,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>2023</v>
@@ -21745,7 +21745,7 @@
         </is>
       </c>
       <c r="D17" s="16" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>2025</v>
@@ -21786,7 +21786,7 @@
         </is>
       </c>
       <c r="D18" s="33" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>1998</v>
@@ -21824,7 +21824,7 @@
         </is>
       </c>
       <c r="D19" s="16" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>2016</v>
@@ -21855,7 +21855,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J480"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="9.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -41576,7 +41576,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col width="24.1640625" customWidth="1" style="19" min="1" max="1"/>
     <col width="34.83203125" customWidth="1" style="19" min="2" max="2"/>
@@ -43752,7 +43752,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G839"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="21.83203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="21.83203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="41.6640625" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
     <col width="9.33203125" customWidth="1" style="10" min="2" max="2"/>

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -17,19 +17,18 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'index - old version'!$A$1:$G$803</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -110,12 +109,6 @@
       <color rgb="FF000000"/>
       <sz val="13"/>
     </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -147,7 +140,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -217,7 +210,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -619,7 +611,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="21.83203125" customWidth="1" style="4" min="1" max="1"/>
     <col width="77.33203125" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
@@ -1403,8 +1395,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y403"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <dimension ref="A1:Y406"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="11.33203125" customWidth="1" style="7" min="1" max="1"/>
     <col width="13.33203125" customWidth="1" style="7" min="2" max="2"/>
@@ -1430,8 +1422,8 @@
     <col width="21.5" customWidth="1" style="7" min="23" max="23"/>
     <col width="26.83203125" customWidth="1" style="7" min="24" max="24"/>
     <col width="20.83203125" customWidth="1" style="7" min="25" max="25"/>
-    <col width="10.83203125" customWidth="1" style="7" min="26" max="56"/>
-    <col width="10.83203125" customWidth="1" style="7" min="57" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="7" min="26" max="58"/>
+    <col width="10.83203125" customWidth="1" style="7" min="59" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="6">
@@ -21189,7 +21181,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C307" s="33" t="n">
+      <c r="C307" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D307" s="7" t="inlineStr">
@@ -21251,7 +21243,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C308" s="33" t="n">
+      <c r="C308" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D308" s="7" t="inlineStr">
@@ -21315,7 +21307,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C309" s="33" t="n">
+      <c r="C309" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D309" s="7" t="inlineStr">
@@ -21377,7 +21369,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C310" s="33" t="n">
+      <c r="C310" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D310" s="7" t="inlineStr">
@@ -21439,7 +21431,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C311" s="33" t="n">
+      <c r="C311" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D311" s="7" t="inlineStr">
@@ -21501,7 +21493,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C312" s="33" t="n">
+      <c r="C312" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D312" s="7" t="inlineStr">
@@ -21563,7 +21555,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C313" s="33" t="n">
+      <c r="C313" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D313" s="7" t="inlineStr">
@@ -21625,7 +21617,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C314" s="33" t="n">
+      <c r="C314" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D314" s="7" t="inlineStr">
@@ -21687,7 +21679,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C315" s="33" t="n">
+      <c r="C315" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D315" s="7" t="inlineStr">
@@ -21749,7 +21741,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C316" s="33" t="n">
+      <c r="C316" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D316" s="7" t="inlineStr">
@@ -21811,7 +21803,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C317" s="33" t="n">
+      <c r="C317" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D317" s="7" t="inlineStr">
@@ -21873,7 +21865,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C318" s="33" t="n">
+      <c r="C318" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D318" s="7" t="inlineStr">
@@ -21935,7 +21927,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C319" s="33" t="n">
+      <c r="C319" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D319" s="7" t="inlineStr">
@@ -21997,7 +21989,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C320" s="33" t="n">
+      <c r="C320" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D320" s="7" t="inlineStr">
@@ -22059,7 +22051,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C321" s="33" t="n">
+      <c r="C321" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D321" s="7" t="inlineStr">
@@ -22121,7 +22113,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C322" s="33" t="n">
+      <c r="C322" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D322" s="7" t="inlineStr">
@@ -22183,7 +22175,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C323" s="33" t="n">
+      <c r="C323" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D323" s="7" t="inlineStr">
@@ -22245,7 +22237,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C324" s="33" t="n">
+      <c r="C324" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D324" s="7" t="inlineStr">
@@ -22307,7 +22299,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C325" s="33" t="n">
+      <c r="C325" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D325" s="7" t="inlineStr">
@@ -22369,7 +22361,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C326" s="33" t="n">
+      <c r="C326" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D326" s="7" t="inlineStr">
@@ -22431,7 +22423,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C327" s="33" t="n">
+      <c r="C327" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D327" s="7" t="inlineStr">
@@ -22493,7 +22485,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C328" s="33" t="n">
+      <c r="C328" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D328" s="7" t="inlineStr">
@@ -22555,7 +22547,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C329" s="33" t="n">
+      <c r="C329" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D329" s="7" t="inlineStr">
@@ -22617,7 +22609,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C330" s="33" t="n">
+      <c r="C330" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D330" s="7" t="inlineStr">
@@ -22679,7 +22671,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C331" s="33" t="n">
+      <c r="C331" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D331" s="7" t="inlineStr">
@@ -22741,7 +22733,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C332" s="33" t="n">
+      <c r="C332" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D332" s="7" t="inlineStr">
@@ -22803,7 +22795,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C333" s="33" t="n">
+      <c r="C333" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D333" s="7" t="inlineStr">
@@ -22865,7 +22857,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C334" s="33" t="n">
+      <c r="C334" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D334" s="7" t="inlineStr">
@@ -22927,7 +22919,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C335" s="33" t="n">
+      <c r="C335" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D335" s="7" t="inlineStr">
@@ -22989,7 +22981,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C336" s="33" t="n">
+      <c r="C336" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D336" s="7" t="inlineStr">
@@ -23051,7 +23043,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C337" s="33" t="n">
+      <c r="C337" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D337" s="7" t="inlineStr">
@@ -23115,7 +23107,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C338" s="33" t="n">
+      <c r="C338" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D338" s="7" t="inlineStr">
@@ -23182,7 +23174,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C339" s="33" t="n">
+      <c r="C339" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D339" s="7" t="inlineStr">
@@ -23249,7 +23241,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C340" s="33" t="n">
+      <c r="C340" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D340" s="7" t="inlineStr">
@@ -23313,7 +23305,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C341" s="33" t="n">
+      <c r="C341" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D341" s="7" t="inlineStr">
@@ -23382,7 +23374,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C342" s="33" t="n">
+      <c r="C342" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D342" s="7" t="inlineStr">
@@ -23444,7 +23436,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C343" s="33" t="n">
+      <c r="C343" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D343" s="7" t="inlineStr">
@@ -23508,7 +23500,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C344" s="33" t="n">
+      <c r="C344" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D344" s="7" t="inlineStr">
@@ -23570,7 +23562,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C345" s="33" t="n">
+      <c r="C345" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D345" s="7" t="inlineStr">
@@ -23632,7 +23624,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C346" s="33" t="n">
+      <c r="C346" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D346" s="7" t="inlineStr">
@@ -23694,7 +23686,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C347" s="33" t="n">
+      <c r="C347" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D347" s="7" t="inlineStr">
@@ -23756,7 +23748,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C348" s="33" t="n">
+      <c r="C348" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D348" s="7" t="inlineStr">
@@ -23818,7 +23810,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C349" s="33" t="n">
+      <c r="C349" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D349" s="7" t="inlineStr">
@@ -23880,7 +23872,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C350" s="33" t="n">
+      <c r="C350" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D350" s="7" t="inlineStr">
@@ -23944,7 +23936,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C351" s="33" t="n">
+      <c r="C351" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D351" s="7" t="inlineStr">
@@ -24008,7 +24000,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C352" s="33" t="n">
+      <c r="C352" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D352" s="7" t="inlineStr">
@@ -24072,7 +24064,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C353" s="33" t="n">
+      <c r="C353" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D353" s="7" t="inlineStr">
@@ -24136,7 +24128,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C354" s="33" t="n">
+      <c r="C354" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D354" s="7" t="inlineStr">
@@ -24200,7 +24192,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C355" s="33" t="n">
+      <c r="C355" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D355" s="7" t="inlineStr">
@@ -24264,7 +24256,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C356" s="33" t="n">
+      <c r="C356" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D356" s="7" t="inlineStr">
@@ -24328,7 +24320,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C357" s="33" t="n">
+      <c r="C357" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D357" s="7" t="inlineStr">
@@ -24392,7 +24384,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C358" s="33" t="n">
+      <c r="C358" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D358" s="7" t="inlineStr">
@@ -24456,7 +24448,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C359" s="33" t="n">
+      <c r="C359" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D359" s="7" t="inlineStr">
@@ -24520,7 +24512,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C360" s="33" t="n">
+      <c r="C360" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D360" s="7" t="inlineStr">
@@ -24584,7 +24576,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C361" s="33" t="n">
+      <c r="C361" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D361" s="7" t="inlineStr">
@@ -24648,7 +24640,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C362" s="33" t="n">
+      <c r="C362" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D362" s="7" t="inlineStr">
@@ -24712,7 +24704,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C363" s="33" t="n">
+      <c r="C363" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D363" s="7" t="inlineStr">
@@ -24776,7 +24768,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C364" s="33" t="n">
+      <c r="C364" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D364" s="7" t="inlineStr">
@@ -24840,7 +24832,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C365" s="33" t="n">
+      <c r="C365" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D365" s="7" t="inlineStr">
@@ -24904,7 +24896,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C366" s="33" t="n">
+      <c r="C366" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D366" s="7" t="inlineStr">
@@ -24968,7 +24960,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C367" s="33" t="n">
+      <c r="C367" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D367" s="7" t="inlineStr">
@@ -25032,7 +25024,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C368" s="33" t="n">
+      <c r="C368" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D368" s="7" t="inlineStr">
@@ -25096,7 +25088,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C369" s="33" t="n">
+      <c r="C369" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D369" s="7" t="inlineStr">
@@ -25158,7 +25150,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C370" s="33" t="n">
+      <c r="C370" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D370" s="7" t="inlineStr">
@@ -25220,7 +25212,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C371" s="33" t="n">
+      <c r="C371" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D371" s="7" t="inlineStr">
@@ -25282,7 +25274,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C372" s="33" t="n">
+      <c r="C372" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D372" s="7" t="inlineStr">
@@ -25344,7 +25336,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C373" s="33" t="n">
+      <c r="C373" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D373" s="7" t="inlineStr">
@@ -25406,7 +25398,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C374" s="33" t="n">
+      <c r="C374" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D374" s="7" t="inlineStr">
@@ -25468,7 +25460,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C375" s="33" t="n">
+      <c r="C375" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D375" s="7" t="inlineStr">
@@ -25530,7 +25522,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C376" s="33" t="n">
+      <c r="C376" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D376" s="7" t="inlineStr">
@@ -25592,7 +25584,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C377" s="33" t="n">
+      <c r="C377" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D377" s="7" t="inlineStr">
@@ -25654,7 +25646,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C378" s="33" t="n">
+      <c r="C378" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D378" s="7" t="inlineStr">
@@ -25716,7 +25708,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C379" s="33" t="n">
+      <c r="C379" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D379" s="7" t="inlineStr">
@@ -25778,7 +25770,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C380" s="33" t="n">
+      <c r="C380" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D380" s="7" t="inlineStr">
@@ -25840,7 +25832,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C381" s="33" t="n">
+      <c r="C381" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D381" s="7" t="inlineStr">
@@ -25902,7 +25894,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C382" s="33" t="n">
+      <c r="C382" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D382" s="7" t="inlineStr">
@@ -25964,7 +25956,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C383" s="33" t="n">
+      <c r="C383" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D383" s="7" t="inlineStr">
@@ -26026,7 +26018,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C384" s="33" t="n">
+      <c r="C384" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D384" s="7" t="inlineStr">
@@ -26088,7 +26080,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C385" s="33" t="n">
+      <c r="C385" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D385" s="7" t="inlineStr">
@@ -26150,7 +26142,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C386" s="33" t="n">
+      <c r="C386" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D386" s="7" t="inlineStr">
@@ -26212,7 +26204,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C387" s="33" t="n">
+      <c r="C387" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D387" s="7" t="inlineStr">
@@ -26276,7 +26268,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C388" s="33" t="n">
+      <c r="C388" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D388" s="7" t="inlineStr">
@@ -26340,7 +26332,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C389" s="33" t="n">
+      <c r="C389" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D389" s="7" t="inlineStr">
@@ -26404,7 +26396,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C390" s="33" t="n">
+      <c r="C390" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D390" s="7" t="inlineStr">
@@ -26468,7 +26460,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C391" s="33" t="n">
+      <c r="C391" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D391" s="7" t="inlineStr">
@@ -26532,7 +26524,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C392" s="33" t="n">
+      <c r="C392" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D392" s="7" t="inlineStr">
@@ -26596,7 +26588,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C393" s="33" t="n">
+      <c r="C393" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D393" s="7" t="inlineStr">
@@ -26660,7 +26652,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C394" s="33" t="n">
+      <c r="C394" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D394" s="7" t="inlineStr">
@@ -26722,7 +26714,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C395" s="33" t="n">
+      <c r="C395" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D395" s="7" t="inlineStr">
@@ -26784,7 +26776,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C396" s="33" t="n">
+      <c r="C396" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D396" s="7" t="inlineStr">
@@ -26846,7 +26838,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C397" s="33" t="n">
+      <c r="C397" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D397" s="7" t="inlineStr">
@@ -26908,7 +26900,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C398" s="33" t="n">
+      <c r="C398" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D398" s="7" t="inlineStr">
@@ -26970,7 +26962,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C399" s="33" t="n">
+      <c r="C399" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D399" s="7" t="inlineStr">
@@ -27032,7 +27024,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C400" s="33" t="n">
+      <c r="C400" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D400" s="7" t="inlineStr">
@@ -27094,7 +27086,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C401" s="33" t="n">
+      <c r="C401" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D401" s="7" t="inlineStr">
@@ -27156,7 +27148,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C402" s="33" t="n">
+      <c r="C402" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D402" s="7" t="inlineStr">
@@ -27218,7 +27210,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C403" s="33" t="n">
+      <c r="C403" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="D403" s="7" t="inlineStr">
@@ -27264,6 +27256,198 @@
         </is>
       </c>
       <c r="S403" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="22" t="inlineStr">
+        <is>
+          <t>00233</t>
+        </is>
+      </c>
+      <c r="B404" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C404" s="16" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D404" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E404" s="7" t="inlineStr">
+        <is>
+          <t>untitled [0233].jpg</t>
+        </is>
+      </c>
+      <c r="F404" s="7" t="inlineStr">
+        <is>
+          <t>untitled [0233]</t>
+        </is>
+      </c>
+      <c r="G404" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H404" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I404" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J404" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K404" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L404" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M404" s="7" t="inlineStr">
+        <is>
+          <t>pen on paper</t>
+        </is>
+      </c>
+      <c r="S404" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="22" t="inlineStr">
+        <is>
+          <t>00234</t>
+        </is>
+      </c>
+      <c r="B405" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C405" s="16" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D405" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E405" s="7" t="inlineStr">
+        <is>
+          <t>untitled [0234].jpg</t>
+        </is>
+      </c>
+      <c r="F405" s="7" t="inlineStr">
+        <is>
+          <t>untitled [0234]</t>
+        </is>
+      </c>
+      <c r="G405" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H405" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I405" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J405" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K405" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L405" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M405" s="7" t="inlineStr">
+        <is>
+          <t>pen on paper</t>
+        </is>
+      </c>
+      <c r="S405" s="7" t="inlineStr">
+        <is>
+          <t>box 1 (A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="22" t="inlineStr">
+        <is>
+          <t>00247</t>
+        </is>
+      </c>
+      <c r="B406" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C406" s="16" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D406" s="7" t="inlineStr">
+        <is>
+          <t>collected 1989-1998</t>
+        </is>
+      </c>
+      <c r="E406" s="7" t="inlineStr">
+        <is>
+          <t>untitled [0247].jpg</t>
+        </is>
+      </c>
+      <c r="F406" s="7" t="inlineStr">
+        <is>
+          <t>untitled [0247]</t>
+        </is>
+      </c>
+      <c r="G406" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H406" s="7" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I406" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J406" s="7" t="inlineStr">
+        <is>
+          <t>c. 1989-98</t>
+        </is>
+      </c>
+      <c r="K406" s="7" t="inlineStr">
+        <is>
+          <t>collected-1989-1998</t>
+        </is>
+      </c>
+      <c r="L406" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="M406" s="7" t="inlineStr">
+        <is>
+          <t>pen on paper</t>
+        </is>
+      </c>
+      <c r="S406" s="7" t="inlineStr">
         <is>
           <t>box 1 (A4)</t>
         </is>
@@ -27282,7 +27466,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="31.83203125" customWidth="1" style="1" min="1" max="1"/>
     <col width="43.1640625" customWidth="1" style="1" min="2" max="2"/>
@@ -27293,8 +27477,8 @@
     <col width="21" customWidth="1" style="7" min="7" max="7"/>
     <col width="28.1640625" customWidth="1" style="7" min="8" max="8"/>
     <col width="51" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" style="1" min="10" max="41"/>
-    <col width="10.83203125" customWidth="1" style="1" min="42" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="1" min="10" max="43"/>
+    <col width="10.83203125" customWidth="1" style="1" min="44" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -28029,7 +28213,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="D20" s="33" t="n">
+      <c r="D20" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="E20" s="1" t="n">
@@ -28065,7 +28249,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="D21" s="33" t="n">
+      <c r="D21" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="E21" s="1" t="n">
@@ -28096,7 +28280,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="D22" s="33" t="n">
+      <c r="D22" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="E22" s="1" t="n">
@@ -28134,7 +28318,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="D23" s="33" t="n">
+      <c r="D23" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="E23" s="1" t="n">
@@ -28166,7 +28350,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J530"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="9.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -47906,7 +48090,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G481" s="33" t="n">
+      <c r="G481" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H481" t="n">
@@ -47947,7 +48131,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G482" s="33" t="n">
+      <c r="G482" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H482" t="n">
@@ -47988,7 +48172,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G483" s="33" t="n">
+      <c r="G483" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H483" t="n">
@@ -48029,7 +48213,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G484" s="33" t="n">
+      <c r="G484" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H484" t="n">
@@ -48070,7 +48254,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G485" s="33" t="n">
+      <c r="G485" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H485" t="n">
@@ -48111,7 +48295,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G486" s="33" t="n">
+      <c r="G486" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H486" t="n">
@@ -48152,7 +48336,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G487" s="33" t="n">
+      <c r="G487" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H487" t="n">
@@ -48193,7 +48377,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G488" s="33" t="n">
+      <c r="G488" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H488" t="n">
@@ -48234,7 +48418,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G489" s="33" t="n">
+      <c r="G489" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H489" t="n">
@@ -48275,7 +48459,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G490" s="33" t="n">
+      <c r="G490" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H490" t="n">
@@ -48316,7 +48500,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G491" s="33" t="n">
+      <c r="G491" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H491" t="n">
@@ -48357,7 +48541,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G492" s="33" t="n">
+      <c r="G492" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H492" t="n">
@@ -48398,7 +48582,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G493" s="33" t="n">
+      <c r="G493" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H493" t="n">
@@ -48439,7 +48623,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G494" s="33" t="n">
+      <c r="G494" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H494" t="n">
@@ -48480,7 +48664,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G495" s="33" t="n">
+      <c r="G495" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H495" t="n">
@@ -48521,7 +48705,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G496" s="33" t="n">
+      <c r="G496" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H496" t="n">
@@ -48562,7 +48746,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G497" s="33" t="n">
+      <c r="G497" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H497" t="n">
@@ -48603,7 +48787,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G498" s="33" t="n">
+      <c r="G498" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H498" t="n">
@@ -48644,7 +48828,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G499" s="33" t="n">
+      <c r="G499" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H499" t="n">
@@ -48685,7 +48869,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G500" s="33" t="n">
+      <c r="G500" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H500" t="n">
@@ -48726,7 +48910,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G501" s="33" t="n">
+      <c r="G501" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H501" t="n">
@@ -48767,7 +48951,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G502" s="33" t="n">
+      <c r="G502" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H502" t="n">
@@ -48808,7 +48992,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G503" s="33" t="n">
+      <c r="G503" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H503" t="n">
@@ -48849,7 +49033,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G504" s="33" t="n">
+      <c r="G504" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H504" t="n">
@@ -48890,7 +49074,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G505" s="33" t="n">
+      <c r="G505" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H505" t="n">
@@ -48931,7 +49115,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G506" s="33" t="n">
+      <c r="G506" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H506" t="n">
@@ -48972,7 +49156,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G507" s="33" t="n">
+      <c r="G507" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H507" t="n">
@@ -49013,7 +49197,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G508" s="33" t="n">
+      <c r="G508" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H508" t="n">
@@ -49054,7 +49238,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G509" s="33" t="n">
+      <c r="G509" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H509" t="n">
@@ -49095,7 +49279,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G510" s="33" t="n">
+      <c r="G510" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H510" t="n">
@@ -49136,7 +49320,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G511" s="33" t="n">
+      <c r="G511" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H511" t="n">
@@ -49177,7 +49361,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G512" s="33" t="n">
+      <c r="G512" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H512" t="n">
@@ -49218,7 +49402,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G513" s="33" t="n">
+      <c r="G513" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H513" t="n">
@@ -49259,7 +49443,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G514" s="33" t="n">
+      <c r="G514" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H514" t="n">
@@ -49300,7 +49484,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G515" s="33" t="n">
+      <c r="G515" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H515" t="n">
@@ -49341,7 +49525,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G516" s="33" t="n">
+      <c r="G516" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H516" t="n">
@@ -49382,7 +49566,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G517" s="33" t="n">
+      <c r="G517" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H517" t="n">
@@ -49423,7 +49607,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G518" s="33" t="n">
+      <c r="G518" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H518" t="n">
@@ -49464,7 +49648,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G519" s="33" t="n">
+      <c r="G519" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H519" t="n">
@@ -49505,7 +49689,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G520" s="33" t="n">
+      <c r="G520" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H520" t="n">
@@ -49546,7 +49730,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G521" s="33" t="n">
+      <c r="G521" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H521" t="n">
@@ -49587,7 +49771,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G522" s="33" t="n">
+      <c r="G522" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H522" t="n">
@@ -49628,7 +49812,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G523" s="33" t="n">
+      <c r="G523" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H523" t="n">
@@ -49669,7 +49853,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G524" s="33" t="n">
+      <c r="G524" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H524" t="n">
@@ -49710,7 +49894,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G525" s="33" t="n">
+      <c r="G525" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H525" t="n">
@@ -49751,7 +49935,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G526" s="33" t="n">
+      <c r="G526" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H526" t="n">
@@ -49792,7 +49976,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G527" s="33" t="n">
+      <c r="G527" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H527" t="n">
@@ -49833,7 +50017,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G528" s="33" t="n">
+      <c r="G528" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H528" t="n">
@@ -49874,7 +50058,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G529" s="33" t="n">
+      <c r="G529" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H529" t="n">
@@ -49915,7 +50099,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G530" s="33" t="n">
+      <c r="G530" s="16" t="n">
         <v>46074</v>
       </c>
       <c r="H530" t="n">
@@ -49937,7 +50121,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col width="24.1640625" customWidth="1" style="19" min="1" max="1"/>
     <col width="34.83203125" customWidth="1" style="19" min="2" max="2"/>
@@ -49950,8 +50134,8 @@
     <col width="11.33203125" bestFit="1" customWidth="1" style="19" min="9" max="9"/>
     <col width="12.1640625" bestFit="1" customWidth="1" style="19" min="10" max="10"/>
     <col width="33.6640625" customWidth="1" style="19" min="11" max="11"/>
-    <col width="10.83203125" customWidth="1" style="19" min="12" max="34"/>
-    <col width="10.83203125" customWidth="1" style="19" min="35" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="19" min="12" max="36"/>
+    <col width="10.83203125" customWidth="1" style="19" min="37" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -52113,7 +52297,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="26.33203125" customWidth="1" min="1" max="1"/>
     <col width="38.5" customWidth="1" min="2" max="2"/>
@@ -52155,7 +52339,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G839"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="21.83203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="21.83203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="41.6640625" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
     <col width="9.33203125" customWidth="1" style="10" min="2" max="2"/>
@@ -52165,8 +52349,8 @@
     <col width="20.1640625" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
     <col width="48.1640625" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
     <col width="21.83203125" customWidth="1" style="10" min="8" max="256"/>
-    <col width="21.83203125" customWidth="1" style="14" min="257" max="284"/>
-    <col width="21.83203125" customWidth="1" style="14" min="285" max="16384"/>
+    <col width="21.83203125" customWidth="1" style="14" min="257" max="286"/>
+    <col width="21.83203125" customWidth="1" style="14" min="287" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -1422,8 +1422,8 @@
     <col width="21.5" customWidth="1" style="7" min="23" max="23"/>
     <col width="26.83203125" customWidth="1" style="7" min="24" max="24"/>
     <col width="20.83203125" customWidth="1" style="7" min="25" max="25"/>
-    <col width="10.83203125" customWidth="1" style="7" min="26" max="58"/>
-    <col width="10.83203125" customWidth="1" style="7" min="59" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="7" min="26" max="59"/>
+    <col width="10.83203125" customWidth="1" style="7" min="60" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="6">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="C6" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="C7" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="C8" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="C10" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="C11" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="C12" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="C14" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="C16" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="C17" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="C18" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C19" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="C20" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="C22" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="C23" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="C24" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="C25" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="C26" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="C27" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="C28" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="C29" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="C30" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="C31" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="C32" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="C33" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="C34" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="C35" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="C36" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C37" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="C38" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="C39" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="C40" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="C41" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="C42" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="C43" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="C44" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="C45" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="C46" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="C47" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="C48" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="C49" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="C50" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="C51" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="C52" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="C53" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="C54" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="C55" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="C56" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="C57" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="C58" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="C59" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="C60" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="C61" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="C62" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="C63" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="C64" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="C65" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="C66" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="C67" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="C68" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="C69" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="C70" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="C71" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="C72" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="C73" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         </is>
       </c>
       <c r="C74" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         </is>
       </c>
       <c r="C75" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="C76" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="C77" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="C78" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="C79" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="C80" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="C81" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="C82" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="C83" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         </is>
       </c>
       <c r="C84" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         </is>
       </c>
       <c r="C85" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="C86" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         </is>
       </c>
       <c r="C87" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="C88" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="C89" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="C90" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="C91" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="C92" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="C93" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="C94" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="C95" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="C96" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="C97" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="C98" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="C99" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         </is>
       </c>
       <c r="C100" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         </is>
       </c>
       <c r="C101" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         </is>
       </c>
       <c r="C102" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="C103" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         </is>
       </c>
       <c r="C104" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         </is>
       </c>
       <c r="C105" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="C106" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="C107" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="C108" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="C109" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="C110" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         </is>
       </c>
       <c r="C111" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="C112" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="C113" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         </is>
       </c>
       <c r="C114" s="16" t="n">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
       </c>
       <c r="F342" s="7" t="inlineStr">
         <is>
-          <t>3 commentaries</t>
+          <t>unrelated commentaries</t>
         </is>
       </c>
       <c r="G342" s="7" t="n">
@@ -27477,8 +27477,8 @@
     <col width="21" customWidth="1" style="7" min="7" max="7"/>
     <col width="28.1640625" customWidth="1" style="7" min="8" max="8"/>
     <col width="51" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" style="1" min="10" max="43"/>
-    <col width="10.83203125" customWidth="1" style="1" min="44" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="1" min="10" max="44"/>
+    <col width="10.83203125" customWidth="1" style="1" min="45" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -28140,7 +28140,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>46072</v>
+        <v>46074</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>1998</v>
@@ -50134,8 +50134,8 @@
     <col width="11.33203125" bestFit="1" customWidth="1" style="19" min="9" max="9"/>
     <col width="12.1640625" bestFit="1" customWidth="1" style="19" min="10" max="10"/>
     <col width="33.6640625" customWidth="1" style="19" min="11" max="11"/>
-    <col width="10.83203125" customWidth="1" style="19" min="12" max="36"/>
-    <col width="10.83203125" customWidth="1" style="19" min="37" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="19" min="12" max="37"/>
+    <col width="10.83203125" customWidth="1" style="19" min="38" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -52349,8 +52349,8 @@
     <col width="20.1640625" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
     <col width="48.1640625" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
     <col width="21.83203125" customWidth="1" style="10" min="8" max="256"/>
-    <col width="21.83203125" customWidth="1" style="14" min="257" max="286"/>
-    <col width="21.83203125" customWidth="1" style="14" min="287" max="16384"/>
+    <col width="21.83203125" customWidth="1" style="14" min="257" max="287"/>
+    <col width="21.83203125" customWidth="1" style="14" min="288" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dlf/Developer/dotlineform/dotlineform-site/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F842E7-4BD2-E248-8ACE-8488073EDC31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7C9E50-8659-DF4B-97FA-68F460057DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12034" uniqueCount="4021">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12087" uniqueCount="4039">
   <si>
     <t>Works</t>
   </si>
@@ -12092,6 +12092,60 @@
   </si>
   <si>
     <t>2006, 2015</t>
+  </si>
+  <si>
+    <t>wa,symbols</t>
+  </si>
+  <si>
+    <t>wa source - wa (3)</t>
+  </si>
+  <si>
+    <t>wa source - wa (2)</t>
+  </si>
+  <si>
+    <t>wa source - wa (7)</t>
+  </si>
+  <si>
+    <t>wa source - wa (4)</t>
+  </si>
+  <si>
+    <t>wa source - wa (5)</t>
+  </si>
+  <si>
+    <t>wa source - wa (6)</t>
+  </si>
+  <si>
+    <t>wa source - wa (yoko takenami)</t>
+  </si>
+  <si>
+    <t>2008, 2011</t>
+  </si>
+  <si>
+    <t>ink/wa (yoko takenami).jpg</t>
+  </si>
+  <si>
+    <t>ink/wa (6).jpg</t>
+  </si>
+  <si>
+    <t>ink/wa (5).jpg</t>
+  </si>
+  <si>
+    <t>ink/wa (4).jpg</t>
+  </si>
+  <si>
+    <t>ink/wa (7).jpg</t>
+  </si>
+  <si>
+    <t>ink/wa (3).jpg</t>
+  </si>
+  <si>
+    <t>ink/wa (2).jpg</t>
+  </si>
+  <si>
+    <t>ink/wa.jpg</t>
+  </si>
+  <si>
+    <t>lipseyes.jpg</t>
   </si>
 </sst>
 </file>
@@ -13162,7 +13216,7 @@
     <col min="10" max="10" width="10.83203125" style="7" customWidth="1"/>
     <col min="11" max="11" width="16.5" style="7" customWidth="1"/>
     <col min="12" max="12" width="20.83203125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="43.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.83203125" style="7" customWidth="1"/>
     <col min="14" max="15" width="20.83203125" style="7" customWidth="1"/>
     <col min="16" max="16" width="10.83203125" style="7" customWidth="1"/>
     <col min="17" max="17" width="20.83203125" style="7" customWidth="1"/>
@@ -35660,19 +35714,28 @@
       </c>
       <c r="C511" s="16"/>
       <c r="D511" s="7" t="s">
-        <v>4015</v>
+        <v>3679</v>
       </c>
       <c r="E511" s="7" t="s">
-        <v>4014</v>
+        <v>3679</v>
+      </c>
+      <c r="F511" s="7" t="s">
+        <v>4038</v>
       </c>
       <c r="G511" s="7" t="s">
-        <v>4014</v>
+        <v>3679</v>
       </c>
       <c r="H511" s="7">
         <v>30.5</v>
       </c>
       <c r="I511" s="7">
         <v>30.5</v>
+      </c>
+      <c r="J511" s="7">
+        <v>2003</v>
+      </c>
+      <c r="K511" s="7">
+        <v>2003</v>
       </c>
       <c r="L511" s="7" t="s">
         <v>673</v>
@@ -35881,6 +35944,39 @@
         <v>3116</v>
       </c>
       <c r="C517" s="16"/>
+      <c r="D517" s="7" t="s">
+        <v>3975</v>
+      </c>
+      <c r="E517" s="7" t="s">
+        <v>3975</v>
+      </c>
+      <c r="F517" s="7" t="s">
+        <v>4030</v>
+      </c>
+      <c r="G517" s="7" t="s">
+        <v>4028</v>
+      </c>
+      <c r="H517" s="7">
+        <v>33.5</v>
+      </c>
+      <c r="I517" s="7">
+        <v>35</v>
+      </c>
+      <c r="J517" s="7">
+        <v>2008</v>
+      </c>
+      <c r="K517" s="7">
+        <v>2008</v>
+      </c>
+      <c r="L517" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="M517" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="N517" s="7">
+        <v>5</v>
+      </c>
       <c r="Z517" s="7"/>
     </row>
     <row r="518" spans="1:26" x14ac:dyDescent="0.2">
@@ -35888,6 +35984,39 @@
         <v>3117</v>
       </c>
       <c r="C518" s="16"/>
+      <c r="D518" s="7" t="s">
+        <v>3975</v>
+      </c>
+      <c r="E518" s="7" t="s">
+        <v>3975</v>
+      </c>
+      <c r="F518" s="7" t="s">
+        <v>4031</v>
+      </c>
+      <c r="G518" s="7" t="s">
+        <v>4027</v>
+      </c>
+      <c r="H518" s="7">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="I518" s="7">
+        <v>24.3</v>
+      </c>
+      <c r="J518" s="7">
+        <v>2008</v>
+      </c>
+      <c r="K518" s="7">
+        <v>2008</v>
+      </c>
+      <c r="L518" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="M518" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="N518" s="7">
+        <v>5</v>
+      </c>
       <c r="Z518" s="7"/>
     </row>
     <row r="519" spans="1:26" x14ac:dyDescent="0.2">
@@ -35895,6 +36024,39 @@
         <v>3118</v>
       </c>
       <c r="C519" s="16"/>
+      <c r="D519" s="7" t="s">
+        <v>3975</v>
+      </c>
+      <c r="E519" s="7" t="s">
+        <v>3975</v>
+      </c>
+      <c r="F519" s="7" t="s">
+        <v>4032</v>
+      </c>
+      <c r="G519" s="7" t="s">
+        <v>4026</v>
+      </c>
+      <c r="H519" s="7">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="I519" s="7">
+        <v>24.3</v>
+      </c>
+      <c r="J519" s="7">
+        <v>2008</v>
+      </c>
+      <c r="K519" s="7">
+        <v>2008</v>
+      </c>
+      <c r="L519" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="M519" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="N519" s="7">
+        <v>5</v>
+      </c>
       <c r="Z519" s="7"/>
     </row>
     <row r="520" spans="1:26" x14ac:dyDescent="0.2">
@@ -35902,6 +36064,39 @@
         <v>3119</v>
       </c>
       <c r="C520" s="16"/>
+      <c r="D520" s="7" t="s">
+        <v>3975</v>
+      </c>
+      <c r="E520" s="7" t="s">
+        <v>3975</v>
+      </c>
+      <c r="F520" s="7" t="s">
+        <v>4033</v>
+      </c>
+      <c r="G520" s="7" t="s">
+        <v>4025</v>
+      </c>
+      <c r="H520" s="7">
+        <v>24.3</v>
+      </c>
+      <c r="I520" s="7">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="J520" s="7">
+        <v>2008</v>
+      </c>
+      <c r="K520" s="7">
+        <v>2008</v>
+      </c>
+      <c r="L520" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="M520" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="N520" s="7">
+        <v>5</v>
+      </c>
       <c r="Z520" s="7"/>
     </row>
     <row r="521" spans="1:26" x14ac:dyDescent="0.2">
@@ -35909,6 +36104,39 @@
         <v>3120</v>
       </c>
       <c r="C521" s="16"/>
+      <c r="D521" s="7" t="s">
+        <v>3975</v>
+      </c>
+      <c r="E521" s="7" t="s">
+        <v>3975</v>
+      </c>
+      <c r="F521" s="7" t="s">
+        <v>4034</v>
+      </c>
+      <c r="G521" s="7" t="s">
+        <v>4024</v>
+      </c>
+      <c r="H521" s="7">
+        <v>24.3</v>
+      </c>
+      <c r="I521" s="7">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="J521" s="7">
+        <v>2008</v>
+      </c>
+      <c r="K521" s="7">
+        <v>2008</v>
+      </c>
+      <c r="L521" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="M521" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="N521" s="7">
+        <v>5</v>
+      </c>
       <c r="Z521" s="7"/>
     </row>
     <row r="522" spans="1:26" x14ac:dyDescent="0.2">
@@ -35916,6 +36144,39 @@
         <v>3121</v>
       </c>
       <c r="C522" s="16"/>
+      <c r="D522" s="7" t="s">
+        <v>3975</v>
+      </c>
+      <c r="E522" s="7" t="s">
+        <v>3975</v>
+      </c>
+      <c r="F522" s="7" t="s">
+        <v>4035</v>
+      </c>
+      <c r="G522" s="7" t="s">
+        <v>4022</v>
+      </c>
+      <c r="H522" s="7">
+        <v>24.3</v>
+      </c>
+      <c r="I522" s="7">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="J522" s="7">
+        <v>2008</v>
+      </c>
+      <c r="K522" s="7">
+        <v>2008</v>
+      </c>
+      <c r="L522" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="M522" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="N522" s="7">
+        <v>5</v>
+      </c>
       <c r="Z522" s="7"/>
     </row>
     <row r="523" spans="1:26" x14ac:dyDescent="0.2">
@@ -35923,6 +36184,39 @@
         <v>3122</v>
       </c>
       <c r="C523" s="16"/>
+      <c r="D523" s="7" t="s">
+        <v>3975</v>
+      </c>
+      <c r="E523" s="7" t="s">
+        <v>3975</v>
+      </c>
+      <c r="F523" s="7" t="s">
+        <v>4036</v>
+      </c>
+      <c r="G523" s="7" t="s">
+        <v>4023</v>
+      </c>
+      <c r="H523" s="7">
+        <v>24.3</v>
+      </c>
+      <c r="I523" s="7">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="J523" s="7">
+        <v>2008</v>
+      </c>
+      <c r="K523" s="7">
+        <v>2008</v>
+      </c>
+      <c r="L523" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="M523" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="N523" s="7">
+        <v>5</v>
+      </c>
       <c r="Z523" s="7"/>
     </row>
     <row r="524" spans="1:26" x14ac:dyDescent="0.2">
@@ -35930,6 +36224,39 @@
         <v>3123</v>
       </c>
       <c r="C524" s="16"/>
+      <c r="D524" s="7" t="s">
+        <v>3975</v>
+      </c>
+      <c r="E524" s="7" t="s">
+        <v>3975</v>
+      </c>
+      <c r="F524" s="7" t="s">
+        <v>4037</v>
+      </c>
+      <c r="G524" s="7" t="s">
+        <v>3975</v>
+      </c>
+      <c r="H524" s="7">
+        <v>24</v>
+      </c>
+      <c r="I524" s="7">
+        <v>27</v>
+      </c>
+      <c r="J524" s="7">
+        <v>2008</v>
+      </c>
+      <c r="K524" s="7">
+        <v>2008</v>
+      </c>
+      <c r="L524" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="M524" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="N524" s="7">
+        <v>5</v>
+      </c>
       <c r="Z524" s="7"/>
     </row>
     <row r="525" spans="1:26" x14ac:dyDescent="0.2">
@@ -35996,7 +36323,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.83203125" style="1" customWidth="1"/>
@@ -36753,6 +37080,23 @@
       </c>
       <c r="H31" s="7" t="s">
         <v>3289</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>3975</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>3975</v>
+      </c>
+      <c r="E32" s="1">
+        <v>2008</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>4029</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>4021</v>
       </c>
     </row>
   </sheetData>

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dlf/Developer/dotlineform/dotlineform-site/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA584F94-FCEF-9D42-9BED-5F277BDC97D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDB7C69-7C02-E24D-9301-08E831BBA5D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8717" uniqueCount="3198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8721" uniqueCount="3211">
   <si>
     <t>Works</t>
   </si>
@@ -9565,9 +9565,6 @@
     <t>add remaining works and series text</t>
   </si>
   <si>
-    <t>9 (A3)</t>
-  </si>
-  <si>
     <t>00373 - monoprint</t>
   </si>
   <si>
@@ -9632,6 +9629,48 @@
   </si>
   <si>
     <t>00383 - qrnt.jpg</t>
+  </si>
+  <si>
+    <t>00384 - glass</t>
+  </si>
+  <si>
+    <t>nerve 2</t>
+  </si>
+  <si>
+    <t>00525</t>
+  </si>
+  <si>
+    <t>form mobile</t>
+  </si>
+  <si>
+    <t>12 (A3)</t>
+  </si>
+  <si>
+    <t>00526</t>
+  </si>
+  <si>
+    <t>00527</t>
+  </si>
+  <si>
+    <t>00528</t>
+  </si>
+  <si>
+    <t>00529</t>
+  </si>
+  <si>
+    <t>00530</t>
+  </si>
+  <si>
+    <t>00531</t>
+  </si>
+  <si>
+    <t>00532</t>
+  </si>
+  <si>
+    <t>00533</t>
+  </si>
+  <si>
+    <t>00534</t>
   </si>
 </sst>
 </file>
@@ -10658,7 +10697,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z529"/>
+  <dimension ref="A1:Z535"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="7" customWidth="1"/>
@@ -32967,10 +33006,10 @@
       </c>
       <c r="C496" s="10"/>
       <c r="F496" s="7" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="G496" s="7" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="H496" s="7">
         <v>25</v>
@@ -32978,8 +33017,8 @@
       <c r="I496" s="7">
         <v>25</v>
       </c>
-      <c r="N496" s="7" t="s">
-        <v>3175</v>
+      <c r="N496" s="7">
+        <v>6</v>
       </c>
       <c r="Z496" s="7"/>
     </row>
@@ -32989,10 +33028,10 @@
       </c>
       <c r="C497" s="10"/>
       <c r="F497" s="7" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="G497" s="7" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="H497" s="7">
         <v>25</v>
@@ -33000,8 +33039,8 @@
       <c r="I497" s="7">
         <v>25</v>
       </c>
-      <c r="N497" s="7" t="s">
-        <v>3175</v>
+      <c r="N497" s="7">
+        <v>6</v>
       </c>
       <c r="Z497" s="7"/>
     </row>
@@ -33011,10 +33050,10 @@
       </c>
       <c r="C498" s="10"/>
       <c r="F498" s="7" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="G498" s="7" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="H498" s="7">
         <v>40.5</v>
@@ -33022,8 +33061,8 @@
       <c r="I498" s="7">
         <v>30.5</v>
       </c>
-      <c r="N498" s="7" t="s">
-        <v>3175</v>
+      <c r="N498" s="7">
+        <v>13</v>
       </c>
       <c r="Z498" s="7"/>
     </row>
@@ -33033,10 +33072,10 @@
       </c>
       <c r="C499" s="10"/>
       <c r="F499" s="7" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="G499" s="7" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="H499" s="7">
         <v>40.5</v>
@@ -33044,8 +33083,8 @@
       <c r="I499" s="7">
         <v>30.5</v>
       </c>
-      <c r="N499" s="7" t="s">
-        <v>3175</v>
+      <c r="N499" s="7">
+        <v>13</v>
       </c>
       <c r="Z499" s="7"/>
     </row>
@@ -33055,10 +33094,10 @@
       </c>
       <c r="C500" s="10"/>
       <c r="F500" s="7" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G500" s="7" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="H500" s="7">
         <v>29.4</v>
@@ -33066,8 +33105,8 @@
       <c r="I500" s="7">
         <v>21</v>
       </c>
-      <c r="N500" s="7" t="s">
-        <v>3175</v>
+      <c r="N500" s="7">
+        <v>13</v>
       </c>
       <c r="Z500" s="7"/>
     </row>
@@ -33077,10 +33116,10 @@
       </c>
       <c r="C501" s="10"/>
       <c r="F501" s="7" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G501" s="7" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="H501" s="7">
         <v>42</v>
@@ -33088,8 +33127,8 @@
       <c r="I501" s="7">
         <v>29.7</v>
       </c>
-      <c r="N501" s="7" t="s">
-        <v>3175</v>
+      <c r="N501" s="7">
+        <v>6</v>
       </c>
       <c r="Z501" s="7"/>
     </row>
@@ -33099,10 +33138,10 @@
       </c>
       <c r="C502" s="10"/>
       <c r="F502" s="7" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="G502" s="7" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="H502" s="7">
         <v>27.5</v>
@@ -33110,8 +33149,8 @@
       <c r="I502" s="7">
         <v>20</v>
       </c>
-      <c r="N502" s="7" t="s">
-        <v>3175</v>
+      <c r="N502" s="7">
+        <v>6</v>
       </c>
       <c r="Z502" s="7"/>
     </row>
@@ -33121,10 +33160,10 @@
       </c>
       <c r="C503" s="10"/>
       <c r="F503" s="7" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="G503" s="7" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="H503" s="7">
         <v>29.7</v>
@@ -33132,8 +33171,8 @@
       <c r="I503" s="7">
         <v>21</v>
       </c>
-      <c r="N503" s="7" t="s">
-        <v>3175</v>
+      <c r="N503" s="7">
+        <v>6</v>
       </c>
       <c r="Z503" s="7"/>
     </row>
@@ -33143,10 +33182,10 @@
       </c>
       <c r="C504" s="10"/>
       <c r="F504" s="7" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="G504" s="7" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="H504" s="7">
         <v>29.7</v>
@@ -33154,8 +33193,8 @@
       <c r="I504" s="7">
         <v>21</v>
       </c>
-      <c r="N504" s="7" t="s">
-        <v>3175</v>
+      <c r="N504" s="7">
+        <v>6</v>
       </c>
       <c r="Z504" s="7"/>
     </row>
@@ -33165,10 +33204,10 @@
       </c>
       <c r="C505" s="10"/>
       <c r="F505" s="7" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="G505" s="7" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="H505" s="7">
         <v>29.7</v>
@@ -33176,8 +33215,8 @@
       <c r="I505" s="7">
         <v>21</v>
       </c>
-      <c r="N505" s="7" t="s">
-        <v>3175</v>
+      <c r="N505" s="7">
+        <v>6</v>
       </c>
       <c r="Z505" s="7"/>
     </row>
@@ -33187,19 +33226,16 @@
       </c>
       <c r="C506" s="10"/>
       <c r="F506" s="7" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="G506" s="7" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="H506" s="7">
         <v>21</v>
       </c>
       <c r="I506" s="7">
         <v>29.7</v>
-      </c>
-      <c r="N506" s="7" t="s">
-        <v>3175</v>
       </c>
       <c r="Z506" s="7"/>
     </row>
@@ -33208,6 +33244,12 @@
         <v>3106</v>
       </c>
       <c r="C507" s="10"/>
+      <c r="F507" s="7" t="s">
+        <v>3197</v>
+      </c>
+      <c r="N507" s="7">
+        <v>13</v>
+      </c>
       <c r="Z507" s="7"/>
     </row>
     <row r="508" spans="1:26" x14ac:dyDescent="0.2">
@@ -33922,16 +33964,70 @@
       <c r="Z525" s="7"/>
     </row>
     <row r="526" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A526" s="16" t="s">
+        <v>3199</v>
+      </c>
+      <c r="F526" s="7" t="s">
+        <v>3198</v>
+      </c>
+      <c r="N526" s="7" t="s">
+        <v>3142</v>
+      </c>
       <c r="Z526" s="7"/>
     </row>
     <row r="527" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A527" s="16" t="s">
+        <v>3202</v>
+      </c>
+      <c r="F527" s="7" t="s">
+        <v>3200</v>
+      </c>
+      <c r="N527" s="7" t="s">
+        <v>3201</v>
+      </c>
       <c r="Z527" s="7"/>
     </row>
     <row r="528" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A528" s="16" t="s">
+        <v>3203</v>
+      </c>
       <c r="Z528" s="7"/>
     </row>
-    <row r="529" spans="26:26" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A529" s="16" t="s">
+        <v>3204</v>
+      </c>
       <c r="Z529" s="7"/>
+    </row>
+    <row r="530" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A530" s="16" t="s">
+        <v>3205</v>
+      </c>
+    </row>
+    <row r="531" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A531" s="16" t="s">
+        <v>3206</v>
+      </c>
+    </row>
+    <row r="532" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A532" s="16" t="s">
+        <v>3207</v>
+      </c>
+    </row>
+    <row r="533" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A533" s="16" t="s">
+        <v>3208</v>
+      </c>
+    </row>
+    <row r="534" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A534" s="16" t="s">
+        <v>3209</v>
+      </c>
+    </row>
+    <row r="535" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A535" s="16" t="s">
+        <v>3210</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z495">

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -36665,7 +36665,7 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>2025</v>

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -36495,7 +36495,7 @@
         </is>
       </c>
       <c r="D3" s="10" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>2025</v>
@@ -36555,7 +36555,7 @@
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>1998</v>
@@ -36588,7 +36588,7 @@
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>1998</v>
@@ -36616,7 +36616,7 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>1996</v>
@@ -36703,7 +36703,7 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>2021</v>
@@ -36734,7 +36734,7 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>2010</v>
@@ -36765,7 +36765,7 @@
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>2025</v>
@@ -36809,7 +36809,7 @@
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>2023</v>
@@ -36835,7 +36835,7 @@
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>2023</v>
@@ -36878,7 +36878,7 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>2025</v>
@@ -36928,7 +36928,7 @@
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>2011</v>
@@ -36954,7 +36954,7 @@
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>2020</v>
@@ -36987,7 +36987,7 @@
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>2023</v>
@@ -37018,7 +37018,7 @@
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>2023</v>
@@ -37049,7 +37049,7 @@
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>2016</v>
@@ -37080,7 +37080,7 @@
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>2010</v>
@@ -37131,7 +37131,7 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>2004</v>
@@ -37159,7 +37159,7 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>2009</v>
@@ -37197,7 +37197,7 @@
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>1994</v>
@@ -37223,7 +37223,7 @@
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>2013</v>
@@ -37266,7 +37266,7 @@
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>1993</v>
@@ -37299,7 +37299,7 @@
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>1995</v>
@@ -37387,7 +37387,7 @@
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>2001</v>

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -36489,7 +36489,7 @@
         </is>
       </c>
       <c r="D3" s="10" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>2025</v>
@@ -36549,7 +36549,7 @@
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>1998</v>
@@ -36582,7 +36582,7 @@
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>1998</v>
@@ -36610,7 +36610,7 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>1996</v>
@@ -36659,7 +36659,7 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>2025</v>
@@ -36697,7 +36697,7 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>2021</v>
@@ -36728,7 +36728,7 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>2010</v>
@@ -36759,7 +36759,7 @@
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>2025</v>
@@ -36803,7 +36803,7 @@
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>2023</v>
@@ -36829,7 +36829,7 @@
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>2023</v>
@@ -36872,7 +36872,7 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>2025</v>
@@ -36922,7 +36922,7 @@
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>2011</v>
@@ -36948,7 +36948,7 @@
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>2020</v>
@@ -36981,7 +36981,7 @@
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>2023</v>
@@ -37012,7 +37012,7 @@
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>2023</v>
@@ -37043,7 +37043,7 @@
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>2016</v>
@@ -37074,7 +37074,7 @@
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>2010</v>
@@ -37125,7 +37125,7 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>2004</v>
@@ -37153,7 +37153,7 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>2009</v>
@@ -37191,7 +37191,7 @@
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>1994</v>
@@ -37217,7 +37217,7 @@
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>2013</v>
@@ -37260,7 +37260,7 @@
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>1993</v>
@@ -37293,7 +37293,7 @@
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>1995</v>
@@ -37381,7 +37381,7 @@
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>46082</v>
+        <v>46086</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>2001</v>

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -37570,7 +37570,7 @@
         </is>
       </c>
       <c r="G2" s="9" t="n">
-        <v>46067</v>
+        <v>46086</v>
       </c>
       <c r="H2" s="5" t="n">
         <v>5906</v>
@@ -37612,7 +37612,7 @@
         </is>
       </c>
       <c r="G3" s="9" t="n">
-        <v>46067</v>
+        <v>46086</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>5906</v>
@@ -37654,7 +37654,7 @@
         </is>
       </c>
       <c r="G4" s="9" t="n">
-        <v>46067</v>
+        <v>46086</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>5906</v>
@@ -37696,7 +37696,7 @@
         </is>
       </c>
       <c r="G5" s="9" t="n">
-        <v>46067</v>
+        <v>46086</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>5906</v>
@@ -37738,7 +37738,7 @@
         </is>
       </c>
       <c r="G6" s="9" t="n">
-        <v>46067</v>
+        <v>46086</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>5906</v>
@@ -37780,7 +37780,7 @@
         </is>
       </c>
       <c r="G7" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>4724</v>
@@ -37821,7 +37821,7 @@
         </is>
       </c>
       <c r="G8" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>4724</v>
@@ -37862,7 +37862,7 @@
         </is>
       </c>
       <c r="G9" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>4724</v>
@@ -37903,7 +37903,7 @@
         </is>
       </c>
       <c r="G10" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>4724</v>
@@ -37944,7 +37944,7 @@
         </is>
       </c>
       <c r="G11" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>4724</v>
@@ -37985,7 +37985,7 @@
         </is>
       </c>
       <c r="G12" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>4724</v>
@@ -38026,7 +38026,7 @@
         </is>
       </c>
       <c r="G13" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H13" s="1" t="n">
         <v>4724</v>
@@ -38067,7 +38067,7 @@
         </is>
       </c>
       <c r="G14" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H14" s="1" t="n">
         <v>4724</v>
@@ -38108,7 +38108,7 @@
         </is>
       </c>
       <c r="G15" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>4724</v>
@@ -38149,7 +38149,7 @@
         </is>
       </c>
       <c r="G16" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H16" s="1" t="n">
         <v>4724</v>
@@ -38190,7 +38190,7 @@
         </is>
       </c>
       <c r="G17" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>4724</v>
@@ -38231,7 +38231,7 @@
         </is>
       </c>
       <c r="G18" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H18" s="1" t="n">
         <v>4724</v>
@@ -38272,7 +38272,7 @@
         </is>
       </c>
       <c r="G19" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H19" s="1" t="n">
         <v>4724</v>
@@ -38313,7 +38313,7 @@
         </is>
       </c>
       <c r="G20" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H20" s="1" t="n">
         <v>4724</v>
@@ -38354,7 +38354,7 @@
         </is>
       </c>
       <c r="G21" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H21" s="1" t="n">
         <v>4724</v>
@@ -38395,7 +38395,7 @@
         </is>
       </c>
       <c r="G22" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H22" s="1" t="n">
         <v>4724</v>
@@ -38436,7 +38436,7 @@
         </is>
       </c>
       <c r="G23" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H23" s="1" t="n">
         <v>4724</v>
@@ -38477,7 +38477,7 @@
         </is>
       </c>
       <c r="G24" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H24" s="1" t="n">
         <v>4724</v>
@@ -38518,7 +38518,7 @@
         </is>
       </c>
       <c r="G25" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>4724</v>
@@ -38559,7 +38559,7 @@
         </is>
       </c>
       <c r="G26" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H26" s="1" t="n">
         <v>4724</v>
@@ -38600,7 +38600,7 @@
         </is>
       </c>
       <c r="G27" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H27" s="1" t="n">
         <v>4724</v>
@@ -38641,7 +38641,7 @@
         </is>
       </c>
       <c r="G28" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H28" s="1" t="n">
         <v>4724</v>
@@ -38682,7 +38682,7 @@
         </is>
       </c>
       <c r="G29" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H29" s="1" t="n">
         <v>4724</v>
@@ -38723,7 +38723,7 @@
         </is>
       </c>
       <c r="G30" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H30" s="1" t="n">
         <v>4724</v>
@@ -38764,7 +38764,7 @@
         </is>
       </c>
       <c r="G31" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H31" s="1" t="n">
         <v>4724</v>
@@ -38805,7 +38805,7 @@
         </is>
       </c>
       <c r="G32" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H32" s="1" t="n">
         <v>4724</v>
@@ -38846,7 +38846,7 @@
         </is>
       </c>
       <c r="G33" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H33" s="1" t="n">
         <v>4724</v>
@@ -38887,7 +38887,7 @@
         </is>
       </c>
       <c r="G34" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H34" s="1" t="n">
         <v>4724</v>
@@ -38928,7 +38928,7 @@
         </is>
       </c>
       <c r="G35" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H35" s="1" t="n">
         <v>4724</v>
@@ -38969,7 +38969,7 @@
         </is>
       </c>
       <c r="G36" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H36" s="1" t="n">
         <v>4724</v>
@@ -39010,7 +39010,7 @@
         </is>
       </c>
       <c r="G37" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H37" s="1" t="n">
         <v>4724</v>
@@ -39051,7 +39051,7 @@
         </is>
       </c>
       <c r="G38" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H38" s="1" t="n">
         <v>4724</v>
@@ -39092,7 +39092,7 @@
         </is>
       </c>
       <c r="G39" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H39" s="1" t="n">
         <v>4724</v>
@@ -39133,7 +39133,7 @@
         </is>
       </c>
       <c r="G40" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H40" s="1" t="n">
         <v>4724</v>
@@ -39174,7 +39174,7 @@
         </is>
       </c>
       <c r="G41" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H41" s="1" t="n">
         <v>4724</v>
@@ -39215,7 +39215,7 @@
         </is>
       </c>
       <c r="G42" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H42" s="1" t="n">
         <v>4724</v>
@@ -39256,7 +39256,7 @@
         </is>
       </c>
       <c r="G43" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H43" s="1" t="n">
         <v>4724</v>
@@ -39297,7 +39297,7 @@
         </is>
       </c>
       <c r="G44" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H44" s="1" t="n">
         <v>4724</v>
@@ -39338,7 +39338,7 @@
         </is>
       </c>
       <c r="G45" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H45" s="1" t="n">
         <v>4724</v>
@@ -39379,7 +39379,7 @@
         </is>
       </c>
       <c r="G46" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H46" s="1" t="n">
         <v>4724</v>
@@ -39420,7 +39420,7 @@
         </is>
       </c>
       <c r="G47" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H47" s="1" t="n">
         <v>4724</v>
@@ -39461,7 +39461,7 @@
         </is>
       </c>
       <c r="G48" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H48" s="1" t="n">
         <v>4724</v>
@@ -39502,7 +39502,7 @@
         </is>
       </c>
       <c r="G49" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H49" s="1" t="n">
         <v>4724</v>
@@ -39543,7 +39543,7 @@
         </is>
       </c>
       <c r="G50" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H50" s="1" t="n">
         <v>4724</v>
@@ -39584,7 +39584,7 @@
         </is>
       </c>
       <c r="G51" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H51" s="1" t="n">
         <v>4724</v>
@@ -39625,7 +39625,7 @@
         </is>
       </c>
       <c r="G52" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H52" s="1" t="n">
         <v>4724</v>
@@ -39666,7 +39666,7 @@
         </is>
       </c>
       <c r="G53" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H53" s="1" t="n">
         <v>4724</v>
@@ -39707,7 +39707,7 @@
         </is>
       </c>
       <c r="G54" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H54" s="1" t="n">
         <v>4724</v>
@@ -39748,7 +39748,7 @@
         </is>
       </c>
       <c r="G55" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H55" s="1" t="n">
         <v>4724</v>
@@ -39789,7 +39789,7 @@
         </is>
       </c>
       <c r="G56" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H56" s="1" t="n">
         <v>4724</v>
@@ -39830,7 +39830,7 @@
         </is>
       </c>
       <c r="G57" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H57" s="1" t="n">
         <v>4724</v>
@@ -39871,7 +39871,7 @@
         </is>
       </c>
       <c r="G58" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H58" s="1" t="n">
         <v>4724</v>
@@ -39912,7 +39912,7 @@
         </is>
       </c>
       <c r="G59" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H59" s="1" t="n">
         <v>4724</v>
@@ -39953,7 +39953,7 @@
         </is>
       </c>
       <c r="G60" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H60" s="1" t="n">
         <v>4724</v>
@@ -39994,7 +39994,7 @@
         </is>
       </c>
       <c r="G61" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H61" s="1" t="n">
         <v>4724</v>
@@ -40035,7 +40035,7 @@
         </is>
       </c>
       <c r="G62" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H62" s="1" t="n">
         <v>4724</v>
@@ -40076,7 +40076,7 @@
         </is>
       </c>
       <c r="G63" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H63" s="1" t="n">
         <v>4724</v>
@@ -40117,7 +40117,7 @@
         </is>
       </c>
       <c r="G64" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H64" s="1" t="n">
         <v>4724</v>
@@ -40158,7 +40158,7 @@
         </is>
       </c>
       <c r="G65" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H65" s="1" t="n">
         <v>4724</v>
@@ -40199,7 +40199,7 @@
         </is>
       </c>
       <c r="G66" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H66" s="1" t="n">
         <v>4724</v>
@@ -40240,7 +40240,7 @@
         </is>
       </c>
       <c r="G67" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H67" s="1" t="n">
         <v>4724</v>
@@ -40281,7 +40281,7 @@
         </is>
       </c>
       <c r="G68" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H68" s="1" t="n">
         <v>4724</v>
@@ -40322,7 +40322,7 @@
         </is>
       </c>
       <c r="G69" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H69" s="1" t="n">
         <v>4724</v>
@@ -40363,7 +40363,7 @@
         </is>
       </c>
       <c r="G70" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H70" s="1" t="n">
         <v>4724</v>
@@ -40404,7 +40404,7 @@
         </is>
       </c>
       <c r="G71" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H71" s="1" t="n">
         <v>4724</v>
@@ -40445,7 +40445,7 @@
         </is>
       </c>
       <c r="G72" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H72" s="1" t="n">
         <v>4724</v>
@@ -40486,7 +40486,7 @@
         </is>
       </c>
       <c r="G73" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H73" s="1" t="n">
         <v>4724</v>
@@ -40527,7 +40527,7 @@
         </is>
       </c>
       <c r="G74" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H74" s="1" t="n">
         <v>4724</v>
@@ -40568,7 +40568,7 @@
         </is>
       </c>
       <c r="G75" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H75" s="1" t="n">
         <v>4724</v>
@@ -40609,7 +40609,7 @@
         </is>
       </c>
       <c r="G76" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H76" s="1" t="n">
         <v>4724</v>
@@ -40650,7 +40650,7 @@
         </is>
       </c>
       <c r="G77" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H77" s="1" t="n">
         <v>4724</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="G78" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H78" s="1" t="n">
         <v>4724</v>
@@ -40732,7 +40732,7 @@
         </is>
       </c>
       <c r="G79" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H79" s="1" t="n">
         <v>4724</v>
@@ -40773,7 +40773,7 @@
         </is>
       </c>
       <c r="G80" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H80" s="1" t="n">
         <v>4724</v>
@@ -40814,7 +40814,7 @@
         </is>
       </c>
       <c r="G81" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H81" s="1" t="n">
         <v>4724</v>
@@ -40855,7 +40855,7 @@
         </is>
       </c>
       <c r="G82" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H82" s="1" t="n">
         <v>4724</v>
@@ -40896,7 +40896,7 @@
         </is>
       </c>
       <c r="G83" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H83" s="1" t="n">
         <v>4724</v>
@@ -40937,7 +40937,7 @@
         </is>
       </c>
       <c r="G84" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H84" s="1" t="n">
         <v>4724</v>
@@ -40978,7 +40978,7 @@
         </is>
       </c>
       <c r="G85" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H85" s="1" t="n">
         <v>4724</v>
@@ -41019,7 +41019,7 @@
         </is>
       </c>
       <c r="G86" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H86" s="1" t="n">
         <v>4724</v>
@@ -41060,7 +41060,7 @@
         </is>
       </c>
       <c r="G87" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H87" s="1" t="n">
         <v>4724</v>
@@ -41101,7 +41101,7 @@
         </is>
       </c>
       <c r="G88" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H88" s="1" t="n">
         <v>4724</v>
@@ -41142,7 +41142,7 @@
         </is>
       </c>
       <c r="G89" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H89" s="1" t="n">
         <v>4724</v>
@@ -41183,7 +41183,7 @@
         </is>
       </c>
       <c r="G90" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H90" s="1" t="n">
         <v>4724</v>
@@ -41224,7 +41224,7 @@
         </is>
       </c>
       <c r="G91" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H91" s="1" t="n">
         <v>4724</v>
@@ -41265,7 +41265,7 @@
         </is>
       </c>
       <c r="G92" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H92" s="1" t="n">
         <v>4724</v>
@@ -41306,7 +41306,7 @@
         </is>
       </c>
       <c r="G93" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H93" s="1" t="n">
         <v>4724</v>
@@ -41347,7 +41347,7 @@
         </is>
       </c>
       <c r="G94" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H94" s="1" t="n">
         <v>4724</v>
@@ -41388,7 +41388,7 @@
         </is>
       </c>
       <c r="G95" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H95" s="1" t="n">
         <v>4724</v>
@@ -41429,7 +41429,7 @@
         </is>
       </c>
       <c r="G96" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H96" s="1" t="n">
         <v>4724</v>
@@ -41470,7 +41470,7 @@
         </is>
       </c>
       <c r="G97" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H97" s="1" t="n">
         <v>4724</v>
@@ -41511,7 +41511,7 @@
         </is>
       </c>
       <c r="G98" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H98" s="1" t="n">
         <v>4724</v>
@@ -41552,7 +41552,7 @@
         </is>
       </c>
       <c r="G99" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H99" s="1" t="n">
         <v>4724</v>
@@ -41593,7 +41593,7 @@
         </is>
       </c>
       <c r="G100" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H100" s="1" t="n">
         <v>4724</v>
@@ -41634,7 +41634,7 @@
         </is>
       </c>
       <c r="G101" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H101" s="1" t="n">
         <v>4724</v>
@@ -41675,7 +41675,7 @@
         </is>
       </c>
       <c r="G102" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H102" s="1" t="n">
         <v>4724</v>
@@ -41716,7 +41716,7 @@
         </is>
       </c>
       <c r="G103" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H103" s="1" t="n">
         <v>4724</v>
@@ -41757,7 +41757,7 @@
         </is>
       </c>
       <c r="G104" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H104" s="1" t="n">
         <v>4724</v>
@@ -41798,7 +41798,7 @@
         </is>
       </c>
       <c r="G105" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H105" s="1" t="n">
         <v>4724</v>
@@ -41839,7 +41839,7 @@
         </is>
       </c>
       <c r="G106" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H106" s="1" t="n">
         <v>4724</v>
@@ -41880,7 +41880,7 @@
         </is>
       </c>
       <c r="G107" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H107" s="1" t="n">
         <v>4724</v>
@@ -41921,7 +41921,7 @@
         </is>
       </c>
       <c r="G108" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H108" s="1" t="n">
         <v>4724</v>
@@ -41962,7 +41962,7 @@
         </is>
       </c>
       <c r="G109" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H109" s="1" t="n">
         <v>4724</v>
@@ -42003,7 +42003,7 @@
         </is>
       </c>
       <c r="G110" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H110" s="1" t="n">
         <v>4724</v>
@@ -42044,7 +42044,7 @@
         </is>
       </c>
       <c r="G111" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H111" s="1" t="n">
         <v>4724</v>
@@ -42085,7 +42085,7 @@
         </is>
       </c>
       <c r="G112" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H112" s="1" t="n">
         <v>4724</v>
@@ -42126,7 +42126,7 @@
         </is>
       </c>
       <c r="G113" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H113" s="1" t="n">
         <v>4724</v>
@@ -42167,7 +42167,7 @@
         </is>
       </c>
       <c r="G114" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H114" s="1" t="n">
         <v>4724</v>
@@ -42208,7 +42208,7 @@
         </is>
       </c>
       <c r="G115" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H115" s="1" t="n">
         <v>4724</v>
@@ -42249,7 +42249,7 @@
         </is>
       </c>
       <c r="G116" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H116" s="1" t="n">
         <v>4724</v>
@@ -42290,7 +42290,7 @@
         </is>
       </c>
       <c r="G117" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H117" s="1" t="n">
         <v>4724</v>
@@ -42331,7 +42331,7 @@
         </is>
       </c>
       <c r="G118" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H118" s="1" t="n">
         <v>4724</v>
@@ -42372,7 +42372,7 @@
         </is>
       </c>
       <c r="G119" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H119" s="1" t="n">
         <v>4724</v>
@@ -42413,7 +42413,7 @@
         </is>
       </c>
       <c r="G120" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H120" s="1" t="n">
         <v>4724</v>
@@ -42454,7 +42454,7 @@
         </is>
       </c>
       <c r="G121" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H121" s="1" t="n">
         <v>4724</v>
@@ -42495,7 +42495,7 @@
         </is>
       </c>
       <c r="G122" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H122" s="1" t="n">
         <v>4724</v>
@@ -42536,7 +42536,7 @@
         </is>
       </c>
       <c r="G123" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H123" s="1" t="n">
         <v>4724</v>
@@ -42577,7 +42577,7 @@
         </is>
       </c>
       <c r="G124" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H124" s="1" t="n">
         <v>4724</v>
@@ -42618,7 +42618,7 @@
         </is>
       </c>
       <c r="G125" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H125" s="1" t="n">
         <v>4724</v>
@@ -42659,7 +42659,7 @@
         </is>
       </c>
       <c r="G126" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H126" s="1" t="n">
         <v>4724</v>
@@ -42700,7 +42700,7 @@
         </is>
       </c>
       <c r="G127" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H127" s="1" t="n">
         <v>4724</v>
@@ -42741,7 +42741,7 @@
         </is>
       </c>
       <c r="G128" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H128" s="1" t="n">
         <v>4724</v>
@@ -42782,7 +42782,7 @@
         </is>
       </c>
       <c r="G129" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H129" s="1" t="n">
         <v>4724</v>
@@ -42823,7 +42823,7 @@
         </is>
       </c>
       <c r="G130" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H130" s="1" t="n">
         <v>4724</v>
@@ -42864,7 +42864,7 @@
         </is>
       </c>
       <c r="G131" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H131" s="1" t="n">
         <v>4724</v>
@@ -42905,7 +42905,7 @@
         </is>
       </c>
       <c r="G132" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H132" s="1" t="n">
         <v>4724</v>
@@ -42946,7 +42946,7 @@
         </is>
       </c>
       <c r="G133" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H133" s="1" t="n">
         <v>4724</v>
@@ -42987,7 +42987,7 @@
         </is>
       </c>
       <c r="G134" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H134" s="1" t="n">
         <v>4724</v>
@@ -43028,7 +43028,7 @@
         </is>
       </c>
       <c r="G135" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H135" s="1" t="n">
         <v>4724</v>
@@ -43069,7 +43069,7 @@
         </is>
       </c>
       <c r="G136" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H136" s="1" t="n">
         <v>4724</v>
@@ -43110,7 +43110,7 @@
         </is>
       </c>
       <c r="G137" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H137" s="1" t="n">
         <v>4724</v>
@@ -43151,7 +43151,7 @@
         </is>
       </c>
       <c r="G138" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H138" s="1" t="n">
         <v>4724</v>
@@ -43192,7 +43192,7 @@
         </is>
       </c>
       <c r="G139" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H139" s="1" t="n">
         <v>4724</v>
@@ -43233,7 +43233,7 @@
         </is>
       </c>
       <c r="G140" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H140" s="1" t="n">
         <v>4724</v>
@@ -43274,7 +43274,7 @@
         </is>
       </c>
       <c r="G141" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H141" s="1" t="n">
         <v>4724</v>
@@ -43315,7 +43315,7 @@
         </is>
       </c>
       <c r="G142" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H142" s="1" t="n">
         <v>4724</v>
@@ -43356,7 +43356,7 @@
         </is>
       </c>
       <c r="G143" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H143" s="1" t="n">
         <v>4724</v>
@@ -43397,7 +43397,7 @@
         </is>
       </c>
       <c r="G144" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H144" s="1" t="n">
         <v>4724</v>
@@ -43438,7 +43438,7 @@
         </is>
       </c>
       <c r="G145" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H145" s="1" t="n">
         <v>4724</v>
@@ -43479,7 +43479,7 @@
         </is>
       </c>
       <c r="G146" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H146" s="1" t="n">
         <v>4724</v>
@@ -43520,7 +43520,7 @@
         </is>
       </c>
       <c r="G147" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H147" s="1" t="n">
         <v>4724</v>
@@ -43561,7 +43561,7 @@
         </is>
       </c>
       <c r="G148" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H148" s="1" t="n">
         <v>4724</v>
@@ -43602,7 +43602,7 @@
         </is>
       </c>
       <c r="G149" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H149" s="1" t="n">
         <v>4724</v>
@@ -43643,7 +43643,7 @@
         </is>
       </c>
       <c r="G150" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H150" s="1" t="n">
         <v>4724</v>
@@ -43684,7 +43684,7 @@
         </is>
       </c>
       <c r="G151" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H151" s="1" t="n">
         <v>4724</v>
@@ -43725,7 +43725,7 @@
         </is>
       </c>
       <c r="G152" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H152" s="1" t="n">
         <v>4724</v>
@@ -43766,7 +43766,7 @@
         </is>
       </c>
       <c r="G153" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H153" s="1" t="n">
         <v>4724</v>
@@ -43807,7 +43807,7 @@
         </is>
       </c>
       <c r="G154" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H154" s="1" t="n">
         <v>4724</v>
@@ -43848,7 +43848,7 @@
         </is>
       </c>
       <c r="G155" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H155" s="1" t="n">
         <v>4724</v>
@@ -43889,7 +43889,7 @@
         </is>
       </c>
       <c r="G156" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H156" s="1" t="n">
         <v>4724</v>
@@ -43930,7 +43930,7 @@
         </is>
       </c>
       <c r="G157" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H157" s="1" t="n">
         <v>4724</v>
@@ -43971,7 +43971,7 @@
         </is>
       </c>
       <c r="G158" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H158" s="1" t="n">
         <v>4724</v>
@@ -44012,7 +44012,7 @@
         </is>
       </c>
       <c r="G159" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H159" s="1" t="n">
         <v>4724</v>
@@ -44053,7 +44053,7 @@
         </is>
       </c>
       <c r="G160" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H160" s="1" t="n">
         <v>4724</v>
@@ -44094,7 +44094,7 @@
         </is>
       </c>
       <c r="G161" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H161" s="1" t="n">
         <v>4724</v>
@@ -44135,7 +44135,7 @@
         </is>
       </c>
       <c r="G162" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H162" s="1" t="n">
         <v>4724</v>
@@ -44176,7 +44176,7 @@
         </is>
       </c>
       <c r="G163" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H163" s="1" t="n">
         <v>4724</v>
@@ -44217,7 +44217,7 @@
         </is>
       </c>
       <c r="G164" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H164" s="1" t="n">
         <v>4724</v>
@@ -44258,7 +44258,7 @@
         </is>
       </c>
       <c r="G165" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H165" s="1" t="n">
         <v>4724</v>
@@ -44299,7 +44299,7 @@
         </is>
       </c>
       <c r="G166" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H166" s="1" t="n">
         <v>4724</v>
@@ -44340,7 +44340,7 @@
         </is>
       </c>
       <c r="G167" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H167" s="1" t="n">
         <v>4724</v>
@@ -44381,7 +44381,7 @@
         </is>
       </c>
       <c r="G168" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H168" s="1" t="n">
         <v>4724</v>
@@ -44422,7 +44422,7 @@
         </is>
       </c>
       <c r="G169" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H169" s="1" t="n">
         <v>4724</v>
@@ -44463,7 +44463,7 @@
         </is>
       </c>
       <c r="G170" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H170" s="1" t="n">
         <v>4724</v>
@@ -44504,7 +44504,7 @@
         </is>
       </c>
       <c r="G171" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H171" s="1" t="n">
         <v>4724</v>
@@ -44545,7 +44545,7 @@
         </is>
       </c>
       <c r="G172" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H172" s="1" t="n">
         <v>4724</v>
@@ -44586,7 +44586,7 @@
         </is>
       </c>
       <c r="G173" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H173" s="1" t="n">
         <v>4724</v>
@@ -44627,7 +44627,7 @@
         </is>
       </c>
       <c r="G174" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H174" s="1" t="n">
         <v>4724</v>
@@ -44668,7 +44668,7 @@
         </is>
       </c>
       <c r="G175" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H175" s="1" t="n">
         <v>4724</v>
@@ -44709,7 +44709,7 @@
         </is>
       </c>
       <c r="G176" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H176" s="1" t="n">
         <v>4724</v>
@@ -44750,7 +44750,7 @@
         </is>
       </c>
       <c r="G177" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H177" s="1" t="n">
         <v>4724</v>
@@ -44791,7 +44791,7 @@
         </is>
       </c>
       <c r="G178" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H178" s="1" t="n">
         <v>4724</v>
@@ -44832,7 +44832,7 @@
         </is>
       </c>
       <c r="G179" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H179" s="1" t="n">
         <v>4724</v>
@@ -44873,7 +44873,7 @@
         </is>
       </c>
       <c r="G180" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H180" s="1" t="n">
         <v>4724</v>
@@ -44914,7 +44914,7 @@
         </is>
       </c>
       <c r="G181" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H181" s="1" t="n">
         <v>4724</v>
@@ -44955,7 +44955,7 @@
         </is>
       </c>
       <c r="G182" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H182" s="1" t="n">
         <v>4724</v>
@@ -44996,7 +44996,7 @@
         </is>
       </c>
       <c r="G183" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H183" s="1" t="n">
         <v>4724</v>
@@ -45037,7 +45037,7 @@
         </is>
       </c>
       <c r="G184" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H184" s="1" t="n">
         <v>4724</v>
@@ -45078,7 +45078,7 @@
         </is>
       </c>
       <c r="G185" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H185" s="1" t="n">
         <v>4724</v>
@@ -45119,7 +45119,7 @@
         </is>
       </c>
       <c r="G186" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H186" s="1" t="n">
         <v>4724</v>
@@ -45160,7 +45160,7 @@
         </is>
       </c>
       <c r="G187" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H187" s="1" t="n">
         <v>4724</v>
@@ -45201,7 +45201,7 @@
         </is>
       </c>
       <c r="G188" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H188" s="1" t="n">
         <v>4724</v>
@@ -45242,7 +45242,7 @@
         </is>
       </c>
       <c r="G189" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H189" s="1" t="n">
         <v>4724</v>
@@ -45283,7 +45283,7 @@
         </is>
       </c>
       <c r="G190" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H190" s="1" t="n">
         <v>4724</v>
@@ -45324,7 +45324,7 @@
         </is>
       </c>
       <c r="G191" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H191" s="1" t="n">
         <v>4724</v>
@@ -45365,7 +45365,7 @@
         </is>
       </c>
       <c r="G192" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H192" s="1" t="n">
         <v>4724</v>
@@ -45406,7 +45406,7 @@
         </is>
       </c>
       <c r="G193" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H193" s="1" t="n">
         <v>4724</v>
@@ -45447,7 +45447,7 @@
         </is>
       </c>
       <c r="G194" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H194" s="1" t="n">
         <v>4724</v>
@@ -45488,7 +45488,7 @@
         </is>
       </c>
       <c r="G195" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H195" s="1" t="n">
         <v>4724</v>
@@ -45529,7 +45529,7 @@
         </is>
       </c>
       <c r="G196" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H196" s="1" t="n">
         <v>4724</v>
@@ -45570,7 +45570,7 @@
         </is>
       </c>
       <c r="G197" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H197" s="1" t="n">
         <v>4724</v>
@@ -45611,7 +45611,7 @@
         </is>
       </c>
       <c r="G198" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H198" s="1" t="n">
         <v>4724</v>
@@ -45652,7 +45652,7 @@
         </is>
       </c>
       <c r="G199" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H199" s="1" t="n">
         <v>4724</v>
@@ -45693,7 +45693,7 @@
         </is>
       </c>
       <c r="G200" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H200" s="1" t="n">
         <v>4724</v>
@@ -45734,7 +45734,7 @@
         </is>
       </c>
       <c r="G201" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H201" s="1" t="n">
         <v>4724</v>
@@ -45775,7 +45775,7 @@
         </is>
       </c>
       <c r="G202" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H202" s="1" t="n">
         <v>4724</v>
@@ -45816,7 +45816,7 @@
         </is>
       </c>
       <c r="G203" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H203" s="1" t="n">
         <v>4724</v>
@@ -45857,7 +45857,7 @@
         </is>
       </c>
       <c r="G204" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H204" s="1" t="n">
         <v>4724</v>
@@ -45898,7 +45898,7 @@
         </is>
       </c>
       <c r="G205" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H205" s="1" t="n">
         <v>4724</v>
@@ -45939,7 +45939,7 @@
         </is>
       </c>
       <c r="G206" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H206" s="1" t="n">
         <v>4724</v>
@@ -45980,7 +45980,7 @@
         </is>
       </c>
       <c r="G207" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H207" s="1" t="n">
         <v>4724</v>
@@ -46021,7 +46021,7 @@
         </is>
       </c>
       <c r="G208" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H208" s="1" t="n">
         <v>4724</v>
@@ -46062,7 +46062,7 @@
         </is>
       </c>
       <c r="G209" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H209" s="1" t="n">
         <v>4724</v>
@@ -46103,7 +46103,7 @@
         </is>
       </c>
       <c r="G210" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H210" s="1" t="n">
         <v>4724</v>
@@ -46144,7 +46144,7 @@
         </is>
       </c>
       <c r="G211" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H211" s="1" t="n">
         <v>4724</v>
@@ -46185,7 +46185,7 @@
         </is>
       </c>
       <c r="G212" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H212" s="1" t="n">
         <v>4724</v>
@@ -46226,7 +46226,7 @@
         </is>
       </c>
       <c r="G213" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H213" s="1" t="n">
         <v>4724</v>
@@ -46267,7 +46267,7 @@
         </is>
       </c>
       <c r="G214" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H214" s="1" t="n">
         <v>4724</v>
@@ -46308,7 +46308,7 @@
         </is>
       </c>
       <c r="G215" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H215" s="1" t="n">
         <v>4724</v>
@@ -46349,7 +46349,7 @@
         </is>
       </c>
       <c r="G216" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H216" s="1" t="n">
         <v>4724</v>
@@ -46390,7 +46390,7 @@
         </is>
       </c>
       <c r="G217" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H217" s="1" t="n">
         <v>4724</v>
@@ -46431,7 +46431,7 @@
         </is>
       </c>
       <c r="G218" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H218" s="1" t="n">
         <v>4724</v>
@@ -46472,7 +46472,7 @@
         </is>
       </c>
       <c r="G219" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H219" s="1" t="n">
         <v>4724</v>
@@ -46513,7 +46513,7 @@
         </is>
       </c>
       <c r="G220" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H220" s="1" t="n">
         <v>4724</v>
@@ -46554,7 +46554,7 @@
         </is>
       </c>
       <c r="G221" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H221" s="1" t="n">
         <v>4724</v>
@@ -46595,7 +46595,7 @@
         </is>
       </c>
       <c r="G222" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H222" s="1" t="n">
         <v>4724</v>
@@ -46636,7 +46636,7 @@
         </is>
       </c>
       <c r="G223" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H223" s="1" t="n">
         <v>4724</v>
@@ -46677,7 +46677,7 @@
         </is>
       </c>
       <c r="G224" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H224" s="1" t="n">
         <v>4724</v>
@@ -46718,7 +46718,7 @@
         </is>
       </c>
       <c r="G225" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H225" s="1" t="n">
         <v>4724</v>
@@ -46759,7 +46759,7 @@
         </is>
       </c>
       <c r="G226" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H226" s="1" t="n">
         <v>4724</v>
@@ -46800,7 +46800,7 @@
         </is>
       </c>
       <c r="G227" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H227" s="1" t="n">
         <v>4724</v>
@@ -46841,7 +46841,7 @@
         </is>
       </c>
       <c r="G228" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H228" s="1" t="n">
         <v>4724</v>
@@ -46882,7 +46882,7 @@
         </is>
       </c>
       <c r="G229" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H229" s="1" t="n">
         <v>4724</v>
@@ -46923,7 +46923,7 @@
         </is>
       </c>
       <c r="G230" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H230" s="1" t="n">
         <v>4724</v>
@@ -46964,7 +46964,7 @@
         </is>
       </c>
       <c r="G231" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H231" s="1" t="n">
         <v>4724</v>
@@ -47005,7 +47005,7 @@
         </is>
       </c>
       <c r="G232" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H232" s="1" t="n">
         <v>4724</v>
@@ -47046,7 +47046,7 @@
         </is>
       </c>
       <c r="G233" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H233" s="1" t="n">
         <v>4724</v>
@@ -47087,7 +47087,7 @@
         </is>
       </c>
       <c r="G234" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H234" s="1" t="n">
         <v>4724</v>
@@ -47128,7 +47128,7 @@
         </is>
       </c>
       <c r="G235" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H235" s="1" t="n">
         <v>4724</v>
@@ -47169,7 +47169,7 @@
         </is>
       </c>
       <c r="G236" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H236" s="1" t="n">
         <v>4724</v>
@@ -47210,7 +47210,7 @@
         </is>
       </c>
       <c r="G237" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H237" s="1" t="n">
         <v>4724</v>
@@ -47251,7 +47251,7 @@
         </is>
       </c>
       <c r="G238" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H238" s="1" t="n">
         <v>4724</v>
@@ -47292,7 +47292,7 @@
         </is>
       </c>
       <c r="G239" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H239" s="1" t="n">
         <v>4724</v>
@@ -47333,7 +47333,7 @@
         </is>
       </c>
       <c r="G240" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H240" s="1" t="n">
         <v>4724</v>
@@ -47374,7 +47374,7 @@
         </is>
       </c>
       <c r="G241" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H241" s="1" t="n">
         <v>4724</v>
@@ -47415,7 +47415,7 @@
         </is>
       </c>
       <c r="G242" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H242" s="1" t="n">
         <v>4724</v>
@@ -47456,7 +47456,7 @@
         </is>
       </c>
       <c r="G243" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H243" s="1" t="n">
         <v>4724</v>
@@ -47497,7 +47497,7 @@
         </is>
       </c>
       <c r="G244" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H244" s="1" t="n">
         <v>4724</v>
@@ -47538,7 +47538,7 @@
         </is>
       </c>
       <c r="G245" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H245" s="1" t="n">
         <v>4724</v>
@@ -47579,7 +47579,7 @@
         </is>
       </c>
       <c r="G246" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H246" s="1" t="n">
         <v>4724</v>
@@ -47620,7 +47620,7 @@
         </is>
       </c>
       <c r="G247" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H247" s="1" t="n">
         <v>4724</v>
@@ -47661,7 +47661,7 @@
         </is>
       </c>
       <c r="G248" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H248" s="1" t="n">
         <v>4724</v>
@@ -47702,7 +47702,7 @@
         </is>
       </c>
       <c r="G249" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H249" s="1" t="n">
         <v>4724</v>
@@ -47743,7 +47743,7 @@
         </is>
       </c>
       <c r="G250" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H250" s="1" t="n">
         <v>4724</v>
@@ -47784,7 +47784,7 @@
         </is>
       </c>
       <c r="G251" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H251" s="1" t="n">
         <v>4724</v>
@@ -47825,7 +47825,7 @@
         </is>
       </c>
       <c r="G252" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H252" s="1" t="n">
         <v>4724</v>
@@ -47866,7 +47866,7 @@
         </is>
       </c>
       <c r="G253" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H253" s="1" t="n">
         <v>4724</v>
@@ -47907,7 +47907,7 @@
         </is>
       </c>
       <c r="G254" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H254" s="1" t="n">
         <v>4724</v>
@@ -47948,7 +47948,7 @@
         </is>
       </c>
       <c r="G255" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H255" s="1" t="n">
         <v>4724</v>
@@ -47989,7 +47989,7 @@
         </is>
       </c>
       <c r="G256" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H256" s="1" t="n">
         <v>4724</v>
@@ -48030,7 +48030,7 @@
         </is>
       </c>
       <c r="G257" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H257" s="1" t="n">
         <v>4724</v>
@@ -48071,7 +48071,7 @@
         </is>
       </c>
       <c r="G258" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H258" s="1" t="n">
         <v>4724</v>
@@ -48112,7 +48112,7 @@
         </is>
       </c>
       <c r="G259" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H259" s="1" t="n">
         <v>4724</v>
@@ -48153,7 +48153,7 @@
         </is>
       </c>
       <c r="G260" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H260" s="1" t="n">
         <v>4724</v>
@@ -48194,7 +48194,7 @@
         </is>
       </c>
       <c r="G261" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H261" s="1" t="n">
         <v>4724</v>
@@ -48235,7 +48235,7 @@
         </is>
       </c>
       <c r="G262" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H262" s="1" t="n">
         <v>4724</v>
@@ -48276,7 +48276,7 @@
         </is>
       </c>
       <c r="G263" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H263" s="1" t="n">
         <v>9000</v>
@@ -48317,7 +48317,7 @@
         </is>
       </c>
       <c r="G264" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H264" s="1" t="n">
         <v>9000</v>
@@ -48358,7 +48358,7 @@
         </is>
       </c>
       <c r="G265" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H265" s="1" t="n">
         <v>9000</v>
@@ -48399,7 +48399,7 @@
         </is>
       </c>
       <c r="G266" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H266" s="1" t="n">
         <v>9000</v>
@@ -48440,7 +48440,7 @@
         </is>
       </c>
       <c r="G267" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H267" s="1" t="n">
         <v>3543</v>
@@ -48481,7 +48481,7 @@
         </is>
       </c>
       <c r="G268" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H268" s="1" t="n">
         <v>3543</v>
@@ -48522,7 +48522,7 @@
         </is>
       </c>
       <c r="G269" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H269" s="1" t="n">
         <v>3543</v>
@@ -48563,7 +48563,7 @@
         </is>
       </c>
       <c r="G270" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H270" s="1" t="n">
         <v>3543</v>
@@ -48604,7 +48604,7 @@
         </is>
       </c>
       <c r="G271" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H271" s="1" t="n">
         <v>3543</v>
@@ -48645,7 +48645,7 @@
         </is>
       </c>
       <c r="G272" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H272" s="1" t="n">
         <v>3543</v>
@@ -48686,7 +48686,7 @@
         </is>
       </c>
       <c r="G273" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H273" s="1" t="n">
         <v>3543</v>
@@ -48727,7 +48727,7 @@
         </is>
       </c>
       <c r="G274" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H274" s="1" t="n">
         <v>3543</v>
@@ -48768,7 +48768,7 @@
         </is>
       </c>
       <c r="G275" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H275" s="1" t="n">
         <v>3543</v>
@@ -48809,7 +48809,7 @@
         </is>
       </c>
       <c r="G276" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H276" s="1" t="n">
         <v>3543</v>
@@ -48850,7 +48850,7 @@
         </is>
       </c>
       <c r="G277" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H277" s="1" t="n">
         <v>3543</v>
@@ -48891,7 +48891,7 @@
         </is>
       </c>
       <c r="G278" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H278" s="1" t="n">
         <v>3543</v>
@@ -48932,7 +48932,7 @@
         </is>
       </c>
       <c r="G279" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H279" s="1" t="n">
         <v>3543</v>
@@ -48973,7 +48973,7 @@
         </is>
       </c>
       <c r="G280" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H280" s="1" t="n">
         <v>3543</v>
@@ -49014,7 +49014,7 @@
         </is>
       </c>
       <c r="G281" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H281" s="1" t="n">
         <v>3543</v>
@@ -49055,7 +49055,7 @@
         </is>
       </c>
       <c r="G282" s="10" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="H282" s="1" t="n">
         <v>3543</v>
@@ -49096,7 +49096,7 @@
         </is>
       </c>
       <c r="G283" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H283" s="1" t="n">
         <v>2169</v>
@@ -49137,7 +49137,7 @@
         </is>
       </c>
       <c r="G284" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H284" s="1" t="n">
         <v>5315</v>
@@ -49178,7 +49178,7 @@
         </is>
       </c>
       <c r="G285" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H285" s="1" t="n">
         <v>7087</v>
@@ -49219,7 +49219,7 @@
         </is>
       </c>
       <c r="G286" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H286" s="1" t="n">
         <v>7087</v>
@@ -49260,7 +49260,7 @@
         </is>
       </c>
       <c r="G287" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H287" s="1" t="n">
         <v>1400</v>
@@ -49301,7 +49301,7 @@
         </is>
       </c>
       <c r="G288" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H288" s="1" t="n">
         <v>7087</v>
@@ -49342,7 +49342,7 @@
         </is>
       </c>
       <c r="G289" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H289" s="1" t="n">
         <v>1400</v>
@@ -49383,7 +49383,7 @@
         </is>
       </c>
       <c r="G290" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H290" t="n">
         <v>8268</v>
@@ -49424,7 +49424,7 @@
         </is>
       </c>
       <c r="G291" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H291" t="n">
         <v>8268</v>
@@ -49465,7 +49465,7 @@
         </is>
       </c>
       <c r="G292" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H292" t="n">
         <v>8268</v>
@@ -49506,7 +49506,7 @@
         </is>
       </c>
       <c r="G293" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H293" t="n">
         <v>4000</v>
@@ -49547,7 +49547,7 @@
         </is>
       </c>
       <c r="G294" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H294" t="n">
         <v>2362</v>
@@ -49588,7 +49588,7 @@
         </is>
       </c>
       <c r="G295" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H295" t="n">
         <v>2362</v>
@@ -49629,7 +49629,7 @@
         </is>
       </c>
       <c r="G296" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H296" t="n">
         <v>2362</v>
@@ -49670,7 +49670,7 @@
         </is>
       </c>
       <c r="G297" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H297" t="n">
         <v>2362</v>
@@ -49711,7 +49711,7 @@
         </is>
       </c>
       <c r="G298" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H298" t="n">
         <v>2362</v>
@@ -49752,7 +49752,7 @@
         </is>
       </c>
       <c r="G299" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H299" t="n">
         <v>2362</v>
@@ -49793,7 +49793,7 @@
         </is>
       </c>
       <c r="G300" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H300" t="n">
         <v>2362</v>
@@ -49834,7 +49834,7 @@
         </is>
       </c>
       <c r="G301" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H301" t="n">
         <v>2362</v>
@@ -49875,7 +49875,7 @@
         </is>
       </c>
       <c r="G302" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H302" t="n">
         <v>2362</v>
@@ -49916,7 +49916,7 @@
         </is>
       </c>
       <c r="G303" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H303" t="n">
         <v>2362</v>
@@ -49957,7 +49957,7 @@
         </is>
       </c>
       <c r="G304" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H304" t="n">
         <v>2362</v>
@@ -49998,7 +49998,7 @@
         </is>
       </c>
       <c r="G305" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H305" t="n">
         <v>2362</v>
@@ -50039,7 +50039,7 @@
         </is>
       </c>
       <c r="G306" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H306" t="n">
         <v>2362</v>
@@ -50080,7 +50080,7 @@
         </is>
       </c>
       <c r="G307" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H307" t="n">
         <v>2362</v>
@@ -50121,7 +50121,7 @@
         </is>
       </c>
       <c r="G308" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H308" t="n">
         <v>2362</v>
@@ -50162,7 +50162,7 @@
         </is>
       </c>
       <c r="G309" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H309" t="n">
         <v>2362</v>
@@ -50203,7 +50203,7 @@
         </is>
       </c>
       <c r="G310" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H310" t="n">
         <v>2362</v>
@@ -50244,7 +50244,7 @@
         </is>
       </c>
       <c r="G311" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H311" t="n">
         <v>2362</v>
@@ -50285,7 +50285,7 @@
         </is>
       </c>
       <c r="G312" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H312" t="n">
         <v>2362</v>
@@ -50326,7 +50326,7 @@
         </is>
       </c>
       <c r="G313" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H313" t="n">
         <v>2362</v>
@@ -50367,7 +50367,7 @@
         </is>
       </c>
       <c r="G314" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H314" t="n">
         <v>2362</v>
@@ -50408,7 +50408,7 @@
         </is>
       </c>
       <c r="G315" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H315" t="n">
         <v>2362</v>
@@ -50449,7 +50449,7 @@
         </is>
       </c>
       <c r="G316" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H316" t="n">
         <v>2362</v>
@@ -50490,7 +50490,7 @@
         </is>
       </c>
       <c r="G317" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H317" t="n">
         <v>2362</v>
@@ -50531,7 +50531,7 @@
         </is>
       </c>
       <c r="G318" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H318" t="n">
         <v>2362</v>
@@ -50572,7 +50572,7 @@
         </is>
       </c>
       <c r="G319" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H319" t="n">
         <v>2362</v>
@@ -50613,7 +50613,7 @@
         </is>
       </c>
       <c r="G320" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H320" t="n">
         <v>2362</v>
@@ -50654,7 +50654,7 @@
         </is>
       </c>
       <c r="G321" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H321" t="n">
         <v>2362</v>
@@ -50695,7 +50695,7 @@
         </is>
       </c>
       <c r="G322" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H322" t="n">
         <v>2362</v>
@@ -50736,7 +50736,7 @@
         </is>
       </c>
       <c r="G323" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H323" t="n">
         <v>2362</v>
@@ -50777,7 +50777,7 @@
         </is>
       </c>
       <c r="G324" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H324" t="n">
         <v>2362</v>
@@ -50818,7 +50818,7 @@
         </is>
       </c>
       <c r="G325" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H325" t="n">
         <v>2362</v>
@@ -50859,7 +50859,7 @@
         </is>
       </c>
       <c r="G326" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H326" t="n">
         <v>2362</v>
@@ -50900,7 +50900,7 @@
         </is>
       </c>
       <c r="G327" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H327" t="n">
         <v>2362</v>
@@ -50941,7 +50941,7 @@
         </is>
       </c>
       <c r="G328" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H328" t="n">
         <v>2362</v>
@@ -50982,7 +50982,7 @@
         </is>
       </c>
       <c r="G329" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H329" t="n">
         <v>2362</v>
@@ -51023,7 +51023,7 @@
         </is>
       </c>
       <c r="G330" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H330" t="n">
         <v>2362</v>
@@ -51064,7 +51064,7 @@
         </is>
       </c>
       <c r="G331" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H331" t="n">
         <v>2362</v>
@@ -51105,7 +51105,7 @@
         </is>
       </c>
       <c r="G332" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H332" t="n">
         <v>2362</v>
@@ -51146,7 +51146,7 @@
         </is>
       </c>
       <c r="G333" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H333" t="n">
         <v>2362</v>
@@ -51187,7 +51187,7 @@
         </is>
       </c>
       <c r="G334" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H334" t="n">
         <v>2362</v>
@@ -51228,7 +51228,7 @@
         </is>
       </c>
       <c r="G335" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H335" t="n">
         <v>2362</v>
@@ -51269,7 +51269,7 @@
         </is>
       </c>
       <c r="G336" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H336" t="n">
         <v>2362</v>
@@ -51310,7 +51310,7 @@
         </is>
       </c>
       <c r="G337" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H337" t="n">
         <v>2362</v>
@@ -51351,7 +51351,7 @@
         </is>
       </c>
       <c r="G338" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H338" t="n">
         <v>2362</v>
@@ -51392,7 +51392,7 @@
         </is>
       </c>
       <c r="G339" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H339" t="n">
         <v>2362</v>
@@ -51433,7 +51433,7 @@
         </is>
       </c>
       <c r="G340" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H340" t="n">
         <v>2362</v>
@@ -51474,7 +51474,7 @@
         </is>
       </c>
       <c r="G341" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H341" t="n">
         <v>2362</v>
@@ -51515,7 +51515,7 @@
         </is>
       </c>
       <c r="G342" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H342" t="n">
         <v>5906</v>
@@ -51556,7 +51556,7 @@
         </is>
       </c>
       <c r="G343" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H343" t="n">
         <v>5906</v>
@@ -51597,7 +51597,7 @@
         </is>
       </c>
       <c r="G344" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H344" t="n">
         <v>5906</v>
@@ -51638,7 +51638,7 @@
         </is>
       </c>
       <c r="G345" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H345" t="n">
         <v>5906</v>
@@ -51679,7 +51679,7 @@
         </is>
       </c>
       <c r="G346" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H346" t="n">
         <v>5906</v>
@@ -51720,7 +51720,7 @@
         </is>
       </c>
       <c r="G347" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H347" t="n">
         <v>5906</v>
@@ -51761,7 +51761,7 @@
         </is>
       </c>
       <c r="G348" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H348" t="n">
         <v>5906</v>
@@ -51802,7 +51802,7 @@
         </is>
       </c>
       <c r="G349" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H349" t="n">
         <v>5906</v>
@@ -51843,7 +51843,7 @@
         </is>
       </c>
       <c r="G350" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H350" t="n">
         <v>4000</v>
@@ -51884,7 +51884,7 @@
         </is>
       </c>
       <c r="G351" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H351" t="n">
         <v>4000</v>
@@ -51925,7 +51925,7 @@
         </is>
       </c>
       <c r="G352" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H352" t="n">
         <v>4000</v>
@@ -51966,7 +51966,7 @@
         </is>
       </c>
       <c r="G353" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H353" t="n">
         <v>4000</v>
@@ -52007,7 +52007,7 @@
         </is>
       </c>
       <c r="G354" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H354" t="n">
         <v>4000</v>
@@ -52048,7 +52048,7 @@
         </is>
       </c>
       <c r="G355" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H355" t="n">
         <v>4000</v>
@@ -52089,7 +52089,7 @@
         </is>
       </c>
       <c r="G356" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H356" t="n">
         <v>4000</v>
@@ -52130,7 +52130,7 @@
         </is>
       </c>
       <c r="G357" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H357" t="n">
         <v>4000</v>
@@ -52171,7 +52171,7 @@
         </is>
       </c>
       <c r="G358" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H358" t="n">
         <v>4000</v>
@@ -52212,7 +52212,7 @@
         </is>
       </c>
       <c r="G359" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H359" t="n">
         <v>2000</v>
@@ -52253,7 +52253,7 @@
         </is>
       </c>
       <c r="G360" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H360" t="n">
         <v>2000</v>
@@ -52294,7 +52294,7 @@
         </is>
       </c>
       <c r="G361" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H361" t="n">
         <v>2688</v>
@@ -52335,7 +52335,7 @@
         </is>
       </c>
       <c r="G362" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H362" t="n">
         <v>2688</v>
@@ -52376,7 +52376,7 @@
         </is>
       </c>
       <c r="G363" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H363" t="n">
         <v>2084</v>
@@ -52417,7 +52417,7 @@
         </is>
       </c>
       <c r="G364" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H364" t="n">
         <v>2084</v>
@@ -52458,7 +52458,7 @@
         </is>
       </c>
       <c r="G365" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H365" t="n">
         <v>7087</v>
@@ -52499,7 +52499,7 @@
         </is>
       </c>
       <c r="G366" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H366" t="n">
         <v>5906</v>
@@ -52540,7 +52540,7 @@
         </is>
       </c>
       <c r="G367" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H367" t="n">
         <v>5906</v>
@@ -52581,7 +52581,7 @@
         </is>
       </c>
       <c r="G368" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H368" t="n">
         <v>5906</v>
@@ -52622,7 +52622,7 @@
         </is>
       </c>
       <c r="G369" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H369" t="n">
         <v>7087</v>
@@ -52663,7 +52663,7 @@
         </is>
       </c>
       <c r="G370" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H370" t="n">
         <v>5906</v>
@@ -52704,7 +52704,7 @@
         </is>
       </c>
       <c r="G371" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H371" t="n">
         <v>5906</v>
@@ -52745,7 +52745,7 @@
         </is>
       </c>
       <c r="G372" s="10" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="H372" t="n">
         <v>5906</v>
@@ -52786,7 +52786,7 @@
         </is>
       </c>
       <c r="G373" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H373" t="n">
         <v>3543</v>
@@ -52827,7 +52827,7 @@
         </is>
       </c>
       <c r="G374" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H374" t="n">
         <v>3543</v>
@@ -52868,7 +52868,7 @@
         </is>
       </c>
       <c r="G375" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H375" t="n">
         <v>3543</v>
@@ -52909,7 +52909,7 @@
         </is>
       </c>
       <c r="G376" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H376" t="n">
         <v>3543</v>
@@ -52950,7 +52950,7 @@
         </is>
       </c>
       <c r="G377" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H377" t="n">
         <v>3543</v>
@@ -52991,7 +52991,7 @@
         </is>
       </c>
       <c r="G378" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H378" t="n">
         <v>3543</v>
@@ -53032,7 +53032,7 @@
         </is>
       </c>
       <c r="G379" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H379" t="n">
         <v>3543</v>
@@ -53073,7 +53073,7 @@
         </is>
       </c>
       <c r="G380" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H380" t="n">
         <v>3543</v>
@@ -53114,7 +53114,7 @@
         </is>
       </c>
       <c r="G381" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H381" t="n">
         <v>3543</v>
@@ -53155,7 +53155,7 @@
         </is>
       </c>
       <c r="G382" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H382" t="n">
         <v>3543</v>
@@ -53196,7 +53196,7 @@
         </is>
       </c>
       <c r="G383" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H383" t="n">
         <v>3543</v>
@@ -53237,7 +53237,7 @@
         </is>
       </c>
       <c r="G384" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H384" t="n">
         <v>3543</v>
@@ -53278,7 +53278,7 @@
         </is>
       </c>
       <c r="G385" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H385" t="n">
         <v>3543</v>
@@ -53319,7 +53319,7 @@
         </is>
       </c>
       <c r="G386" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H386" t="n">
         <v>3543</v>
@@ -53360,7 +53360,7 @@
         </is>
       </c>
       <c r="G387" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H387" t="n">
         <v>3543</v>
@@ -53401,7 +53401,7 @@
         </is>
       </c>
       <c r="G388" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H388" t="n">
         <v>3543</v>
@@ -53442,7 +53442,7 @@
         </is>
       </c>
       <c r="G389" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H389" t="n">
         <v>3543</v>
@@ -53483,7 +53483,7 @@
         </is>
       </c>
       <c r="G390" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H390" t="n">
         <v>3543</v>
@@ -53524,7 +53524,7 @@
         </is>
       </c>
       <c r="G391" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H391" t="n">
         <v>3543</v>
@@ -53565,7 +53565,7 @@
         </is>
       </c>
       <c r="G392" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H392" t="n">
         <v>3543</v>
@@ -53606,7 +53606,7 @@
         </is>
       </c>
       <c r="G393" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H393" t="n">
         <v>3543</v>
@@ -53647,7 +53647,7 @@
         </is>
       </c>
       <c r="G394" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H394" t="n">
         <v>3543</v>
@@ -53688,7 +53688,7 @@
         </is>
       </c>
       <c r="G395" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H395" t="n">
         <v>3543</v>
@@ -53729,7 +53729,7 @@
         </is>
       </c>
       <c r="G396" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H396" t="n">
         <v>3543</v>
@@ -53770,7 +53770,7 @@
         </is>
       </c>
       <c r="G397" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H397" t="n">
         <v>3543</v>
@@ -53811,7 +53811,7 @@
         </is>
       </c>
       <c r="G398" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H398" t="n">
         <v>3543</v>
@@ -53852,7 +53852,7 @@
         </is>
       </c>
       <c r="G399" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H399" t="n">
         <v>3543</v>
@@ -53893,7 +53893,7 @@
         </is>
       </c>
       <c r="G400" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H400" t="n">
         <v>3543</v>
@@ -53934,7 +53934,7 @@
         </is>
       </c>
       <c r="G401" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H401" t="n">
         <v>3543</v>
@@ -53975,7 +53975,7 @@
         </is>
       </c>
       <c r="G402" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H402" t="n">
         <v>3543</v>
@@ -54016,7 +54016,7 @@
         </is>
       </c>
       <c r="G403" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H403" t="n">
         <v>3543</v>
@@ -54057,7 +54057,7 @@
         </is>
       </c>
       <c r="G404" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H404" t="n">
         <v>3543</v>
@@ -54098,7 +54098,7 @@
         </is>
       </c>
       <c r="G405" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H405" t="n">
         <v>3543</v>
@@ -54139,7 +54139,7 @@
         </is>
       </c>
       <c r="G406" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H406" t="n">
         <v>3543</v>
@@ -54180,7 +54180,7 @@
         </is>
       </c>
       <c r="G407" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H407" t="n">
         <v>3543</v>
@@ -54221,7 +54221,7 @@
         </is>
       </c>
       <c r="G408" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H408" t="n">
         <v>3543</v>
@@ -54262,7 +54262,7 @@
         </is>
       </c>
       <c r="G409" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H409" t="n">
         <v>3543</v>
@@ -54303,7 +54303,7 @@
         </is>
       </c>
       <c r="G410" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H410" t="n">
         <v>3543</v>
@@ -54344,7 +54344,7 @@
         </is>
       </c>
       <c r="G411" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H411" t="n">
         <v>3543</v>
@@ -54385,7 +54385,7 @@
         </is>
       </c>
       <c r="G412" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H412" t="n">
         <v>3543</v>
@@ -54426,7 +54426,7 @@
         </is>
       </c>
       <c r="G413" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H413" t="n">
         <v>3543</v>
@@ -54467,7 +54467,7 @@
         </is>
       </c>
       <c r="G414" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H414" t="n">
         <v>3543</v>
@@ -54508,7 +54508,7 @@
         </is>
       </c>
       <c r="G415" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H415" t="n">
         <v>3543</v>
@@ -54549,7 +54549,7 @@
         </is>
       </c>
       <c r="G416" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H416" t="n">
         <v>3543</v>
@@ -54590,7 +54590,7 @@
         </is>
       </c>
       <c r="G417" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H417" t="n">
         <v>3543</v>
@@ -54631,7 +54631,7 @@
         </is>
       </c>
       <c r="G418" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H418" t="n">
         <v>3543</v>
@@ -54672,7 +54672,7 @@
         </is>
       </c>
       <c r="G419" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H419" t="n">
         <v>3543</v>
@@ -54713,7 +54713,7 @@
         </is>
       </c>
       <c r="G420" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H420" t="n">
         <v>3543</v>
@@ -54754,7 +54754,7 @@
         </is>
       </c>
       <c r="G421" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H421" t="n">
         <v>3543</v>
@@ -54795,7 +54795,7 @@
         </is>
       </c>
       <c r="G422" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H422" t="n">
         <v>3543</v>
@@ -54836,7 +54836,7 @@
         </is>
       </c>
       <c r="G423" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H423" t="n">
         <v>3543</v>
@@ -54877,7 +54877,7 @@
         </is>
       </c>
       <c r="G424" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H424" t="n">
         <v>3543</v>
@@ -54918,7 +54918,7 @@
         </is>
       </c>
       <c r="G425" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H425" t="n">
         <v>3543</v>
@@ -54959,7 +54959,7 @@
         </is>
       </c>
       <c r="G426" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H426" t="n">
         <v>3543</v>
@@ -55000,7 +55000,7 @@
         </is>
       </c>
       <c r="G427" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H427" t="n">
         <v>3543</v>
@@ -55041,7 +55041,7 @@
         </is>
       </c>
       <c r="G428" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H428" t="n">
         <v>3543</v>
@@ -55082,7 +55082,7 @@
         </is>
       </c>
       <c r="G429" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H429" t="n">
         <v>3543</v>
@@ -55123,7 +55123,7 @@
         </is>
       </c>
       <c r="G430" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H430" t="n">
         <v>3543</v>
@@ -55164,7 +55164,7 @@
         </is>
       </c>
       <c r="G431" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H431" t="n">
         <v>3543</v>
@@ -55205,7 +55205,7 @@
         </is>
       </c>
       <c r="G432" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H432" t="n">
         <v>3543</v>
@@ -55246,7 +55246,7 @@
         </is>
       </c>
       <c r="G433" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H433" t="n">
         <v>3543</v>
@@ -55287,7 +55287,7 @@
         </is>
       </c>
       <c r="G434" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H434" t="n">
         <v>3543</v>
@@ -55328,7 +55328,7 @@
         </is>
       </c>
       <c r="G435" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H435" t="n">
         <v>3543</v>
@@ -55369,7 +55369,7 @@
         </is>
       </c>
       <c r="G436" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H436" t="n">
         <v>3543</v>
@@ -55410,7 +55410,7 @@
         </is>
       </c>
       <c r="G437" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H437" t="n">
         <v>3543</v>
@@ -55451,7 +55451,7 @@
         </is>
       </c>
       <c r="G438" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H438" t="n">
         <v>3543</v>
@@ -55492,7 +55492,7 @@
         </is>
       </c>
       <c r="G439" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H439" t="n">
         <v>3543</v>
@@ -55533,7 +55533,7 @@
         </is>
       </c>
       <c r="G440" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H440" t="n">
         <v>3543</v>
@@ -55574,7 +55574,7 @@
         </is>
       </c>
       <c r="G441" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H441" t="n">
         <v>3543</v>
@@ -55615,7 +55615,7 @@
         </is>
       </c>
       <c r="G442" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H442" t="n">
         <v>3543</v>
@@ -55656,7 +55656,7 @@
         </is>
       </c>
       <c r="G443" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H443" t="n">
         <v>3543</v>
@@ -55697,7 +55697,7 @@
         </is>
       </c>
       <c r="G444" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H444" t="n">
         <v>3543</v>
@@ -55738,7 +55738,7 @@
         </is>
       </c>
       <c r="G445" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H445" t="n">
         <v>3543</v>
@@ -55779,7 +55779,7 @@
         </is>
       </c>
       <c r="G446" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H446" t="n">
         <v>3543</v>
@@ -55820,7 +55820,7 @@
         </is>
       </c>
       <c r="G447" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H447" t="n">
         <v>3543</v>
@@ -55861,7 +55861,7 @@
         </is>
       </c>
       <c r="G448" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H448" t="n">
         <v>2000</v>
@@ -55902,7 +55902,7 @@
         </is>
       </c>
       <c r="G449" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H449" t="n">
         <v>2000</v>
@@ -55943,7 +55943,7 @@
         </is>
       </c>
       <c r="G450" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H450" t="n">
         <v>2000</v>
@@ -55984,7 +55984,7 @@
         </is>
       </c>
       <c r="G451" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H451" t="n">
         <v>2000</v>
@@ -56025,7 +56025,7 @@
         </is>
       </c>
       <c r="G452" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H452" t="n">
         <v>2000</v>
@@ -56066,7 +56066,7 @@
         </is>
       </c>
       <c r="G453" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H453" t="n">
         <v>2000</v>
@@ -56107,7 +56107,7 @@
         </is>
       </c>
       <c r="G454" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H454" t="n">
         <v>2000</v>
@@ -56148,7 +56148,7 @@
         </is>
       </c>
       <c r="G455" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H455" t="n">
         <v>2000</v>
@@ -56189,7 +56189,7 @@
         </is>
       </c>
       <c r="G456" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H456" t="n">
         <v>2000</v>
@@ -56230,7 +56230,7 @@
         </is>
       </c>
       <c r="G457" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H457" t="n">
         <v>2000</v>
@@ -56271,7 +56271,7 @@
         </is>
       </c>
       <c r="G458" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H458" t="n">
         <v>2000</v>
@@ -56312,7 +56312,7 @@
         </is>
       </c>
       <c r="G459" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H459" t="n">
         <v>2000</v>
@@ -56353,7 +56353,7 @@
         </is>
       </c>
       <c r="G460" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H460" t="n">
         <v>3316</v>
@@ -56394,7 +56394,7 @@
         </is>
       </c>
       <c r="G461" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H461" t="n">
         <v>3316</v>
@@ -56435,7 +56435,7 @@
         </is>
       </c>
       <c r="G462" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H462" t="n">
         <v>2785</v>
@@ -56476,7 +56476,7 @@
         </is>
       </c>
       <c r="G463" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H463" t="n">
         <v>2785</v>
@@ -56517,7 +56517,7 @@
         </is>
       </c>
       <c r="G464" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H464" t="n">
         <v>4032</v>
@@ -56558,7 +56558,7 @@
         </is>
       </c>
       <c r="G465" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H465" t="n">
         <v>4032</v>
@@ -56599,7 +56599,7 @@
         </is>
       </c>
       <c r="G466" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H466" t="n">
         <v>3047</v>
@@ -56640,7 +56640,7 @@
         </is>
       </c>
       <c r="G467" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H467" t="n">
         <v>4032</v>
@@ -56681,7 +56681,7 @@
         </is>
       </c>
       <c r="G468" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H468" t="n">
         <v>4032</v>
@@ -56722,7 +56722,7 @@
         </is>
       </c>
       <c r="G469" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H469" t="n">
         <v>3661</v>
@@ -56763,7 +56763,7 @@
         </is>
       </c>
       <c r="G470" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H470" t="n">
         <v>3607</v>
@@ -56804,7 +56804,7 @@
         </is>
       </c>
       <c r="G471" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H471" t="n">
         <v>4028</v>
@@ -56845,7 +56845,7 @@
         </is>
       </c>
       <c r="G472" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H472" t="n">
         <v>4028</v>
@@ -56886,7 +56886,7 @@
         </is>
       </c>
       <c r="G473" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H473" t="n">
         <v>4028</v>
@@ -56927,7 +56927,7 @@
         </is>
       </c>
       <c r="G474" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H474" t="n">
         <v>4028</v>
@@ -56968,7 +56968,7 @@
         </is>
       </c>
       <c r="G475" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H475" t="n">
         <v>4028</v>
@@ -57009,7 +57009,7 @@
         </is>
       </c>
       <c r="G476" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H476" t="n">
         <v>4028</v>
@@ -57050,7 +57050,7 @@
         </is>
       </c>
       <c r="G477" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H477" t="n">
         <v>4028</v>
@@ -57091,7 +57091,7 @@
         </is>
       </c>
       <c r="G478" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H478" t="n">
         <v>3895</v>
@@ -57132,7 +57132,7 @@
         </is>
       </c>
       <c r="G479" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H479" t="n">
         <v>2784</v>
@@ -57173,7 +57173,7 @@
         </is>
       </c>
       <c r="G480" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="H480" t="n">
         <v>4028</v>
@@ -57214,7 +57214,7 @@
         </is>
       </c>
       <c r="G481" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H481" t="n">
         <v>2138</v>
@@ -57255,7 +57255,7 @@
         </is>
       </c>
       <c r="G482" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H482" t="n">
         <v>4038</v>
@@ -57296,7 +57296,7 @@
         </is>
       </c>
       <c r="G483" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H483" t="n">
         <v>4038</v>
@@ -57337,7 +57337,7 @@
         </is>
       </c>
       <c r="G484" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H484" t="n">
         <v>4038</v>
@@ -57378,7 +57378,7 @@
         </is>
       </c>
       <c r="G485" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H485" t="n">
         <v>4038</v>
@@ -57419,7 +57419,7 @@
         </is>
       </c>
       <c r="G486" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H486" t="n">
         <v>4038</v>
@@ -57460,7 +57460,7 @@
         </is>
       </c>
       <c r="G487" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H487" t="n">
         <v>4038</v>
@@ -57501,7 +57501,7 @@
         </is>
       </c>
       <c r="G488" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H488" t="n">
         <v>4038</v>
@@ -57542,7 +57542,7 @@
         </is>
       </c>
       <c r="G489" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H489" t="n">
         <v>4038</v>
@@ -57583,7 +57583,7 @@
         </is>
       </c>
       <c r="G490" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H490" t="n">
         <v>4038</v>
@@ -57624,7 +57624,7 @@
         </is>
       </c>
       <c r="G491" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H491" t="n">
         <v>5712</v>
@@ -57665,7 +57665,7 @@
         </is>
       </c>
       <c r="G492" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H492" t="n">
         <v>2472</v>
@@ -57706,7 +57706,7 @@
         </is>
       </c>
       <c r="G493" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H493" t="n">
         <v>2472</v>
@@ -57747,7 +57747,7 @@
         </is>
       </c>
       <c r="G494" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H494" t="n">
         <v>2472</v>
@@ -57788,7 +57788,7 @@
         </is>
       </c>
       <c r="G495" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H495" t="n">
         <v>2472</v>
@@ -57829,7 +57829,7 @@
         </is>
       </c>
       <c r="G496" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H496" t="n">
         <v>2472</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G497" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H497" t="n">
         <v>5192</v>
@@ -57911,7 +57911,7 @@
         </is>
       </c>
       <c r="G498" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H498" t="n">
         <v>6525</v>
@@ -57952,7 +57952,7 @@
         </is>
       </c>
       <c r="G499" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H499" t="n">
         <v>2000</v>
@@ -57993,7 +57993,7 @@
         </is>
       </c>
       <c r="G500" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H500" t="n">
         <v>4179</v>
@@ -58034,7 +58034,7 @@
         </is>
       </c>
       <c r="G501" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H501" t="n">
         <v>5983</v>
@@ -58075,7 +58075,7 @@
         </is>
       </c>
       <c r="G502" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H502" t="n">
         <v>2242</v>
@@ -58116,7 +58116,7 @@
         </is>
       </c>
       <c r="G503" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H503" t="n">
         <v>3240</v>
@@ -58157,7 +58157,7 @@
         </is>
       </c>
       <c r="G504" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H504" t="n">
         <v>2869</v>
@@ -58198,7 +58198,7 @@
         </is>
       </c>
       <c r="G505" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H505" t="n">
         <v>2750</v>
@@ -58239,7 +58239,7 @@
         </is>
       </c>
       <c r="G506" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H506" t="n">
         <v>2665</v>
@@ -58280,7 +58280,7 @@
         </is>
       </c>
       <c r="G507" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H507" t="n">
         <v>2971</v>
@@ -58321,7 +58321,7 @@
         </is>
       </c>
       <c r="G508" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H508" t="n">
         <v>2979</v>
@@ -58362,7 +58362,7 @@
         </is>
       </c>
       <c r="G509" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H509" t="n">
         <v>2896</v>
@@ -58403,7 +58403,7 @@
         </is>
       </c>
       <c r="G510" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H510" t="n">
         <v>3015</v>
@@ -58444,7 +58444,7 @@
         </is>
       </c>
       <c r="G511" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H511" t="n">
         <v>1985</v>
@@ -58485,7 +58485,7 @@
         </is>
       </c>
       <c r="G512" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H512" t="n">
         <v>1859</v>
@@ -58526,7 +58526,7 @@
         </is>
       </c>
       <c r="G513" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H513" t="n">
         <v>3566</v>
@@ -58567,7 +58567,7 @@
         </is>
       </c>
       <c r="G514" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H514" t="n">
         <v>3566</v>
@@ -58608,7 +58608,7 @@
         </is>
       </c>
       <c r="G515" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H515" t="n">
         <v>3566</v>
@@ -58649,7 +58649,7 @@
         </is>
       </c>
       <c r="G516" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H516" t="n">
         <v>3566</v>
@@ -58690,7 +58690,7 @@
         </is>
       </c>
       <c r="G517" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H517" t="n">
         <v>3566</v>
@@ -58731,7 +58731,7 @@
         </is>
       </c>
       <c r="G518" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H518" t="n">
         <v>3566</v>
@@ -58772,7 +58772,7 @@
         </is>
       </c>
       <c r="G519" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H519" t="n">
         <v>3566</v>
@@ -58813,7 +58813,7 @@
         </is>
       </c>
       <c r="G520" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H520" t="n">
         <v>3566</v>
@@ -58854,7 +58854,7 @@
         </is>
       </c>
       <c r="G521" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H521" t="n">
         <v>3566</v>
@@ -58895,7 +58895,7 @@
         </is>
       </c>
       <c r="G522" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H522" t="n">
         <v>3566</v>
@@ -58936,7 +58936,7 @@
         </is>
       </c>
       <c r="G523" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H523" t="n">
         <v>3566</v>
@@ -58977,7 +58977,7 @@
         </is>
       </c>
       <c r="G524" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H524" t="n">
         <v>3566</v>
@@ -59018,7 +59018,7 @@
         </is>
       </c>
       <c r="G525" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H525" t="n">
         <v>3566</v>
@@ -59059,7 +59059,7 @@
         </is>
       </c>
       <c r="G526" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H526" t="n">
         <v>3566</v>
@@ -59100,7 +59100,7 @@
         </is>
       </c>
       <c r="G527" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H527" t="n">
         <v>3566</v>
@@ -59141,7 +59141,7 @@
         </is>
       </c>
       <c r="G528" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H528" t="n">
         <v>3566</v>
@@ -59182,7 +59182,7 @@
         </is>
       </c>
       <c r="G529" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H529" t="n">
         <v>3566</v>
@@ -59223,7 +59223,7 @@
         </is>
       </c>
       <c r="G530" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H530" t="n">
         <v>1828</v>
@@ -59264,7 +59264,7 @@
         </is>
       </c>
       <c r="G531" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="H531" t="n">
         <v>2480</v>

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20580" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20580" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Works'!$A$1:$Y$550</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1375,8 +1375,8 @@
     <col width="15.1640625" customWidth="1" style="7" min="23" max="23"/>
     <col width="21.5" customWidth="1" style="7" min="24" max="24"/>
     <col width="26.83203125" customWidth="1" style="7" min="25" max="25"/>
-    <col width="10.83203125" customWidth="1" style="7" min="27" max="64"/>
-    <col width="10.83203125" customWidth="1" style="7" min="65" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="7" min="27" max="66"/>
+    <col width="10.83203125" customWidth="1" style="7" min="67" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="6">
@@ -28216,7 +28216,7 @@
       </c>
       <c r="B429" s="7" t="inlineStr">
         <is>
-          <t>published</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="C429" s="24" t="n">
@@ -28224,12 +28224,12 @@
       </c>
       <c r="D429" s="7" t="inlineStr">
         <is>
-          <t>molecules</t>
+          <t>molecule-forms</t>
         </is>
       </c>
       <c r="E429" s="7" t="inlineStr">
         <is>
-          <t>molecules</t>
+          <t>molecule forms</t>
         </is>
       </c>
       <c r="F429" s="7" t="inlineStr">
@@ -36392,7 +36392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="31.83203125" customWidth="1" style="1" min="1" max="1"/>
@@ -36403,8 +36403,8 @@
     <col width="21" bestFit="1" customWidth="1" style="7" min="6" max="6"/>
     <col width="21" customWidth="1" style="7" min="7" max="7"/>
     <col width="51" bestFit="1" customWidth="1" style="1" min="8" max="8"/>
-    <col width="10.83203125" customWidth="1" style="1" min="9" max="47"/>
-    <col width="10.83203125" customWidth="1" style="1" min="48" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="1" min="9" max="49"/>
+    <col width="10.83203125" customWidth="1" style="1" min="50" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -37203,12 +37203,12 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>molecules</t>
+          <t>molecule-forms</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>molecules</t>
+          <t>molecule forms</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -37225,66 +37225,59 @@
       <c r="F30" s="7" t="n">
         <v>2013</v>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>molecules</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>molecules</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>2013</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>2013</v>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>00460</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>monoprints-residues</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>monoprints and residues</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>mouse-story</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>mouse story</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>46086</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>1993</v>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>1991-93</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>00160</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>nerve</t>
+          <t>mouse-story</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>nerve</t>
+          <t>mouse story</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -37296,165 +37289,198 @@
         <v>46086</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>1990-95</t>
-        </is>
-      </c>
-      <c r="H33" s="1" t="inlineStr">
-        <is>
-          <t>works and details to publish</t>
+          <t>1991-93</t>
+        </is>
+      </c>
+      <c r="G33" s="16" t="inlineStr">
+        <is>
+          <t>00160</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>nerve-forms</t>
+          <t>nerve</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>nerve forms</t>
-        </is>
+          <t>nerve</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>46086</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>2004</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>2004</v>
+        <v>1995</v>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>1990-95</t>
+        </is>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>add remaining works and series text</t>
+          <t>works and details to publish</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>particle-theory</t>
+          <t>nerve-forms</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>particle theory</t>
+          <t>nerve forms</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>2004</v>
+      </c>
+      <c r="H35" s="1" t="inlineStr">
+        <is>
+          <t>add remaining works and series text</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>qrnt</t>
+          <t>particle-theory</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>quantum random number theory</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>2009, 2015</t>
+          <t>particle theory</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>qrnt</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>46086</v>
+          <t>quantum random number theory</t>
+        </is>
       </c>
       <c r="E37" s="1" t="n">
-        <v>2001</v>
-      </c>
-      <c r="F37" s="7" t="n">
-        <v>2001</v>
-      </c>
-      <c r="G37" s="16" t="inlineStr">
-        <is>
-          <t>00142</t>
+        <v>2015</v>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>2009, 2015</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>spiders</t>
+          <t>r</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>spiders</t>
-        </is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>46086</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>2006</v>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>2006, 2015</t>
+        <v>2001</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>2001</v>
+      </c>
+      <c r="G38" s="16" t="inlineStr">
+        <is>
+          <t>00142</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>string-theory</t>
+          <t>spiders</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>string theory</t>
+          <t>spiders</t>
         </is>
       </c>
       <c r="E39" s="1" t="n">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>2005-12</t>
-        </is>
-      </c>
-      <c r="G39" s="16" t="inlineStr">
-        <is>
-          <t>00573</t>
+          <t>2006, 2015</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
+          <t>string-theory</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>string theory</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>2012</v>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>2005-12</t>
+        </is>
+      </c>
+      <c r="G40" s="16" t="inlineStr">
+        <is>
+          <t>00573</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
           <t>wa</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
+      <c r="B41" s="1" t="inlineStr">
         <is>
           <t>wa</t>
         </is>
       </c>
-      <c r="E40" s="1" t="n">
+      <c r="E41" s="1" t="n">
         <v>2008</v>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>2008, 2011</t>
         </is>
@@ -51829,12 +51855,12 @@
       </c>
       <c r="D350" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 1 - detail 1.jpg</t>
+          <t>forest 1 - detail 1.jpg</t>
         </is>
       </c>
       <c r="E350" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 1 - detail 1</t>
+          <t>forest 1 - detail 1</t>
         </is>
       </c>
       <c r="F350" s="1" t="inlineStr">
@@ -51870,12 +51896,12 @@
       </c>
       <c r="D351" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 1 - detail 2.jpg</t>
+          <t>forest 1 - detail 2.jpg</t>
         </is>
       </c>
       <c r="E351" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 1 - detail 2</t>
+          <t>forest 1 - detail 2</t>
         </is>
       </c>
       <c r="F351" s="1" t="inlineStr">
@@ -51911,12 +51937,12 @@
       </c>
       <c r="D352" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 1 - detail 3.jpg</t>
+          <t>forest 1 - detail 3.jpg</t>
         </is>
       </c>
       <c r="E352" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 1 - detail 3</t>
+          <t>forest 1 - detail 3</t>
         </is>
       </c>
       <c r="F352" s="1" t="inlineStr">
@@ -51952,12 +51978,12 @@
       </c>
       <c r="D353" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 2 - detail 1.jpg</t>
+          <t>forest 2 - detail 1.jpg</t>
         </is>
       </c>
       <c r="E353" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 2 - detail 1</t>
+          <t>forest 2 - detail 1</t>
         </is>
       </c>
       <c r="F353" s="1" t="inlineStr">
@@ -51993,12 +52019,12 @@
       </c>
       <c r="D354" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 2 - detail 2.jpg</t>
+          <t>forest 2 - detail 2.jpg</t>
         </is>
       </c>
       <c r="E354" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 2 - detail 2</t>
+          <t>forest 2 - detail 2</t>
         </is>
       </c>
       <c r="F354" s="1" t="inlineStr">
@@ -52034,12 +52060,12 @@
       </c>
       <c r="D355" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 2 - detail 3.jpg</t>
+          <t>forest 2 - detail 3.jpg</t>
         </is>
       </c>
       <c r="E355" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 2 - detail 3</t>
+          <t>forest 2 - detail 3</t>
         </is>
       </c>
       <c r="F355" s="1" t="inlineStr">
@@ -52075,12 +52101,12 @@
       </c>
       <c r="D356" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 3 - detail 1.jpg</t>
+          <t>forest 3 - detail 1.jpg</t>
         </is>
       </c>
       <c r="E356" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 3 - detail 1</t>
+          <t>forest 3 - detail 1</t>
         </is>
       </c>
       <c r="F356" s="1" t="inlineStr">
@@ -52116,12 +52142,12 @@
       </c>
       <c r="D357" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 3 - detail 2.jpg</t>
+          <t>forest 3 - detail 2.jpg</t>
         </is>
       </c>
       <c r="E357" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 3 - detail 2</t>
+          <t>forest 3 - detail 2</t>
         </is>
       </c>
       <c r="F357" s="1" t="inlineStr">
@@ -52157,12 +52183,12 @@
       </c>
       <c r="D358" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 3 - detail 3.jpg</t>
+          <t>forest 3 - detail 3.jpg</t>
         </is>
       </c>
       <c r="E358" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 3 - detail 3</t>
+          <t>forest 3 - detail 3</t>
         </is>
       </c>
       <c r="F358" s="1" t="inlineStr">
@@ -52198,12 +52224,12 @@
       </c>
       <c r="D359" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 4 - detail 1.jpg</t>
+          <t>forest 4 - detail 1.jpg</t>
         </is>
       </c>
       <c r="E359" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 4 - detail 1</t>
+          <t>forest 4 - detail 1</t>
         </is>
       </c>
       <c r="F359" s="1" t="inlineStr">
@@ -52239,12 +52265,12 @@
       </c>
       <c r="D360" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 4 - detail 2.jpg</t>
+          <t>forest 4 - detail 2.jpg</t>
         </is>
       </c>
       <c r="E360" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 4 - detail 2</t>
+          <t>forest 4 - detail 2</t>
         </is>
       </c>
       <c r="F360" s="1" t="inlineStr">
@@ -52280,12 +52306,12 @@
       </c>
       <c r="D361" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 4 - detail 3.jpg</t>
+          <t>forest 4 - detail 3.jpg</t>
         </is>
       </c>
       <c r="E361" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 4 - detail 3</t>
+          <t>forest 4 - detail 3</t>
         </is>
       </c>
       <c r="F361" s="1" t="inlineStr">
@@ -52321,12 +52347,12 @@
       </c>
       <c r="D362" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 4 - detail 4.jpg</t>
+          <t>forest 4 - detail 4.jpg</t>
         </is>
       </c>
       <c r="E362" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 4 - detail 4</t>
+          <t>forest 4 - detail 4</t>
         </is>
       </c>
       <c r="F362" s="1" t="inlineStr">
@@ -52362,12 +52388,12 @@
       </c>
       <c r="D363" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 4 - detail 5.jpg</t>
+          <t>forest 4 - detail 5.jpg</t>
         </is>
       </c>
       <c r="E363" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 4 - detail 5</t>
+          <t>forest 4 - detail 5</t>
         </is>
       </c>
       <c r="F363" s="1" t="inlineStr">
@@ -52403,12 +52429,12 @@
       </c>
       <c r="D364" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 4 - detail 6.jpg</t>
+          <t>forest 4 - detail 6.jpg</t>
         </is>
       </c>
       <c r="E364" s="1" t="inlineStr">
         <is>
-          <t>forests (2023) - forest 4 - detail 6</t>
+          <t>forest 4 - detail 6</t>
         </is>
       </c>
       <c r="F364" s="1" t="inlineStr">
@@ -59298,8 +59324,8 @@
     <col width="11.33203125" bestFit="1" customWidth="1" style="13" min="9" max="9"/>
     <col width="12.1640625" bestFit="1" customWidth="1" style="13" min="10" max="10"/>
     <col width="33.6640625" customWidth="1" style="13" min="11" max="11"/>
-    <col width="10.83203125" customWidth="1" style="13" min="12" max="41"/>
-    <col width="10.83203125" customWidth="1" style="13" min="42" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="13" min="12" max="43"/>
+    <col width="10.83203125" customWidth="1" style="13" min="44" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="C9" s="24" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         </is>
       </c>
       <c r="C53" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C55" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="C57" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="C59" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="C61" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C63" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         </is>
       </c>
       <c r="C65" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         </is>
       </c>
       <c r="C67" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         </is>
       </c>
       <c r="C77" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="C79" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         </is>
       </c>
       <c r="C81" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         </is>
       </c>
       <c r="C83" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="C85" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="C87" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         </is>
       </c>
       <c r="C89" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="C91" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="C93" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         </is>
       </c>
       <c r="C94" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="C95" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         </is>
       </c>
       <c r="C96" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="C97" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         </is>
       </c>
       <c r="C98" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="C99" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="C100" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="C101" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="C102" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="C103" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="C104" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         </is>
       </c>
       <c r="C105" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="C106" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="C107" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="C108" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="C109" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="C110" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="C111" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="C112" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         </is>
       </c>
       <c r="C113" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="C114" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="C115" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="C116" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         </is>
       </c>
       <c r="C117" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="C118" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         </is>
       </c>
       <c r="C119" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         </is>
       </c>
       <c r="C120" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         </is>
       </c>
       <c r="C121" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         </is>
       </c>
       <c r="C122" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         </is>
       </c>
       <c r="C123" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="C124" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="C125" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         </is>
       </c>
       <c r="C126" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="C127" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         </is>
       </c>
       <c r="C128" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         </is>
       </c>
       <c r="C129" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="C131" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         </is>
       </c>
       <c r="C132" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         </is>
       </c>
       <c r="C133" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         </is>
       </c>
       <c r="C134" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         </is>
       </c>
       <c r="C135" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         </is>
       </c>
       <c r="C136" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         </is>
       </c>
       <c r="C137" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         </is>
       </c>
       <c r="C138" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         </is>
       </c>
       <c r="C139" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         </is>
       </c>
       <c r="C140" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         </is>
       </c>
       <c r="C141" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         </is>
       </c>
       <c r="C142" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         </is>
       </c>
       <c r="C143" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         </is>
       </c>
       <c r="C144" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         </is>
       </c>
       <c r="C145" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         </is>
       </c>
       <c r="C146" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         </is>
       </c>
       <c r="C147" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         </is>
       </c>
       <c r="C148" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         </is>
       </c>
       <c r="C149" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         </is>
       </c>
       <c r="C150" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D150" s="7" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         </is>
       </c>
       <c r="C151" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         </is>
       </c>
       <c r="C152" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         </is>
       </c>
       <c r="C153" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         </is>
       </c>
       <c r="C154" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         </is>
       </c>
       <c r="C155" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         </is>
       </c>
       <c r="C156" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D156" s="7" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         </is>
       </c>
       <c r="C157" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         </is>
       </c>
       <c r="C158" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D158" s="7" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         </is>
       </c>
       <c r="C159" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         </is>
       </c>
       <c r="C160" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         </is>
       </c>
       <c r="C161" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         </is>
       </c>
       <c r="C162" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D162" s="7" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         </is>
       </c>
       <c r="C163" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="C164" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D164" s="7" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         </is>
       </c>
       <c r="C165" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         </is>
       </c>
       <c r="C166" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D166" s="7" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="C167" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="C168" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D168" s="7" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         </is>
       </c>
       <c r="C169" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="C170" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         </is>
       </c>
       <c r="C171" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         </is>
       </c>
       <c r="C172" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D172" s="7" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         </is>
       </c>
       <c r="C173" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         </is>
       </c>
       <c r="C174" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D174" s="7" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         </is>
       </c>
       <c r="C175" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         </is>
       </c>
       <c r="C176" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D176" s="7" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         </is>
       </c>
       <c r="C177" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         </is>
       </c>
       <c r="C178" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D178" s="7" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="C179" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="C180" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
         </is>
       </c>
       <c r="C181" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         </is>
       </c>
       <c r="C182" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D182" s="7" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         </is>
       </c>
       <c r="C183" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="C184" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D184" s="7" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         </is>
       </c>
       <c r="C185" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         </is>
       </c>
       <c r="C186" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D186" s="7" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         </is>
       </c>
       <c r="C187" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="C188" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D188" s="7" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         </is>
       </c>
       <c r="C189" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         </is>
       </c>
       <c r="C190" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D190" s="7" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         </is>
       </c>
       <c r="C191" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D191" s="7" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="C192" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D192" s="7" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         </is>
       </c>
       <c r="C193" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         </is>
       </c>
       <c r="C194" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D194" s="7" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         </is>
       </c>
       <c r="C195" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="C196" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D196" s="7" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         </is>
       </c>
       <c r="C197" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D197" s="7" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         </is>
       </c>
       <c r="C198" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D198" s="7" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         </is>
       </c>
       <c r="C199" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D199" s="7" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         </is>
       </c>
       <c r="C200" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D200" s="7" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         </is>
       </c>
       <c r="C201" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D201" s="7" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         </is>
       </c>
       <c r="C202" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D202" s="7" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         </is>
       </c>
       <c r="C203" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D203" s="7" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         </is>
       </c>
       <c r="C204" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D204" s="7" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="C205" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D205" s="7" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         </is>
       </c>
       <c r="C206" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D206" s="7" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         </is>
       </c>
       <c r="C207" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D207" s="7" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         </is>
       </c>
       <c r="C208" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D208" s="7" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         </is>
       </c>
       <c r="C209" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D209" s="7" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         </is>
       </c>
       <c r="C210" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D210" s="7" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         </is>
       </c>
       <c r="C211" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D211" s="7" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         </is>
       </c>
       <c r="C212" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D212" s="7" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         </is>
       </c>
       <c r="C213" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D213" s="7" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         </is>
       </c>
       <c r="C214" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D214" s="7" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         </is>
       </c>
       <c r="C215" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D215" s="7" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         </is>
       </c>
       <c r="C216" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D216" s="7" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         </is>
       </c>
       <c r="C217" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D217" s="7" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         </is>
       </c>
       <c r="C218" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D218" s="7" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         </is>
       </c>
       <c r="C219" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D219" s="7" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         </is>
       </c>
       <c r="C220" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D220" s="7" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         </is>
       </c>
       <c r="C221" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D221" s="7" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         </is>
       </c>
       <c r="C222" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D222" s="7" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         </is>
       </c>
       <c r="C223" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D223" s="7" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         </is>
       </c>
       <c r="C224" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D224" s="7" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         </is>
       </c>
       <c r="C225" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D225" s="7" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         </is>
       </c>
       <c r="C226" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D226" s="1" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         </is>
       </c>
       <c r="C227" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D227" s="1" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         </is>
       </c>
       <c r="C228" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D228" s="1" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         </is>
       </c>
       <c r="C229" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D229" s="1" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         </is>
       </c>
       <c r="C230" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D230" s="1" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="C231" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D231" s="1" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         </is>
       </c>
       <c r="C232" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D232" s="1" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         </is>
       </c>
       <c r="C233" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D233" s="7" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         </is>
       </c>
       <c r="C234" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D234" s="7" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         </is>
       </c>
       <c r="C235" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D235" s="1" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         </is>
       </c>
       <c r="C236" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D236" s="1" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         </is>
       </c>
       <c r="C237" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D237" s="1" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         </is>
       </c>
       <c r="C238" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D238" s="1" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         </is>
       </c>
       <c r="C239" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D239" s="1" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         </is>
       </c>
       <c r="C240" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D240" s="1" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         </is>
       </c>
       <c r="C241" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D241" s="1" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         </is>
       </c>
       <c r="C242" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D242" s="1" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         </is>
       </c>
       <c r="C243" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D243" s="1" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         </is>
       </c>
       <c r="C244" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D244" s="1" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         </is>
       </c>
       <c r="C245" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D245" s="1" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         </is>
       </c>
       <c r="C246" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D246" s="1" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         </is>
       </c>
       <c r="C247" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D247" s="7" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         </is>
       </c>
       <c r="C248" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D248" s="1" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         </is>
       </c>
       <c r="C249" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D249" s="1" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         </is>
       </c>
       <c r="C250" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D250" s="1" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         </is>
       </c>
       <c r="C251" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D251" s="1" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         </is>
       </c>
       <c r="C252" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D252" s="1" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="C253" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D253" s="1" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         </is>
       </c>
       <c r="C254" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D254" s="1" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         </is>
       </c>
       <c r="C255" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D255" s="1" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         </is>
       </c>
       <c r="C256" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D256" s="1" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         </is>
       </c>
       <c r="C257" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D257" s="1" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         </is>
       </c>
       <c r="C258" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D258" s="1" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         </is>
       </c>
       <c r="C259" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D259" s="1" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         </is>
       </c>
       <c r="C260" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D260" s="1" t="inlineStr">
         <is>
@@ -17524,7 +17524,7 @@
         </is>
       </c>
       <c r="C261" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D261" s="1" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         </is>
       </c>
       <c r="C262" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D262" s="1" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         </is>
       </c>
       <c r="C263" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D263" s="1" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="C264" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D264" s="1" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         </is>
       </c>
       <c r="C265" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D265" s="1" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         </is>
       </c>
       <c r="C266" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D266" s="1" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         </is>
       </c>
       <c r="C267" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D267" s="1" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="C268" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D268" s="1" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         </is>
       </c>
       <c r="C269" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D269" s="1" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         </is>
       </c>
       <c r="C270" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D270" s="1" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         </is>
       </c>
       <c r="C271" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D271" s="1" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         </is>
       </c>
       <c r="C272" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D272" s="1" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         </is>
       </c>
       <c r="C273" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D273" s="1" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         </is>
       </c>
       <c r="C274" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D274" s="1" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         </is>
       </c>
       <c r="C275" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D275" s="1" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         </is>
       </c>
       <c r="C276" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D276" s="1" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         </is>
       </c>
       <c r="C277" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D277" s="1" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         </is>
       </c>
       <c r="C278" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D278" s="1" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         </is>
       </c>
       <c r="C279" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D279" s="1" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         </is>
       </c>
       <c r="C280" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D280" s="1" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         </is>
       </c>
       <c r="C281" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D281" s="1" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         </is>
       </c>
       <c r="C282" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D282" s="1" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         </is>
       </c>
       <c r="C283" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D283" s="1" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         </is>
       </c>
       <c r="C284" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D284" s="1" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         </is>
       </c>
       <c r="C285" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D285" s="1" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         </is>
       </c>
       <c r="C286" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D286" s="7" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         </is>
       </c>
       <c r="C287" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D287" s="7" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         </is>
       </c>
       <c r="C288" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D288" s="7" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         </is>
       </c>
       <c r="C289" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D289" s="7" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         </is>
       </c>
       <c r="C290" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D290" s="7" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         </is>
       </c>
       <c r="C291" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D291" s="7" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         </is>
       </c>
       <c r="C292" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D292" s="7" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         </is>
       </c>
       <c r="C293" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D293" s="7" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         </is>
       </c>
       <c r="C294" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D294" s="7" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         </is>
       </c>
       <c r="C295" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D295" s="7" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         </is>
       </c>
       <c r="C296" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D296" s="7" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         </is>
       </c>
       <c r="C297" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D297" s="7" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         </is>
       </c>
       <c r="C298" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D298" s="7" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         </is>
       </c>
       <c r="C299" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D299" s="7" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         </is>
       </c>
       <c r="C300" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D300" s="7" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
         </is>
       </c>
       <c r="C301" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D301" s="7" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         </is>
       </c>
       <c r="C302" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D302" s="7" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         </is>
       </c>
       <c r="C303" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D303" s="7" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         </is>
       </c>
       <c r="C304" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D304" s="7" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         </is>
       </c>
       <c r="C305" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D305" s="7" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         </is>
       </c>
       <c r="C306" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D306" s="7" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         </is>
       </c>
       <c r="C307" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D307" s="7" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         </is>
       </c>
       <c r="C308" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D308" s="7" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         </is>
       </c>
       <c r="C309" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D309" s="7" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         </is>
       </c>
       <c r="C310" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D310" s="7" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         </is>
       </c>
       <c r="C311" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D311" s="7" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="C312" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D312" s="7" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         </is>
       </c>
       <c r="C313" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D313" s="7" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         </is>
       </c>
       <c r="C314" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D314" s="7" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         </is>
       </c>
       <c r="C315" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D315" s="7" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="C316" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D316" s="7" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         </is>
       </c>
       <c r="C317" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D317" s="7" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         </is>
       </c>
       <c r="C318" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D318" s="7" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         </is>
       </c>
       <c r="C319" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D319" s="7" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="C320" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D320" s="7" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         </is>
       </c>
       <c r="C321" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D321" s="7" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         </is>
       </c>
       <c r="C322" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D322" s="7" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="C323" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D323" s="7" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         </is>
       </c>
       <c r="C324" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D324" s="7" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         </is>
       </c>
       <c r="C325" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D325" s="7" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         </is>
       </c>
       <c r="C326" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D326" s="7" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         </is>
       </c>
       <c r="C327" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D327" s="7" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         </is>
       </c>
       <c r="C328" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D328" s="7" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         </is>
       </c>
       <c r="C329" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D329" s="7" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         </is>
       </c>
       <c r="C330" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D330" s="7" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         </is>
       </c>
       <c r="C331" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D331" s="7" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         </is>
       </c>
       <c r="C332" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D332" s="7" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         </is>
       </c>
       <c r="C333" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D333" s="7" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         </is>
       </c>
       <c r="C334" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D334" s="7" t="inlineStr">
         <is>
@@ -22357,7 +22357,7 @@
         </is>
       </c>
       <c r="C335" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D335" s="7" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         </is>
       </c>
       <c r="C336" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D336" s="7" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         </is>
       </c>
       <c r="C337" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D337" s="7" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         </is>
       </c>
       <c r="C338" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D338" s="7" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         </is>
       </c>
       <c r="C339" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D339" s="7" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         </is>
       </c>
       <c r="C340" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D340" s="7" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         </is>
       </c>
       <c r="C341" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D341" s="7" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         </is>
       </c>
       <c r="C342" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D342" s="7" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="C343" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D343" s="7" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         </is>
       </c>
       <c r="C344" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D344" s="7" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         </is>
       </c>
       <c r="C345" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D345" s="7" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         </is>
       </c>
       <c r="C346" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D346" s="1" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         </is>
       </c>
       <c r="C347" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D347" s="7" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="C348" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D348" s="7" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         </is>
       </c>
       <c r="C349" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D349" s="7" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         </is>
       </c>
       <c r="C350" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D350" s="7" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         </is>
       </c>
       <c r="C351" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D351" s="7" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         </is>
       </c>
       <c r="C352" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D352" s="7" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         </is>
       </c>
       <c r="C353" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D353" s="7" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         </is>
       </c>
       <c r="C354" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D354" s="7" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         </is>
       </c>
       <c r="C355" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D355" s="7" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         </is>
       </c>
       <c r="C356" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D356" s="7" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         </is>
       </c>
       <c r="C357" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D357" s="7" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         </is>
       </c>
       <c r="C358" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D358" s="7" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         </is>
       </c>
       <c r="C359" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D359" s="7" t="inlineStr">
         <is>
@@ -23892,7 +23892,7 @@
         </is>
       </c>
       <c r="C360" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D360" s="7" t="inlineStr">
         <is>
@@ -23952,7 +23952,7 @@
         </is>
       </c>
       <c r="C361" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D361" s="7" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         </is>
       </c>
       <c r="C362" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D362" s="7" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         </is>
       </c>
       <c r="C363" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D363" s="7" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         </is>
       </c>
       <c r="C364" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D364" s="7" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         </is>
       </c>
       <c r="C365" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D365" s="7" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         </is>
       </c>
       <c r="C366" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D366" s="7" t="inlineStr">
         <is>
@@ -24319,7 +24319,7 @@
         </is>
       </c>
       <c r="C367" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D367" s="7" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         </is>
       </c>
       <c r="C368" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D368" s="7" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         </is>
       </c>
       <c r="C369" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D369" s="7" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         </is>
       </c>
       <c r="C370" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D370" s="7" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         </is>
       </c>
       <c r="C371" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D371" s="7" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         </is>
       </c>
       <c r="C372" s="10" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="D372" s="7" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         </is>
       </c>
       <c r="C373" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D373" s="7" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         </is>
       </c>
       <c r="C374" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D374" s="7" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         </is>
       </c>
       <c r="C375" s="22" t="n">
-        <v>46055</v>
+        <v>46086</v>
       </c>
       <c r="D375" s="7" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         </is>
       </c>
       <c r="C376" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D376" s="7" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         </is>
       </c>
       <c r="C377" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D377" s="7" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         </is>
       </c>
       <c r="C378" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D378" s="7" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         </is>
       </c>
       <c r="C379" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D379" s="7" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         </is>
       </c>
       <c r="C380" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D380" s="7" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         </is>
       </c>
       <c r="C381" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D381" s="7" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         </is>
       </c>
       <c r="C382" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D382" s="7" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         </is>
       </c>
       <c r="C383" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D383" s="7" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         </is>
       </c>
       <c r="C384" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D384" s="7" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         </is>
       </c>
       <c r="C385" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D385" s="7" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         </is>
       </c>
       <c r="C386" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D386" s="7" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         </is>
       </c>
       <c r="C387" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D387" s="7" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         </is>
       </c>
       <c r="C388" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D388" s="7" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         </is>
       </c>
       <c r="C389" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D389" s="7" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         </is>
       </c>
       <c r="C390" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D390" s="7" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         </is>
       </c>
       <c r="C391" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D391" s="7" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         </is>
       </c>
       <c r="C392" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D392" s="7" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         </is>
       </c>
       <c r="C393" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D393" s="7" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         </is>
       </c>
       <c r="C394" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D394" s="7" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         </is>
       </c>
       <c r="C395" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D395" s="7" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         </is>
       </c>
       <c r="C396" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D396" s="7" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         </is>
       </c>
       <c r="C397" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D397" s="7" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         </is>
       </c>
       <c r="C398" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D398" s="7" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         </is>
       </c>
       <c r="C399" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D399" s="7" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="C400" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D400" s="7" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         </is>
       </c>
       <c r="C401" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D401" s="7" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         </is>
       </c>
       <c r="C402" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D402" s="7" t="inlineStr">
         <is>
@@ -26570,7 +26570,7 @@
         </is>
       </c>
       <c r="C403" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D403" s="7" t="inlineStr">
         <is>
@@ -26633,7 +26633,7 @@
         </is>
       </c>
       <c r="C404" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D404" s="7" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         </is>
       </c>
       <c r="C405" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D405" s="7" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         </is>
       </c>
       <c r="C406" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D406" s="7" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         </is>
       </c>
       <c r="C407" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D407" s="7" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         </is>
       </c>
       <c r="C408" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D408" s="7" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         </is>
       </c>
       <c r="C409" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D409" s="7" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         </is>
       </c>
       <c r="C410" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D410" s="7" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         </is>
       </c>
       <c r="C411" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D411" s="7" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         </is>
       </c>
       <c r="C412" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D412" s="7" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         </is>
       </c>
       <c r="C413" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D413" s="7" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         </is>
       </c>
       <c r="C414" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D414" s="7" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         </is>
       </c>
       <c r="C415" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D415" s="7" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         </is>
       </c>
       <c r="C416" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D416" s="7" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         </is>
       </c>
       <c r="C417" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D417" s="7" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
         </is>
       </c>
       <c r="C418" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D418" s="7" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         </is>
       </c>
       <c r="C419" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D419" s="7" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         </is>
       </c>
       <c r="C420" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D420" s="7" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         </is>
       </c>
       <c r="C421" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D421" s="7" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         </is>
       </c>
       <c r="C422" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D422" s="7" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         </is>
       </c>
       <c r="C423" s="22" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D423" s="7" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         </is>
       </c>
       <c r="C424" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D424" s="7" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         </is>
       </c>
       <c r="C425" s="22" t="n">
-        <v>46066</v>
+        <v>46086</v>
       </c>
       <c r="D425" s="7" t="inlineStr">
         <is>
@@ -28024,7 +28024,7 @@
         </is>
       </c>
       <c r="C426" s="22" t="n">
-        <v>46067</v>
+        <v>46086</v>
       </c>
       <c r="D426" s="7" t="inlineStr">
         <is>
@@ -28087,7 +28087,7 @@
         </is>
       </c>
       <c r="C427" s="24" t="n">
-        <v>46067</v>
+        <v>46086</v>
       </c>
       <c r="D427" s="7" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         </is>
       </c>
       <c r="C428" s="24" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D428" s="7" t="inlineStr">
         <is>
@@ -28216,11 +28216,11 @@
       </c>
       <c r="B429" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>published</t>
         </is>
       </c>
       <c r="C429" s="24" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D429" s="7" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         </is>
       </c>
       <c r="C430" s="24" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D430" s="7" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         </is>
       </c>
       <c r="C431" s="24" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D431" s="7" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         </is>
       </c>
       <c r="C432" s="24" t="n">
-        <v>46069</v>
+        <v>46086</v>
       </c>
       <c r="D432" s="7" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         </is>
       </c>
       <c r="C433" s="22" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="D433" s="7" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         </is>
       </c>
       <c r="C434" s="24" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="D434" s="7" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         </is>
       </c>
       <c r="C435" s="24" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="D435" s="7" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         </is>
       </c>
       <c r="C436" s="24" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="D436" s="7" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         </is>
       </c>
       <c r="C437" s="24" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="D437" s="7" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         </is>
       </c>
       <c r="C438" s="24" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="D438" s="7" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         </is>
       </c>
       <c r="C439" s="24" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="D439" s="7" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         </is>
       </c>
       <c r="C440" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D440" s="7" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         </is>
       </c>
       <c r="C441" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D441" s="7" t="inlineStr">
         <is>
@@ -29041,7 +29041,7 @@
         </is>
       </c>
       <c r="C442" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D442" s="7" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         </is>
       </c>
       <c r="C443" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D443" s="7" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         </is>
       </c>
       <c r="C444" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D444" s="7" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         </is>
       </c>
       <c r="C445" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D445" s="7" t="inlineStr">
         <is>
@@ -29293,7 +29293,7 @@
         </is>
       </c>
       <c r="C446" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D446" s="7" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         </is>
       </c>
       <c r="C447" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D447" s="7" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         </is>
       </c>
       <c r="C448" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D448" s="7" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         </is>
       </c>
       <c r="C449" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D449" s="7" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         </is>
       </c>
       <c r="C450" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D450" s="7" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         </is>
       </c>
       <c r="C451" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D451" s="7" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         </is>
       </c>
       <c r="C452" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D452" s="7" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         </is>
       </c>
       <c r="C453" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D453" s="7" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         </is>
       </c>
       <c r="C454" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D454" s="7" t="inlineStr">
         <is>
@@ -29860,7 +29860,7 @@
         </is>
       </c>
       <c r="C455" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D455" s="7" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         </is>
       </c>
       <c r="C456" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D456" s="7" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         </is>
       </c>
       <c r="C457" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D457" s="7" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         </is>
       </c>
       <c r="C458" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D458" s="7" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         </is>
       </c>
       <c r="C459" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D459" s="7" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         </is>
       </c>
       <c r="C460" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D460" s="7" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         </is>
       </c>
       <c r="C461" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D461" s="7" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         </is>
       </c>
       <c r="C462" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D462" s="7" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         </is>
       </c>
       <c r="C463" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D463" s="7" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         </is>
       </c>
       <c r="C464" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D464" s="7" t="inlineStr">
         <is>
@@ -30490,7 +30490,7 @@
         </is>
       </c>
       <c r="C465" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D465" s="7" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         </is>
       </c>
       <c r="C466" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D466" s="7" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         </is>
       </c>
       <c r="C467" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D467" s="7" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         </is>
       </c>
       <c r="C468" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D468" s="7" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         </is>
       </c>
       <c r="C469" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D469" s="7" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         </is>
       </c>
       <c r="C470" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D470" s="7" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         </is>
       </c>
       <c r="C471" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D471" s="7" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         </is>
       </c>
       <c r="C472" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D472" s="7" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
         </is>
       </c>
       <c r="C473" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D473" s="7" t="inlineStr">
         <is>
@@ -31057,7 +31057,7 @@
         </is>
       </c>
       <c r="C474" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D474" s="7" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         </is>
       </c>
       <c r="C475" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D475" s="7" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         </is>
       </c>
       <c r="C476" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D476" s="7" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         </is>
       </c>
       <c r="C477" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D477" s="7" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         </is>
       </c>
       <c r="C478" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D478" s="7" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         </is>
       </c>
       <c r="C479" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D479" s="7" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         </is>
       </c>
       <c r="C480" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D480" s="7" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         </is>
       </c>
       <c r="C481" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D481" s="7" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         </is>
       </c>
       <c r="C482" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D482" s="7" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         </is>
       </c>
       <c r="C483" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D483" s="7" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         </is>
       </c>
       <c r="C484" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D484" s="7" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         </is>
       </c>
       <c r="C485" s="22" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D485" s="7" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         </is>
       </c>
       <c r="C486" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D486" s="26" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         </is>
       </c>
       <c r="C487" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D487" s="26" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         </is>
       </c>
       <c r="C488" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D488" s="26" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         </is>
       </c>
       <c r="C489" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D489" s="1" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         </is>
       </c>
       <c r="C490" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D490" s="1" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         </is>
       </c>
       <c r="C491" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D491" s="1" t="inlineStr">
         <is>
@@ -32185,7 +32185,7 @@
         </is>
       </c>
       <c r="C492" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D492" s="1" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         </is>
       </c>
       <c r="C493" s="10" t="n">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="D493" s="1" t="inlineStr">
         <is>
@@ -32303,7 +32303,7 @@
         </is>
       </c>
       <c r="C494" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D494" s="7" t="inlineStr">
         <is>
@@ -34279,7 +34279,7 @@
         </is>
       </c>
       <c r="C536" s="10" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D536" s="7" t="inlineStr">
         <is>

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -14,7 +14,7 @@
     <sheet name="SeriesSort" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Works'!$A$1:$Y$550</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Works'!$A$1:$Y$581</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -575,7 +575,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="21.83203125" customWidth="1" style="4" min="1" max="1"/>
     <col width="77.33203125" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
@@ -1326,7 +1326,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Z581"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="11.33203125" customWidth="1" style="7" min="1" max="1"/>
     <col width="13.33203125" customWidth="1" style="7" min="2" max="2"/>
@@ -1351,8 +1351,8 @@
     <col width="15.1640625" customWidth="1" style="7" min="23" max="23"/>
     <col width="21.5" customWidth="1" style="7" min="24" max="24"/>
     <col width="26.83203125" customWidth="1" style="7" min="25" max="25"/>
-    <col width="10.83203125" customWidth="1" style="7" min="27" max="71"/>
-    <col width="10.83203125" customWidth="1" style="7" min="72" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="7" min="27" max="74"/>
+    <col width="10.83203125" customWidth="1" style="7" min="75" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="6">
@@ -36493,6 +36493,14 @@
           <t>00526</t>
         </is>
       </c>
+      <c r="B527" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C527" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D527" s="7" t="inlineStr">
         <is>
           <t>2-bodies</t>
@@ -36511,6 +36519,11 @@
       <c r="G527" s="7" t="inlineStr">
         <is>
           <t>00526 - body.jpg</t>
+        </is>
+      </c>
+      <c r="H527" s="7" t="inlineStr">
+        <is>
+          <t>body</t>
         </is>
       </c>
       <c r="I527" s="7" t="n">
@@ -36543,6 +36556,14 @@
           <t>00527</t>
         </is>
       </c>
+      <c r="B528" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C528" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D528" s="7" t="inlineStr">
         <is>
           <t>2-bodies</t>
@@ -36561,6 +36582,11 @@
       <c r="G528" s="7" t="inlineStr">
         <is>
           <t>00527 - body.jpg</t>
+        </is>
+      </c>
+      <c r="H528" s="7" t="inlineStr">
+        <is>
+          <t>body</t>
         </is>
       </c>
       <c r="I528" s="7" t="n">
@@ -36593,6 +36619,14 @@
           <t>00528</t>
         </is>
       </c>
+      <c r="B529" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C529" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D529" s="7" t="inlineStr">
         <is>
           <t>2-bodies</t>
@@ -36611,6 +36645,11 @@
       <c r="G529" s="7" t="inlineStr">
         <is>
           <t>00528 - body.jpg</t>
+        </is>
+      </c>
+      <c r="H529" s="7" t="inlineStr">
+        <is>
+          <t>body</t>
         </is>
       </c>
       <c r="I529" s="7" t="n">
@@ -36642,6 +36681,14 @@
           <t>00529</t>
         </is>
       </c>
+      <c r="B530" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C530" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D530" s="7" t="inlineStr">
         <is>
           <t>2-bodies</t>
@@ -36659,7 +36706,12 @@
       </c>
       <c r="G530" s="7" t="inlineStr">
         <is>
-          <t>00529 - body.jpg</t>
+          <t>00529 - body residue.jpg</t>
+        </is>
+      </c>
+      <c r="H530" s="7" t="inlineStr">
+        <is>
+          <t>body residue</t>
         </is>
       </c>
       <c r="I530" s="7" t="n">
@@ -36691,6 +36743,14 @@
           <t>00530</t>
         </is>
       </c>
+      <c r="B531" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C531" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D531" s="7" t="inlineStr">
         <is>
           <t>2-bodies</t>
@@ -36708,7 +36768,12 @@
       </c>
       <c r="G531" s="7" t="inlineStr">
         <is>
-          <t>00530 - body.jpg</t>
+          <t>00530 - body curves.jpg</t>
+        </is>
+      </c>
+      <c r="H531" s="7" t="inlineStr">
+        <is>
+          <t>body curves</t>
         </is>
       </c>
       <c r="I531" s="7" t="n">
@@ -36740,6 +36805,14 @@
           <t>00531</t>
         </is>
       </c>
+      <c r="B532" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C532" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D532" s="7" t="inlineStr">
         <is>
           <t>2-bodies</t>
@@ -36758,6 +36831,11 @@
       <c r="G532" s="7" t="inlineStr">
         <is>
           <t>00531 - body monoprint.jpg</t>
+        </is>
+      </c>
+      <c r="H532" s="7" t="inlineStr">
+        <is>
+          <t>body monoprint</t>
         </is>
       </c>
       <c r="I532" s="7" t="n">
@@ -36789,6 +36867,14 @@
           <t>00532</t>
         </is>
       </c>
+      <c r="B533" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C533" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D533" s="7" t="inlineStr">
         <is>
           <t>2-bodies</t>
@@ -36807,6 +36893,11 @@
       <c r="G533" s="7" t="inlineStr">
         <is>
           <t>00532 - body monoprint petals.jpg</t>
+        </is>
+      </c>
+      <c r="H533" s="7" t="inlineStr">
+        <is>
+          <t>body monoprint petals</t>
         </is>
       </c>
       <c r="I533" s="7" t="n">
@@ -36838,6 +36929,14 @@
           <t>00533</t>
         </is>
       </c>
+      <c r="B534" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C534" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D534" s="7" t="inlineStr">
         <is>
           <t>2-bodies</t>
@@ -36855,7 +36954,12 @@
       </c>
       <c r="G534" s="7" t="inlineStr">
         <is>
-          <t>00553 - 2 bodies monoprint.jpg</t>
+          <t>00533 - 2 bodies monoprint.jpg</t>
+        </is>
+      </c>
+      <c r="H534" s="7" t="inlineStr">
+        <is>
+          <t>2 bodies monoprint</t>
         </is>
       </c>
       <c r="I534" s="7" t="n">
@@ -36887,6 +36991,14 @@
           <t>00534</t>
         </is>
       </c>
+      <c r="B535" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C535" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D535" s="7" t="inlineStr">
         <is>
           <t>2-bodies</t>
@@ -36904,14 +37016,19 @@
       </c>
       <c r="G535" s="7" t="inlineStr">
         <is>
-          <t>00554 - 2 bodies monoprint.jpg</t>
+          <t>00534 - 2 bodies monoprint.jpg</t>
+        </is>
+      </c>
+      <c r="H535" s="7" t="inlineStr">
+        <is>
+          <t>2 bodies monoprint</t>
         </is>
       </c>
       <c r="I535" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J535" s="7" t="n">
         <v>64</v>
-      </c>
-      <c r="J535" s="7" t="n">
-        <v>50</v>
       </c>
       <c r="K535" s="7" t="n">
         <v>2025</v>
@@ -37634,6 +37751,14 @@
           <t>00546</t>
         </is>
       </c>
+      <c r="B547" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C547" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D547" s="7" t="inlineStr">
         <is>
           <t>tree</t>
@@ -37650,6 +37775,11 @@
         </is>
       </c>
       <c r="G547" s="7" t="inlineStr">
+        <is>
+          <t>tree.jpg</t>
+        </is>
+      </c>
+      <c r="H547" s="7" t="inlineStr">
         <is>
           <t>tree.jpg</t>
         </is>
@@ -37660,6 +37790,12 @@
       <c r="J547" s="7" t="n">
         <v>20.9</v>
       </c>
+      <c r="K547" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L547" s="7" t="n">
+        <v>2024</v>
+      </c>
       <c r="M547" s="7" t="inlineStr">
         <is>
           <t>photograph</t>
@@ -37682,6 +37818,14 @@
           <t>00547</t>
         </is>
       </c>
+      <c r="B548" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C548" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D548" s="7" t="inlineStr">
         <is>
           <t>tree</t>
@@ -37698,6 +37842,11 @@
         </is>
       </c>
       <c r="G548" s="7" t="inlineStr">
+        <is>
+          <t>tree (tint).jpg</t>
+        </is>
+      </c>
+      <c r="H548" s="7" t="inlineStr">
         <is>
           <t>tree (tint).jpg</t>
         </is>
@@ -37708,6 +37857,12 @@
       <c r="J548" s="7" t="n">
         <v>22.9</v>
       </c>
+      <c r="K548" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L548" s="7" t="n">
+        <v>2024</v>
+      </c>
       <c r="M548" s="7" t="inlineStr">
         <is>
           <t>photograph</t>
@@ -37728,6 +37883,14 @@
           <t>00548</t>
         </is>
       </c>
+      <c r="B549" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C549" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D549" s="7" t="inlineStr">
         <is>
           <t>tree</t>
@@ -37744,6 +37907,11 @@
         </is>
       </c>
       <c r="G549" s="7" t="inlineStr">
+        <is>
+          <t>tree source.jpg</t>
+        </is>
+      </c>
+      <c r="H549" s="7" t="inlineStr">
         <is>
           <t>tree source.jpg</t>
         </is>
@@ -37754,6 +37922,12 @@
       <c r="J549" s="7" t="n">
         <v>24</v>
       </c>
+      <c r="K549" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L549" s="7" t="n">
+        <v>2024</v>
+      </c>
       <c r="M549" s="7" t="inlineStr">
         <is>
           <t>digital composite</t>
@@ -39807,7 +39981,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y550"/>
+  <autoFilter ref="A1:Y581"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -39819,8 +39993,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <dimension ref="A1:I42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="31.83203125" customWidth="1" style="1" min="1" max="1"/>
     <col width="43.1640625" customWidth="1" style="1" min="2" max="2"/>
@@ -39831,8 +40005,8 @@
     <col width="21" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
     <col width="21" customWidth="1" style="7" min="8" max="8"/>
     <col width="51" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" style="1" min="10" max="55"/>
-    <col width="10.83203125" customWidth="1" style="1" min="56" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="1" min="10" max="58"/>
+    <col width="10.83203125" customWidth="1" style="1" min="59" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -39898,6 +40072,14 @@
           <t>primary</t>
         </is>
       </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="F2" s="1" t="n">
         <v>2025</v>
       </c>
@@ -41148,6 +41330,42 @@
       <c r="G41" s="7" t="inlineStr">
         <is>
           <t>2008, 2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>tree</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>tree</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="F42" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H42" s="16" t="inlineStr">
+        <is>
+          <t>00546</t>
         </is>
       </c>
     </row>
@@ -41163,8 +41381,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J533"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <dimension ref="A1:J569"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="9.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -62967,7 +63185,7 @@
     <row r="532">
       <c r="A532" s="16" t="inlineStr">
         <is>
-          <t>00571</t>
+          <t>00536</t>
         </is>
       </c>
       <c r="B532" s="5" t="inlineStr">
@@ -62977,17 +63195,17 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>details</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>2012-01-06 - 12-30-44.jpg</t>
+          <t>model 2 - 001.jpg</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>2012-01-06 - 12-30-44</t>
+          <t>model 2 - 001</t>
         </is>
       </c>
       <c r="F532" s="1" t="inlineStr">
@@ -62999,16 +63217,16 @@
         <v>46094</v>
       </c>
       <c r="H532" t="n">
-        <v>3264</v>
+        <v>3031</v>
       </c>
       <c r="I532" t="n">
-        <v>2448</v>
+        <v>4629</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="16" t="inlineStr">
         <is>
-          <t>00536</t>
+          <t>00571</t>
         </is>
       </c>
       <c r="B533" s="5" t="inlineStr">
@@ -63018,17 +63236,17 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>details</t>
+          <t>working</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>model 2 - 001.jpg</t>
+          <t>2012-01-06 - 12-30-44.jpg</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>model 2 - 001</t>
+          <t>2012-01-06 - 12-30-44</t>
         </is>
       </c>
       <c r="F533" s="1" t="inlineStr">
@@ -63040,10 +63258,1486 @@
         <v>46094</v>
       </c>
       <c r="H533" t="n">
-        <v>3031</v>
+        <v>3264</v>
       </c>
       <c r="I533" t="n">
-        <v>4629</v>
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>00526</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>00526-001.jpg</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F534" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G534" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H534" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I534" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>00526</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>00526-002.jpg</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F535" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G535" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H535" t="n">
+        <v>3024</v>
+      </c>
+      <c r="I535" t="n">
+        <v>4032</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>00526</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>00526-003.jpg</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F536" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G536" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H536" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I536" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>00527</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>00527-001.jpg</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F537" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G537" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H537" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I537" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>00527</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>00527-002.jpg</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F538" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G538" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H538" t="n">
+        <v>3024</v>
+      </c>
+      <c r="I538" t="n">
+        <v>4032</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>00527</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>00527-003.jpg</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F539" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G539" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H539" t="n">
+        <v>3024</v>
+      </c>
+      <c r="I539" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>00528</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>00528-001.jpg</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F540" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G540" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H540" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I540" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>00528</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>00528-002.jpg</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F541" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G541" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H541" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I541" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>00528</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>00528-003.jpg</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F542" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G542" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H542" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I542" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>00529</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>00529-001.jpg</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F543" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G543" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H543" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I543" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>00529</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>00529-002.jpg</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F544" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G544" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H544" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I544" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>00529</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>00529-003.jpg</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F545" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G545" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H545" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I545" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>00529</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>00529-004.jpg</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F546" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G546" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H546" t="n">
+        <v>3024</v>
+      </c>
+      <c r="I546" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>00529</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>00529-005.jpg</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F547" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G547" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H547" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I547" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>00529</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>00529-006.jpg</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F548" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G548" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H548" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I548" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>00530</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>00530-001.jpg</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F549" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G549" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H549" t="n">
+        <v>3024</v>
+      </c>
+      <c r="I549" t="n">
+        <v>4032</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>00530</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>00530-002.jpg</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F550" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G550" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H550" t="n">
+        <v>3024</v>
+      </c>
+      <c r="I550" t="n">
+        <v>4032</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>00530</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>00530-003.jpg</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F551" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G551" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H551" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I551" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>00530</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>00530-004.jpg</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F552" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G552" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H552" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I552" t="n">
+        <v>2667</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>00531</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>00531-001.jpg</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F553" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G553" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H553" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I553" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>00531</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>00531-002.jpg</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F554" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G554" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H554" t="n">
+        <v>3024</v>
+      </c>
+      <c r="I554" t="n">
+        <v>4032</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>00531</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>00531-003.jpg</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F555" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G555" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H555" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I555" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>00531</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>00531-004.jpg</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F556" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G556" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H556" t="n">
+        <v>3024</v>
+      </c>
+      <c r="I556" t="n">
+        <v>4032</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>00532</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>00532-001.jpg</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F557" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G557" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H557" t="n">
+        <v>3024</v>
+      </c>
+      <c r="I557" t="n">
+        <v>4032</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>00532</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>00532-002.jpg</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F558" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G558" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H558" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I558" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>00532</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>00532-003.jpg</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F559" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G559" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H559" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I559" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>00532</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>00532-004.jpg</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F560" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G560" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H560" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I560" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>00533</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>00533-001.jpg</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F561" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G561" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H561" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I561" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>00533</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>00533-002.jpg</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F562" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G562" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H562" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I562" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>00533</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>00533-003.jpg</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F563" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G563" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H563" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I563" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>00533</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>00533-004.jpg</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F564" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G564" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H564" t="n">
+        <v>3024</v>
+      </c>
+      <c r="I564" t="n">
+        <v>4032</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>00533</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>00533-005.jpg</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F565" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G565" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H565" t="n">
+        <v>3024</v>
+      </c>
+      <c r="I565" t="n">
+        <v>4032</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>00534</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>00534-001.jpg</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F566" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G566" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H566" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I566" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>00534</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>00534-002.jpg</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F567" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G567" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H567" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I567" t="n">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>00534</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>00534-003.jpg</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F568" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G568" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H568" t="n">
+        <v>3024</v>
+      </c>
+      <c r="I568" t="n">
+        <v>4032</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>00534</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>00534-004.jpg</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>body detail</t>
+        </is>
+      </c>
+      <c r="F569" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G569" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H569" t="n">
+        <v>4032</v>
+      </c>
+      <c r="I569" t="n">
+        <v>2688</v>
       </c>
     </row>
   </sheetData>
@@ -63058,7 +64752,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" outlineLevelCol="0"/>
   <cols>
     <col width="24.1640625" customWidth="1" style="13" min="1" max="1"/>
     <col width="34.83203125" customWidth="1" style="13" min="2" max="2"/>
@@ -63071,8 +64765,8 @@
     <col width="11.33203125" bestFit="1" customWidth="1" style="13" min="9" max="9"/>
     <col width="12.1640625" bestFit="1" customWidth="1" style="13" min="10" max="10"/>
     <col width="33.6640625" customWidth="1" style="13" min="11" max="11"/>
-    <col width="10.83203125" customWidth="1" style="13" min="12" max="48"/>
-    <col width="10.83203125" customWidth="1" style="13" min="49" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="13" min="12" max="51"/>
+    <col width="10.83203125" customWidth="1" style="13" min="52" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -65234,7 +66928,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
   <cols>
     <col width="26.33203125" customWidth="1" min="1" max="1"/>
     <col width="38.5" customWidth="1" min="2" max="2"/>

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -14,7 +14,7 @@
     <sheet name="SeriesSort" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Works'!$A$1:$Y$581</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Works'!$A$1:$Y$582</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,10 +22,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -126,7 +127,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -174,6 +175,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1325,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z581"/>
+  <dimension ref="A1:Z582"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="11.33203125" customWidth="1" style="7" min="1" max="1"/>
@@ -1351,8 +1353,8 @@
     <col width="15.1640625" customWidth="1" style="7" min="23" max="23"/>
     <col width="21.5" customWidth="1" style="7" min="24" max="24"/>
     <col width="26.83203125" customWidth="1" style="7" min="25" max="25"/>
-    <col width="10.83203125" customWidth="1" style="7" min="27" max="74"/>
-    <col width="10.83203125" customWidth="1" style="7" min="75" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="7" min="27" max="75"/>
+    <col width="10.83203125" customWidth="1" style="7" min="76" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="6">
@@ -27095,7 +27097,14 @@
           <t>00385</t>
         </is>
       </c>
-      <c r="C386" s="10" t="n"/>
+      <c r="B386" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C386" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D386" s="7" t="inlineStr">
         <is>
           <t>nerve-forms</t>
@@ -27154,7 +27163,14 @@
           <t>00386</t>
         </is>
       </c>
-      <c r="C387" s="10" t="n"/>
+      <c r="B387" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C387" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D387" s="7" t="inlineStr">
         <is>
           <t>nerve-forms</t>
@@ -27213,7 +27229,14 @@
           <t>00387</t>
         </is>
       </c>
-      <c r="C388" s="10" t="n"/>
+      <c r="B388" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C388" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D388" s="7" t="inlineStr">
         <is>
           <t>nerve-forms</t>
@@ -36440,6 +36463,14 @@
           <t>00525</t>
         </is>
       </c>
+      <c r="B526" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C526" s="25" t="n">
+        <v>46094</v>
+      </c>
       <c r="D526" s="7" t="inlineStr">
         <is>
           <t>nerve-forms</t>
@@ -36458,6 +36489,11 @@
       <c r="G526" s="7" t="inlineStr">
         <is>
           <t>nerve 2.jpg</t>
+        </is>
+      </c>
+      <c r="H526" s="7" t="inlineStr">
+        <is>
+          <t>nerve 2</t>
         </is>
       </c>
       <c r="I526" s="7" t="n">
@@ -39980,8 +40016,70 @@
         <v>7</v>
       </c>
     </row>
+    <row r="582">
+      <c r="A582" s="16" t="inlineStr">
+        <is>
+          <t>00581</t>
+        </is>
+      </c>
+      <c r="B582" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C582" s="25" t="n">
+        <v>46094</v>
+      </c>
+      <c r="D582" s="7" t="inlineStr">
+        <is>
+          <t>nerve-forms</t>
+        </is>
+      </c>
+      <c r="E582" s="7" t="inlineStr">
+        <is>
+          <t>nerve-forms</t>
+        </is>
+      </c>
+      <c r="F582" s="7" t="inlineStr">
+        <is>
+          <t>nerve forms</t>
+        </is>
+      </c>
+      <c r="G582" s="7" t="inlineStr">
+        <is>
+          <t>nerve forms.jpg</t>
+        </is>
+      </c>
+      <c r="H582" s="7" t="inlineStr">
+        <is>
+          <t>nerve forms</t>
+        </is>
+      </c>
+      <c r="I582" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="J582" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="K582" s="7" t="n">
+        <v>2004</v>
+      </c>
+      <c r="L582" s="7" t="n">
+        <v>2004</v>
+      </c>
+      <c r="M582" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="N582" s="7" t="inlineStr">
+        <is>
+          <t>digital c-type print</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y581"/>
+  <autoFilter ref="A1:Y582"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -40005,8 +40103,8 @@
     <col width="21" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
     <col width="21" customWidth="1" style="7" min="8" max="8"/>
     <col width="51" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" style="1" min="10" max="58"/>
-    <col width="10.83203125" customWidth="1" style="1" min="59" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="1" min="10" max="59"/>
+    <col width="10.83203125" customWidth="1" style="1" min="60" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -41136,15 +41234,28 @@
           <t>primary</t>
         </is>
       </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="n">
+        <v>46094</v>
+      </c>
       <c r="F35" s="1" t="n">
         <v>2004</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>2004</v>
       </c>
+      <c r="H35" s="16" t="inlineStr">
+        <is>
+          <t>00581</t>
+        </is>
+      </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>add remaining works and series text</t>
+          <t>add videos</t>
         </is>
       </c>
     </row>
@@ -64765,8 +64876,8 @@
     <col width="11.33203125" bestFit="1" customWidth="1" style="13" min="9" max="9"/>
     <col width="12.1640625" bestFit="1" customWidth="1" style="13" min="10" max="10"/>
     <col width="33.6640625" customWidth="1" style="13" min="11" max="11"/>
-    <col width="10.83203125" customWidth="1" style="13" min="12" max="51"/>
-    <col width="10.83203125" customWidth="1" style="13" min="52" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="13" min="12" max="52"/>
+    <col width="10.83203125" customWidth="1" style="13" min="53" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20580" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20580" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,10 +22,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -126,7 +127,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -174,6 +175,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +577,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="21.83203125" customWidth="1" style="4" min="1" max="1"/>
     <col width="77.33203125" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
@@ -1326,7 +1328,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Z616"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="11.33203125" customWidth="1" style="7" min="1" max="1"/>
     <col width="13.33203125" customWidth="1" style="7" min="2" max="2"/>
@@ -1351,8 +1353,8 @@
     <col width="15.1640625" customWidth="1" style="7" min="23" max="23"/>
     <col width="21.5" customWidth="1" style="7" min="24" max="24"/>
     <col width="26.83203125" customWidth="1" style="7" min="25" max="25"/>
-    <col width="10.83203125" customWidth="1" style="7" min="27" max="79"/>
-    <col width="10.83203125" customWidth="1" style="7" min="80" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="7" min="27" max="80"/>
+    <col width="10.83203125" customWidth="1" style="7" min="81" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="6">
@@ -27293,7 +27295,14 @@
           <t>00388</t>
         </is>
       </c>
-      <c r="C389" s="10" t="n"/>
+      <c r="B389" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C389" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D389" s="7" t="inlineStr">
         <is>
           <t>lipseyes</t>
@@ -42310,7 +42319,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="31.83203125" customWidth="1" style="1" min="1" max="1"/>
     <col width="43.1640625" customWidth="1" style="1" min="2" max="2"/>
@@ -42321,8 +42330,8 @@
     <col width="21" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
     <col width="21" customWidth="1" style="7" min="8" max="8"/>
     <col width="51" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" style="1" min="10" max="63"/>
-    <col width="10.83203125" customWidth="1" style="1" min="64" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="1" min="10" max="64"/>
+    <col width="10.83203125" customWidth="1" style="1" min="65" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -43163,24 +43172,37 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>lips-eyes</t>
+          <t>lipseyes</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>lips eyes</t>
+          <t>lipseyes</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="n">
+        <v>46094</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>2003</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>2003</v>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>00388</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -43754,7 +43776,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J575"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="9.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -67370,7 +67392,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" outlineLevelCol="0"/>
   <cols>
     <col width="24.1640625" customWidth="1" style="13" min="1" max="1"/>
     <col width="34.83203125" customWidth="1" style="13" min="2" max="2"/>
@@ -67383,8 +67405,8 @@
     <col width="11.33203125" bestFit="1" customWidth="1" style="13" min="9" max="9"/>
     <col width="12.1640625" bestFit="1" customWidth="1" style="13" min="10" max="10"/>
     <col width="33.6640625" customWidth="1" style="13" min="11" max="11"/>
-    <col width="10.83203125" customWidth="1" style="13" min="12" max="56"/>
-    <col width="10.83203125" customWidth="1" style="13" min="57" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="13" min="12" max="57"/>
+    <col width="10.83203125" customWidth="1" style="13" min="58" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -69546,7 +69568,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
   <cols>
     <col width="26.33203125" customWidth="1" min="1" max="1"/>
     <col width="38.5" customWidth="1" min="2" max="2"/>

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -14,7 +14,7 @@
     <sheet name="SeriesSort" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Works'!$A$1:$Y$616</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Works'!$A$1:$Y$618</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,7 +28,7 @@
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -95,6 +95,12 @@
       <family val="2"/>
       <color rgb="FF000000"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1327,7 +1333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z616"/>
+  <dimension ref="A1:Z618"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="11.33203125" customWidth="1" style="7" min="1" max="1"/>
@@ -1353,8 +1359,8 @@
     <col width="15.1640625" customWidth="1" style="7" min="23" max="23"/>
     <col width="21.5" customWidth="1" style="7" min="24" max="24"/>
     <col width="26.83203125" customWidth="1" style="7" min="25" max="25"/>
-    <col width="10.83203125" customWidth="1" style="7" min="27" max="80"/>
-    <col width="10.83203125" customWidth="1" style="7" min="81" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="7" min="27" max="81"/>
+    <col width="10.83203125" customWidth="1" style="7" min="82" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="6">
@@ -27468,7 +27474,14 @@
           <t>00391</t>
         </is>
       </c>
-      <c r="C392" s="10" t="n"/>
+      <c r="B392" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C392" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D392" s="1" t="inlineStr">
         <is>
           <t>composite-blue-red-smoke</t>
@@ -42305,8 +42318,140 @@
         </is>
       </c>
     </row>
+    <row r="617">
+      <c r="A617" s="16" t="inlineStr">
+        <is>
+          <t>00616</t>
+        </is>
+      </c>
+      <c r="B617" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C617" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="D617" s="1" t="inlineStr">
+        <is>
+          <t>composite-blue-red-smoke</t>
+        </is>
+      </c>
+      <c r="E617" s="1" t="inlineStr">
+        <is>
+          <t>composite-blue-red-smoke</t>
+        </is>
+      </c>
+      <c r="F617" s="1" t="inlineStr">
+        <is>
+          <t>composite (blue red smoke)</t>
+        </is>
+      </c>
+      <c r="G617" s="7" t="inlineStr">
+        <is>
+          <t>composite (smoke).jpg</t>
+        </is>
+      </c>
+      <c r="H617" s="7" t="inlineStr">
+        <is>
+          <t>composite (smoke)</t>
+        </is>
+      </c>
+      <c r="I617" s="7" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="J617" s="7" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="K617" s="7" t="n">
+        <v>2004</v>
+      </c>
+      <c r="L617" s="7" t="n">
+        <v>2004</v>
+      </c>
+      <c r="M617" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="N617" s="7" t="inlineStr">
+        <is>
+          <t>digital c-type print</t>
+        </is>
+      </c>
+      <c r="O617" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="P617" s="7" t="inlineStr">
+        <is>
+          <t>signed 2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="16" t="inlineStr">
+        <is>
+          <t>00617</t>
+        </is>
+      </c>
+      <c r="B618" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C618" s="25" t="n">
+        <v>46094</v>
+      </c>
+      <c r="D618" s="1" t="inlineStr">
+        <is>
+          <t>composite-blue-red-smoke</t>
+        </is>
+      </c>
+      <c r="E618" s="1" t="inlineStr">
+        <is>
+          <t>composite-blue-red-smoke</t>
+        </is>
+      </c>
+      <c r="F618" s="1" t="inlineStr">
+        <is>
+          <t>composite (blue red smoke)</t>
+        </is>
+      </c>
+      <c r="G618" s="7" t="inlineStr">
+        <is>
+          <t>composite (red).jpg</t>
+        </is>
+      </c>
+      <c r="H618" s="7" t="inlineStr">
+        <is>
+          <t>composite (red)</t>
+        </is>
+      </c>
+      <c r="I618" s="7" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="J618" s="7" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="K618" s="7" t="n">
+        <v>2004</v>
+      </c>
+      <c r="L618" s="7" t="n">
+        <v>2004</v>
+      </c>
+      <c r="M618" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="N618" s="7" t="inlineStr">
+        <is>
+          <t>digital c-type print</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y616"/>
+  <autoFilter ref="A1:Y618"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -42330,8 +42475,8 @@
     <col width="21" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
     <col width="21" customWidth="1" style="7" min="8" max="8"/>
     <col width="51" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" style="1" min="10" max="64"/>
-    <col width="10.83203125" customWidth="1" style="1" min="65" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="1" min="10" max="65"/>
+    <col width="10.83203125" customWidth="1" style="1" min="66" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -42615,12 +42760,25 @@
           <t>primary</t>
         </is>
       </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>46094</v>
+      </c>
       <c r="F9" s="1" t="n">
         <v>2004</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>2004</v>
       </c>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>00391</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -43190,7 +43348,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E26" s="25" t="n">
+      <c r="E26" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="F26" s="1" t="n">
@@ -67405,8 +67563,8 @@
     <col width="11.33203125" bestFit="1" customWidth="1" style="13" min="9" max="9"/>
     <col width="12.1640625" bestFit="1" customWidth="1" style="13" min="10" max="10"/>
     <col width="33.6640625" customWidth="1" style="13" min="11" max="11"/>
-    <col width="10.83203125" customWidth="1" style="13" min="12" max="57"/>
-    <col width="10.83203125" customWidth="1" style="13" min="58" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="13" min="12" max="58"/>
+    <col width="10.83203125" customWidth="1" style="13" min="59" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20580" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20580" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <sheet name="SeriesSort" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Works'!$A$1:$Y$618</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Works'!$A$1:$Y$620</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,13 +22,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -96,12 +95,6 @@
       <color rgb="FF000000"/>
       <sz val="13"/>
     </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -133,7 +126,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,7 +174,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -583,7 +575,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="21.83203125" customWidth="1" style="4" min="1" max="1"/>
     <col width="77.33203125" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
@@ -1333,8 +1325,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z618"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <dimension ref="A1:Z620"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="11.33203125" customWidth="1" style="7" min="1" max="1"/>
     <col width="13.33203125" customWidth="1" style="7" min="2" max="2"/>
@@ -1359,8 +1351,8 @@
     <col width="15.1640625" customWidth="1" style="7" min="23" max="23"/>
     <col width="21.5" customWidth="1" style="7" min="24" max="24"/>
     <col width="26.83203125" customWidth="1" style="7" min="25" max="25"/>
-    <col width="10.83203125" customWidth="1" style="7" min="27" max="81"/>
-    <col width="10.83203125" customWidth="1" style="7" min="82" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="7" min="27" max="83"/>
+    <col width="10.83203125" customWidth="1" style="7" min="84" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="6">
@@ -27415,7 +27407,14 @@
           <t>00390</t>
         </is>
       </c>
-      <c r="C391" s="10" t="n"/>
+      <c r="B391" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C391" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D391" s="7" t="inlineStr">
         <is>
           <t>forest</t>
@@ -27540,7 +27539,14 @@
           <t>00392</t>
         </is>
       </c>
-      <c r="C393" s="10" t="n"/>
+      <c r="B393" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C393" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D393" s="7" t="inlineStr">
         <is>
           <t>forest</t>
@@ -27599,7 +27605,14 @@
           <t>00393</t>
         </is>
       </c>
-      <c r="C394" s="10" t="n"/>
+      <c r="B394" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C394" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D394" s="7" t="inlineStr">
         <is>
           <t>forest</t>
@@ -42399,7 +42412,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C618" s="25" t="n">
+      <c r="C618" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="D618" s="1" t="inlineStr">
@@ -42450,8 +42463,132 @@
         </is>
       </c>
     </row>
+    <row r="619">
+      <c r="A619" s="16" t="inlineStr">
+        <is>
+          <t>00618</t>
+        </is>
+      </c>
+      <c r="B619" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C619" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="D619" s="7" t="inlineStr">
+        <is>
+          <t>forest</t>
+        </is>
+      </c>
+      <c r="E619" s="7" t="inlineStr">
+        <is>
+          <t>forest</t>
+        </is>
+      </c>
+      <c r="F619" s="7" t="inlineStr">
+        <is>
+          <t>forest</t>
+        </is>
+      </c>
+      <c r="G619" s="7" t="inlineStr">
+        <is>
+          <t>forest 2.jpg</t>
+        </is>
+      </c>
+      <c r="H619" s="7" t="inlineStr">
+        <is>
+          <t>forest 2</t>
+        </is>
+      </c>
+      <c r="I619" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="J619" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K619" s="7" t="n">
+        <v>2003</v>
+      </c>
+      <c r="L619" s="7" t="n">
+        <v>2003</v>
+      </c>
+      <c r="M619" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="N619" s="7" t="inlineStr">
+        <is>
+          <t>digital c-type print</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="16" t="inlineStr">
+        <is>
+          <t>00619</t>
+        </is>
+      </c>
+      <c r="B620" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C620" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="D620" s="7" t="inlineStr">
+        <is>
+          <t>forest</t>
+        </is>
+      </c>
+      <c r="E620" s="7" t="inlineStr">
+        <is>
+          <t>forest</t>
+        </is>
+      </c>
+      <c r="F620" s="7" t="inlineStr">
+        <is>
+          <t>forest</t>
+        </is>
+      </c>
+      <c r="G620" s="7" t="inlineStr">
+        <is>
+          <t>body 1.jpg</t>
+        </is>
+      </c>
+      <c r="H620" s="7" t="inlineStr">
+        <is>
+          <t>body 1</t>
+        </is>
+      </c>
+      <c r="I620" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="J620" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K620" s="7" t="n">
+        <v>2003</v>
+      </c>
+      <c r="L620" s="7" t="n">
+        <v>2003</v>
+      </c>
+      <c r="M620" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="N620" s="7" t="inlineStr">
+        <is>
+          <t>digital c-type print</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y618"/>
+  <autoFilter ref="A1:Y620"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -42464,7 +42601,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="31.83203125" customWidth="1" style="1" min="1" max="1"/>
     <col width="43.1640625" customWidth="1" style="1" min="2" max="2"/>
@@ -42475,8 +42612,8 @@
     <col width="21" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
     <col width="21" customWidth="1" style="7" min="8" max="8"/>
     <col width="51" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" style="1" min="10" max="65"/>
-    <col width="10.83203125" customWidth="1" style="1" min="66" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="1" min="10" max="67"/>
+    <col width="10.83203125" customWidth="1" style="1" min="68" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -42765,7 +42902,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="F9" s="1" t="n">
@@ -42942,11 +43079,24 @@
           <t>primary</t>
         </is>
       </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="F14" s="1" t="n">
         <v>2003</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>2003</v>
+      </c>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>00392</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -43934,7 +44084,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J575"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="9.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -67550,7 +67700,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col width="24.1640625" customWidth="1" style="13" min="1" max="1"/>
     <col width="34.83203125" customWidth="1" style="13" min="2" max="2"/>
@@ -67563,8 +67713,8 @@
     <col width="11.33203125" bestFit="1" customWidth="1" style="13" min="9" max="9"/>
     <col width="12.1640625" bestFit="1" customWidth="1" style="13" min="10" max="10"/>
     <col width="33.6640625" customWidth="1" style="13" min="11" max="11"/>
-    <col width="10.83203125" customWidth="1" style="13" min="12" max="58"/>
-    <col width="10.83203125" customWidth="1" style="13" min="59" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="13" min="12" max="60"/>
+    <col width="10.83203125" customWidth="1" style="13" min="61" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -69725,8 +69875,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="26.33203125" customWidth="1" min="1" max="1"/>
     <col width="38.5" customWidth="1" min="2" max="2"/>
@@ -69756,6 +69906,18 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>forest</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>title,work_id</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20580" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20580" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <sheet name="SeriesSort" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Works'!$A$1:$Y$620</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Works'!$A$1:$Y$621</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -575,7 +575,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="21.83203125" customWidth="1" style="4" min="1" max="1"/>
     <col width="77.33203125" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
@@ -1325,8 +1325,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z620"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <dimension ref="A1:Z621"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="11.33203125" customWidth="1" style="7" min="1" max="1"/>
     <col width="13.33203125" customWidth="1" style="7" min="2" max="2"/>
@@ -1351,8 +1351,8 @@
     <col width="15.1640625" customWidth="1" style="7" min="23" max="23"/>
     <col width="21.5" customWidth="1" style="7" min="24" max="24"/>
     <col width="26.83203125" customWidth="1" style="7" min="25" max="25"/>
-    <col width="10.83203125" customWidth="1" style="7" min="27" max="83"/>
-    <col width="10.83203125" customWidth="1" style="7" min="84" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="7" min="27" max="85"/>
+    <col width="10.83203125" customWidth="1" style="7" min="86" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="6">
@@ -26829,7 +26829,14 @@
           <t>00379</t>
         </is>
       </c>
-      <c r="C380" s="10" t="n"/>
+      <c r="B380" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C380" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D380" s="7" t="inlineStr">
         <is>
           <t>harmony</t>
@@ -26847,12 +26854,12 @@
       </c>
       <c r="G380" s="7" t="inlineStr">
         <is>
-          <t>00379 - harmony.jpg</t>
+          <t>harmony 3.jpg</t>
         </is>
       </c>
       <c r="H380" s="7" t="inlineStr">
         <is>
-          <t>00379 - harmony</t>
+          <t>harmony 3</t>
         </is>
       </c>
       <c r="I380" s="7" t="n">
@@ -26861,6 +26868,22 @@
       <c r="J380" s="7" t="n">
         <v>20</v>
       </c>
+      <c r="K380" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="L380" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="M380" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="N380" s="7" t="inlineStr">
+        <is>
+          <t>pen on paper</t>
+        </is>
+      </c>
       <c r="O380" s="7" t="n">
         <v>6</v>
       </c>
@@ -26872,7 +26895,14 @@
           <t>00380</t>
         </is>
       </c>
-      <c r="C381" s="10" t="n"/>
+      <c r="B381" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C381" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D381" s="7" t="inlineStr">
         <is>
           <t>harmony</t>
@@ -26890,12 +26920,12 @@
       </c>
       <c r="G381" s="7" t="inlineStr">
         <is>
-          <t>00380 - harmony.jpg</t>
+          <t>harmony 1.jpg</t>
         </is>
       </c>
       <c r="H381" s="7" t="inlineStr">
         <is>
-          <t>00380 - harmony</t>
+          <t>harmony 1</t>
         </is>
       </c>
       <c r="I381" s="7" t="n">
@@ -26904,6 +26934,22 @@
       <c r="J381" s="7" t="n">
         <v>21</v>
       </c>
+      <c r="K381" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="L381" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="M381" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="N381" s="7" t="inlineStr">
+        <is>
+          <t>pen on paper</t>
+        </is>
+      </c>
       <c r="O381" s="7" t="n">
         <v>6</v>
       </c>
@@ -26915,7 +26961,14 @@
           <t>00381</t>
         </is>
       </c>
-      <c r="C382" s="10" t="n"/>
+      <c r="B382" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C382" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D382" s="7" t="inlineStr">
         <is>
           <t>harmony</t>
@@ -26933,12 +26986,12 @@
       </c>
       <c r="G382" s="7" t="inlineStr">
         <is>
-          <t>00381 - harmony.jpg</t>
+          <t>harmony 2.jpg</t>
         </is>
       </c>
       <c r="H382" s="7" t="inlineStr">
         <is>
-          <t>00381 - harmony</t>
+          <t>harmony 2</t>
         </is>
       </c>
       <c r="I382" s="7" t="n">
@@ -26947,6 +27000,22 @@
       <c r="J382" s="7" t="n">
         <v>21</v>
       </c>
+      <c r="K382" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="L382" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="M382" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="N382" s="7" t="inlineStr">
+        <is>
+          <t>pen on paper</t>
+        </is>
+      </c>
       <c r="O382" s="7" t="n">
         <v>6</v>
       </c>
@@ -26958,7 +27027,14 @@
           <t>00382</t>
         </is>
       </c>
-      <c r="C383" s="10" t="n"/>
+      <c r="B383" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C383" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="D383" s="7" t="inlineStr">
         <is>
           <t>harmony</t>
@@ -26976,12 +27052,12 @@
       </c>
       <c r="G383" s="7" t="inlineStr">
         <is>
-          <t>00382 - harmony.jpg</t>
+          <t>harmony 2 residue.jpg</t>
         </is>
       </c>
       <c r="H383" s="7" t="inlineStr">
         <is>
-          <t>00382 - harmony</t>
+          <t>harmony 2 residue</t>
         </is>
       </c>
       <c r="I383" s="7" t="n">
@@ -26990,6 +27066,22 @@
       <c r="J383" s="7" t="n">
         <v>21</v>
       </c>
+      <c r="K383" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="L383" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="M383" s="7" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="N383" s="7" t="inlineStr">
+        <is>
+          <t>pen on paper</t>
+        </is>
+      </c>
       <c r="O383" s="7" t="n">
         <v>6</v>
       </c>
@@ -27386,6 +27478,12 @@
       <c r="J390" s="7" t="n">
         <v>30</v>
       </c>
+      <c r="K390" s="7" t="n">
+        <v>2011</v>
+      </c>
+      <c r="L390" s="7" t="n">
+        <v>2011</v>
+      </c>
       <c r="M390" s="7" t="inlineStr">
         <is>
           <t>digital print</t>
@@ -42587,8 +42685,70 @@
         </is>
       </c>
     </row>
+    <row r="621">
+      <c r="A621" s="16" t="inlineStr">
+        <is>
+          <t>00620</t>
+        </is>
+      </c>
+      <c r="B621" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C621" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="D621" s="7" t="inlineStr">
+        <is>
+          <t>harmony</t>
+        </is>
+      </c>
+      <c r="E621" s="7" t="inlineStr">
+        <is>
+          <t>harmony</t>
+        </is>
+      </c>
+      <c r="F621" s="7" t="inlineStr">
+        <is>
+          <t>harmony</t>
+        </is>
+      </c>
+      <c r="G621" s="7" t="inlineStr">
+        <is>
+          <t>harmony 3 (version).jpg</t>
+        </is>
+      </c>
+      <c r="H621" s="7" t="inlineStr">
+        <is>
+          <t>harmony 3 (version)</t>
+        </is>
+      </c>
+      <c r="I621" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J621" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="K621" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="L621" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="M621" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="N621" s="7" t="inlineStr">
+        <is>
+          <t>digital c-type print</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y620"/>
+  <autoFilter ref="A1:Y621"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -42600,8 +42760,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <dimension ref="A1:I43"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="31.83203125" customWidth="1" style="1" min="1" max="1"/>
     <col width="43.1640625" customWidth="1" style="1" min="2" max="2"/>
@@ -42612,8 +42772,8 @@
     <col width="21" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
     <col width="21" customWidth="1" style="7" min="8" max="8"/>
     <col width="51" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" style="1" min="10" max="67"/>
-    <col width="10.83203125" customWidth="1" style="1" min="68" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="1" min="10" max="69"/>
+    <col width="10.83203125" customWidth="1" style="1" min="70" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -44000,12 +44160,12 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>wa</t>
+          <t>tree</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>wa</t>
+          <t>tree</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -44022,28 +44182,26 @@
         <v>46094</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>2008, 2011</t>
-        </is>
+        <v>2024</v>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>2024</v>
       </c>
       <c r="H41" s="16" t="inlineStr">
         <is>
-          <t>00615</t>
+          <t>00546</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>tree</t>
+          <t>wa</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>tree</t>
+          <t>wa</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -44060,14 +44218,52 @@
         <v>46094</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>2024</v>
+        <v>2008</v>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>2008, 2011</t>
+        </is>
       </c>
       <c r="H42" s="16" t="inlineStr">
         <is>
-          <t>00546</t>
+          <t>00615</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>harmony</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>harmony</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="F43" s="1" t="n">
+        <v>2009</v>
+      </c>
+      <c r="G43" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="H43" s="16" t="inlineStr">
+        <is>
+          <t>00379</t>
         </is>
       </c>
     </row>
@@ -44083,8 +44279,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J575"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <dimension ref="A1:J588"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="9.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -67688,6 +67884,539 @@
         <v>2112</v>
       </c>
     </row>
+    <row r="576">
+      <c r="A576" s="16" t="inlineStr">
+        <is>
+          <t>00620</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>harmony 3.1.jpg</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>harmony 3.1</t>
+        </is>
+      </c>
+      <c r="F576" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G576" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H576" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I576" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="16" t="inlineStr">
+        <is>
+          <t>00620</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>harmony 3.2.jpg</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>harmony 3.2</t>
+        </is>
+      </c>
+      <c r="F577" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G577" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H577" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I577" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="16" t="inlineStr">
+        <is>
+          <t>00620</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>harmony 3.3.jpg</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>harmony 3.3</t>
+        </is>
+      </c>
+      <c r="F578" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G578" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H578" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I578" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="16" t="inlineStr">
+        <is>
+          <t>00620</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>harmony 3.4.jpg</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>harmony 3.4</t>
+        </is>
+      </c>
+      <c r="F579" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G579" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H579" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I579" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="16" t="inlineStr">
+        <is>
+          <t>00620</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>harmony 3.5.jpg</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>harmony 3.5</t>
+        </is>
+      </c>
+      <c r="F580" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G580" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H580" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I580" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="16" t="inlineStr">
+        <is>
+          <t>00620</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>harmony 3.6.jpg</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>harmony 3.6</t>
+        </is>
+      </c>
+      <c r="F581" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G581" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H581" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I581" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="16" t="inlineStr">
+        <is>
+          <t>00620</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>007</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>harmony 3.7.jpg</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>harmony 3.7</t>
+        </is>
+      </c>
+      <c r="F582" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G582" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H582" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I582" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="16" t="inlineStr">
+        <is>
+          <t>00620</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>harmony 3.8.jpg</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>harmony 3.8</t>
+        </is>
+      </c>
+      <c r="F583" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G583" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H583" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I583" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="16" t="inlineStr">
+        <is>
+          <t>00620</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>harmony 3.9.jpg</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>harmony 3.9</t>
+        </is>
+      </c>
+      <c r="F584" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G584" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H584" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I584" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="16" t="inlineStr">
+        <is>
+          <t>00620</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>harmony 3.10.jpg</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>harmony 3.10</t>
+        </is>
+      </c>
+      <c r="F585" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G585" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H585" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I585" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="16" t="inlineStr">
+        <is>
+          <t>00620</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>harmony 3.11.jpg</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>harmony 3.11</t>
+        </is>
+      </c>
+      <c r="F586" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G586" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H586" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I586" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="16" t="inlineStr">
+        <is>
+          <t>00620</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>harmony 3.12.jpg</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>harmony 3.12</t>
+        </is>
+      </c>
+      <c r="F587" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G587" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H587" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I587" t="n">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="16" t="inlineStr">
+        <is>
+          <t>00620</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>harmony 3.13.jpg</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>harmony 3.13</t>
+        </is>
+      </c>
+      <c r="F588" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G588" s="10" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H588" t="n">
+        <v>3543</v>
+      </c>
+      <c r="I588" t="n">
+        <v>3543</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -67700,7 +68429,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" outlineLevelCol="0"/>
   <cols>
     <col width="24.1640625" customWidth="1" style="13" min="1" max="1"/>
     <col width="34.83203125" customWidth="1" style="13" min="2" max="2"/>
@@ -67713,8 +68442,8 @@
     <col width="11.33203125" bestFit="1" customWidth="1" style="13" min="9" max="9"/>
     <col width="12.1640625" bestFit="1" customWidth="1" style="13" min="10" max="10"/>
     <col width="33.6640625" customWidth="1" style="13" min="11" max="11"/>
-    <col width="10.83203125" customWidth="1" style="13" min="12" max="60"/>
-    <col width="10.83203125" customWidth="1" style="13" min="61" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="13" min="12" max="62"/>
+    <col width="10.83203125" customWidth="1" style="13" min="63" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -69875,8 +70604,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
   <cols>
     <col width="26.33203125" customWidth="1" min="1" max="1"/>
     <col width="38.5" customWidth="1" min="2" max="2"/>
@@ -69918,6 +70647,18 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>harmony</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>title,work_id</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -575,7 +575,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="21.83203125" customWidth="1" style="4" min="1" max="1"/>
     <col width="77.33203125" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
@@ -1326,7 +1326,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Z621"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="11.33203125" customWidth="1" style="7" min="1" max="1"/>
     <col width="13.33203125" customWidth="1" style="7" min="2" max="2"/>
@@ -42761,7 +42761,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="31.83203125" customWidth="1" style="1" min="1" max="1"/>
     <col width="43.1640625" customWidth="1" style="1" min="2" max="2"/>
@@ -44280,7 +44280,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J588"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="9.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -68429,7 +68429,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col width="24.1640625" customWidth="1" style="13" min="1" max="1"/>
     <col width="34.83203125" customWidth="1" style="13" min="2" max="2"/>
@@ -70605,7 +70605,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="26.33203125" customWidth="1" min="1" max="1"/>
     <col width="38.5" customWidth="1" min="2" max="2"/>

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20580" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20580" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,13 +22,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -96,12 +95,6 @@
       <color rgb="FF000000"/>
       <sz val="13"/>
     </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -133,7 +126,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,7 +174,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -583,7 +575,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="21.83203125" customWidth="1" style="4" min="1" max="1"/>
     <col width="77.33203125" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
@@ -1334,7 +1326,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Z621"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="11.33203125" customWidth="1" style="7" min="1" max="1"/>
     <col width="13.33203125" customWidth="1" style="7" min="2" max="2"/>
@@ -1359,8 +1351,8 @@
     <col width="15.1640625" customWidth="1" style="7" min="23" max="23"/>
     <col width="21.5" customWidth="1" style="7" min="24" max="24"/>
     <col width="26.83203125" customWidth="1" style="7" min="25" max="25"/>
-    <col width="10.83203125" customWidth="1" style="7" min="27" max="87"/>
-    <col width="10.83203125" customWidth="1" style="7" min="88" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="7" min="27" max="88"/>
+    <col width="10.83203125" customWidth="1" style="7" min="89" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="6">
@@ -1501,7 +1493,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n">
+      <c r="C2" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -1566,7 +1558,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n">
+      <c r="C3" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D3" s="7" t="inlineStr">
@@ -1631,7 +1623,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1696,7 +1688,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -1761,7 +1753,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -1828,7 +1820,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -1895,7 +1887,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -2039,7 +2031,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -2106,7 +2098,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -2173,7 +2165,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -2240,7 +2232,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -2307,7 +2299,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -2374,7 +2366,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C15" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -2439,7 +2431,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -2504,7 +2496,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C17" s="10" t="n">
+      <c r="C17" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -2569,7 +2561,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C18" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -2634,7 +2626,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C19" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -2699,7 +2691,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C20" s="10" t="n">
+      <c r="C20" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -2764,7 +2756,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C21" s="10" t="n">
+      <c r="C21" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -2829,7 +2821,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C22" s="10" t="n">
+      <c r="C22" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -2894,7 +2886,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C23" s="10" t="n">
+      <c r="C23" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -2961,7 +2953,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C24" s="10" t="n">
+      <c r="C24" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -3028,7 +3020,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C25" s="10" t="n">
+      <c r="C25" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -3095,7 +3087,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C26" s="10" t="n">
+      <c r="C26" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -3162,7 +3154,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C27" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -3229,7 +3221,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="C28" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -3296,7 +3288,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C29" s="10" t="n">
+      <c r="C29" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -3363,7 +3355,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C30" s="10" t="n">
+      <c r="C30" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -3430,7 +3422,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C31" s="10" t="n">
+      <c r="C31" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -3497,7 +3489,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C32" s="10" t="n">
+      <c r="C32" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -3564,7 +3556,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C33" s="10" t="n">
+      <c r="C33" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -3631,7 +3623,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C34" s="10" t="n">
+      <c r="C34" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -3698,7 +3690,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C35" s="10" t="n">
+      <c r="C35" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -3765,7 +3757,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C36" s="10" t="n">
+      <c r="C36" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -3832,7 +3824,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C37" s="10" t="n">
+      <c r="C37" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -3899,7 +3891,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C38" s="10" t="n">
+      <c r="C38" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -3966,7 +3958,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C39" s="10" t="n">
+      <c r="C39" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -4033,7 +4025,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C40" s="10" t="n">
+      <c r="C40" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -4100,7 +4092,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C41" s="10" t="n">
+      <c r="C41" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -4167,7 +4159,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C42" s="10" t="n">
+      <c r="C42" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -4234,7 +4226,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C43" s="10" t="n">
+      <c r="C43" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -4301,7 +4293,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C44" s="10" t="n">
+      <c r="C44" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -4368,7 +4360,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C45" s="10" t="n">
+      <c r="C45" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -4435,7 +4427,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C46" s="10" t="n">
+      <c r="C46" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -4502,7 +4494,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C47" s="10" t="n">
+      <c r="C47" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -4569,7 +4561,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C48" s="10" t="n">
+      <c r="C48" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -4636,7 +4628,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C49" s="10" t="n">
+      <c r="C49" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -4703,7 +4695,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C50" s="10" t="n">
+      <c r="C50" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -4770,7 +4762,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C51" s="10" t="n">
+      <c r="C51" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -4837,7 +4829,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C52" s="10" t="n">
+      <c r="C52" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -4904,7 +4896,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C53" s="10" t="n">
+      <c r="C53" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -4971,7 +4963,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C54" s="10" t="n">
+      <c r="C54" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -5038,7 +5030,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C55" s="10" t="n">
+      <c r="C55" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -5105,7 +5097,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C56" s="10" t="n">
+      <c r="C56" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -5172,7 +5164,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C57" s="10" t="n">
+      <c r="C57" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -5239,7 +5231,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C58" s="10" t="n">
+      <c r="C58" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -5306,7 +5298,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C59" s="10" t="n">
+      <c r="C59" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -5373,7 +5365,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C60" s="10" t="n">
+      <c r="C60" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -5440,7 +5432,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C61" s="10" t="n">
+      <c r="C61" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -5507,7 +5499,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C62" s="10" t="n">
+      <c r="C62" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -5574,7 +5566,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C63" s="10" t="n">
+      <c r="C63" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -5641,7 +5633,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C64" s="10" t="n">
+      <c r="C64" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -5708,7 +5700,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C65" s="10" t="n">
+      <c r="C65" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -5775,7 +5767,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C66" s="10" t="n">
+      <c r="C66" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -5842,7 +5834,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C67" s="10" t="n">
+      <c r="C67" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -5909,7 +5901,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C68" s="10" t="n">
+      <c r="C68" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -5976,7 +5968,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C69" s="10" t="n">
+      <c r="C69" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -6043,7 +6035,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C70" s="10" t="n">
+      <c r="C70" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -6110,7 +6102,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C71" s="10" t="n">
+      <c r="C71" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -6177,7 +6169,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C72" s="10" t="n">
+      <c r="C72" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -6244,7 +6236,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C73" s="10" t="n">
+      <c r="C73" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -6311,7 +6303,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C74" s="10" t="n">
+      <c r="C74" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D74" s="7" t="inlineStr">
@@ -6378,7 +6370,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C75" s="10" t="n">
+      <c r="C75" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -6445,7 +6437,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C76" s="10" t="n">
+      <c r="C76" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D76" s="7" t="inlineStr">
@@ -6512,7 +6504,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C77" s="10" t="n">
+      <c r="C77" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -6579,7 +6571,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C78" s="10" t="n">
+      <c r="C78" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -6646,7 +6638,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C79" s="10" t="n">
+      <c r="C79" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -6713,7 +6705,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C80" s="10" t="n">
+      <c r="C80" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D80" s="7" t="inlineStr">
@@ -6780,7 +6772,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C81" s="10" t="n">
+      <c r="C81" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D81" s="7" t="inlineStr">
@@ -6847,7 +6839,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C82" s="10" t="n">
+      <c r="C82" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D82" s="7" t="inlineStr">
@@ -6914,7 +6906,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C83" s="10" t="n">
+      <c r="C83" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -6981,7 +6973,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C84" s="10" t="n">
+      <c r="C84" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D84" s="7" t="inlineStr">
@@ -7048,7 +7040,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C85" s="10" t="n">
+      <c r="C85" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D85" s="7" t="inlineStr">
@@ -7115,7 +7107,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C86" s="10" t="n">
+      <c r="C86" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D86" s="7" t="inlineStr">
@@ -7182,7 +7174,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C87" s="10" t="n">
+      <c r="C87" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -7249,7 +7241,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C88" s="10" t="n">
+      <c r="C88" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D88" s="7" t="inlineStr">
@@ -7316,7 +7308,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C89" s="10" t="n">
+      <c r="C89" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D89" s="7" t="inlineStr">
@@ -7383,7 +7375,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C90" s="10" t="n">
+      <c r="C90" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D90" s="7" t="inlineStr">
@@ -7450,7 +7442,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C91" s="10" t="n">
+      <c r="C91" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D91" s="7" t="inlineStr">
@@ -7517,7 +7509,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C92" s="10" t="n">
+      <c r="C92" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D92" s="7" t="inlineStr">
@@ -7584,7 +7576,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C93" s="10" t="n">
+      <c r="C93" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D93" s="7" t="inlineStr">
@@ -7651,7 +7643,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C94" s="10" t="n">
+      <c r="C94" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D94" s="7" t="inlineStr">
@@ -7718,7 +7710,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C95" s="10" t="n">
+      <c r="C95" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -7785,7 +7777,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C96" s="10" t="n">
+      <c r="C96" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D96" s="7" t="inlineStr">
@@ -7852,7 +7844,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C97" s="10" t="n">
+      <c r="C97" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -7919,7 +7911,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C98" s="10" t="n">
+      <c r="C98" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D98" s="7" t="inlineStr">
@@ -7986,7 +7978,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C99" s="10" t="n">
+      <c r="C99" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D99" s="7" t="inlineStr">
@@ -8053,7 +8045,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C100" s="10" t="n">
+      <c r="C100" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -8120,7 +8112,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C101" s="10" t="n">
+      <c r="C101" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D101" s="7" t="inlineStr">
@@ -8187,7 +8179,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C102" s="10" t="n">
+      <c r="C102" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D102" s="7" t="inlineStr">
@@ -8254,7 +8246,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C103" s="10" t="n">
+      <c r="C103" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -8321,7 +8313,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C104" s="10" t="n">
+      <c r="C104" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -8388,7 +8380,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C105" s="10" t="n">
+      <c r="C105" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D105" s="7" t="inlineStr">
@@ -8455,7 +8447,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C106" s="10" t="n">
+      <c r="C106" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -8522,7 +8514,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C107" s="10" t="n">
+      <c r="C107" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D107" s="7" t="inlineStr">
@@ -8589,7 +8581,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C108" s="10" t="n">
+      <c r="C108" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -8656,7 +8648,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C109" s="10" t="n">
+      <c r="C109" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -8723,7 +8715,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C110" s="10" t="n">
+      <c r="C110" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D110" s="7" t="inlineStr">
@@ -8790,7 +8782,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C111" s="10" t="n">
+      <c r="C111" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D111" s="7" t="inlineStr">
@@ -8857,7 +8849,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C112" s="10" t="n">
+      <c r="C112" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D112" s="7" t="inlineStr">
@@ -8922,7 +8914,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C113" s="10" t="n">
+      <c r="C113" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D113" s="7" t="inlineStr">
@@ -8989,7 +8981,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C114" s="10" t="n">
+      <c r="C114" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D114" s="7" t="inlineStr">
@@ -9056,7 +9048,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C115" s="10" t="n">
+      <c r="C115" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D115" s="1" t="inlineStr">
@@ -9128,7 +9120,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C116" s="10" t="n">
+      <c r="C116" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D116" s="1" t="inlineStr">
@@ -9200,7 +9192,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C117" s="10" t="n">
+      <c r="C117" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D117" s="1" t="inlineStr">
@@ -9272,7 +9264,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C118" s="10" t="n">
+      <c r="C118" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D118" s="1" t="inlineStr">
@@ -9344,7 +9336,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C119" s="10" t="n">
+      <c r="C119" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D119" s="1" t="inlineStr">
@@ -9416,7 +9408,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C120" s="10" t="n">
+      <c r="C120" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D120" s="1" t="inlineStr">
@@ -9488,7 +9480,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C121" s="10" t="n">
+      <c r="C121" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D121" s="1" t="inlineStr">
@@ -9560,7 +9552,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C122" s="10" t="n">
+      <c r="C122" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D122" s="1" t="inlineStr">
@@ -9632,7 +9624,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C123" s="10" t="n">
+      <c r="C123" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D123" s="1" t="inlineStr">
@@ -9704,7 +9696,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C124" s="10" t="n">
+      <c r="C124" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D124" s="1" t="inlineStr">
@@ -9776,7 +9768,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C125" s="10" t="n">
+      <c r="C125" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D125" s="1" t="inlineStr">
@@ -9848,7 +9840,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C126" s="10" t="n">
+      <c r="C126" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D126" s="1" t="inlineStr">
@@ -9920,7 +9912,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C127" s="10" t="n">
+      <c r="C127" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D127" s="1" t="inlineStr">
@@ -9992,7 +9984,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C128" s="10" t="n">
+      <c r="C128" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D128" s="1" t="inlineStr">
@@ -10064,7 +10056,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C129" s="10" t="n">
+      <c r="C129" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D129" s="1" t="inlineStr">
@@ -10136,7 +10128,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C130" s="10" t="n">
+      <c r="C130" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D130" s="1" t="inlineStr">
@@ -10208,7 +10200,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C131" s="10" t="n">
+      <c r="C131" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D131" s="7" t="inlineStr">
@@ -10273,7 +10265,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C132" s="10" t="n">
+      <c r="C132" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D132" s="7" t="inlineStr">
@@ -10340,7 +10332,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C133" s="10" t="n">
+      <c r="C133" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D133" s="7" t="inlineStr">
@@ -10405,7 +10397,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C134" s="10" t="n">
+      <c r="C134" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D134" s="7" t="inlineStr">
@@ -10470,7 +10462,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C135" s="10" t="n">
+      <c r="C135" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D135" s="7" t="inlineStr">
@@ -10535,7 +10527,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C136" s="10" t="n">
+      <c r="C136" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D136" s="7" t="inlineStr">
@@ -10600,7 +10592,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C137" s="10" t="n">
+      <c r="C137" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D137" s="7" t="inlineStr">
@@ -10665,7 +10657,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C138" s="10" t="n">
+      <c r="C138" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D138" s="7" t="inlineStr">
@@ -10730,7 +10722,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C139" s="10" t="n">
+      <c r="C139" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D139" s="7" t="inlineStr">
@@ -10795,7 +10787,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C140" s="10" t="n">
+      <c r="C140" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D140" s="7" t="inlineStr">
@@ -10860,7 +10852,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C141" s="10" t="n">
+      <c r="C141" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D141" s="7" t="inlineStr">
@@ -10925,7 +10917,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C142" s="10" t="n">
+      <c r="C142" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D142" s="7" t="inlineStr">
@@ -10990,7 +10982,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C143" s="10" t="n">
+      <c r="C143" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D143" s="7" t="inlineStr">
@@ -11055,7 +11047,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C144" s="10" t="n">
+      <c r="C144" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D144" s="7" t="inlineStr">
@@ -11120,7 +11112,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C145" s="10" t="n">
+      <c r="C145" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D145" s="7" t="inlineStr">
@@ -11185,7 +11177,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C146" s="10" t="n">
+      <c r="C146" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D146" s="7" t="inlineStr">
@@ -11250,7 +11242,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C147" s="10" t="n">
+      <c r="C147" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D147" s="7" t="inlineStr">
@@ -11315,7 +11307,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C148" s="10" t="n">
+      <c r="C148" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D148" s="7" t="inlineStr">
@@ -11380,7 +11372,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C149" s="10" t="n">
+      <c r="C149" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D149" s="7" t="inlineStr">
@@ -11445,7 +11437,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C150" s="10" t="n">
+      <c r="C150" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D150" s="7" t="inlineStr">
@@ -11510,7 +11502,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C151" s="10" t="n">
+      <c r="C151" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D151" s="7" t="inlineStr">
@@ -11575,7 +11567,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C152" s="10" t="n">
+      <c r="C152" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D152" s="7" t="inlineStr">
@@ -11640,7 +11632,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C153" s="10" t="n">
+      <c r="C153" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D153" s="7" t="inlineStr">
@@ -11705,7 +11697,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C154" s="10" t="n">
+      <c r="C154" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D154" s="7" t="inlineStr">
@@ -11770,7 +11762,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C155" s="10" t="n">
+      <c r="C155" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D155" s="7" t="inlineStr">
@@ -11835,7 +11827,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C156" s="10" t="n">
+      <c r="C156" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D156" s="7" t="inlineStr">
@@ -11900,7 +11892,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C157" s="10" t="n">
+      <c r="C157" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D157" s="7" t="inlineStr">
@@ -11965,7 +11957,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C158" s="10" t="n">
+      <c r="C158" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D158" s="7" t="inlineStr">
@@ -12030,7 +12022,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C159" s="10" t="n">
+      <c r="C159" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D159" s="7" t="inlineStr">
@@ -12095,7 +12087,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C160" s="10" t="n">
+      <c r="C160" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D160" s="7" t="inlineStr">
@@ -12162,7 +12154,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C161" s="10" t="n">
+      <c r="C161" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D161" s="7" t="inlineStr">
@@ -12232,7 +12224,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C162" s="10" t="n">
+      <c r="C162" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D162" s="7" t="inlineStr">
@@ -12302,7 +12294,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C163" s="10" t="n">
+      <c r="C163" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D163" s="7" t="inlineStr">
@@ -12369,7 +12361,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C164" s="10" t="n">
+      <c r="C164" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D164" s="7" t="inlineStr">
@@ -12441,7 +12433,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C165" s="10" t="n">
+      <c r="C165" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D165" s="7" t="inlineStr">
@@ -12506,7 +12498,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C166" s="10" t="n">
+      <c r="C166" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D166" s="7" t="inlineStr">
@@ -12573,7 +12565,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C167" s="10" t="n">
+      <c r="C167" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D167" s="7" t="inlineStr">
@@ -12638,7 +12630,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C168" s="10" t="n">
+      <c r="C168" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D168" s="7" t="inlineStr">
@@ -12703,7 +12695,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C169" s="10" t="n">
+      <c r="C169" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D169" s="7" t="inlineStr">
@@ -12768,7 +12760,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C170" s="10" t="n">
+      <c r="C170" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D170" s="7" t="inlineStr">
@@ -12833,7 +12825,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C171" s="10" t="n">
+      <c r="C171" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D171" s="7" t="inlineStr">
@@ -12898,7 +12890,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C172" s="10" t="n">
+      <c r="C172" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D172" s="7" t="inlineStr">
@@ -12963,7 +12955,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C173" s="10" t="n">
+      <c r="C173" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D173" s="7" t="inlineStr">
@@ -13030,7 +13022,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C174" s="10" t="n">
+      <c r="C174" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D174" s="7" t="inlineStr">
@@ -13097,7 +13089,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C175" s="10" t="n">
+      <c r="C175" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D175" s="7" t="inlineStr">
@@ -13164,7 +13156,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C176" s="10" t="n">
+      <c r="C176" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D176" s="7" t="inlineStr">
@@ -13231,7 +13223,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C177" s="10" t="n">
+      <c r="C177" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D177" s="7" t="inlineStr">
@@ -13298,7 +13290,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C178" s="10" t="n">
+      <c r="C178" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D178" s="7" t="inlineStr">
@@ -13365,7 +13357,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C179" s="10" t="n">
+      <c r="C179" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D179" s="7" t="inlineStr">
@@ -13432,7 +13424,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C180" s="10" t="n">
+      <c r="C180" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D180" s="7" t="inlineStr">
@@ -13499,7 +13491,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C181" s="10" t="n">
+      <c r="C181" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D181" s="7" t="inlineStr">
@@ -13566,7 +13558,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C182" s="10" t="n">
+      <c r="C182" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D182" s="7" t="inlineStr">
@@ -13633,7 +13625,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C183" s="10" t="n">
+      <c r="C183" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D183" s="7" t="inlineStr">
@@ -13700,7 +13692,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C184" s="10" t="n">
+      <c r="C184" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D184" s="7" t="inlineStr">
@@ -13767,7 +13759,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C185" s="10" t="n">
+      <c r="C185" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D185" s="7" t="inlineStr">
@@ -13834,7 +13826,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C186" s="10" t="n">
+      <c r="C186" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D186" s="7" t="inlineStr">
@@ -13901,7 +13893,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C187" s="10" t="n">
+      <c r="C187" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D187" s="7" t="inlineStr">
@@ -13968,7 +13960,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C188" s="10" t="n">
+      <c r="C188" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D188" s="7" t="inlineStr">
@@ -14035,7 +14027,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C189" s="10" t="n">
+      <c r="C189" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D189" s="7" t="inlineStr">
@@ -14102,7 +14094,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C190" s="10" t="n">
+      <c r="C190" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D190" s="7" t="inlineStr">
@@ -14169,7 +14161,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C191" s="10" t="n">
+      <c r="C191" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D191" s="7" t="inlineStr">
@@ -14236,7 +14228,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C192" s="10" t="n">
+      <c r="C192" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D192" s="7" t="inlineStr">
@@ -14301,7 +14293,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C193" s="10" t="n">
+      <c r="C193" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D193" s="7" t="inlineStr">
@@ -14366,7 +14358,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C194" s="10" t="n">
+      <c r="C194" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D194" s="7" t="inlineStr">
@@ -14431,7 +14423,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C195" s="10" t="n">
+      <c r="C195" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D195" s="7" t="inlineStr">
@@ -14496,7 +14488,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C196" s="10" t="n">
+      <c r="C196" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D196" s="7" t="inlineStr">
@@ -14561,7 +14553,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C197" s="10" t="n">
+      <c r="C197" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D197" s="7" t="inlineStr">
@@ -14626,7 +14618,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C198" s="10" t="n">
+      <c r="C198" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D198" s="7" t="inlineStr">
@@ -14688,7 +14680,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C199" s="10" t="n">
+      <c r="C199" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D199" s="7" t="inlineStr">
@@ -14753,7 +14745,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C200" s="10" t="n">
+      <c r="C200" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D200" s="7" t="inlineStr">
@@ -14818,7 +14810,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C201" s="10" t="n">
+      <c r="C201" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D201" s="7" t="inlineStr">
@@ -14883,7 +14875,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C202" s="10" t="n">
+      <c r="C202" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D202" s="7" t="inlineStr">
@@ -14948,7 +14940,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C203" s="10" t="n">
+      <c r="C203" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D203" s="7" t="inlineStr">
@@ -15013,7 +15005,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C204" s="10" t="n">
+      <c r="C204" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D204" s="7" t="inlineStr">
@@ -15078,7 +15070,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C205" s="10" t="n">
+      <c r="C205" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D205" s="7" t="inlineStr">
@@ -15143,7 +15135,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C206" s="10" t="n">
+      <c r="C206" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D206" s="7" t="inlineStr">
@@ -15208,7 +15200,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C207" s="10" t="n">
+      <c r="C207" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D207" s="7" t="inlineStr">
@@ -15273,7 +15265,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C208" s="10" t="n">
+      <c r="C208" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D208" s="7" t="inlineStr">
@@ -15338,7 +15330,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C209" s="10" t="n">
+      <c r="C209" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D209" s="7" t="inlineStr">
@@ -15403,7 +15395,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C210" s="10" t="n">
+      <c r="C210" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D210" s="7" t="inlineStr">
@@ -15470,7 +15462,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C211" s="10" t="n">
+      <c r="C211" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D211" s="7" t="inlineStr">
@@ -15537,7 +15529,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C212" s="10" t="n">
+      <c r="C212" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D212" s="7" t="inlineStr">
@@ -15604,7 +15596,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C213" s="10" t="n">
+      <c r="C213" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D213" s="7" t="inlineStr">
@@ -15671,7 +15663,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C214" s="10" t="n">
+      <c r="C214" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D214" s="7" t="inlineStr">
@@ -15738,7 +15730,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C215" s="10" t="n">
+      <c r="C215" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D215" s="7" t="inlineStr">
@@ -15805,7 +15797,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C216" s="10" t="n">
+      <c r="C216" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D216" s="7" t="inlineStr">
@@ -15872,7 +15864,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C217" s="10" t="n">
+      <c r="C217" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D217" s="7" t="inlineStr">
@@ -15937,7 +15929,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C218" s="10" t="n">
+      <c r="C218" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D218" s="7" t="inlineStr">
@@ -16002,7 +15994,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C219" s="10" t="n">
+      <c r="C219" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D219" s="7" t="inlineStr">
@@ -16067,7 +16059,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C220" s="10" t="n">
+      <c r="C220" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D220" s="7" t="inlineStr">
@@ -16132,7 +16124,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C221" s="10" t="n">
+      <c r="C221" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D221" s="7" t="inlineStr">
@@ -16197,7 +16189,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C222" s="10" t="n">
+      <c r="C222" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D222" s="7" t="inlineStr">
@@ -16262,7 +16254,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C223" s="10" t="n">
+      <c r="C223" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D223" s="7" t="inlineStr">
@@ -16327,7 +16319,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C224" s="10" t="n">
+      <c r="C224" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D224" s="7" t="inlineStr">
@@ -16392,7 +16384,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C225" s="10" t="n">
+      <c r="C225" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D225" s="7" t="inlineStr">
@@ -16457,7 +16449,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C226" s="10" t="n">
+      <c r="C226" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D226" s="7" t="inlineStr">
@@ -16522,7 +16514,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C227" s="10" t="n">
+      <c r="C227" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D227" s="1" t="inlineStr">
@@ -16589,7 +16581,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C228" s="10" t="n">
+      <c r="C228" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D228" s="1" t="inlineStr">
@@ -16656,7 +16648,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C229" s="10" t="n">
+      <c r="C229" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D229" s="1" t="inlineStr">
@@ -16723,7 +16715,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C230" s="10" t="n">
+      <c r="C230" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D230" s="1" t="inlineStr">
@@ -16790,7 +16782,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C231" s="10" t="n">
+      <c r="C231" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D231" s="1" t="inlineStr">
@@ -16857,7 +16849,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C232" s="10" t="n">
+      <c r="C232" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D232" s="1" t="inlineStr">
@@ -16924,7 +16916,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C233" s="10" t="n">
+      <c r="C233" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D233" s="1" t="inlineStr">
@@ -16991,7 +16983,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C234" s="10" t="n">
+      <c r="C234" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D234" s="7" t="inlineStr">
@@ -17058,7 +17050,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C235" s="10" t="n">
+      <c r="C235" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D235" s="7" t="inlineStr">
@@ -17125,7 +17117,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C236" s="10" t="n">
+      <c r="C236" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D236" s="1" t="inlineStr">
@@ -17192,7 +17184,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C237" s="10" t="n">
+      <c r="C237" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D237" s="1" t="inlineStr">
@@ -17259,7 +17251,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C238" s="10" t="n">
+      <c r="C238" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D238" s="1" t="inlineStr">
@@ -17326,7 +17318,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C239" s="10" t="n">
+      <c r="C239" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D239" s="1" t="inlineStr">
@@ -17393,7 +17385,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C240" s="10" t="n">
+      <c r="C240" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D240" s="1" t="inlineStr">
@@ -17460,7 +17452,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C241" s="10" t="n">
+      <c r="C241" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D241" s="1" t="inlineStr">
@@ -17527,7 +17519,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C242" s="10" t="n">
+      <c r="C242" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D242" s="1" t="inlineStr">
@@ -17594,7 +17586,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C243" s="10" t="n">
+      <c r="C243" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D243" s="1" t="inlineStr">
@@ -17661,7 +17653,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C244" s="10" t="n">
+      <c r="C244" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D244" s="1" t="inlineStr">
@@ -17728,7 +17720,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C245" s="10" t="n">
+      <c r="C245" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D245" s="1" t="inlineStr">
@@ -17795,7 +17787,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C246" s="10" t="n">
+      <c r="C246" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D246" s="1" t="inlineStr">
@@ -17862,7 +17854,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C247" s="10" t="n">
+      <c r="C247" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D247" s="1" t="inlineStr">
@@ -17929,7 +17921,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C248" s="10" t="n">
+      <c r="C248" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D248" s="7" t="inlineStr">
@@ -17996,7 +17988,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C249" s="10" t="n">
+      <c r="C249" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D249" s="1" t="inlineStr">
@@ -18063,7 +18055,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C250" s="10" t="n">
+      <c r="C250" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D250" s="1" t="inlineStr">
@@ -18130,7 +18122,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C251" s="10" t="n">
+      <c r="C251" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D251" s="1" t="inlineStr">
@@ -18197,7 +18189,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C252" s="10" t="n">
+      <c r="C252" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D252" s="1" t="inlineStr">
@@ -18264,7 +18256,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C253" s="10" t="n">
+      <c r="C253" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D253" s="1" t="inlineStr">
@@ -18331,7 +18323,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C254" s="10" t="n">
+      <c r="C254" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D254" s="1" t="inlineStr">
@@ -18398,7 +18390,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C255" s="10" t="n">
+      <c r="C255" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D255" s="1" t="inlineStr">
@@ -18465,7 +18457,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C256" s="10" t="n">
+      <c r="C256" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D256" s="1" t="inlineStr">
@@ -18532,7 +18524,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C257" s="10" t="n">
+      <c r="C257" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D257" s="1" t="inlineStr">
@@ -18599,7 +18591,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C258" s="10" t="n">
+      <c r="C258" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D258" s="1" t="inlineStr">
@@ -18666,7 +18658,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C259" s="10" t="n">
+      <c r="C259" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D259" s="1" t="inlineStr">
@@ -18733,7 +18725,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C260" s="10" t="n">
+      <c r="C260" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D260" s="1" t="inlineStr">
@@ -18800,7 +18792,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C261" s="10" t="n">
+      <c r="C261" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D261" s="1" t="inlineStr">
@@ -18867,7 +18859,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C262" s="10" t="n">
+      <c r="C262" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D262" s="1" t="inlineStr">
@@ -18934,7 +18926,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C263" s="10" t="n">
+      <c r="C263" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D263" s="1" t="inlineStr">
@@ -19001,7 +18993,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C264" s="10" t="n">
+      <c r="C264" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D264" s="1" t="inlineStr">
@@ -19068,7 +19060,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C265" s="10" t="n">
+      <c r="C265" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D265" s="1" t="inlineStr">
@@ -19135,7 +19127,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C266" s="10" t="n">
+      <c r="C266" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D266" s="1" t="inlineStr">
@@ -19202,7 +19194,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C267" s="10" t="n">
+      <c r="C267" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D267" s="1" t="inlineStr">
@@ -19269,7 +19261,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C268" s="10" t="n">
+      <c r="C268" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D268" s="1" t="inlineStr">
@@ -19336,7 +19328,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C269" s="10" t="n">
+      <c r="C269" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D269" s="1" t="inlineStr">
@@ -19403,7 +19395,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C270" s="10" t="n">
+      <c r="C270" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D270" s="1" t="inlineStr">
@@ -19470,7 +19462,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C271" s="10" t="n">
+      <c r="C271" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D271" s="1" t="inlineStr">
@@ -19537,7 +19529,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C272" s="10" t="n">
+      <c r="C272" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D272" s="1" t="inlineStr">
@@ -19604,7 +19596,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C273" s="10" t="n">
+      <c r="C273" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D273" s="1" t="inlineStr">
@@ -19671,7 +19663,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C274" s="10" t="n">
+      <c r="C274" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D274" s="1" t="inlineStr">
@@ -19738,7 +19730,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C275" s="10" t="n">
+      <c r="C275" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D275" s="1" t="inlineStr">
@@ -19805,7 +19797,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C276" s="10" t="n">
+      <c r="C276" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D276" s="1" t="inlineStr">
@@ -19872,7 +19864,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C277" s="10" t="n">
+      <c r="C277" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D277" s="1" t="inlineStr">
@@ -19939,7 +19931,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C278" s="10" t="n">
+      <c r="C278" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D278" s="1" t="inlineStr">
@@ -20006,7 +19998,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C279" s="10" t="n">
+      <c r="C279" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D279" s="1" t="inlineStr">
@@ -20073,7 +20065,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C280" s="10" t="n">
+      <c r="C280" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D280" s="1" t="inlineStr">
@@ -20140,7 +20132,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C281" s="10" t="n">
+      <c r="C281" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D281" s="1" t="inlineStr">
@@ -20207,7 +20199,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C282" s="10" t="n">
+      <c r="C282" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D282" s="1" t="inlineStr">
@@ -20274,7 +20266,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C283" s="10" t="n">
+      <c r="C283" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D283" s="1" t="inlineStr">
@@ -20341,7 +20333,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C284" s="10" t="n">
+      <c r="C284" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D284" s="1" t="inlineStr">
@@ -20408,7 +20400,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C285" s="10" t="n">
+      <c r="C285" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D285" s="1" t="inlineStr">
@@ -20475,7 +20467,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C286" s="10" t="n">
+      <c r="C286" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D286" s="1" t="inlineStr">
@@ -24430,7 +24422,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C341" s="10" t="n">
+      <c r="C341" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D341" s="7" t="inlineStr">
@@ -24495,7 +24487,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C342" s="10" t="n">
+      <c r="C342" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D342" s="7" t="inlineStr">
@@ -24560,7 +24552,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C343" s="10" t="n">
+      <c r="C343" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D343" s="7" t="inlineStr">
@@ -24625,7 +24617,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C344" s="10" t="n">
+      <c r="C344" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D344" s="7" t="inlineStr">
@@ -24690,7 +24682,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C345" s="10" t="n">
+      <c r="C345" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D345" s="7" t="inlineStr">
@@ -24755,7 +24747,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C346" s="10" t="n">
+      <c r="C346" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D346" s="7" t="inlineStr">
@@ -24820,7 +24812,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C347" s="10" t="n">
+      <c r="C347" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D347" s="1" t="inlineStr">
@@ -24885,7 +24877,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C348" s="10" t="n">
+      <c r="C348" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D348" s="7" t="inlineStr">
@@ -24950,7 +24942,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C349" s="10" t="n">
+      <c r="C349" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D349" s="7" t="inlineStr">
@@ -25015,7 +25007,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C350" s="10" t="n">
+      <c r="C350" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D350" s="7" t="inlineStr">
@@ -25080,7 +25072,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C351" s="10" t="n">
+      <c r="C351" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D351" s="7" t="inlineStr">
@@ -25145,7 +25137,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C352" s="10" t="n">
+      <c r="C352" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D352" s="7" t="inlineStr">
@@ -25210,7 +25202,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C353" s="10" t="n">
+      <c r="C353" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D353" s="7" t="inlineStr">
@@ -25275,7 +25267,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C354" s="10" t="n">
+      <c r="C354" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D354" s="7" t="inlineStr">
@@ -25340,7 +25332,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C355" s="10" t="n">
+      <c r="C355" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D355" s="7" t="inlineStr">
@@ -25405,7 +25397,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C356" s="10" t="n">
+      <c r="C356" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D356" s="7" t="inlineStr">
@@ -25470,7 +25462,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C357" s="10" t="n">
+      <c r="C357" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D357" s="7" t="inlineStr">
@@ -25535,7 +25527,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C358" s="10" t="n">
+      <c r="C358" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D358" s="7" t="inlineStr">
@@ -25600,7 +25592,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C359" s="10" t="n">
+      <c r="C359" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D359" s="7" t="inlineStr">
@@ -25665,7 +25657,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C360" s="10" t="n">
+      <c r="C360" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D360" s="7" t="inlineStr">
@@ -25730,7 +25722,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C361" s="10" t="n">
+      <c r="C361" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D361" s="7" t="inlineStr">
@@ -25867,7 +25859,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C363" s="10" t="n">
+      <c r="C363" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D363" s="7" t="inlineStr">
@@ -25932,7 +25924,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C364" s="10" t="n">
+      <c r="C364" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D364" s="7" t="inlineStr">
@@ -25997,7 +25989,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C365" s="10" t="n">
+      <c r="C365" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D365" s="7" t="inlineStr">
@@ -26062,7 +26054,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C366" s="10" t="n">
+      <c r="C366" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D366" s="7" t="inlineStr">
@@ -26127,7 +26119,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C367" s="10" t="n">
+      <c r="C367" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D367" s="7" t="inlineStr">
@@ -26192,7 +26184,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C368" s="10" t="n">
+      <c r="C368" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D368" s="7" t="inlineStr">
@@ -26257,7 +26249,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C369" s="10" t="n">
+      <c r="C369" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D369" s="7" t="inlineStr">
@@ -26322,7 +26314,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C370" s="10" t="n">
+      <c r="C370" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D370" s="7" t="inlineStr">
@@ -26387,7 +26379,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C371" s="10" t="n">
+      <c r="C371" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D371" s="7" t="inlineStr">
@@ -26452,7 +26444,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C372" s="10" t="n">
+      <c r="C372" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D372" s="7" t="inlineStr">
@@ -26518,7 +26510,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C373" s="10" t="n">
+      <c r="C373" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D373" s="7" t="inlineStr">
@@ -26579,7 +26571,7 @@
           <t>00373</t>
         </is>
       </c>
-      <c r="C374" s="10" t="n"/>
+      <c r="C374" s="22" t="n"/>
       <c r="D374" s="7" t="inlineStr">
         <is>
           <t>monoprints-residues</t>
@@ -26622,7 +26614,7 @@
           <t>00374</t>
         </is>
       </c>
-      <c r="C375" s="10" t="n"/>
+      <c r="C375" s="22" t="n"/>
       <c r="D375" s="7" t="inlineStr">
         <is>
           <t>monoprints-residues</t>
@@ -26665,7 +26657,7 @@
           <t>00375</t>
         </is>
       </c>
-      <c r="C376" s="10" t="n"/>
+      <c r="C376" s="22" t="n"/>
       <c r="D376" s="1" t="inlineStr">
         <is>
           <t>all-the-colours</t>
@@ -26708,7 +26700,7 @@
           <t>00376</t>
         </is>
       </c>
-      <c r="C377" s="10" t="n"/>
+      <c r="C377" s="22" t="n"/>
       <c r="D377" s="7" t="inlineStr">
         <is>
           <t>monoprints-residues</t>
@@ -26751,7 +26743,7 @@
           <t>00377</t>
         </is>
       </c>
-      <c r="C378" s="10" t="n"/>
+      <c r="C378" s="22" t="n"/>
       <c r="D378" s="7" t="inlineStr">
         <is>
           <t>monoprints-residues</t>
@@ -26794,7 +26786,14 @@
           <t>00378</t>
         </is>
       </c>
-      <c r="C379" s="10" t="n"/>
+      <c r="B379" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C379" s="22" t="n">
+        <v>46094</v>
+      </c>
       <c r="D379" s="7" t="inlineStr">
         <is>
           <t>mm</t>
@@ -26812,12 +26811,12 @@
       </c>
       <c r="G379" s="7" t="inlineStr">
         <is>
-          <t>00378 - mm.jpg</t>
+          <t>mm quantum.jpg</t>
         </is>
       </c>
       <c r="H379" s="7" t="inlineStr">
         <is>
-          <t>00378 - mm</t>
+          <t>mm quantum</t>
         </is>
       </c>
       <c r="I379" s="7" t="n">
@@ -26826,6 +26825,22 @@
       <c r="J379" s="7" t="n">
         <v>29.7</v>
       </c>
+      <c r="K379" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="L379" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="M379" s="7" t="inlineStr">
+        <is>
+          <t>paper collage</t>
+        </is>
+      </c>
+      <c r="N379" s="7" t="inlineStr">
+        <is>
+          <t>paper collage</t>
+        </is>
+      </c>
       <c r="O379" s="7" t="n">
         <v>6</v>
       </c>
@@ -26842,7 +26857,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C380" s="10" t="n">
+      <c r="C380" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D380" s="7" t="inlineStr">
@@ -26908,7 +26923,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C381" s="10" t="n">
+      <c r="C381" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D381" s="7" t="inlineStr">
@@ -26974,7 +26989,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C382" s="10" t="n">
+      <c r="C382" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D382" s="7" t="inlineStr">
@@ -27040,7 +27055,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C383" s="10" t="n">
+      <c r="C383" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D383" s="7" t="inlineStr">
@@ -27101,7 +27116,7 @@
           <t>00383</t>
         </is>
       </c>
-      <c r="C384" s="10" t="n"/>
+      <c r="C384" s="22" t="n"/>
       <c r="D384" s="7" t="inlineStr">
         <is>
           <t>qrnt</t>
@@ -27157,7 +27172,7 @@
           <t>00384</t>
         </is>
       </c>
-      <c r="C385" s="10" t="n"/>
+      <c r="C385" s="22" t="n"/>
       <c r="D385" s="7" t="inlineStr">
         <is>
           <t>glass-forms</t>
@@ -27200,7 +27215,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C386" s="10" t="n">
+      <c r="C386" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D386" s="7" t="inlineStr">
@@ -27266,7 +27281,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C387" s="10" t="n">
+      <c r="C387" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D387" s="7" t="inlineStr">
@@ -27332,7 +27347,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C388" s="10" t="n">
+      <c r="C388" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D388" s="7" t="inlineStr">
@@ -27398,7 +27413,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C389" s="10" t="n">
+      <c r="C389" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D389" s="7" t="inlineStr">
@@ -27464,7 +27479,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C390" s="10" t="n">
+      <c r="C390" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D390" s="7" t="inlineStr">
@@ -27529,7 +27544,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C391" s="10" t="n">
+      <c r="C391" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D391" s="7" t="inlineStr">
@@ -27595,7 +27610,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C392" s="10" t="n">
+      <c r="C392" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D392" s="1" t="inlineStr">
@@ -27661,7 +27676,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C393" s="10" t="n">
+      <c r="C393" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D393" s="7" t="inlineStr">
@@ -27727,7 +27742,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C394" s="10" t="n">
+      <c r="C394" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D394" s="7" t="inlineStr">
@@ -27793,7 +27808,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C395" s="10" t="n">
+      <c r="C395" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D395" s="7" t="inlineStr">
@@ -27859,7 +27874,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C396" s="10" t="n">
+      <c r="C396" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D396" s="7" t="inlineStr">
@@ -27925,7 +27940,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C397" s="10" t="n">
+      <c r="C397" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D397" s="7" t="inlineStr">
@@ -27991,7 +28006,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C398" s="10" t="n">
+      <c r="C398" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D398" s="7" t="inlineStr">
@@ -28057,7 +28072,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C399" s="10" t="n">
+      <c r="C399" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D399" s="7" t="inlineStr">
@@ -28123,7 +28138,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C400" s="10" t="n">
+      <c r="C400" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D400" s="7" t="inlineStr">
@@ -28189,7 +28204,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C401" s="10" t="n">
+      <c r="C401" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D401" s="7" t="inlineStr">
@@ -28255,7 +28270,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C402" s="10" t="n">
+      <c r="C402" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D402" s="7" t="inlineStr">
@@ -28321,7 +28336,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C403" s="10" t="n">
+      <c r="C403" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D403" s="7" t="inlineStr">
@@ -36085,7 +36100,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C517" s="10" t="n">
+      <c r="C517" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D517" s="24" t="inlineStr">
@@ -36153,7 +36168,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C518" s="10" t="n">
+      <c r="C518" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D518" s="24" t="inlineStr">
@@ -36221,7 +36236,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C519" s="10" t="n">
+      <c r="C519" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D519" s="24" t="inlineStr">
@@ -36289,7 +36304,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C520" s="10" t="n">
+      <c r="C520" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D520" s="1" t="inlineStr">
@@ -36359,7 +36374,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C521" s="10" t="n">
+      <c r="C521" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D521" s="1" t="inlineStr">
@@ -36423,7 +36438,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C522" s="10" t="n">
+      <c r="C522" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D522" s="1" t="inlineStr">
@@ -36487,7 +36502,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C523" s="10" t="n">
+      <c r="C523" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D523" s="1" t="inlineStr">
@@ -36551,7 +36566,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C524" s="10" t="n">
+      <c r="C524" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D524" s="1" t="inlineStr">
@@ -36615,7 +36630,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C525" s="10" t="n">
+      <c r="C525" s="22" t="n">
         <v>46086</v>
       </c>
       <c r="D525" s="7" t="inlineStr">
@@ -36681,7 +36696,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C526" s="10" t="n">
+      <c r="C526" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D526" s="7" t="inlineStr">
@@ -36747,7 +36762,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C527" s="10" t="n">
+      <c r="C527" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D527" s="7" t="inlineStr">
@@ -36810,7 +36825,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C528" s="10" t="n">
+      <c r="C528" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D528" s="7" t="inlineStr">
@@ -36873,7 +36888,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C529" s="10" t="n">
+      <c r="C529" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D529" s="7" t="inlineStr">
@@ -36935,7 +36950,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C530" s="10" t="n">
+      <c r="C530" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D530" s="7" t="inlineStr">
@@ -36997,7 +37012,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C531" s="10" t="n">
+      <c r="C531" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D531" s="7" t="inlineStr">
@@ -37059,7 +37074,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C532" s="10" t="n">
+      <c r="C532" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D532" s="7" t="inlineStr">
@@ -37121,7 +37136,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C533" s="10" t="n">
+      <c r="C533" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D533" s="7" t="inlineStr">
@@ -37183,7 +37198,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C534" s="10" t="n">
+      <c r="C534" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D534" s="7" t="inlineStr">
@@ -37245,7 +37260,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C535" s="10" t="n">
+      <c r="C535" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D535" s="7" t="inlineStr">
@@ -37307,7 +37322,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C536" s="10" t="n">
+      <c r="C536" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D536" s="7" t="inlineStr">
@@ -37374,7 +37389,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C537" s="10" t="n">
+      <c r="C537" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D537" s="7" t="inlineStr">
@@ -37439,7 +37454,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C538" s="10" t="n">
+      <c r="C538" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D538" s="7" t="inlineStr">
@@ -37504,7 +37519,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C539" s="10" t="n">
+      <c r="C539" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D539" s="7" t="inlineStr">
@@ -37569,7 +37584,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C540" s="10" t="n">
+      <c r="C540" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D540" s="7" t="inlineStr">
@@ -37634,7 +37649,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C541" s="10" t="n">
+      <c r="C541" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D541" s="7" t="inlineStr">
@@ -37699,7 +37714,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C542" s="10" t="n">
+      <c r="C542" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D542" s="7" t="inlineStr">
@@ -37764,7 +37779,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C543" s="10" t="n">
+      <c r="C543" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D543" s="7" t="inlineStr">
@@ -37829,7 +37844,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C544" s="10" t="n">
+      <c r="C544" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D544" s="7" t="inlineStr">
@@ -37894,7 +37909,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C545" s="10" t="n">
+      <c r="C545" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D545" s="7" t="inlineStr">
@@ -37959,7 +37974,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C546" s="10" t="n">
+      <c r="C546" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D546" s="7" t="inlineStr">
@@ -38024,7 +38039,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C547" s="10" t="n">
+      <c r="C547" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D547" s="7" t="inlineStr">
@@ -38091,7 +38106,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C548" s="10" t="n">
+      <c r="C548" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D548" s="7" t="inlineStr">
@@ -38156,7 +38171,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C549" s="10" t="n">
+      <c r="C549" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D549" s="7" t="inlineStr">
@@ -38218,7 +38233,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C550" s="10" t="n">
+      <c r="C550" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D550" s="7" t="inlineStr">
@@ -38283,7 +38298,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C551" s="10" t="n">
+      <c r="C551" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D551" s="7" t="inlineStr">
@@ -38348,7 +38363,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C552" s="10" t="n">
+      <c r="C552" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D552" s="7" t="inlineStr">
@@ -38413,7 +38428,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C553" s="10" t="n">
+      <c r="C553" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D553" s="7" t="inlineStr">
@@ -38478,7 +38493,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C554" s="10" t="n">
+      <c r="C554" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D554" s="7" t="inlineStr">
@@ -38543,7 +38558,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C555" s="10" t="n">
+      <c r="C555" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D555" s="7" t="inlineStr">
@@ -38608,7 +38623,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C556" s="10" t="n">
+      <c r="C556" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D556" s="7" t="inlineStr">
@@ -38673,7 +38688,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C557" s="10" t="n">
+      <c r="C557" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D557" s="7" t="inlineStr">
@@ -38738,7 +38753,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C558" s="10" t="n">
+      <c r="C558" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D558" s="7" t="inlineStr">
@@ -38803,7 +38818,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C559" s="10" t="n">
+      <c r="C559" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D559" s="7" t="inlineStr">
@@ -38868,7 +38883,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C560" s="10" t="n">
+      <c r="C560" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D560" s="7" t="inlineStr">
@@ -38933,7 +38948,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C561" s="10" t="n">
+      <c r="C561" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D561" s="7" t="inlineStr">
@@ -38995,7 +39010,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C562" s="10" t="n">
+      <c r="C562" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D562" s="7" t="inlineStr">
@@ -39057,7 +39072,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C563" s="10" t="n">
+      <c r="C563" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D563" s="7" t="inlineStr">
@@ -39119,7 +39134,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C564" s="10" t="n">
+      <c r="C564" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D564" s="7" t="inlineStr">
@@ -39181,7 +39196,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C565" s="10" t="n">
+      <c r="C565" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D565" s="7" t="inlineStr">
@@ -39243,7 +39258,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C566" s="10" t="n">
+      <c r="C566" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D566" s="7" t="inlineStr">
@@ -39305,7 +39320,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C567" s="10" t="n">
+      <c r="C567" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D567" s="7" t="inlineStr">
@@ -39367,7 +39382,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C568" s="10" t="n">
+      <c r="C568" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D568" s="7" t="inlineStr">
@@ -39429,7 +39444,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C569" s="10" t="n">
+      <c r="C569" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D569" s="7" t="inlineStr">
@@ -39491,7 +39506,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C570" s="10" t="n">
+      <c r="C570" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D570" s="7" t="inlineStr">
@@ -39553,7 +39568,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C571" s="10" t="n">
+      <c r="C571" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D571" s="7" t="inlineStr">
@@ -39615,7 +39630,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C572" s="10" t="n">
+      <c r="C572" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D572" s="7" t="inlineStr">
@@ -39677,7 +39692,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C573" s="10" t="n">
+      <c r="C573" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D573" s="7" t="inlineStr">
@@ -39739,7 +39754,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C574" s="10" t="n">
+      <c r="C574" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D574" s="7" t="inlineStr">
@@ -39804,7 +39819,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C575" s="10" t="n">
+      <c r="C575" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D575" s="7" t="inlineStr">
@@ -39869,7 +39884,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C576" s="10" t="n">
+      <c r="C576" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D576" s="7" t="inlineStr">
@@ -39934,7 +39949,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C577" s="10" t="n">
+      <c r="C577" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D577" s="7" t="inlineStr">
@@ -39999,7 +40014,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C578" s="10" t="n">
+      <c r="C578" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D578" s="7" t="inlineStr">
@@ -40064,7 +40079,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C579" s="10" t="n">
+      <c r="C579" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D579" s="7" t="inlineStr">
@@ -40129,7 +40144,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C580" s="10" t="n">
+      <c r="C580" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D580" s="7" t="inlineStr">
@@ -40194,7 +40209,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C581" s="10" t="n">
+      <c r="C581" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D581" s="7" t="inlineStr">
@@ -40259,7 +40274,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C582" s="10" t="n">
+      <c r="C582" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D582" s="7" t="inlineStr">
@@ -40321,7 +40336,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C583" s="10" t="n">
+      <c r="C583" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D583" s="7" t="inlineStr">
@@ -40383,7 +40398,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C584" s="10" t="n">
+      <c r="C584" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D584" s="7" t="inlineStr">
@@ -40445,7 +40460,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C585" s="10" t="n">
+      <c r="C585" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D585" s="7" t="inlineStr">
@@ -40507,7 +40522,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C586" s="10" t="n">
+      <c r="C586" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D586" s="7" t="inlineStr">
@@ -40569,7 +40584,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C587" s="10" t="n">
+      <c r="C587" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D587" s="7" t="inlineStr">
@@ -40631,7 +40646,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C588" s="10" t="n">
+      <c r="C588" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D588" s="7" t="inlineStr">
@@ -40693,7 +40708,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C589" s="10" t="n">
+      <c r="C589" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D589" s="7" t="inlineStr">
@@ -40755,7 +40770,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C590" s="10" t="n">
+      <c r="C590" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D590" s="7" t="inlineStr">
@@ -40817,7 +40832,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C591" s="10" t="n">
+      <c r="C591" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D591" s="7" t="inlineStr">
@@ -40882,7 +40897,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C592" s="10" t="n">
+      <c r="C592" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D592" s="7" t="inlineStr">
@@ -40947,7 +40962,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C593" s="10" t="n">
+      <c r="C593" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D593" s="7" t="inlineStr">
@@ -41012,7 +41027,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C594" s="10" t="n">
+      <c r="C594" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D594" s="7" t="inlineStr">
@@ -41077,7 +41092,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C595" s="10" t="n">
+      <c r="C595" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D595" s="7" t="inlineStr">
@@ -41142,7 +41157,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C596" s="10" t="n">
+      <c r="C596" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D596" s="7" t="inlineStr">
@@ -41207,7 +41222,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C597" s="10" t="n">
+      <c r="C597" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D597" s="7" t="inlineStr">
@@ -41272,7 +41287,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C598" s="10" t="n">
+      <c r="C598" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D598" s="7" t="inlineStr">
@@ -41337,7 +41352,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C599" s="10" t="n">
+      <c r="C599" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D599" s="7" t="inlineStr">
@@ -41402,7 +41417,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C600" s="10" t="n">
+      <c r="C600" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D600" s="7" t="inlineStr">
@@ -41467,7 +41482,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C601" s="10" t="n">
+      <c r="C601" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D601" s="7" t="inlineStr">
@@ -41529,7 +41544,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C602" s="10" t="n">
+      <c r="C602" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D602" s="7" t="inlineStr">
@@ -41591,7 +41606,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C603" s="10" t="n">
+      <c r="C603" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D603" s="7" t="inlineStr">
@@ -41653,7 +41668,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C604" s="10" t="n">
+      <c r="C604" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D604" s="7" t="inlineStr">
@@ -41715,7 +41730,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C605" s="10" t="n">
+      <c r="C605" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D605" s="7" t="inlineStr">
@@ -41777,7 +41792,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C606" s="10" t="n">
+      <c r="C606" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D606" s="7" t="inlineStr">
@@ -41839,7 +41854,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C607" s="10" t="n">
+      <c r="C607" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D607" s="7" t="inlineStr">
@@ -41901,7 +41916,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C608" s="10" t="n">
+      <c r="C608" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D608" s="7" t="inlineStr">
@@ -41963,7 +41978,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C609" s="10" t="n">
+      <c r="C609" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D609" s="7" t="inlineStr">
@@ -42025,7 +42040,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C610" s="10" t="n">
+      <c r="C610" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D610" s="7" t="inlineStr">
@@ -42087,7 +42102,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C611" s="10" t="n">
+      <c r="C611" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D611" s="7" t="inlineStr">
@@ -42149,7 +42164,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C612" s="10" t="n">
+      <c r="C612" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D612" s="7" t="inlineStr">
@@ -42211,7 +42226,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C613" s="10" t="n">
+      <c r="C613" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D613" s="7" t="inlineStr">
@@ -42273,7 +42288,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C614" s="10" t="n">
+      <c r="C614" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D614" s="7" t="inlineStr">
@@ -42335,7 +42350,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C615" s="10" t="n">
+      <c r="C615" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D615" s="7" t="inlineStr">
@@ -42397,7 +42412,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C616" s="10" t="n">
+      <c r="C616" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D616" s="7" t="inlineStr">
@@ -42459,7 +42474,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C617" s="10" t="n">
+      <c r="C617" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D617" s="1" t="inlineStr">
@@ -42529,7 +42544,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C618" s="10" t="n">
+      <c r="C618" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D618" s="1" t="inlineStr">
@@ -42591,7 +42606,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C619" s="10" t="n">
+      <c r="C619" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D619" s="7" t="inlineStr">
@@ -42653,7 +42668,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C620" s="10" t="n">
+      <c r="C620" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D620" s="7" t="inlineStr">
@@ -42715,7 +42730,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C621" s="10" t="n">
+      <c r="C621" s="22" t="n">
         <v>46094</v>
       </c>
       <c r="D621" s="7" t="inlineStr">
@@ -42780,7 +42795,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="31.83203125" customWidth="1" style="1" min="1" max="1"/>
     <col width="43.1640625" customWidth="1" style="1" min="2" max="2"/>
@@ -42791,8 +42806,8 @@
     <col width="21" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
     <col width="21" customWidth="1" style="7" min="8" max="8"/>
     <col width="51" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" style="1" min="10" max="71"/>
-    <col width="10.83203125" customWidth="1" style="1" min="72" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="1" min="10" max="72"/>
+    <col width="10.83203125" customWidth="1" style="1" min="73" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -43465,12 +43480,12 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>heaven-and-earth</t>
+          <t>harmony</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>heaven and earth</t>
+          <t>harmony</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -43484,24 +43499,29 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>46086</v>
+        <v>46094</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>2011</v>
+        <v>2009</v>
+      </c>
+      <c r="H20" s="16" t="inlineStr">
+        <is>
+          <t>00379</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>intuition-2020</t>
+          <t>heaven-and-earth</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>intuition (2020)</t>
+          <t>heaven and earth</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
@@ -43518,28 +43538,21 @@
         <v>46086</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>2020</v>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>c. 2001-11</t>
-        </is>
-      </c>
-      <c r="I21" s="1" t="inlineStr">
-        <is>
-          <t>put track listing in work_prose</t>
-        </is>
+        <v>2011</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>2011</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>kylie-structures</t>
+          <t>intuition-2020</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>kylie structures</t>
+          <t>intuition (2020)</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -43556,26 +43569,28 @@
         <v>46086</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>00520</t>
+        <v>2020</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>c. 2001-11</t>
+        </is>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>put track listing in work_prose</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>landscapes</t>
+          <t>kylie-structures</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>landscapes</t>
+          <t>kylie structures</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -43599,19 +43614,19 @@
       </c>
       <c r="H23" s="16" t="inlineStr">
         <is>
-          <t>00516</t>
+          <t>00520</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>leaf</t>
+          <t>landscapes</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>leaf</t>
+          <t>landscapes</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -43628,133 +43643,136 @@
         <v>46086</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>2016</v>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
-        <is>
-          <t>add details</t>
+        <v>2023</v>
+      </c>
+      <c r="H24" s="16" t="inlineStr">
+        <is>
+          <t>00516</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
+          <t>leaf</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>leaf</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>46086</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>2016</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>2016</v>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>add details</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
           <t>learning-to-draw-landscapes</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr">
         <is>
           <t>learning to draw landscapes</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>46086</v>
-      </c>
-      <c r="F25" s="1" t="n">
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>46086</v>
+      </c>
+      <c r="F26" s="1" t="n">
         <v>2010</v>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>c. 2010?, 2022</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H26" s="16" t="inlineStr">
         <is>
           <t>00127</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>lipseyes</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>lipseyes</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="n">
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="n">
         <v>46094</v>
       </c>
-      <c r="F26" s="1" t="n">
+      <c r="F27" s="1" t="n">
         <v>2003</v>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="G27" s="7" t="n">
         <v>2003</v>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H27" s="16" t="inlineStr">
         <is>
           <t>00388</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>living-surface-hand-form</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>living surface hand form</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>46086</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>2004</v>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>1989, 2004</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>living-surface-hand-form</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>living surface hand form</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -43770,34 +43788,24 @@
       <c r="E28" s="9" t="n">
         <v>46086</v>
       </c>
-      <c r="F28" s="1" t="n">
-        <v>2009</v>
+      <c r="F28" s="7" t="n">
+        <v>2004</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>2004-15</t>
-        </is>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>00477</t>
-        </is>
-      </c>
-      <c r="I28" s="1" t="inlineStr">
-        <is>
-          <t>add dall-e versions</t>
+          <t>1989, 2004</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>models</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>models</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -43810,30 +43818,37 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E29" s="10" t="n">
-        <v>46094</v>
+      <c r="E29" s="9" t="n">
+        <v>46086</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>1994</v>
-      </c>
-      <c r="G29" s="7" t="n">
-        <v>1994</v>
+        <v>2009</v>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>2004-15</t>
+        </is>
       </c>
       <c r="H29" s="16" t="inlineStr">
         <is>
-          <t>00540</t>
+          <t>00477</t>
+        </is>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>add dall-e versions</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>molecule-forms</t>
+          <t>models</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>molecule forms</t>
+          <t>models</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -43847,24 +43862,29 @@
         </is>
       </c>
       <c r="E30" s="10" t="n">
-        <v>46086</v>
+        <v>46094</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>2013</v>
+        <v>1994</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>2013</v>
+        <v>1994</v>
+      </c>
+      <c r="H30" s="16" t="inlineStr">
+        <is>
+          <t>00540</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>molecules</t>
+          <t>molecule-forms</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>molecules</t>
+          <t>molecule forms</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
@@ -43886,76 +43906,69 @@
       <c r="G31" s="7" t="n">
         <v>2013</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>molecules</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>molecules</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>46086</v>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>2013</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>2013</v>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>00460</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>monoprints-residues</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
+      <c r="B33" s="1" t="inlineStr">
         <is>
           <t>monoprints and residues</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>primary</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>mouse-story</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="inlineStr">
-        <is>
-          <t>mouse story</t>
-        </is>
-      </c>
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>46086</v>
-      </c>
-      <c r="F33" s="1" t="n">
-        <v>1993</v>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>1991-93</t>
-        </is>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
-        <is>
-          <t>00160</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>nerve</t>
+          <t>mouse-story</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>nerve</t>
+          <t>mouse story</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -43972,28 +43985,28 @@
         <v>46086</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>1990-95</t>
-        </is>
-      </c>
-      <c r="I34" s="1" t="inlineStr">
-        <is>
-          <t>works and details to publish</t>
+          <t>1991-93</t>
+        </is>
+      </c>
+      <c r="H34" s="16" t="inlineStr">
+        <is>
+          <t>00160</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>nerve-forms</t>
+          <t>nerve</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>nerve forms</t>
+          <t>nerve</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -44007,34 +44020,31 @@
         </is>
       </c>
       <c r="E35" s="10" t="n">
-        <v>46094</v>
+        <v>46086</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>2004</v>
-      </c>
-      <c r="G35" s="7" t="n">
-        <v>2004</v>
-      </c>
-      <c r="H35" s="16" t="inlineStr">
-        <is>
-          <t>00581</t>
+        <v>1995</v>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>1990-95</t>
         </is>
       </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>add videos</t>
+          <t>works and details to publish</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>particle-theory</t>
+          <t>nerve-forms</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>particle theory</t>
+          <t>nerve forms</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
@@ -44051,26 +44061,31 @@
         <v>46094</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="H36" s="16" t="inlineStr">
         <is>
-          <t>00553</t>
+          <t>00581</t>
+        </is>
+      </c>
+      <c r="I36" s="1" t="inlineStr">
+        <is>
+          <t>add videos</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>qrnt</t>
+          <t>particle-theory</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>quantum random number theory</t>
+          <t>particle theory</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -44078,24 +44093,35 @@
           <t>primary</t>
         </is>
       </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>46094</v>
+      </c>
       <c r="F37" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>2009, 2015</t>
+        <v>2008</v>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>2008</v>
+      </c>
+      <c r="H37" s="16" t="inlineStr">
+        <is>
+          <t>00553</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>qrnt</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>quantum random number theory</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -44103,35 +44129,24 @@
           <t>primary</t>
         </is>
       </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>46086</v>
-      </c>
       <c r="F38" s="1" t="n">
-        <v>2001</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>2001</v>
-      </c>
-      <c r="H38" s="16" t="inlineStr">
-        <is>
-          <t>00142</t>
+        <v>2015</v>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>2009, 2015</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>spiders</t>
+          <t>r</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>spiders</t>
+          <t>r</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -44145,29 +44160,29 @@
         </is>
       </c>
       <c r="E39" s="10" t="n">
-        <v>46094</v>
+        <v>46086</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>2006</v>
+        <v>2001</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>2006</v>
+        <v>2001</v>
       </c>
       <c r="H39" s="16" t="inlineStr">
         <is>
-          <t>00402</t>
+          <t>00142</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>string-theory</t>
+          <t>spiders</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>string theory</t>
+          <t>spiders</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
@@ -44184,28 +44199,26 @@
         <v>46094</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>2012</v>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>2005-12</t>
-        </is>
+        <v>2006</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>2006</v>
       </c>
       <c r="H40" s="16" t="inlineStr">
         <is>
-          <t>00573</t>
+          <t>00402</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>tree</t>
+          <t>string-theory</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>tree</t>
+          <t>string theory</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -44222,26 +44235,28 @@
         <v>46094</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="G41" s="7" t="n">
-        <v>2024</v>
+        <v>2012</v>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>2005-12</t>
+        </is>
       </c>
       <c r="H41" s="16" t="inlineStr">
         <is>
-          <t>00546</t>
+          <t>00573</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>wa</t>
+          <t>tree</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>wa</t>
+          <t>tree</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -44258,28 +44273,26 @@
         <v>46094</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>2008, 2011</t>
-        </is>
+        <v>2024</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>2024</v>
       </c>
       <c r="H42" s="16" t="inlineStr">
         <is>
-          <t>00615</t>
+          <t>00546</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>harmony</t>
+          <t>wa</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>harmony</t>
+          <t>wa</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -44296,14 +44309,16 @@
         <v>46094</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>2009</v>
-      </c>
-      <c r="G43" s="7" t="n">
-        <v>2009</v>
+        <v>2008</v>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>2008, 2011</t>
+        </is>
       </c>
       <c r="H43" s="16" t="inlineStr">
         <is>
-          <t>00379</t>
+          <t>00615</t>
         </is>
       </c>
     </row>
@@ -44323,7 +44338,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J1111"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="9.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -68532,7 +68547,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G590" s="25" t="n">
+      <c r="G590" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H590" t="n">
@@ -68573,7 +68588,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G591" s="25" t="n">
+      <c r="G591" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H591" t="n">
@@ -68614,7 +68629,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G592" s="25" t="n">
+      <c r="G592" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H592" t="n">
@@ -68655,7 +68670,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G593" s="25" t="n">
+      <c r="G593" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H593" t="n">
@@ -68696,7 +68711,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G594" s="25" t="n">
+      <c r="G594" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H594" t="n">
@@ -68737,7 +68752,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G595" s="25" t="n">
+      <c r="G595" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H595" t="n">
@@ -68778,7 +68793,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G596" s="25" t="n">
+      <c r="G596" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H596" t="n">
@@ -68819,7 +68834,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G597" s="25" t="n">
+      <c r="G597" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H597" t="n">
@@ -68860,7 +68875,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G598" s="25" t="n">
+      <c r="G598" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H598" t="n">
@@ -68901,7 +68916,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G599" s="25" t="n">
+      <c r="G599" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H599" t="n">
@@ -68942,7 +68957,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G600" s="25" t="n">
+      <c r="G600" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H600" t="n">
@@ -68983,7 +68998,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G601" s="25" t="n">
+      <c r="G601" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H601" t="n">
@@ -69024,7 +69039,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G602" s="25" t="n">
+      <c r="G602" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H602" t="n">
@@ -69065,7 +69080,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G603" s="25" t="n">
+      <c r="G603" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H603" t="n">
@@ -69106,7 +69121,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G604" s="25" t="n">
+      <c r="G604" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H604" t="n">
@@ -69147,7 +69162,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G605" s="25" t="n">
+      <c r="G605" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H605" t="n">
@@ -69188,7 +69203,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G606" s="25" t="n">
+      <c r="G606" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H606" t="n">
@@ -69229,7 +69244,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G607" s="25" t="n">
+      <c r="G607" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H607" t="n">
@@ -69270,7 +69285,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G608" s="25" t="n">
+      <c r="G608" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H608" t="n">
@@ -69311,7 +69326,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G609" s="25" t="n">
+      <c r="G609" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H609" t="n">
@@ -69352,7 +69367,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G610" s="25" t="n">
+      <c r="G610" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H610" t="n">
@@ -69393,7 +69408,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G611" s="25" t="n">
+      <c r="G611" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H611" t="n">
@@ -69434,7 +69449,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G612" s="25" t="n">
+      <c r="G612" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H612" t="n">
@@ -69475,7 +69490,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G613" s="25" t="n">
+      <c r="G613" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H613" t="n">
@@ -69516,7 +69531,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G614" s="25" t="n">
+      <c r="G614" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H614" t="n">
@@ -69557,7 +69572,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G615" s="25" t="n">
+      <c r="G615" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H615" t="n">
@@ -69598,7 +69613,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G616" s="25" t="n">
+      <c r="G616" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H616" t="n">
@@ -69639,7 +69654,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G617" s="25" t="n">
+      <c r="G617" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H617" t="n">
@@ -69680,7 +69695,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G618" s="25" t="n">
+      <c r="G618" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H618" t="n">
@@ -69721,7 +69736,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G619" s="25" t="n">
+      <c r="G619" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H619" t="n">
@@ -69762,7 +69777,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G620" s="25" t="n">
+      <c r="G620" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H620" t="n">
@@ -69803,7 +69818,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G621" s="25" t="n">
+      <c r="G621" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H621" t="n">
@@ -69844,7 +69859,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G622" s="25" t="n">
+      <c r="G622" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H622" t="n">
@@ -69885,7 +69900,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G623" s="25" t="n">
+      <c r="G623" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H623" t="n">
@@ -69926,7 +69941,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G624" s="25" t="n">
+      <c r="G624" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H624" t="n">
@@ -69967,7 +69982,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G625" s="25" t="n">
+      <c r="G625" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H625" t="n">
@@ -70008,7 +70023,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G626" s="25" t="n">
+      <c r="G626" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H626" t="n">
@@ -70049,7 +70064,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G627" s="25" t="n">
+      <c r="G627" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H627" t="n">
@@ -70090,7 +70105,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G628" s="25" t="n">
+      <c r="G628" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H628" t="n">
@@ -70131,7 +70146,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G629" s="25" t="n">
+      <c r="G629" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H629" t="n">
@@ -70172,7 +70187,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G630" s="25" t="n">
+      <c r="G630" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H630" t="n">
@@ -70213,7 +70228,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G631" s="25" t="n">
+      <c r="G631" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H631" t="n">
@@ -70254,7 +70269,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G632" s="25" t="n">
+      <c r="G632" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H632" t="n">
@@ -70295,7 +70310,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G633" s="25" t="n">
+      <c r="G633" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H633" t="n">
@@ -70336,7 +70351,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G634" s="25" t="n">
+      <c r="G634" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H634" t="n">
@@ -70377,7 +70392,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G635" s="25" t="n">
+      <c r="G635" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H635" t="n">
@@ -70418,7 +70433,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G636" s="25" t="n">
+      <c r="G636" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H636" t="n">
@@ -70459,7 +70474,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G637" s="25" t="n">
+      <c r="G637" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H637" t="n">
@@ -70500,7 +70515,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G638" s="25" t="n">
+      <c r="G638" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H638" t="n">
@@ -70541,7 +70556,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G639" s="25" t="n">
+      <c r="G639" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H639" t="n">
@@ -70582,7 +70597,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G640" s="25" t="n">
+      <c r="G640" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H640" t="n">
@@ -70623,7 +70638,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G641" s="25" t="n">
+      <c r="G641" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H641" t="n">
@@ -70664,7 +70679,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G642" s="25" t="n">
+      <c r="G642" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H642" t="n">
@@ -70705,7 +70720,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G643" s="25" t="n">
+      <c r="G643" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H643" t="n">
@@ -70746,7 +70761,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G644" s="25" t="n">
+      <c r="G644" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H644" t="n">
@@ -70787,7 +70802,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G645" s="25" t="n">
+      <c r="G645" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H645" t="n">
@@ -70828,7 +70843,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G646" s="25" t="n">
+      <c r="G646" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H646" t="n">
@@ -70869,7 +70884,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G647" s="25" t="n">
+      <c r="G647" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H647" t="n">
@@ -70910,7 +70925,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G648" s="25" t="n">
+      <c r="G648" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H648" t="n">
@@ -70951,7 +70966,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G649" s="25" t="n">
+      <c r="G649" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H649" t="n">
@@ -70992,7 +71007,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G650" s="25" t="n">
+      <c r="G650" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H650" t="n">
@@ -71033,7 +71048,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G651" s="25" t="n">
+      <c r="G651" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H651" t="n">
@@ -71074,7 +71089,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G652" s="25" t="n">
+      <c r="G652" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H652" t="n">
@@ -71115,7 +71130,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G653" s="25" t="n">
+      <c r="G653" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H653" t="n">
@@ -71156,7 +71171,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G654" s="25" t="n">
+      <c r="G654" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H654" t="n">
@@ -71197,7 +71212,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G655" s="25" t="n">
+      <c r="G655" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H655" t="n">
@@ -71238,7 +71253,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G656" s="25" t="n">
+      <c r="G656" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H656" t="n">
@@ -71279,7 +71294,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G657" s="25" t="n">
+      <c r="G657" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H657" t="n">
@@ -71320,7 +71335,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G658" s="25" t="n">
+      <c r="G658" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H658" t="n">
@@ -71361,7 +71376,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G659" s="25" t="n">
+      <c r="G659" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H659" t="n">
@@ -71402,7 +71417,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G660" s="25" t="n">
+      <c r="G660" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H660" t="n">
@@ -71443,7 +71458,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G661" s="25" t="n">
+      <c r="G661" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H661" t="n">
@@ -71484,7 +71499,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G662" s="25" t="n">
+      <c r="G662" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H662" t="n">
@@ -71525,7 +71540,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G663" s="25" t="n">
+      <c r="G663" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H663" t="n">
@@ -71566,7 +71581,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G664" s="25" t="n">
+      <c r="G664" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H664" t="n">
@@ -71607,7 +71622,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G665" s="25" t="n">
+      <c r="G665" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H665" t="n">
@@ -71648,7 +71663,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G666" s="25" t="n">
+      <c r="G666" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H666" t="n">
@@ -71689,7 +71704,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G667" s="25" t="n">
+      <c r="G667" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H667" t="n">
@@ -71730,7 +71745,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G668" s="25" t="n">
+      <c r="G668" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H668" t="n">
@@ -71771,7 +71786,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G669" s="25" t="n">
+      <c r="G669" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H669" t="n">
@@ -71812,7 +71827,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G670" s="25" t="n">
+      <c r="G670" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H670" t="n">
@@ -71853,7 +71868,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G671" s="25" t="n">
+      <c r="G671" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H671" t="n">
@@ -71894,7 +71909,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G672" s="25" t="n">
+      <c r="G672" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H672" t="n">
@@ -71935,7 +71950,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G673" s="25" t="n">
+      <c r="G673" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H673" t="n">
@@ -71976,7 +71991,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G674" s="25" t="n">
+      <c r="G674" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H674" t="n">
@@ -72017,7 +72032,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G675" s="25" t="n">
+      <c r="G675" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H675" t="n">
@@ -72058,7 +72073,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G676" s="25" t="n">
+      <c r="G676" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H676" t="n">
@@ -72099,7 +72114,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G677" s="25" t="n">
+      <c r="G677" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H677" t="n">
@@ -72140,7 +72155,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G678" s="25" t="n">
+      <c r="G678" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H678" t="n">
@@ -72181,7 +72196,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G679" s="25" t="n">
+      <c r="G679" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H679" t="n">
@@ -72222,7 +72237,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G680" s="25" t="n">
+      <c r="G680" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H680" t="n">
@@ -72263,7 +72278,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G681" s="25" t="n">
+      <c r="G681" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H681" t="n">
@@ -72304,7 +72319,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G682" s="25" t="n">
+      <c r="G682" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H682" t="n">
@@ -72345,7 +72360,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G683" s="25" t="n">
+      <c r="G683" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H683" t="n">
@@ -72386,7 +72401,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G684" s="25" t="n">
+      <c r="G684" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H684" t="n">
@@ -72427,7 +72442,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G685" s="25" t="n">
+      <c r="G685" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H685" t="n">
@@ -72468,7 +72483,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G686" s="25" t="n">
+      <c r="G686" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H686" t="n">
@@ -72509,7 +72524,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G687" s="25" t="n">
+      <c r="G687" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H687" t="n">
@@ -72550,7 +72565,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G688" s="25" t="n">
+      <c r="G688" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H688" t="n">
@@ -72591,7 +72606,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G689" s="25" t="n">
+      <c r="G689" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H689" t="n">
@@ -72632,7 +72647,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G690" s="25" t="n">
+      <c r="G690" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H690" t="n">
@@ -72673,7 +72688,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G691" s="25" t="n">
+      <c r="G691" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H691" t="n">
@@ -72714,7 +72729,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G692" s="25" t="n">
+      <c r="G692" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H692" t="n">
@@ -72755,7 +72770,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G693" s="25" t="n">
+      <c r="G693" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H693" t="n">
@@ -72796,7 +72811,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G694" s="25" t="n">
+      <c r="G694" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H694" t="n">
@@ -72837,7 +72852,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G695" s="25" t="n">
+      <c r="G695" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H695" t="n">
@@ -72878,7 +72893,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G696" s="25" t="n">
+      <c r="G696" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H696" t="n">
@@ -72919,7 +72934,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G697" s="25" t="n">
+      <c r="G697" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H697" t="n">
@@ -72960,7 +72975,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G698" s="25" t="n">
+      <c r="G698" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H698" t="n">
@@ -73001,7 +73016,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G699" s="25" t="n">
+      <c r="G699" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H699" t="n">
@@ -73042,7 +73057,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G700" s="25" t="n">
+      <c r="G700" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H700" t="n">
@@ -73083,7 +73098,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G701" s="25" t="n">
+      <c r="G701" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H701" t="n">
@@ -73124,7 +73139,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G702" s="25" t="n">
+      <c r="G702" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H702" t="n">
@@ -73165,7 +73180,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G703" s="25" t="n">
+      <c r="G703" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H703" t="n">
@@ -73206,7 +73221,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G704" s="25" t="n">
+      <c r="G704" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H704" t="n">
@@ -73247,7 +73262,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G705" s="25" t="n">
+      <c r="G705" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H705" t="n">
@@ -73288,7 +73303,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G706" s="25" t="n">
+      <c r="G706" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H706" t="n">
@@ -73329,7 +73344,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G707" s="25" t="n">
+      <c r="G707" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H707" t="n">
@@ -73370,7 +73385,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G708" s="25" t="n">
+      <c r="G708" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H708" t="n">
@@ -73411,7 +73426,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G709" s="25" t="n">
+      <c r="G709" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H709" t="n">
@@ -73452,7 +73467,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G710" s="25" t="n">
+      <c r="G710" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H710" t="n">
@@ -73493,7 +73508,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G711" s="25" t="n">
+      <c r="G711" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H711" t="n">
@@ -73534,7 +73549,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G712" s="25" t="n">
+      <c r="G712" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H712" t="n">
@@ -73575,7 +73590,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G713" s="25" t="n">
+      <c r="G713" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H713" t="n">
@@ -73616,7 +73631,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G714" s="25" t="n">
+      <c r="G714" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H714" t="n">
@@ -73657,7 +73672,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G715" s="25" t="n">
+      <c r="G715" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H715" t="n">
@@ -73698,7 +73713,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G716" s="25" t="n">
+      <c r="G716" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H716" t="n">
@@ -73739,7 +73754,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G717" s="25" t="n">
+      <c r="G717" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H717" t="n">
@@ -73780,7 +73795,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G718" s="25" t="n">
+      <c r="G718" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H718" t="n">
@@ -73821,7 +73836,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G719" s="25" t="n">
+      <c r="G719" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H719" t="n">
@@ -73862,7 +73877,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G720" s="25" t="n">
+      <c r="G720" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H720" t="n">
@@ -73903,7 +73918,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G721" s="25" t="n">
+      <c r="G721" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H721" t="n">
@@ -73944,7 +73959,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G722" s="25" t="n">
+      <c r="G722" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H722" t="n">
@@ -73985,7 +74000,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G723" s="25" t="n">
+      <c r="G723" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H723" t="n">
@@ -74026,7 +74041,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G724" s="25" t="n">
+      <c r="G724" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H724" t="n">
@@ -74067,7 +74082,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G725" s="25" t="n">
+      <c r="G725" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H725" t="n">
@@ -74108,7 +74123,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G726" s="25" t="n">
+      <c r="G726" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H726" t="n">
@@ -74149,7 +74164,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G727" s="25" t="n">
+      <c r="G727" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H727" t="n">
@@ -74190,7 +74205,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G728" s="25" t="n">
+      <c r="G728" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H728" t="n">
@@ -74231,7 +74246,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G729" s="25" t="n">
+      <c r="G729" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H729" t="n">
@@ -74272,7 +74287,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G730" s="25" t="n">
+      <c r="G730" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H730" t="n">
@@ -74313,7 +74328,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G731" s="25" t="n">
+      <c r="G731" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H731" t="n">
@@ -74354,7 +74369,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G732" s="25" t="n">
+      <c r="G732" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H732" t="n">
@@ -74395,7 +74410,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G733" s="25" t="n">
+      <c r="G733" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H733" t="n">
@@ -74436,7 +74451,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G734" s="25" t="n">
+      <c r="G734" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H734" t="n">
@@ -74477,7 +74492,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G735" s="25" t="n">
+      <c r="G735" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H735" t="n">
@@ -74518,7 +74533,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G736" s="25" t="n">
+      <c r="G736" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H736" t="n">
@@ -74559,7 +74574,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G737" s="25" t="n">
+      <c r="G737" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H737" t="n">
@@ -74600,7 +74615,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G738" s="25" t="n">
+      <c r="G738" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H738" t="n">
@@ -74641,7 +74656,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G739" s="25" t="n">
+      <c r="G739" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H739" t="n">
@@ -74682,7 +74697,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G740" s="25" t="n">
+      <c r="G740" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H740" t="n">
@@ -74723,7 +74738,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G741" s="25" t="n">
+      <c r="G741" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H741" t="n">
@@ -74764,7 +74779,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G742" s="25" t="n">
+      <c r="G742" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H742" t="n">
@@ -74805,7 +74820,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G743" s="25" t="n">
+      <c r="G743" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H743" t="n">
@@ -74846,7 +74861,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G744" s="25" t="n">
+      <c r="G744" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H744" t="n">
@@ -74887,7 +74902,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G745" s="25" t="n">
+      <c r="G745" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H745" t="n">
@@ -74928,7 +74943,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G746" s="25" t="n">
+      <c r="G746" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H746" t="n">
@@ -74969,7 +74984,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G747" s="25" t="n">
+      <c r="G747" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H747" t="n">
@@ -75010,7 +75025,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G748" s="25" t="n">
+      <c r="G748" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H748" t="n">
@@ -75051,7 +75066,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G749" s="25" t="n">
+      <c r="G749" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H749" t="n">
@@ -75092,7 +75107,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G750" s="25" t="n">
+      <c r="G750" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H750" t="n">
@@ -75133,7 +75148,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G751" s="25" t="n">
+      <c r="G751" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H751" t="n">
@@ -75174,7 +75189,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G752" s="25" t="n">
+      <c r="G752" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H752" t="n">
@@ -75215,7 +75230,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G753" s="25" t="n">
+      <c r="G753" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H753" t="n">
@@ -75256,7 +75271,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G754" s="25" t="n">
+      <c r="G754" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H754" t="n">
@@ -75297,7 +75312,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G755" s="25" t="n">
+      <c r="G755" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H755" t="n">
@@ -75338,7 +75353,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G756" s="25" t="n">
+      <c r="G756" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H756" t="n">
@@ -75379,7 +75394,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G757" s="25" t="n">
+      <c r="G757" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H757" t="n">
@@ -75420,7 +75435,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G758" s="25" t="n">
+      <c r="G758" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H758" t="n">
@@ -75461,7 +75476,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G759" s="25" t="n">
+      <c r="G759" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H759" t="n">
@@ -75502,7 +75517,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G760" s="25" t="n">
+      <c r="G760" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H760" t="n">
@@ -75543,7 +75558,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G761" s="25" t="n">
+      <c r="G761" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H761" t="n">
@@ -75584,7 +75599,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G762" s="25" t="n">
+      <c r="G762" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H762" t="n">
@@ -75625,7 +75640,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G763" s="25" t="n">
+      <c r="G763" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H763" t="n">
@@ -75666,7 +75681,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G764" s="25" t="n">
+      <c r="G764" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H764" t="n">
@@ -75707,7 +75722,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G765" s="25" t="n">
+      <c r="G765" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H765" t="n">
@@ -75748,7 +75763,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G766" s="25" t="n">
+      <c r="G766" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H766" t="n">
@@ -75789,7 +75804,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G767" s="25" t="n">
+      <c r="G767" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H767" t="n">
@@ -75830,7 +75845,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G768" s="25" t="n">
+      <c r="G768" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H768" t="n">
@@ -75871,7 +75886,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G769" s="25" t="n">
+      <c r="G769" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H769" t="n">
@@ -75912,7 +75927,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G770" s="25" t="n">
+      <c r="G770" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H770" t="n">
@@ -75953,7 +75968,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G771" s="25" t="n">
+      <c r="G771" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H771" t="n">
@@ -75994,7 +76009,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G772" s="25" t="n">
+      <c r="G772" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H772" t="n">
@@ -76035,7 +76050,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G773" s="25" t="n">
+      <c r="G773" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H773" t="n">
@@ -76076,7 +76091,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G774" s="25" t="n">
+      <c r="G774" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H774" t="n">
@@ -76117,7 +76132,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G775" s="25" t="n">
+      <c r="G775" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H775" t="n">
@@ -76158,7 +76173,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G776" s="25" t="n">
+      <c r="G776" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H776" t="n">
@@ -76199,7 +76214,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G777" s="25" t="n">
+      <c r="G777" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H777" t="n">
@@ -76240,7 +76255,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G778" s="25" t="n">
+      <c r="G778" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H778" t="n">
@@ -76281,7 +76296,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G779" s="25" t="n">
+      <c r="G779" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H779" t="n">
@@ -76322,7 +76337,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G780" s="25" t="n">
+      <c r="G780" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H780" t="n">
@@ -76363,7 +76378,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G781" s="25" t="n">
+      <c r="G781" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H781" t="n">
@@ -76404,7 +76419,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G782" s="25" t="n">
+      <c r="G782" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H782" t="n">
@@ -76445,7 +76460,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G783" s="25" t="n">
+      <c r="G783" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H783" t="n">
@@ -76486,7 +76501,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G784" s="25" t="n">
+      <c r="G784" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H784" t="n">
@@ -76527,7 +76542,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G785" s="25" t="n">
+      <c r="G785" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H785" t="n">
@@ -76568,7 +76583,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G786" s="25" t="n">
+      <c r="G786" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H786" t="n">
@@ -76609,7 +76624,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G787" s="25" t="n">
+      <c r="G787" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H787" t="n">
@@ -76650,7 +76665,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G788" s="25" t="n">
+      <c r="G788" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H788" t="n">
@@ -76691,7 +76706,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G789" s="25" t="n">
+      <c r="G789" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H789" t="n">
@@ -76732,7 +76747,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G790" s="25" t="n">
+      <c r="G790" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H790" t="n">
@@ -76773,7 +76788,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G791" s="25" t="n">
+      <c r="G791" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H791" t="n">
@@ -76814,7 +76829,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G792" s="25" t="n">
+      <c r="G792" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H792" t="n">
@@ -76855,7 +76870,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G793" s="25" t="n">
+      <c r="G793" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H793" t="n">
@@ -76896,7 +76911,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G794" s="25" t="n">
+      <c r="G794" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H794" t="n">
@@ -76937,7 +76952,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G795" s="25" t="n">
+      <c r="G795" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H795" t="n">
@@ -76978,7 +76993,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G796" s="25" t="n">
+      <c r="G796" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H796" t="n">
@@ -77019,7 +77034,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G797" s="25" t="n">
+      <c r="G797" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H797" t="n">
@@ -77060,7 +77075,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G798" s="25" t="n">
+      <c r="G798" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H798" t="n">
@@ -77101,7 +77116,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G799" s="25" t="n">
+      <c r="G799" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H799" t="n">
@@ -77142,7 +77157,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G800" s="25" t="n">
+      <c r="G800" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H800" t="n">
@@ -77183,7 +77198,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G801" s="25" t="n">
+      <c r="G801" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H801" t="n">
@@ -77224,7 +77239,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G802" s="25" t="n">
+      <c r="G802" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H802" t="n">
@@ -77265,7 +77280,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G803" s="25" t="n">
+      <c r="G803" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H803" t="n">
@@ -77306,7 +77321,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G804" s="25" t="n">
+      <c r="G804" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H804" t="n">
@@ -77347,7 +77362,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G805" s="25" t="n">
+      <c r="G805" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H805" t="n">
@@ -77388,7 +77403,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G806" s="25" t="n">
+      <c r="G806" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H806" t="n">
@@ -77429,7 +77444,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G807" s="25" t="n">
+      <c r="G807" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H807" t="n">
@@ -77470,7 +77485,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G808" s="25" t="n">
+      <c r="G808" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H808" t="n">
@@ -77511,7 +77526,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G809" s="25" t="n">
+      <c r="G809" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H809" t="n">
@@ -77552,7 +77567,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G810" s="25" t="n">
+      <c r="G810" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H810" t="n">
@@ -77593,7 +77608,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G811" s="25" t="n">
+      <c r="G811" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H811" t="n">
@@ -77634,7 +77649,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G812" s="25" t="n">
+      <c r="G812" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H812" t="n">
@@ -77675,7 +77690,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G813" s="25" t="n">
+      <c r="G813" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H813" t="n">
@@ -77716,7 +77731,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G814" s="25" t="n">
+      <c r="G814" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H814" t="n">
@@ -77757,7 +77772,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G815" s="25" t="n">
+      <c r="G815" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H815" t="n">
@@ -77798,7 +77813,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G816" s="25" t="n">
+      <c r="G816" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H816" t="n">
@@ -77839,7 +77854,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G817" s="25" t="n">
+      <c r="G817" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H817" t="n">
@@ -77880,7 +77895,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G818" s="25" t="n">
+      <c r="G818" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H818" t="n">
@@ -77921,7 +77936,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G819" s="25" t="n">
+      <c r="G819" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H819" t="n">
@@ -77962,7 +77977,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G820" s="25" t="n">
+      <c r="G820" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H820" t="n">
@@ -78003,7 +78018,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G821" s="25" t="n">
+      <c r="G821" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H821" t="n">
@@ -78044,7 +78059,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G822" s="25" t="n">
+      <c r="G822" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H822" t="n">
@@ -78085,7 +78100,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G823" s="25" t="n">
+      <c r="G823" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H823" t="n">
@@ -78126,7 +78141,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G824" s="25" t="n">
+      <c r="G824" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H824" t="n">
@@ -78167,7 +78182,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G825" s="25" t="n">
+      <c r="G825" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H825" t="n">
@@ -78208,7 +78223,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G826" s="25" t="n">
+      <c r="G826" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H826" t="n">
@@ -78249,7 +78264,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G827" s="25" t="n">
+      <c r="G827" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H827" t="n">
@@ -78290,7 +78305,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G828" s="25" t="n">
+      <c r="G828" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H828" t="n">
@@ -78331,7 +78346,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G829" s="25" t="n">
+      <c r="G829" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H829" t="n">
@@ -78372,7 +78387,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G830" s="25" t="n">
+      <c r="G830" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H830" t="n">
@@ -78413,7 +78428,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G831" s="25" t="n">
+      <c r="G831" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H831" t="n">
@@ -78454,7 +78469,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G832" s="25" t="n">
+      <c r="G832" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H832" t="n">
@@ -78495,7 +78510,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G833" s="25" t="n">
+      <c r="G833" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H833" t="n">
@@ -78536,7 +78551,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G834" s="25" t="n">
+      <c r="G834" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H834" t="n">
@@ -78577,7 +78592,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G835" s="25" t="n">
+      <c r="G835" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H835" t="n">
@@ -78618,7 +78633,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G836" s="25" t="n">
+      <c r="G836" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H836" t="n">
@@ -78659,7 +78674,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G837" s="25" t="n">
+      <c r="G837" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H837" t="n">
@@ -78700,7 +78715,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G838" s="25" t="n">
+      <c r="G838" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H838" t="n">
@@ -78741,7 +78756,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G839" s="25" t="n">
+      <c r="G839" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H839" t="n">
@@ -78782,7 +78797,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G840" s="25" t="n">
+      <c r="G840" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H840" t="n">
@@ -78823,7 +78838,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G841" s="25" t="n">
+      <c r="G841" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H841" t="n">
@@ -78864,7 +78879,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G842" s="25" t="n">
+      <c r="G842" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H842" t="n">
@@ -78905,7 +78920,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G843" s="25" t="n">
+      <c r="G843" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H843" t="n">
@@ -78946,7 +78961,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G844" s="25" t="n">
+      <c r="G844" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H844" t="n">
@@ -78987,7 +79002,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G845" s="25" t="n">
+      <c r="G845" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H845" t="n">
@@ -79028,7 +79043,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G846" s="25" t="n">
+      <c r="G846" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H846" t="n">
@@ -79069,7 +79084,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G847" s="25" t="n">
+      <c r="G847" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H847" t="n">
@@ -79110,7 +79125,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G848" s="25" t="n">
+      <c r="G848" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H848" t="n">
@@ -79151,7 +79166,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G849" s="25" t="n">
+      <c r="G849" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H849" t="n">
@@ -79192,7 +79207,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G850" s="25" t="n">
+      <c r="G850" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H850" t="n">
@@ -79233,7 +79248,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G851" s="25" t="n">
+      <c r="G851" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H851" t="n">
@@ -79274,7 +79289,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G852" s="25" t="n">
+      <c r="G852" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H852" t="n">
@@ -79315,7 +79330,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G853" s="25" t="n">
+      <c r="G853" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H853" t="n">
@@ -79356,7 +79371,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G854" s="25" t="n">
+      <c r="G854" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H854" t="n">
@@ -79397,7 +79412,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G855" s="25" t="n">
+      <c r="G855" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H855" t="n">
@@ -79438,7 +79453,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G856" s="25" t="n">
+      <c r="G856" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H856" t="n">
@@ -79479,7 +79494,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G857" s="25" t="n">
+      <c r="G857" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H857" t="n">
@@ -79520,7 +79535,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G858" s="25" t="n">
+      <c r="G858" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H858" t="n">
@@ -79561,7 +79576,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G859" s="25" t="n">
+      <c r="G859" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H859" t="n">
@@ -79602,7 +79617,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G860" s="25" t="n">
+      <c r="G860" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H860" t="n">
@@ -79643,7 +79658,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G861" s="25" t="n">
+      <c r="G861" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H861" t="n">
@@ -79684,7 +79699,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G862" s="25" t="n">
+      <c r="G862" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H862" t="n">
@@ -79725,7 +79740,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G863" s="25" t="n">
+      <c r="G863" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H863" t="n">
@@ -79766,7 +79781,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G864" s="25" t="n">
+      <c r="G864" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H864" t="n">
@@ -79807,7 +79822,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G865" s="25" t="n">
+      <c r="G865" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H865" t="n">
@@ -79848,7 +79863,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G866" s="25" t="n">
+      <c r="G866" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H866" t="n">
@@ -79889,7 +79904,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G867" s="25" t="n">
+      <c r="G867" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H867" t="n">
@@ -79930,7 +79945,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G868" s="25" t="n">
+      <c r="G868" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H868" t="n">
@@ -79971,7 +79986,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G869" s="25" t="n">
+      <c r="G869" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H869" t="n">
@@ -80012,7 +80027,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G870" s="25" t="n">
+      <c r="G870" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H870" t="n">
@@ -80053,7 +80068,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G871" s="25" t="n">
+      <c r="G871" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H871" t="n">
@@ -80094,7 +80109,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G872" s="25" t="n">
+      <c r="G872" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H872" t="n">
@@ -80135,7 +80150,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G873" s="25" t="n">
+      <c r="G873" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H873" t="n">
@@ -80176,7 +80191,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G874" s="25" t="n">
+      <c r="G874" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H874" t="n">
@@ -80217,7 +80232,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G875" s="25" t="n">
+      <c r="G875" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H875" t="n">
@@ -80258,7 +80273,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G876" s="25" t="n">
+      <c r="G876" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H876" t="n">
@@ -80299,7 +80314,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G877" s="25" t="n">
+      <c r="G877" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H877" t="n">
@@ -80340,7 +80355,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G878" s="25" t="n">
+      <c r="G878" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H878" t="n">
@@ -80381,7 +80396,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G879" s="25" t="n">
+      <c r="G879" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H879" t="n">
@@ -80422,7 +80437,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G880" s="25" t="n">
+      <c r="G880" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H880" t="n">
@@ -80463,7 +80478,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G881" s="25" t="n">
+      <c r="G881" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H881" t="n">
@@ -80504,7 +80519,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G882" s="25" t="n">
+      <c r="G882" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H882" t="n">
@@ -80545,7 +80560,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G883" s="25" t="n">
+      <c r="G883" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H883" t="n">
@@ -80586,7 +80601,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G884" s="25" t="n">
+      <c r="G884" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H884" t="n">
@@ -80627,7 +80642,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G885" s="25" t="n">
+      <c r="G885" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H885" t="n">
@@ -80668,7 +80683,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G886" s="25" t="n">
+      <c r="G886" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H886" t="n">
@@ -80709,7 +80724,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G887" s="25" t="n">
+      <c r="G887" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H887" t="n">
@@ -80750,7 +80765,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G888" s="25" t="n">
+      <c r="G888" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H888" t="n">
@@ -80791,7 +80806,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G889" s="25" t="n">
+      <c r="G889" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H889" t="n">
@@ -80832,7 +80847,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G890" s="25" t="n">
+      <c r="G890" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H890" t="n">
@@ -80873,7 +80888,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G891" s="25" t="n">
+      <c r="G891" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H891" t="n">
@@ -80914,7 +80929,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G892" s="25" t="n">
+      <c r="G892" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H892" t="n">
@@ -80955,7 +80970,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G893" s="25" t="n">
+      <c r="G893" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H893" t="n">
@@ -80996,7 +81011,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G894" s="25" t="n">
+      <c r="G894" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H894" t="n">
@@ -81037,7 +81052,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G895" s="25" t="n">
+      <c r="G895" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H895" t="n">
@@ -81078,7 +81093,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G896" s="25" t="n">
+      <c r="G896" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H896" t="n">
@@ -81119,7 +81134,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G897" s="25" t="n">
+      <c r="G897" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H897" t="n">
@@ -81160,7 +81175,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G898" s="25" t="n">
+      <c r="G898" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H898" t="n">
@@ -81201,7 +81216,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G899" s="25" t="n">
+      <c r="G899" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H899" t="n">
@@ -81242,7 +81257,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G900" s="25" t="n">
+      <c r="G900" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H900" t="n">
@@ -81283,7 +81298,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G901" s="25" t="n">
+      <c r="G901" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H901" t="n">
@@ -81324,7 +81339,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G902" s="25" t="n">
+      <c r="G902" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H902" t="n">
@@ -81365,7 +81380,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G903" s="25" t="n">
+      <c r="G903" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H903" t="n">
@@ -81406,7 +81421,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G904" s="25" t="n">
+      <c r="G904" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H904" t="n">
@@ -81447,7 +81462,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G905" s="25" t="n">
+      <c r="G905" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H905" t="n">
@@ -81488,7 +81503,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G906" s="25" t="n">
+      <c r="G906" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H906" t="n">
@@ -81529,7 +81544,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G907" s="25" t="n">
+      <c r="G907" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H907" t="n">
@@ -81570,7 +81585,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G908" s="25" t="n">
+      <c r="G908" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H908" t="n">
@@ -81611,7 +81626,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G909" s="25" t="n">
+      <c r="G909" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H909" t="n">
@@ -81652,7 +81667,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G910" s="25" t="n">
+      <c r="G910" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H910" t="n">
@@ -81693,7 +81708,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G911" s="25" t="n">
+      <c r="G911" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H911" t="n">
@@ -81734,7 +81749,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G912" s="25" t="n">
+      <c r="G912" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H912" t="n">
@@ -81775,7 +81790,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G913" s="25" t="n">
+      <c r="G913" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H913" t="n">
@@ -81816,7 +81831,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G914" s="25" t="n">
+      <c r="G914" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H914" t="n">
@@ -81857,7 +81872,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G915" s="25" t="n">
+      <c r="G915" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H915" t="n">
@@ -81898,7 +81913,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G916" s="25" t="n">
+      <c r="G916" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H916" t="n">
@@ -81939,7 +81954,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G917" s="25" t="n">
+      <c r="G917" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H917" t="n">
@@ -81980,7 +81995,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G918" s="25" t="n">
+      <c r="G918" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H918" t="n">
@@ -82021,7 +82036,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G919" s="25" t="n">
+      <c r="G919" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H919" t="n">
@@ -82062,7 +82077,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G920" s="25" t="n">
+      <c r="G920" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H920" t="n">
@@ -82103,7 +82118,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G921" s="25" t="n">
+      <c r="G921" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H921" t="n">
@@ -82144,7 +82159,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G922" s="25" t="n">
+      <c r="G922" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H922" t="n">
@@ -82185,7 +82200,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G923" s="25" t="n">
+      <c r="G923" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H923" t="n">
@@ -82226,7 +82241,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G924" s="25" t="n">
+      <c r="G924" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H924" t="n">
@@ -82267,7 +82282,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G925" s="25" t="n">
+      <c r="G925" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H925" t="n">
@@ -82308,7 +82323,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G926" s="25" t="n">
+      <c r="G926" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H926" t="n">
@@ -82349,7 +82364,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G927" s="25" t="n">
+      <c r="G927" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H927" t="n">
@@ -82390,7 +82405,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G928" s="25" t="n">
+      <c r="G928" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H928" t="n">
@@ -82431,7 +82446,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G929" s="25" t="n">
+      <c r="G929" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H929" t="n">
@@ -82472,7 +82487,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G930" s="25" t="n">
+      <c r="G930" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H930" t="n">
@@ -82513,7 +82528,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G931" s="25" t="n">
+      <c r="G931" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H931" t="n">
@@ -82554,7 +82569,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G932" s="25" t="n">
+      <c r="G932" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H932" t="n">
@@ -82595,7 +82610,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G933" s="25" t="n">
+      <c r="G933" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H933" t="n">
@@ -82636,7 +82651,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G934" s="25" t="n">
+      <c r="G934" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H934" t="n">
@@ -82677,7 +82692,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G935" s="25" t="n">
+      <c r="G935" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H935" t="n">
@@ -82718,7 +82733,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G936" s="25" t="n">
+      <c r="G936" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H936" t="n">
@@ -82759,7 +82774,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G937" s="25" t="n">
+      <c r="G937" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H937" t="n">
@@ -82800,7 +82815,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G938" s="25" t="n">
+      <c r="G938" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H938" t="n">
@@ -82841,7 +82856,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G939" s="25" t="n">
+      <c r="G939" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H939" t="n">
@@ -82882,7 +82897,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G940" s="25" t="n">
+      <c r="G940" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H940" t="n">
@@ -82923,7 +82938,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G941" s="25" t="n">
+      <c r="G941" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H941" t="n">
@@ -82964,7 +82979,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G942" s="25" t="n">
+      <c r="G942" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H942" t="n">
@@ -83005,7 +83020,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G943" s="25" t="n">
+      <c r="G943" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H943" t="n">
@@ -83046,7 +83061,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G944" s="25" t="n">
+      <c r="G944" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H944" t="n">
@@ -83087,7 +83102,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G945" s="25" t="n">
+      <c r="G945" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H945" t="n">
@@ -83128,7 +83143,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G946" s="25" t="n">
+      <c r="G946" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H946" t="n">
@@ -83169,7 +83184,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G947" s="25" t="n">
+      <c r="G947" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H947" t="n">
@@ -83210,7 +83225,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G948" s="25" t="n">
+      <c r="G948" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H948" t="n">
@@ -83251,7 +83266,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G949" s="25" t="n">
+      <c r="G949" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H949" t="n">
@@ -83292,7 +83307,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G950" s="25" t="n">
+      <c r="G950" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H950" t="n">
@@ -83333,7 +83348,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G951" s="25" t="n">
+      <c r="G951" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H951" t="n">
@@ -83374,7 +83389,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G952" s="25" t="n">
+      <c r="G952" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H952" t="n">
@@ -83415,7 +83430,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G953" s="25" t="n">
+      <c r="G953" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H953" t="n">
@@ -83456,7 +83471,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G954" s="25" t="n">
+      <c r="G954" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H954" t="n">
@@ -83497,7 +83512,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G955" s="25" t="n">
+      <c r="G955" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H955" t="n">
@@ -83538,7 +83553,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G956" s="25" t="n">
+      <c r="G956" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H956" t="n">
@@ -83579,7 +83594,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G957" s="25" t="n">
+      <c r="G957" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H957" t="n">
@@ -83620,7 +83635,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G958" s="25" t="n">
+      <c r="G958" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H958" t="n">
@@ -83661,7 +83676,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G959" s="25" t="n">
+      <c r="G959" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H959" t="n">
@@ -83702,7 +83717,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G960" s="25" t="n">
+      <c r="G960" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H960" t="n">
@@ -83743,7 +83758,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G961" s="25" t="n">
+      <c r="G961" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H961" t="n">
@@ -83784,7 +83799,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G962" s="25" t="n">
+      <c r="G962" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H962" t="n">
@@ -83825,7 +83840,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G963" s="25" t="n">
+      <c r="G963" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H963" t="n">
@@ -83866,7 +83881,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G964" s="25" t="n">
+      <c r="G964" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H964" t="n">
@@ -83907,7 +83922,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G965" s="25" t="n">
+      <c r="G965" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H965" t="n">
@@ -83948,7 +83963,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G966" s="25" t="n">
+      <c r="G966" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H966" t="n">
@@ -83989,7 +84004,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G967" s="25" t="n">
+      <c r="G967" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H967" t="n">
@@ -84030,7 +84045,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G968" s="25" t="n">
+      <c r="G968" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H968" t="n">
@@ -84071,7 +84086,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G969" s="25" t="n">
+      <c r="G969" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H969" t="n">
@@ -84112,7 +84127,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G970" s="25" t="n">
+      <c r="G970" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H970" t="n">
@@ -84153,7 +84168,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G971" s="25" t="n">
+      <c r="G971" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H971" t="n">
@@ -84194,7 +84209,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G972" s="25" t="n">
+      <c r="G972" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H972" t="n">
@@ -84235,7 +84250,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G973" s="25" t="n">
+      <c r="G973" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H973" t="n">
@@ -84276,7 +84291,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G974" s="25" t="n">
+      <c r="G974" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H974" t="n">
@@ -84317,7 +84332,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G975" s="25" t="n">
+      <c r="G975" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H975" t="n">
@@ -84358,7 +84373,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G976" s="25" t="n">
+      <c r="G976" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H976" t="n">
@@ -84399,7 +84414,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G977" s="25" t="n">
+      <c r="G977" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H977" t="n">
@@ -84440,7 +84455,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G978" s="25" t="n">
+      <c r="G978" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H978" t="n">
@@ -84481,7 +84496,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G979" s="25" t="n">
+      <c r="G979" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H979" t="n">
@@ -84522,7 +84537,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G980" s="25" t="n">
+      <c r="G980" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H980" t="n">
@@ -84563,7 +84578,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G981" s="25" t="n">
+      <c r="G981" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H981" t="n">
@@ -84604,7 +84619,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G982" s="25" t="n">
+      <c r="G982" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H982" t="n">
@@ -84645,7 +84660,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G983" s="25" t="n">
+      <c r="G983" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H983" t="n">
@@ -84686,7 +84701,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G984" s="25" t="n">
+      <c r="G984" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H984" t="n">
@@ -84727,7 +84742,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G985" s="25" t="n">
+      <c r="G985" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H985" t="n">
@@ -84768,7 +84783,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G986" s="25" t="n">
+      <c r="G986" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H986" t="n">
@@ -84809,7 +84824,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G987" s="25" t="n">
+      <c r="G987" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H987" t="n">
@@ -84850,7 +84865,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G988" s="25" t="n">
+      <c r="G988" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H988" t="n">
@@ -84891,7 +84906,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G989" s="25" t="n">
+      <c r="G989" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H989" t="n">
@@ -84932,7 +84947,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G990" s="25" t="n">
+      <c r="G990" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H990" t="n">
@@ -84973,7 +84988,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G991" s="25" t="n">
+      <c r="G991" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H991" t="n">
@@ -85014,7 +85029,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G992" s="25" t="n">
+      <c r="G992" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H992" t="n">
@@ -85055,7 +85070,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G993" s="25" t="n">
+      <c r="G993" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H993" t="n">
@@ -85096,7 +85111,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G994" s="25" t="n">
+      <c r="G994" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H994" t="n">
@@ -85137,7 +85152,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G995" s="25" t="n">
+      <c r="G995" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H995" t="n">
@@ -85178,7 +85193,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G996" s="25" t="n">
+      <c r="G996" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H996" t="n">
@@ -85219,7 +85234,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G997" s="25" t="n">
+      <c r="G997" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H997" t="n">
@@ -85260,7 +85275,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G998" s="25" t="n">
+      <c r="G998" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H998" t="n">
@@ -85301,7 +85316,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G999" s="25" t="n">
+      <c r="G999" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H999" t="n">
@@ -85342,7 +85357,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1000" s="25" t="n">
+      <c r="G1000" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1000" t="n">
@@ -85383,7 +85398,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1001" s="25" t="n">
+      <c r="G1001" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1001" t="n">
@@ -85424,7 +85439,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1002" s="25" t="n">
+      <c r="G1002" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1002" t="n">
@@ -85465,7 +85480,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1003" s="25" t="n">
+      <c r="G1003" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1003" t="n">
@@ -85506,7 +85521,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1004" s="25" t="n">
+      <c r="G1004" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1004" t="n">
@@ -85547,7 +85562,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1005" s="25" t="n">
+      <c r="G1005" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1005" t="n">
@@ -85588,7 +85603,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1006" s="25" t="n">
+      <c r="G1006" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1006" t="n">
@@ -85629,7 +85644,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1007" s="25" t="n">
+      <c r="G1007" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1007" t="n">
@@ -85670,7 +85685,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1008" s="25" t="n">
+      <c r="G1008" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1008" t="n">
@@ -85711,7 +85726,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1009" s="25" t="n">
+      <c r="G1009" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1009" t="n">
@@ -85752,7 +85767,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1010" s="25" t="n">
+      <c r="G1010" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1010" t="n">
@@ -85793,7 +85808,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1011" s="25" t="n">
+      <c r="G1011" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1011" t="n">
@@ -85834,7 +85849,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1012" s="25" t="n">
+      <c r="G1012" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1012" t="n">
@@ -85875,7 +85890,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1013" s="25" t="n">
+      <c r="G1013" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1013" t="n">
@@ -85916,7 +85931,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1014" s="25" t="n">
+      <c r="G1014" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1014" t="n">
@@ -85957,7 +85972,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1015" s="25" t="n">
+      <c r="G1015" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1015" t="n">
@@ -85998,7 +86013,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1016" s="25" t="n">
+      <c r="G1016" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1016" t="n">
@@ -86039,7 +86054,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1017" s="25" t="n">
+      <c r="G1017" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1017" t="n">
@@ -86080,7 +86095,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1018" s="25" t="n">
+      <c r="G1018" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1018" t="n">
@@ -86121,7 +86136,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1019" s="25" t="n">
+      <c r="G1019" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1019" t="n">
@@ -86162,7 +86177,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1020" s="25" t="n">
+      <c r="G1020" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1020" t="n">
@@ -86203,7 +86218,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1021" s="25" t="n">
+      <c r="G1021" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1021" t="n">
@@ -86244,7 +86259,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1022" s="25" t="n">
+      <c r="G1022" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1022" t="n">
@@ -86285,7 +86300,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1023" s="25" t="n">
+      <c r="G1023" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1023" t="n">
@@ -86326,7 +86341,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1024" s="25" t="n">
+      <c r="G1024" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1024" t="n">
@@ -86367,7 +86382,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1025" s="25" t="n">
+      <c r="G1025" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1025" t="n">
@@ -86408,7 +86423,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1026" s="25" t="n">
+      <c r="G1026" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1026" t="n">
@@ -86449,7 +86464,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1027" s="25" t="n">
+      <c r="G1027" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1027" t="n">
@@ -86490,7 +86505,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1028" s="25" t="n">
+      <c r="G1028" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1028" t="n">
@@ -86531,7 +86546,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1029" s="25" t="n">
+      <c r="G1029" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1029" t="n">
@@ -86572,7 +86587,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1030" s="25" t="n">
+      <c r="G1030" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1030" t="n">
@@ -86613,7 +86628,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1031" s="25" t="n">
+      <c r="G1031" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1031" t="n">
@@ -86654,7 +86669,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1032" s="25" t="n">
+      <c r="G1032" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1032" t="n">
@@ -86695,7 +86710,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1033" s="25" t="n">
+      <c r="G1033" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1033" t="n">
@@ -86736,7 +86751,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1034" s="25" t="n">
+      <c r="G1034" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1034" t="n">
@@ -86777,7 +86792,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1035" s="25" t="n">
+      <c r="G1035" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1035" t="n">
@@ -86818,7 +86833,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1036" s="25" t="n">
+      <c r="G1036" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1036" t="n">
@@ -86859,7 +86874,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1037" s="25" t="n">
+      <c r="G1037" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1037" t="n">
@@ -86900,7 +86915,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1038" s="25" t="n">
+      <c r="G1038" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1038" t="n">
@@ -86941,7 +86956,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1039" s="25" t="n">
+      <c r="G1039" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1039" t="n">
@@ -86982,7 +86997,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1040" s="25" t="n">
+      <c r="G1040" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1040" t="n">
@@ -87023,7 +87038,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1041" s="25" t="n">
+      <c r="G1041" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1041" t="n">
@@ -87064,7 +87079,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1042" s="25" t="n">
+      <c r="G1042" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1042" t="n">
@@ -87105,7 +87120,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1043" s="25" t="n">
+      <c r="G1043" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1043" t="n">
@@ -87146,7 +87161,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1044" s="25" t="n">
+      <c r="G1044" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1044" t="n">
@@ -87187,7 +87202,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1045" s="25" t="n">
+      <c r="G1045" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1045" t="n">
@@ -87228,7 +87243,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1046" s="25" t="n">
+      <c r="G1046" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1046" t="n">
@@ -87269,7 +87284,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1047" s="25" t="n">
+      <c r="G1047" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1047" t="n">
@@ -87310,7 +87325,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1048" s="25" t="n">
+      <c r="G1048" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1048" t="n">
@@ -87351,7 +87366,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1049" s="25" t="n">
+      <c r="G1049" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1049" t="n">
@@ -87392,7 +87407,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1050" s="25" t="n">
+      <c r="G1050" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1050" t="n">
@@ -87433,7 +87448,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1051" s="25" t="n">
+      <c r="G1051" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1051" t="n">
@@ -87474,7 +87489,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1052" s="25" t="n">
+      <c r="G1052" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1052" t="n">
@@ -87515,7 +87530,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1053" s="25" t="n">
+      <c r="G1053" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1053" t="n">
@@ -87556,7 +87571,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1054" s="25" t="n">
+      <c r="G1054" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1054" t="n">
@@ -87597,7 +87612,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1055" s="25" t="n">
+      <c r="G1055" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1055" t="n">
@@ -87638,7 +87653,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1056" s="25" t="n">
+      <c r="G1056" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1056" t="n">
@@ -87679,7 +87694,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1057" s="25" t="n">
+      <c r="G1057" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1057" t="n">
@@ -87720,7 +87735,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1058" s="25" t="n">
+      <c r="G1058" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1058" t="n">
@@ -87761,7 +87776,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1059" s="25" t="n">
+      <c r="G1059" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1059" t="n">
@@ -87802,7 +87817,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1060" s="25" t="n">
+      <c r="G1060" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1060" t="n">
@@ -87843,7 +87858,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1061" s="25" t="n">
+      <c r="G1061" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1061" t="n">
@@ -87884,7 +87899,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1062" s="25" t="n">
+      <c r="G1062" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1062" t="n">
@@ -87925,7 +87940,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1063" s="25" t="n">
+      <c r="G1063" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1063" t="n">
@@ -87966,7 +87981,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1064" s="25" t="n">
+      <c r="G1064" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1064" t="n">
@@ -88007,7 +88022,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1065" s="25" t="n">
+      <c r="G1065" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1065" t="n">
@@ -88048,7 +88063,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1066" s="25" t="n">
+      <c r="G1066" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1066" t="n">
@@ -88089,7 +88104,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1067" s="25" t="n">
+      <c r="G1067" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1067" t="n">
@@ -88130,7 +88145,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1068" s="25" t="n">
+      <c r="G1068" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1068" t="n">
@@ -88171,7 +88186,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1069" s="25" t="n">
+      <c r="G1069" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1069" t="n">
@@ -88212,7 +88227,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1070" s="25" t="n">
+      <c r="G1070" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1070" t="n">
@@ -88253,7 +88268,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1071" s="25" t="n">
+      <c r="G1071" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1071" t="n">
@@ -88294,7 +88309,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1072" s="25" t="n">
+      <c r="G1072" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1072" t="n">
@@ -88335,7 +88350,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1073" s="25" t="n">
+      <c r="G1073" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1073" t="n">
@@ -88376,7 +88391,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1074" s="25" t="n">
+      <c r="G1074" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1074" t="n">
@@ -88417,7 +88432,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1075" s="25" t="n">
+      <c r="G1075" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1075" t="n">
@@ -88458,7 +88473,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1076" s="25" t="n">
+      <c r="G1076" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1076" t="n">
@@ -88499,7 +88514,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1077" s="25" t="n">
+      <c r="G1077" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1077" t="n">
@@ -88540,7 +88555,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1078" s="25" t="n">
+      <c r="G1078" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1078" t="n">
@@ -88581,7 +88596,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1079" s="25" t="n">
+      <c r="G1079" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1079" t="n">
@@ -88622,7 +88637,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1080" s="25" t="n">
+      <c r="G1080" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1080" t="n">
@@ -88663,7 +88678,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1081" s="25" t="n">
+      <c r="G1081" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1081" t="n">
@@ -88704,7 +88719,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1082" s="25" t="n">
+      <c r="G1082" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1082" t="n">
@@ -88745,7 +88760,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1083" s="25" t="n">
+      <c r="G1083" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1083" t="n">
@@ -88786,7 +88801,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1084" s="25" t="n">
+      <c r="G1084" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1084" t="n">
@@ -88827,7 +88842,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1085" s="25" t="n">
+      <c r="G1085" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1085" t="n">
@@ -88868,7 +88883,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1086" s="25" t="n">
+      <c r="G1086" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1086" t="n">
@@ -88909,7 +88924,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1087" s="25" t="n">
+      <c r="G1087" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1087" t="n">
@@ -88950,7 +88965,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1088" s="25" t="n">
+      <c r="G1088" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1088" t="n">
@@ -88991,7 +89006,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1089" s="25" t="n">
+      <c r="G1089" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1089" t="n">
@@ -89032,7 +89047,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1090" s="25" t="n">
+      <c r="G1090" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1090" t="n">
@@ -89073,7 +89088,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1091" s="25" t="n">
+      <c r="G1091" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1091" t="n">
@@ -89114,7 +89129,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1092" s="25" t="n">
+      <c r="G1092" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1092" t="n">
@@ -89155,7 +89170,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1093" s="25" t="n">
+      <c r="G1093" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1093" t="n">
@@ -89196,7 +89211,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1094" s="25" t="n">
+      <c r="G1094" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1094" t="n">
@@ -89237,7 +89252,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1095" s="25" t="n">
+      <c r="G1095" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1095" t="n">
@@ -89278,7 +89293,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1096" s="25" t="n">
+      <c r="G1096" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1096" t="n">
@@ -89319,7 +89334,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1097" s="25" t="n">
+      <c r="G1097" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1097" t="n">
@@ -89360,7 +89375,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1098" s="25" t="n">
+      <c r="G1098" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1098" t="n">
@@ -89401,7 +89416,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1099" s="25" t="n">
+      <c r="G1099" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1099" t="n">
@@ -89442,7 +89457,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1100" s="25" t="n">
+      <c r="G1100" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1100" t="n">
@@ -89483,7 +89498,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1101" s="25" t="n">
+      <c r="G1101" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1101" t="n">
@@ -89524,7 +89539,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1102" s="25" t="n">
+      <c r="G1102" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1102" t="n">
@@ -89565,7 +89580,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1103" s="25" t="n">
+      <c r="G1103" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1103" t="n">
@@ -89606,7 +89621,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1104" s="25" t="n">
+      <c r="G1104" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1104" t="n">
@@ -89647,7 +89662,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1105" s="25" t="n">
+      <c r="G1105" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1105" t="n">
@@ -89688,7 +89703,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1106" s="25" t="n">
+      <c r="G1106" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1106" t="n">
@@ -89729,7 +89744,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1107" s="25" t="n">
+      <c r="G1107" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1107" t="n">
@@ -89770,7 +89785,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1108" s="25" t="n">
+      <c r="G1108" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1108" t="n">
@@ -89811,7 +89826,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1109" s="25" t="n">
+      <c r="G1109" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1109" t="n">
@@ -89852,7 +89867,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1110" s="25" t="n">
+      <c r="G1110" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1110" t="n">
@@ -89893,7 +89908,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1111" s="25" t="n">
+      <c r="G1111" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1111" t="n">
@@ -89915,7 +89930,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col width="24.1640625" customWidth="1" style="13" min="1" max="1"/>
     <col width="34.83203125" customWidth="1" style="13" min="2" max="2"/>
@@ -89928,8 +89943,8 @@
     <col width="11.33203125" bestFit="1" customWidth="1" style="13" min="9" max="9"/>
     <col width="12.1640625" bestFit="1" customWidth="1" style="13" min="10" max="10"/>
     <col width="33.6640625" customWidth="1" style="13" min="11" max="11"/>
-    <col width="10.83203125" customWidth="1" style="13" min="12" max="64"/>
-    <col width="10.83203125" customWidth="1" style="13" min="65" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="13" min="12" max="65"/>
+    <col width="10.83203125" customWidth="1" style="13" min="66" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -92091,7 +92106,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="26.33203125" customWidth="1" min="1" max="1"/>
     <col width="38.5" customWidth="1" min="2" max="2"/>

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20580" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20580" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="schema" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,12 +22,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;\,&quot;yes&quot;"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -95,6 +96,12 @@
       <color rgb="FF000000"/>
       <sz val="13"/>
     </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -126,7 +133,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -174,6 +181,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +583,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="21.83203125" customWidth="1" style="4" min="1" max="1"/>
     <col width="77.33203125" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
@@ -1326,7 +1334,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Z621"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="11.33203125" customWidth="1" style="7" min="1" max="1"/>
     <col width="13.33203125" customWidth="1" style="7" min="2" max="2"/>
@@ -1351,8 +1359,8 @@
     <col width="15.1640625" customWidth="1" style="7" min="23" max="23"/>
     <col width="21.5" customWidth="1" style="7" min="24" max="24"/>
     <col width="26.83203125" customWidth="1" style="7" min="25" max="25"/>
-    <col width="10.83203125" customWidth="1" style="7" min="27" max="88"/>
-    <col width="10.83203125" customWidth="1" style="7" min="89" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="7" min="27" max="89"/>
+    <col width="10.83203125" customWidth="1" style="7" min="90" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="6">
@@ -33721,7 +33729,7 @@
         </is>
       </c>
       <c r="C482" s="21" t="n">
-        <v>46086</v>
+        <v>46094</v>
       </c>
       <c r="D482" s="7" t="inlineStr">
         <is>
@@ -42795,7 +42803,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="31.83203125" customWidth="1" style="1" min="1" max="1"/>
     <col width="43.1640625" customWidth="1" style="1" min="2" max="2"/>
@@ -42806,8 +42814,8 @@
     <col width="21" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
     <col width="21" customWidth="1" style="7" min="8" max="8"/>
     <col width="51" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" style="1" min="10" max="72"/>
-    <col width="10.83203125" customWidth="1" style="1" min="73" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="1" min="10" max="73"/>
+    <col width="10.83203125" customWidth="1" style="1" min="74" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -43819,7 +43827,7 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>46086</v>
+        <v>46094</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>2009</v>
@@ -44337,8 +44345,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1111"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <dimension ref="A1:J1124"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="9.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -89918,6 +89926,539 @@
         <v>3024</v>
       </c>
     </row>
+    <row r="1112">
+      <c r="A1112" s="16" t="inlineStr">
+        <is>
+          <t>00481</t>
+        </is>
+      </c>
+      <c r="B1112" s="19" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>mm negative future .1.jpg</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>mm negative future .1</t>
+        </is>
+      </c>
+      <c r="F1112" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1112" s="25" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H1112" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1112" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="16" t="inlineStr">
+        <is>
+          <t>00481</t>
+        </is>
+      </c>
+      <c r="B1113" s="19" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>mm negative future .2.jpg</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>mm negative future .2</t>
+        </is>
+      </c>
+      <c r="F1113" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1113" s="25" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H1113" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1113" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="16" t="inlineStr">
+        <is>
+          <t>00481</t>
+        </is>
+      </c>
+      <c r="B1114" s="19" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>mm negative future .3.jpg</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>mm negative future .3</t>
+        </is>
+      </c>
+      <c r="F1114" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1114" s="25" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H1114" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1114" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="16" t="inlineStr">
+        <is>
+          <t>00481</t>
+        </is>
+      </c>
+      <c r="B1115" s="19" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>mm negative future .4.1.jpg</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>mm negative future .4.1</t>
+        </is>
+      </c>
+      <c r="F1115" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1115" s="25" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H1115" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1115" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="16" t="inlineStr">
+        <is>
+          <t>00481</t>
+        </is>
+      </c>
+      <c r="B1116" s="19" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>mm negative future .4.2.jpg</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>mm negative future .4.2</t>
+        </is>
+      </c>
+      <c r="F1116" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1116" s="25" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H1116" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1116" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="16" t="inlineStr">
+        <is>
+          <t>00481</t>
+        </is>
+      </c>
+      <c r="B1117" s="19" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>mm negative future .4.3.jpg</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>mm negative future .4.3</t>
+        </is>
+      </c>
+      <c r="F1117" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1117" s="25" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H1117" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1117" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="16" t="inlineStr">
+        <is>
+          <t>00481</t>
+        </is>
+      </c>
+      <c r="B1118" s="19" t="inlineStr">
+        <is>
+          <t>007</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>mm negative future .4.4.1.jpg</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>mm negative future .4.4.1</t>
+        </is>
+      </c>
+      <c r="F1118" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1118" s="25" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H1118" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1118" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="16" t="inlineStr">
+        <is>
+          <t>00481</t>
+        </is>
+      </c>
+      <c r="B1119" s="19" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>mm negative future .4.4.2.jpg</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>mm negative future .4.4.2</t>
+        </is>
+      </c>
+      <c r="F1119" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1119" s="25" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H1119" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1119" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="16" t="inlineStr">
+        <is>
+          <t>00481</t>
+        </is>
+      </c>
+      <c r="B1120" s="19" t="inlineStr">
+        <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>mm negative future .4.4.3.jpg</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>mm negative future .4.4.3</t>
+        </is>
+      </c>
+      <c r="F1120" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1120" s="25" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H1120" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1120" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="16" t="inlineStr">
+        <is>
+          <t>00481</t>
+        </is>
+      </c>
+      <c r="B1121" s="19" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>mm negative future .4.4.4.jpg</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>mm negative future .4.4.4</t>
+        </is>
+      </c>
+      <c r="F1121" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1121" s="25" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H1121" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1121" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="16" t="inlineStr">
+        <is>
+          <t>00481</t>
+        </is>
+      </c>
+      <c r="B1122" s="19" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>mm negative future .4.4.jpg</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>mm negative future .4.4</t>
+        </is>
+      </c>
+      <c r="F1122" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1122" s="25" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H1122" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1122" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="16" t="inlineStr">
+        <is>
+          <t>00481</t>
+        </is>
+      </c>
+      <c r="B1123" s="19" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>mm negative future .4.jpg</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>mm negative future .4</t>
+        </is>
+      </c>
+      <c r="F1123" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1123" s="25" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H1123" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1123" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="16" t="inlineStr">
+        <is>
+          <t>00481</t>
+        </is>
+      </c>
+      <c r="B1124" s="19" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>versions II (mm).jpg</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>versions II (mm)</t>
+        </is>
+      </c>
+      <c r="F1124" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1124" s="25" t="n">
+        <v>46094</v>
+      </c>
+      <c r="H1124" t="n">
+        <v>5906</v>
+      </c>
+      <c r="I1124" t="n">
+        <v>11811</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -89930,7 +90471,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" outlineLevelCol="0"/>
   <cols>
     <col width="24.1640625" customWidth="1" style="13" min="1" max="1"/>
     <col width="34.83203125" customWidth="1" style="13" min="2" max="2"/>
@@ -89943,8 +90484,8 @@
     <col width="11.33203125" bestFit="1" customWidth="1" style="13" min="9" max="9"/>
     <col width="12.1640625" bestFit="1" customWidth="1" style="13" min="10" max="10"/>
     <col width="33.6640625" customWidth="1" style="13" min="11" max="11"/>
-    <col width="10.83203125" customWidth="1" style="13" min="12" max="65"/>
-    <col width="10.83203125" customWidth="1" style="13" min="66" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="13" min="12" max="66"/>
+    <col width="10.83203125" customWidth="1" style="13" min="67" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -92106,7 +92647,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
   <cols>
     <col width="26.33203125" customWidth="1" min="1" max="1"/>
     <col width="38.5" customWidth="1" min="2" max="2"/>

--- a/data/works.xlsx
+++ b/data/works.xlsx
@@ -29,7 +29,7 @@
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -99,6 +99,12 @@
     </font>
     <font>
       <name val="Aptos Narrow"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <sz val="8"/>
       <scheme val="minor"/>
@@ -134,7 +140,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -182,6 +188,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
@@ -1334,7 +1341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z629"/>
+  <dimension ref="A1:Z635"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="11.33203125" customWidth="1" style="7" min="1" max="1"/>
@@ -1342,7 +1349,7 @@
     <col width="17" bestFit="1" customWidth="1" style="21" min="3" max="3"/>
     <col width="29.6640625" bestFit="1" customWidth="1" style="7" min="4" max="5"/>
     <col width="35.33203125" customWidth="1" style="7" min="6" max="6"/>
-    <col width="43.1640625" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
+    <col width="50.33203125" customWidth="1" style="7" min="7" max="7"/>
     <col width="44.6640625" customWidth="1" style="7" min="8" max="8"/>
     <col width="13.1640625" customWidth="1" style="7" min="9" max="9"/>
     <col width="14" customWidth="1" style="7" min="10" max="10"/>
@@ -1360,8 +1367,8 @@
     <col width="15.1640625" customWidth="1" style="7" min="23" max="23"/>
     <col width="21.5" customWidth="1" style="7" min="24" max="24"/>
     <col width="26.83203125" customWidth="1" style="7" min="25" max="25"/>
-    <col width="10.83203125" customWidth="1" style="7" min="27" max="91"/>
-    <col width="10.83203125" customWidth="1" style="7" min="92" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="7" min="27" max="95"/>
+    <col width="10.83203125" customWidth="1" style="7" min="96" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="6">
@@ -27125,7 +27132,14 @@
           <t>00383</t>
         </is>
       </c>
-      <c r="C384" s="22" t="n"/>
+      <c r="B384" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C384" s="22" t="n">
+        <v>46095</v>
+      </c>
       <c r="D384" s="7" t="inlineStr">
         <is>
           <t>qrnt</t>
@@ -27143,12 +27157,12 @@
       </c>
       <c r="G384" s="7" t="inlineStr">
         <is>
-          <t>00383 - qrnt.jpg</t>
+          <t>qrnt.jpg</t>
         </is>
       </c>
       <c r="H384" s="7" t="inlineStr">
         <is>
-          <t>00383 - qrnt</t>
+          <t>qrnt</t>
         </is>
       </c>
       <c r="I384" s="7" t="n">
@@ -27173,6 +27187,9 @@
           <t>inkjet print</t>
         </is>
       </c>
+      <c r="O384" s="7" t="n">
+        <v>14</v>
+      </c>
       <c r="Z384" s="7" t="n"/>
     </row>
     <row r="385">
@@ -42831,7 +42848,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C622" s="25" t="n">
+      <c r="C622" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="D622" s="7" t="inlineStr">
@@ -42893,7 +42910,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C623" s="25" t="n">
+      <c r="C623" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="D623" s="7" t="inlineStr">
@@ -42955,7 +42972,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C624" s="25" t="n">
+      <c r="C624" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="D624" s="7" t="inlineStr">
@@ -43017,7 +43034,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C625" s="25" t="n">
+      <c r="C625" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="D625" s="7" t="inlineStr">
@@ -43079,7 +43096,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C626" s="25" t="n">
+      <c r="C626" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="D626" s="7" t="inlineStr">
@@ -43141,7 +43158,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C627" s="25" t="n">
+      <c r="C627" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="D627" s="7" t="inlineStr">
@@ -43203,7 +43220,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C628" s="25" t="n">
+      <c r="C628" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="D628" s="7" t="inlineStr">
@@ -43265,7 +43282,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="C629" s="25" t="n">
+      <c r="C629" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="D629" s="7" t="inlineStr">
@@ -43312,7 +43329,389 @@
       </c>
       <c r="N629" s="7" t="inlineStr">
         <is>
-          <t>digital c-type print</t>
+          <t>digital print</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="16" t="inlineStr">
+        <is>
+          <t>00629</t>
+        </is>
+      </c>
+      <c r="B630" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C630" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="D630" s="7" t="inlineStr">
+        <is>
+          <t>qrnt</t>
+        </is>
+      </c>
+      <c r="E630" s="7" t="inlineStr">
+        <is>
+          <t>qrnt</t>
+        </is>
+      </c>
+      <c r="F630" s="7" t="inlineStr">
+        <is>
+          <t>qrnt</t>
+        </is>
+      </c>
+      <c r="G630" s="7" t="inlineStr">
+        <is>
+          <t>quantum random number theory.jpg</t>
+        </is>
+      </c>
+      <c r="H630" s="7" t="inlineStr">
+        <is>
+          <t>quantum random number theory</t>
+        </is>
+      </c>
+      <c r="I630" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="J630" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="K630" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="L630" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="M630" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="N630" s="7" t="inlineStr">
+        <is>
+          <t>giclée print</t>
+        </is>
+      </c>
+      <c r="O630" s="7" t="inlineStr">
+        <is>
+          <t>framed</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="16" t="inlineStr">
+        <is>
+          <t>00630</t>
+        </is>
+      </c>
+      <c r="B631" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C631" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="D631" s="7" t="inlineStr">
+        <is>
+          <t>qrnt</t>
+        </is>
+      </c>
+      <c r="E631" s="7" t="inlineStr">
+        <is>
+          <t>qrnt</t>
+        </is>
+      </c>
+      <c r="F631" s="7" t="inlineStr">
+        <is>
+          <t>qrnt</t>
+        </is>
+      </c>
+      <c r="G631" s="7" t="inlineStr">
+        <is>
+          <t>quantum random number theory (version).jpg</t>
+        </is>
+      </c>
+      <c r="H631" s="7" t="inlineStr">
+        <is>
+          <t>quantum random number theory (version)</t>
+        </is>
+      </c>
+      <c r="I631" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="J631" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="K631" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="L631" s="7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="M631" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="N631" s="7" t="inlineStr">
+        <is>
+          <t>giclée print</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="16" t="inlineStr">
+        <is>
+          <t>00631</t>
+        </is>
+      </c>
+      <c r="B632" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C632" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="D632" s="7" t="inlineStr">
+        <is>
+          <t>qrnt</t>
+        </is>
+      </c>
+      <c r="E632" s="7" t="inlineStr">
+        <is>
+          <t>qrnt</t>
+        </is>
+      </c>
+      <c r="F632" s="7" t="inlineStr">
+        <is>
+          <t>qrnt</t>
+        </is>
+      </c>
+      <c r="G632" s="7" t="inlineStr">
+        <is>
+          <t>quantum random number theory (form).jpg</t>
+        </is>
+      </c>
+      <c r="H632" s="7" t="inlineStr">
+        <is>
+          <t>quantum random number theory (form)</t>
+        </is>
+      </c>
+      <c r="I632" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="J632" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="K632" s="7" t="n">
+        <v>2015</v>
+      </c>
+      <c r="L632" s="7" t="n">
+        <v>2015</v>
+      </c>
+      <c r="M632" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="N632" s="7" t="inlineStr">
+        <is>
+          <t>pencil on giclée print</t>
+        </is>
+      </c>
+      <c r="O632" s="7" t="inlineStr">
+        <is>
+          <t>framed</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="16" t="inlineStr">
+        <is>
+          <t>00632</t>
+        </is>
+      </c>
+      <c r="B633" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C633" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="D633" s="7" t="inlineStr">
+        <is>
+          <t>qrnt</t>
+        </is>
+      </c>
+      <c r="E633" s="7" t="inlineStr">
+        <is>
+          <t>qrnt</t>
+        </is>
+      </c>
+      <c r="F633" s="7" t="inlineStr">
+        <is>
+          <t>qrnt</t>
+        </is>
+      </c>
+      <c r="G633" s="7" t="inlineStr">
+        <is>
+          <t>quantum random number theory (circle).jpg</t>
+        </is>
+      </c>
+      <c r="H633" s="7" t="inlineStr">
+        <is>
+          <t>quantum random number theory (circle)</t>
+        </is>
+      </c>
+      <c r="I633" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="J633" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="K633" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="L633" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="M633" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="N633" s="7" t="inlineStr">
+        <is>
+          <t>giclée print</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="16" t="inlineStr">
+        <is>
+          <t>00633</t>
+        </is>
+      </c>
+      <c r="B634" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C634" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="D634" s="7" t="inlineStr">
+        <is>
+          <t>qrnt</t>
+        </is>
+      </c>
+      <c r="E634" s="7" t="inlineStr">
+        <is>
+          <t>qrnt</t>
+        </is>
+      </c>
+      <c r="F634" s="7" t="inlineStr">
+        <is>
+          <t>qrnt</t>
+        </is>
+      </c>
+      <c r="G634" s="7" t="inlineStr">
+        <is>
+          <t>quantum random number theory (4 circles).jpg</t>
+        </is>
+      </c>
+      <c r="H634" s="7" t="inlineStr">
+        <is>
+          <t>quantum random number theory (4 circles)</t>
+        </is>
+      </c>
+      <c r="I634" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="J634" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="K634" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="L634" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="M634" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="N634" s="7" t="inlineStr">
+        <is>
+          <t>giclée print</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B635" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C635" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="D635" s="7" t="inlineStr">
+        <is>
+          <t>qrnt</t>
+        </is>
+      </c>
+      <c r="E635" s="7" t="inlineStr">
+        <is>
+          <t>qrnt</t>
+        </is>
+      </c>
+      <c r="F635" s="7" t="inlineStr">
+        <is>
+          <t>qrnt (bits symbols)</t>
+        </is>
+      </c>
+      <c r="G635" s="7" t="inlineStr">
+        <is>
+          <t>bits symbols 1.jpg</t>
+        </is>
+      </c>
+      <c r="H635" s="7" t="inlineStr">
+        <is>
+          <t>bits symbols 1</t>
+        </is>
+      </c>
+      <c r="I635" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="J635" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="K635" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="L635" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="M635" s="7" t="inlineStr">
+        <is>
+          <t>digital print</t>
+        </is>
+      </c>
+      <c r="N635" s="7" t="inlineStr">
+        <is>
+          <t>giclée print</t>
         </is>
       </c>
     </row>
@@ -43341,8 +43740,8 @@
     <col width="21" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
     <col width="21" customWidth="1" style="7" min="8" max="8"/>
     <col width="51" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" style="1" min="10" max="75"/>
-    <col width="10.83203125" customWidth="1" style="1" min="76" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="1" min="10" max="79"/>
+    <col width="10.83203125" customWidth="1" style="1" min="80" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -44685,6 +45084,14 @@
           <t>primary</t>
         </is>
       </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>46095</v>
+      </c>
       <c r="F38" s="1" t="n">
         <v>2015</v>
       </c>
@@ -44693,6 +45100,11 @@
           <t>2009, 2015</t>
         </is>
       </c>
+      <c r="H38" s="16" t="inlineStr">
+        <is>
+          <t>00630</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -44899,7 +45311,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="E44" s="25" t="n">
+      <c r="E44" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="F44" s="1" t="n">
@@ -44926,7 +45338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1140"/>
+  <dimension ref="A1:J1182"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -91235,7 +91647,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1129" s="25" t="n">
+      <c r="G1129" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1129" t="n">
@@ -91276,7 +91688,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1130" s="25" t="n">
+      <c r="G1130" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1130" t="n">
@@ -91317,7 +91729,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1131" s="25" t="n">
+      <c r="G1131" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1131" t="n">
@@ -91358,7 +91770,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1132" s="25" t="n">
+      <c r="G1132" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1132" t="n">
@@ -91399,7 +91811,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1133" s="25" t="n">
+      <c r="G1133" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1133" t="n">
@@ -91440,7 +91852,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1134" s="25" t="n">
+      <c r="G1134" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1134" t="n">
@@ -91481,7 +91893,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1135" s="25" t="n">
+      <c r="G1135" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1135" t="n">
@@ -91522,7 +91934,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1136" s="25" t="n">
+      <c r="G1136" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1136" t="n">
@@ -91563,7 +91975,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1137" s="25" t="n">
+      <c r="G1137" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1137" t="n">
@@ -91604,7 +92016,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1138" s="25" t="n">
+      <c r="G1138" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1138" t="n">
@@ -91645,7 +92057,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1139" s="25" t="n">
+      <c r="G1139" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1139" t="n">
@@ -91686,7 +92098,7 @@
           <t>published</t>
         </is>
       </c>
-      <c r="G1140" s="25" t="n">
+      <c r="G1140" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="H1140" t="n">
@@ -91694,6 +92106,1728 @@
       </c>
       <c r="I1140" t="n">
         <v>4134</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="16" t="inlineStr">
+        <is>
+          <t>00629</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 1.jpg</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 1</t>
+        </is>
+      </c>
+      <c r="F1141" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1141" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1141" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I1141" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="16" t="inlineStr">
+        <is>
+          <t>00629</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 2.jpg</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 2</t>
+        </is>
+      </c>
+      <c r="F1142" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1142" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1142" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I1142" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="16" t="inlineStr">
+        <is>
+          <t>00629</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 3.jpg</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 3</t>
+        </is>
+      </c>
+      <c r="F1143" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1143" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1143" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I1143" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="16" t="inlineStr">
+        <is>
+          <t>00629</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 4.jpg</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 4</t>
+        </is>
+      </c>
+      <c r="F1144" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1144" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1144" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I1144" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="16" t="inlineStr">
+        <is>
+          <t>00629</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 5.jpg</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 5</t>
+        </is>
+      </c>
+      <c r="F1145" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1145" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1145" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I1145" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="16" t="inlineStr">
+        <is>
+          <t>00629</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 6.jpg</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 6</t>
+        </is>
+      </c>
+      <c r="F1146" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1146" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1146" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I1146" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="16" t="inlineStr">
+        <is>
+          <t>00629</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>007</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 7.jpg</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 7</t>
+        </is>
+      </c>
+      <c r="F1147" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1147" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1147" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I1147" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="16" t="inlineStr">
+        <is>
+          <t>00629</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 8.jpg</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 8</t>
+        </is>
+      </c>
+      <c r="F1148" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1148" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1148" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I1148" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="16" t="inlineStr">
+        <is>
+          <t>00629</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 9.jpg</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 9</t>
+        </is>
+      </c>
+      <c r="F1149" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1149" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1149" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I1149" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="16" t="inlineStr">
+        <is>
+          <t>00629</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 10.jpg</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>quantum random number theory (10,000) 10</t>
+        </is>
+      </c>
+      <c r="F1150" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1150" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1150" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I1150" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="16" t="inlineStr">
+        <is>
+          <t>00629</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>install</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>qrnt - Searching for God exhibition - install 1.jpg</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>qrnt - Searching for God exhibition - install 1</t>
+        </is>
+      </c>
+      <c r="F1151" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1151" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1151" t="n">
+        <v>1600</v>
+      </c>
+      <c r="I1151" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="16" t="inlineStr">
+        <is>
+          <t>00629</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>install</t>
+        </is>
+      </c>
+      <c r="D1152" s="25" t="inlineStr">
+        <is>
+          <t>qrnt - Searching for God exhibition - install 2.jpg</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>qrnt - Searching for God exhibition - install 2</t>
+        </is>
+      </c>
+      <c r="F1152" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1152" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1152" t="n">
+        <v>1600</v>
+      </c>
+      <c r="I1152" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="16" t="inlineStr">
+        <is>
+          <t>00629</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>install</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>qrnt - Searching for God exhibition - install 3.jpg</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>qrnt - Searching for God exhibition - install 3</t>
+        </is>
+      </c>
+      <c r="F1153" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1153" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1153" t="n">
+        <v>1296</v>
+      </c>
+      <c r="I1153" t="n">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="16" t="inlineStr">
+        <is>
+          <t>00631</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>qrnt form (2015-06-06).jpg</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>qrnt form (2015-06-06)</t>
+        </is>
+      </c>
+      <c r="F1154" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1154" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1154" t="n">
+        <v>3088</v>
+      </c>
+      <c r="I1154" t="n">
+        <v>3088</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="16" t="inlineStr">
+        <is>
+          <t>00631</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>qrnt form (2015-06-06) detail 1.jpg</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>qrnt form (2015-06-06) detail 1</t>
+        </is>
+      </c>
+      <c r="F1155" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1155" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1155" t="n">
+        <v>3088</v>
+      </c>
+      <c r="I1155" t="n">
+        <v>3088</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="16" t="inlineStr">
+        <is>
+          <t>00631</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>qrnt form (2015-06-06) detail 2.jpg</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>qrnt form (2015-06-06) detail 2</t>
+        </is>
+      </c>
+      <c r="F1156" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1156" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1156" t="n">
+        <v>3088</v>
+      </c>
+      <c r="I1156" t="n">
+        <v>3088</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="16" t="inlineStr">
+        <is>
+          <t>00631</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>qrnt form (2015-06-06) detail 3.jpg</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>qrnt form (2015-06-06) detail 3</t>
+        </is>
+      </c>
+      <c r="F1157" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1157" s="10" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1157" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I1157" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>bits symbols 1.jpg</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>bits symbols 1</t>
+        </is>
+      </c>
+      <c r="F1158" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1158" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1158" t="n">
+        <v>8858</v>
+      </c>
+      <c r="I1158" t="n">
+        <v>8858</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>bits symbols 2.jpg</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>bits symbols 2</t>
+        </is>
+      </c>
+      <c r="F1159" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1159" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1159" t="n">
+        <v>17717</v>
+      </c>
+      <c r="I1159" t="n">
+        <v>11811</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>bits symbols 3.jpg</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>bits symbols 3</t>
+        </is>
+      </c>
+      <c r="F1160" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1160" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1160" t="n">
+        <v>11811</v>
+      </c>
+      <c r="I1160" t="n">
+        <v>11811</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>versions</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>bits symbols 4.jpg</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>bits symbols 4</t>
+        </is>
+      </c>
+      <c r="F1161" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1161" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1161" t="n">
+        <v>11811</v>
+      </c>
+      <c r="I1161" t="n">
+        <v>11811</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>bits symbols 1.1.jpg</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>bits symbols 1.1</t>
+        </is>
+      </c>
+      <c r="F1162" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1162" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1162" t="n">
+        <v>8858</v>
+      </c>
+      <c r="I1162" t="n">
+        <v>8858</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>bits symbols 1.2.jpg</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>bits symbols 1.2</t>
+        </is>
+      </c>
+      <c r="F1163" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1163" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1163" t="n">
+        <v>8858</v>
+      </c>
+      <c r="I1163" t="n">
+        <v>8858</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>007</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>bits symbols 1.3.jpg</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>bits symbols 1.3</t>
+        </is>
+      </c>
+      <c r="F1164" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1164" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1164" t="n">
+        <v>8858</v>
+      </c>
+      <c r="I1164" t="n">
+        <v>8858</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>bits symbols 2.1.jpg</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>bits symbols 2.1</t>
+        </is>
+      </c>
+      <c r="F1165" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1165" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1165" t="n">
+        <v>11811</v>
+      </c>
+      <c r="I1165" t="n">
+        <v>11811</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>bits symbols 2.2.jpg</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>bits symbols 2.2</t>
+        </is>
+      </c>
+      <c r="F1166" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1166" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1166" t="n">
+        <v>11811</v>
+      </c>
+      <c r="I1166" t="n">
+        <v>11811</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>bits symbols 2.3.jpg</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>bits symbols 2.3</t>
+        </is>
+      </c>
+      <c r="F1167" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1167" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1167" t="n">
+        <v>11811</v>
+      </c>
+      <c r="I1167" t="n">
+        <v>11811</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>bits symbols 3.1.jpg</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>bits symbols 3.1</t>
+        </is>
+      </c>
+      <c r="F1168" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1168" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1168" t="n">
+        <v>11811</v>
+      </c>
+      <c r="I1168" t="n">
+        <v>11811</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>bits symbols 3.2.jpg</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>bits symbols 3.2</t>
+        </is>
+      </c>
+      <c r="F1169" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1169" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1169" t="n">
+        <v>11811</v>
+      </c>
+      <c r="I1169" t="n">
+        <v>11811</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>bits symbols 3.3.jpg</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>bits symbols 3.3</t>
+        </is>
+      </c>
+      <c r="F1170" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1170" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1170" t="n">
+        <v>11811</v>
+      </c>
+      <c r="I1170" t="n">
+        <v>11811</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>bits symbols 4.1.jpg</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>bits symbols 4.1</t>
+        </is>
+      </c>
+      <c r="F1171" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1171" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1171" t="n">
+        <v>11811</v>
+      </c>
+      <c r="I1171" t="n">
+        <v>11811</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>bits symbols 4.2.jpg</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>bits symbols 4.2</t>
+        </is>
+      </c>
+      <c r="F1172" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1172" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1172" t="n">
+        <v>11811</v>
+      </c>
+      <c r="I1172" t="n">
+        <v>11811</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>bits symbols 4.3.jpg</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>bits symbols 4.3</t>
+        </is>
+      </c>
+      <c r="F1173" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1173" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1173" t="n">
+        <v>11811</v>
+      </c>
+      <c r="I1173" t="n">
+        <v>11811</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>details ^2</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>bits symbols 1.1.1.jpg</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>bits symbols 1.1.1</t>
+        </is>
+      </c>
+      <c r="F1174" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1174" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1174" t="n">
+        <v>1536</v>
+      </c>
+      <c r="I1174" t="n">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>details ^2</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>bits symbols 1.1.2.jpg</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>bits symbols 1.1.2</t>
+        </is>
+      </c>
+      <c r="F1175" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1175" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1175" t="n">
+        <v>1536</v>
+      </c>
+      <c r="I1175" t="n">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>019</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>details ^2</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>bits symbols 1.1.3.jpg</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>bits symbols 1.1.3</t>
+        </is>
+      </c>
+      <c r="F1176" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1176" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1176" t="n">
+        <v>1536</v>
+      </c>
+      <c r="I1176" t="n">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>020</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>details ^2</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>bits symbols 1.2.1.jpg</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>bits symbols 1.2.1</t>
+        </is>
+      </c>
+      <c r="F1177" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1177" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1177" t="n">
+        <v>1535</v>
+      </c>
+      <c r="I1177" t="n">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>details ^2</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>bits symbols 1.2.2.jpg</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>bits symbols 1.2.2</t>
+        </is>
+      </c>
+      <c r="F1178" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1178" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1178" t="n">
+        <v>1535</v>
+      </c>
+      <c r="I1178" t="n">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>022</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>details ^2</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>bits symbols 1.2.3.jpg</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>bits symbols 1.2.3</t>
+        </is>
+      </c>
+      <c r="F1179" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1179" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1179" t="n">
+        <v>1535</v>
+      </c>
+      <c r="I1179" t="n">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>023</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>details ^2</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>bits symbols 1.3.1.jpg</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>bits symbols 1.3.1</t>
+        </is>
+      </c>
+      <c r="F1180" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1180" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1180" t="n">
+        <v>1535</v>
+      </c>
+      <c r="I1180" t="n">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>024</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>details ^2</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>bits symbols 1.3.2.jpg</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>bits symbols 1.3.2</t>
+        </is>
+      </c>
+      <c r="F1181" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1181" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1181" t="n">
+        <v>1535</v>
+      </c>
+      <c r="I1181" t="n">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="16" t="inlineStr">
+        <is>
+          <t>00634</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>details ^2</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>bits symbols 1.3.3.jpg</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>bits symbols 1.3.3</t>
+        </is>
+      </c>
+      <c r="F1182" s="1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="G1182" s="26" t="n">
+        <v>46095</v>
+      </c>
+      <c r="H1182" t="n">
+        <v>1535</v>
+      </c>
+      <c r="I1182" t="n">
+        <v>1535</v>
       </c>
     </row>
   </sheetData>
@@ -91722,8 +93856,8 @@
     <col width="11.33203125" bestFit="1" customWidth="1" style="13" min="9" max="9"/>
     <col width="12.1640625" bestFit="1" customWidth="1" style="13" min="10" max="10"/>
     <col width="33.6640625" customWidth="1" style="13" min="11" max="11"/>
-    <col width="10.83203125" customWidth="1" style="13" min="12" max="68"/>
-    <col width="10.83203125" customWidth="1" style="13" min="69" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="13" min="12" max="72"/>
+    <col width="10.83203125" customWidth="1" style="13" min="73" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
